--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEAA648-93CC-4C24-9D17-880742500A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D27B2F-9896-444A-81D5-F04C2E3D6FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="169">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -532,6 +532,12 @@
   </si>
   <si>
     <t>Nhận BH Kim Long</t>
+  </si>
+  <si>
+    <t>Nhập kho 26 LE4G(8686) SIM vật lý, 10 LE4G(8686) eSIM</t>
+  </si>
+  <si>
+    <t>Trả BH Ngọc Hoàn (trả trước ID: VNET861385070647584, 0032001EFD)</t>
   </si>
 </sst>
 </file>
@@ -908,6 +914,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -999,9 +1008,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1326,15 +1332,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="62">
+      <c r="A1" s="63">
         <v>46174</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1343,146 +1349,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="71">
+      <c r="A3" s="72">
         <v>46202</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
-      <c r="B6" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="71"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67" t="s">
+      <c r="A7" s="72"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="71">
+      <c r="A9" s="72">
         <v>46203</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="74"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="71"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="68" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="71"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="68" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="68" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="71"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1527,15 +1533,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="87">
+      <c r="A1" s="88">
         <v>46204</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1544,152 +1550,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="71">
+      <c r="A3" s="72">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="76" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="89">
+      <c r="A7" s="90">
         <v>46205</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="75"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="90"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="91"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="90"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="68" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="90"/>
-      <c r="B10" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="68" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="90"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="68" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="90"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="68" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="91"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="68" t="s">
+      <c r="A13" s="92"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="80">
+      <c r="A14" s="81">
         <v>46206</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1701,348 +1707,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="83"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="72" t="s">
+      <c r="A15" s="84"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="75"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="83"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="72" t="s">
+      <c r="A16" s="84"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="75"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="83"/>
-      <c r="B17" s="79"/>
-      <c r="C17" s="72" t="s">
+      <c r="A17" s="84"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="75"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="83"/>
-      <c r="B18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="72" t="s">
+      <c r="A18" s="84"/>
+      <c r="B18" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="75"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="81"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="72" t="s">
+      <c r="A19" s="82"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="75"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="84">
+      <c r="A20" s="85">
         <v>46209</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67" t="s">
+      <c r="A21" s="85"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67" t="s">
+      <c r="A22" s="85"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
-      <c r="B23" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="67" t="s">
+      <c r="A23" s="85"/>
+      <c r="B23" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="72" t="s">
+      <c r="A24" s="85"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="75"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="72" t="s">
+      <c r="A25" s="85"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="75"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="72" t="s">
+      <c r="A26" s="85"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="75"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="72" t="s">
+      <c r="A27" s="85"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="75"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="72" t="s">
+      <c r="A28" s="85"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="75"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="72" t="s">
+      <c r="A29" s="85"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="75"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="72" t="s">
+      <c r="A30" s="85"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="75"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="72" t="s">
+      <c r="A31" s="85"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="84"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="72" t="s">
+      <c r="A32" s="85"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="84"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="72" t="s">
+      <c r="A33" s="85"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="84"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="72" t="s">
+      <c r="A34" s="85"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="82">
+      <c r="A35" s="83">
         <v>46210</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="82"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67" t="s">
+      <c r="A36" s="83"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="82"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67" t="s">
+      <c r="A37" s="83"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="82"/>
-      <c r="B38" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="A38" s="83"/>
+      <c r="B38" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="82"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67" t="s">
+      <c r="A39" s="83"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="82"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67" t="s">
+      <c r="A40" s="83"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="82"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67" t="s">
+      <c r="A41" s="83"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="82"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67" t="s">
+      <c r="A42" s="83"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="82"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67" t="s">
+      <c r="A43" s="83"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="82"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="72" t="s">
+      <c r="A44" s="83"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
-      <c r="F44" s="73"/>
-      <c r="G44" s="74"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="75"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2051,13 +2057,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="C45" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2066,255 +2072,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="80">
+      <c r="A47" s="81">
         <v>46213</v>
       </c>
-      <c r="B47" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="72" t="s">
+      <c r="B47" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="73"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="74"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="75"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="83"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="72" t="s">
+      <c r="A48" s="84"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="74"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="75"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="83"/>
-      <c r="B49" s="86"/>
-      <c r="C49" s="72" t="s">
+      <c r="A49" s="84"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="73"/>
-      <c r="G49" s="74"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="75"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="83"/>
-      <c r="B50" s="86"/>
-      <c r="C50" s="72" t="s">
+      <c r="A50" s="84"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="73"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="73"/>
-      <c r="G50" s="74"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="75"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="81"/>
-      <c r="B51" s="79"/>
-      <c r="C51" s="72" t="s">
+      <c r="A51" s="82"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="73"/>
-      <c r="E51" s="73"/>
-      <c r="F51" s="73"/>
-      <c r="G51" s="74"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="75"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="71">
+      <c r="A52" s="72">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="C52" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="68"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="71"/>
+      <c r="A53" s="72"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="68"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="71">
+      <c r="A54" s="72">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="72" t="s">
+      <c r="C54" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="73"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="75"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="71"/>
-      <c r="B55" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="85" t="s">
+      <c r="A55" s="72"/>
+      <c r="B55" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="85"/>
-      <c r="E55" s="85"/>
-      <c r="F55" s="85"/>
-      <c r="G55" s="85"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="71"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="85" t="s">
+      <c r="A56" s="72"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="85"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
+      <c r="F56" s="86"/>
+      <c r="G56" s="86"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="71"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="85" t="s">
+      <c r="A57" s="72"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="85"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="85"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="71"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="85" t="s">
+      <c r="A58" s="72"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="85"/>
-      <c r="E58" s="85"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="85"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="71"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="85" t="s">
+      <c r="A59" s="72"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="85"/>
-      <c r="E59" s="85"/>
-      <c r="F59" s="85"/>
-      <c r="G59" s="85"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="86"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="71"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="85" t="s">
+      <c r="A60" s="72"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="85"/>
-      <c r="E60" s="85"/>
-      <c r="F60" s="85"/>
-      <c r="G60" s="85"/>
+      <c r="D60" s="86"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="86"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="71"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="85" t="s">
+      <c r="A61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="85"/>
-      <c r="E61" s="85"/>
-      <c r="F61" s="85"/>
-      <c r="G61" s="85"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="71"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="85" t="s">
+      <c r="A62" s="72"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="85"/>
-      <c r="E62" s="85"/>
-      <c r="F62" s="85"/>
-      <c r="G62" s="85"/>
+      <c r="D62" s="86"/>
+      <c r="E62" s="86"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="86"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="71"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="85" t="s">
+      <c r="A63" s="72"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="85"/>
-      <c r="E63" s="85"/>
-      <c r="F63" s="85"/>
-      <c r="G63" s="85"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="86"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="86"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="71">
+      <c r="A64" s="72">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="67" t="s">
+      <c r="C64" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="68"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="71"/>
-      <c r="B65" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="67" t="s">
+      <c r="A65" s="72"/>
+      <c r="B65" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="68"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="71"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67" t="s">
+      <c r="A66" s="72"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="68"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2323,164 +2329,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="67" t="s">
+      <c r="C67" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="71">
+      <c r="A68" s="72">
         <v>46220</v>
       </c>
-      <c r="B68" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="67" t="s">
+      <c r="B68" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="71"/>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="A69" s="72"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="71">
+      <c r="A70" s="72">
         <v>46223</v>
       </c>
-      <c r="B70" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="72" t="s">
+      <c r="B70" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="73"/>
-      <c r="E70" s="73"/>
-      <c r="F70" s="73"/>
-      <c r="G70" s="74"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="75"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="71"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="72" t="s">
+      <c r="A71" s="72"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="73"/>
-      <c r="E71" s="73"/>
-      <c r="F71" s="73"/>
-      <c r="G71" s="74"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="75"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="71"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="72" t="s">
+      <c r="A72" s="72"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="73"/>
-      <c r="E72" s="73"/>
-      <c r="F72" s="73"/>
-      <c r="G72" s="74"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="75"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="71"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="72" t="s">
+      <c r="A73" s="72"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="73"/>
-      <c r="E73" s="73"/>
-      <c r="F73" s="73"/>
-      <c r="G73" s="74"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="75"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="71"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="72" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="73"/>
-      <c r="E74" s="73"/>
-      <c r="F74" s="73"/>
-      <c r="G74" s="74"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="75"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="71"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="72" t="s">
+      <c r="A75" s="72"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="73"/>
-      <c r="E75" s="73"/>
-      <c r="F75" s="73"/>
-      <c r="G75" s="74"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="75"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="71"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="72" t="s">
+      <c r="A76" s="72"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="74"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="75"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="71"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="68" t="s">
+      <c r="A77" s="72"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="69"/>
-      <c r="E77" s="69"/>
-      <c r="F77" s="69"/>
-      <c r="G77" s="70"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="71"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="71"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="68" t="s">
+      <c r="A78" s="72"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="69"/>
-      <c r="E78" s="69"/>
-      <c r="F78" s="69"/>
-      <c r="G78" s="70"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="71"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="71"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="68" t="s">
+      <c r="A79" s="72"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="69"/>
-      <c r="E79" s="69"/>
-      <c r="F79" s="69"/>
-      <c r="G79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="71"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="71"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="68" t="s">
+      <c r="A80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="69"/>
-      <c r="E80" s="69"/>
-      <c r="F80" s="69"/>
-      <c r="G80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="71"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2489,353 +2495,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="67" t="s">
+      <c r="C81" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="68"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="71">
+      <c r="A82" s="72">
         <v>46225</v>
       </c>
-      <c r="B82" s="67" t="s">
+      <c r="B82" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="68"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="71"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="67" t="s">
+      <c r="A83" s="72"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="67"/>
+      <c r="D83" s="68"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="68"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="71"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="67" t="s">
+      <c r="A84" s="72"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="67"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="67"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="68"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="71"/>
-      <c r="B85" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="67" t="s">
+      <c r="A85" s="72"/>
+      <c r="B85" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="67"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="71"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67" t="s">
+      <c r="A86" s="72"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="67"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="68"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="71"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67" t="s">
+      <c r="A87" s="72"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="71"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="67" t="s">
+      <c r="A88" s="72"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="67"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
+      <c r="D88" s="68"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="71"/>
-      <c r="B89" s="67"/>
-      <c r="C89" s="72" t="s">
+      <c r="A89" s="72"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="73"/>
-      <c r="E89" s="73"/>
-      <c r="F89" s="73"/>
-      <c r="G89" s="74"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="74"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="75"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="71"/>
-      <c r="B90" s="67"/>
-      <c r="C90" s="67" t="s">
+      <c r="A90" s="72"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
+      <c r="D90" s="68"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="68"/>
+      <c r="G90" s="68"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="80">
+      <c r="A91" s="81">
         <v>46227</v>
       </c>
-      <c r="B91" s="78" t="s">
+      <c r="B91" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="81"/>
-      <c r="B92" s="79"/>
-      <c r="C92" s="72" t="s">
+      <c r="A92" s="82"/>
+      <c r="B92" s="80"/>
+      <c r="C92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="73"/>
-      <c r="E92" s="73"/>
-      <c r="F92" s="73"/>
-      <c r="G92" s="74"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="74"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="75"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="71">
+      <c r="A93" s="72">
         <v>46228</v>
       </c>
-      <c r="B93" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="67" t="s">
+      <c r="B93" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="67"/>
+      <c r="D93" s="68"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="68"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="71"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="67" t="s">
+      <c r="A94" s="72"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="67"/>
+      <c r="D94" s="68"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="68"/>
+      <c r="G94" s="68"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="71"/>
-      <c r="B95" s="67"/>
-      <c r="C95" s="67" t="s">
+      <c r="A95" s="72"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="67"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="68"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="71"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="67" t="s">
+      <c r="A96" s="72"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="67"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="67"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="71"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="67" t="s">
+      <c r="A97" s="72"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="67"/>
+      <c r="D97" s="68"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="68"/>
+      <c r="G97" s="68"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="71"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="67" t="s">
+      <c r="A98" s="72"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="67"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="71">
+      <c r="A99" s="72">
         <v>46230</v>
       </c>
-      <c r="B99" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="67" t="s">
+      <c r="B99" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="71"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="67" t="s">
+      <c r="A100" s="72"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="67"/>
+      <c r="D100" s="68"/>
+      <c r="E100" s="68"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="68"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="71">
+      <c r="A101" s="72">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="77" t="s">
+      <c r="C101" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="77"/>
-      <c r="E101" s="77"/>
-      <c r="F101" s="77"/>
-      <c r="G101" s="77"/>
+      <c r="D101" s="78"/>
+      <c r="E101" s="78"/>
+      <c r="F101" s="78"/>
+      <c r="G101" s="78"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="71"/>
+      <c r="A102" s="72"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="77" t="s">
+      <c r="C102" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="77"/>
-      <c r="E102" s="77"/>
-      <c r="F102" s="77"/>
-      <c r="G102" s="77"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="78"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="75" t="s">
+      <c r="A103" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="76" t="s">
+      <c r="B103" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="76"/>
-      <c r="E103" s="76"/>
-      <c r="F103" s="76"/>
-      <c r="G103" s="76"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="75"/>
-      <c r="B104" s="67"/>
-      <c r="C104" s="67" t="s">
+      <c r="A104" s="76"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="75"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="67" t="s">
+      <c r="A105" s="76"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="67"/>
+      <c r="D105" s="68"/>
+      <c r="E105" s="68"/>
+      <c r="F105" s="68"/>
+      <c r="G105" s="68"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="75"/>
-      <c r="B106" s="67"/>
-      <c r="C106" s="67" t="s">
+      <c r="A106" s="76"/>
+      <c r="B106" s="68"/>
+      <c r="C106" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="67"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="67"/>
+      <c r="D106" s="68"/>
+      <c r="E106" s="68"/>
+      <c r="F106" s="68"/>
+      <c r="G106" s="68"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="75"/>
-      <c r="B107" s="67"/>
-      <c r="C107" s="67" t="s">
+      <c r="A107" s="76"/>
+      <c r="B107" s="68"/>
+      <c r="C107" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="67"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="67"/>
+      <c r="D107" s="68"/>
+      <c r="E107" s="68"/>
+      <c r="F107" s="68"/>
+      <c r="G107" s="68"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="71">
+      <c r="A108" s="72">
         <v>46234</v>
       </c>
-      <c r="B108" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="67" t="s">
+      <c r="B108" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="67"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="67"/>
-      <c r="G108" s="67"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="71"/>
-      <c r="B109" s="67"/>
-      <c r="C109" s="67" t="s">
+      <c r="A109" s="72"/>
+      <c r="B109" s="68"/>
+      <c r="C109" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="67"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="67"/>
-      <c r="G109" s="67"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="68"/>
+      <c r="F109" s="68"/>
+      <c r="G109" s="68"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -3009,15 +3015,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="87">
+      <c r="A1" s="88">
         <v>46235</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3950,7 +3956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -3959,15 +3965,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="92">
+      <c r="A1" s="93">
         <v>46266</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4247,24 +4253,86 @@
       <c r="G27" s="50"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="93">
+      <c r="A28" s="11">
         <v>46276</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="B28" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>166</v>
       </c>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="48"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="10" t="s">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="G29" s="51"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C30" s="10" t="s">
+      <c r="A30" s="45"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="26" t="s">
         <v>89</v>
+      </c>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="50"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="62">
+        <v>46279</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="10" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D27B2F-9896-444A-81D5-F04C2E3D6FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BF9E0B-5565-45B5-ABC7-090CB821ADC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="170">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -538,6 +538,9 @@
   </si>
   <si>
     <t>Trả BH Ngọc Hoàn (trả trước ID: VNET861385070647584, 0032001EFD)</t>
+  </si>
+  <si>
+    <t>Nhận BH Đại lý Ngọc Hoàn</t>
   </si>
 </sst>
 </file>
@@ -761,7 +764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -917,6 +920,30 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -932,82 +959,61 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1332,15 +1338,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="63">
+      <c r="A1" s="71">
         <v>46174</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1349,146 +1355,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="75"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46202</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68" t="s">
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72">
+      <c r="A9" s="66">
         <v>46203</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="70"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1498,14 +1504,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1516,6 +1514,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1533,15 +1539,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46204</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1550,152 +1556,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="77" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="82">
         <v>46205</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="69" t="s">
+      <c r="A8" s="83"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="71"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="65"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="83"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="65"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
-      <c r="B10" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="91"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="83"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69" t="s">
+      <c r="A13" s="84"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="81">
+      <c r="A14" s="86">
         <v>46206</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="76" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1707,348 +1713,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="73" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="70"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="84"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="73" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="70"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="73" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="84"/>
-      <c r="B18" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="73" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="75"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="70"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="73" t="s">
+      <c r="A19" s="88"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="70"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="89">
         <v>46209</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68" t="s">
+      <c r="A21" s="89"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68" t="s">
+      <c r="A22" s="89"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="68" t="s">
+      <c r="A23" s="89"/>
+      <c r="B23" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="73" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="75"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="73" t="s">
+      <c r="A25" s="89"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="75"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="70"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="73" t="s">
+      <c r="A26" s="89"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="73" t="s">
+      <c r="A27" s="89"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="75"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="73" t="s">
+      <c r="A28" s="89"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="75"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="73" t="s">
+      <c r="A29" s="89"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="73" t="s">
+      <c r="A30" s="89"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="73" t="s">
+      <c r="A31" s="89"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="73" t="s">
+      <c r="A32" s="89"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="73" t="s">
+      <c r="A33" s="89"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="73" t="s">
+      <c r="A34" s="89"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="70"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="83">
+      <c r="A35" s="85">
         <v>46210</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
-      <c r="B38" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="68" t="s">
+      <c r="A38" s="85"/>
+      <c r="B38" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68" t="s">
+      <c r="A40" s="85"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68" t="s">
+      <c r="A42" s="85"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68" t="s">
+      <c r="A43" s="85"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="73" t="s">
+      <c r="A44" s="85"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="75"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="70"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2057,13 +2063,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2072,255 +2078,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="81">
+      <c r="A47" s="86">
         <v>46213</v>
       </c>
-      <c r="B47" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="73" t="s">
+      <c r="B47" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="75"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="84"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="73" t="s">
+      <c r="A48" s="87"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="75"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="70"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="84"/>
-      <c r="B49" s="87"/>
-      <c r="C49" s="73" t="s">
+      <c r="A49" s="87"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="75"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="70"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="87"/>
-      <c r="C50" s="73" t="s">
+      <c r="A50" s="87"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="70"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="73" t="s">
+      <c r="A51" s="88"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="75"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="70"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="72">
+      <c r="A52" s="66">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="72">
+      <c r="A54" s="66">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="75"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="70"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
-      <c r="B55" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="86" t="s">
+      <c r="A55" s="66"/>
+      <c r="B55" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="86" t="s">
+      <c r="A56" s="66"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="90"/>
+      <c r="G56" s="90"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="86" t="s">
+      <c r="A57" s="66"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="86" t="s">
+      <c r="A58" s="66"/>
+      <c r="B58" s="67"/>
+      <c r="C58" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="86" t="s">
+      <c r="A59" s="66"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="86" t="s">
+      <c r="A60" s="66"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="86" t="s">
+      <c r="A61" s="66"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="86"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="90"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="86" t="s">
+      <c r="A62" s="66"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="90"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="86" t="s">
+      <c r="A63" s="66"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
+      <c r="D63" s="90"/>
+      <c r="E63" s="90"/>
+      <c r="F63" s="90"/>
+      <c r="G63" s="90"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="72">
+      <c r="A64" s="66">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="67"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
-      <c r="B65" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="68" t="s">
+      <c r="A65" s="66"/>
+      <c r="B65" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2329,164 +2335,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="72">
+      <c r="A68" s="66">
         <v>46220</v>
       </c>
-      <c r="B68" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="68" t="s">
+      <c r="B68" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68" t="s">
+      <c r="A69" s="66"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="72">
+      <c r="A70" s="66">
         <v>46223</v>
       </c>
-      <c r="B70" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="73" t="s">
+      <c r="B70" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="75"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="70"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="73" t="s">
+      <c r="A71" s="66"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="75"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="70"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="73" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="75"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="70"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="73" t="s">
+      <c r="A73" s="66"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="75"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="69"/>
+      <c r="G73" s="70"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="73" t="s">
+      <c r="A74" s="66"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="75"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="70"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="73" t="s">
+      <c r="A75" s="66"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="75"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="69"/>
+      <c r="G75" s="70"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="73" t="s">
+      <c r="A76" s="66"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="75"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="70"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="69" t="s">
+      <c r="A77" s="66"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="65"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="69" t="s">
+      <c r="A78" s="66"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="71"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="65"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="72"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="69" t="s">
+      <c r="A79" s="66"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
-      <c r="F79" s="70"/>
-      <c r="G79" s="71"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="65"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="69" t="s">
+      <c r="A80" s="66"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="71"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="65"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2495,353 +2501,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="68" t="s">
+      <c r="C81" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="72">
+      <c r="A82" s="66">
         <v>46225</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="67"/>
+      <c r="G82" s="67"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68" t="s">
+      <c r="A83" s="66"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="67"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="67"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68" t="s">
+      <c r="A84" s="66"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="67"/>
+      <c r="F84" s="67"/>
+      <c r="G84" s="67"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
-      <c r="B85" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="68" t="s">
+      <c r="A85" s="66"/>
+      <c r="B85" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="67"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68" t="s">
+      <c r="A86" s="66"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="67"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68" t="s">
+      <c r="A87" s="66"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="67"/>
+      <c r="G87" s="67"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68" t="s">
+      <c r="A88" s="66"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="67"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
-      <c r="B89" s="68"/>
-      <c r="C89" s="73" t="s">
+      <c r="A89" s="66"/>
+      <c r="B89" s="67"/>
+      <c r="C89" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="74"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="75"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
+      <c r="F89" s="69"/>
+      <c r="G89" s="70"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="72"/>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68" t="s">
+      <c r="A90" s="66"/>
+      <c r="B90" s="67"/>
+      <c r="C90" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="67"/>
+      <c r="G90" s="67"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="81">
+      <c r="A91" s="86">
         <v>46227</v>
       </c>
-      <c r="B91" s="79" t="s">
+      <c r="B91" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="67"/>
+      <c r="G91" s="67"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="82"/>
-      <c r="B92" s="80"/>
-      <c r="C92" s="73" t="s">
+      <c r="A92" s="88"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="75"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="70"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="72">
+      <c r="A93" s="66">
         <v>46228</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="68" t="s">
+      <c r="B93" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="67"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68" t="s">
+      <c r="A94" s="66"/>
+      <c r="B94" s="67"/>
+      <c r="C94" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="67"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="72"/>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68" t="s">
+      <c r="A95" s="66"/>
+      <c r="B95" s="67"/>
+      <c r="C95" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
+      <c r="F95" s="67"/>
+      <c r="G95" s="67"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="A96" s="66"/>
+      <c r="B96" s="67"/>
+      <c r="C96" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
+      <c r="D96" s="67"/>
+      <c r="E96" s="67"/>
+      <c r="F96" s="67"/>
+      <c r="G96" s="67"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="72"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="68" t="s">
+      <c r="A97" s="66"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="68"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="67"/>
+      <c r="G97" s="67"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="72"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="68" t="s">
+      <c r="A98" s="66"/>
+      <c r="B98" s="67"/>
+      <c r="C98" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="67"/>
+      <c r="G98" s="67"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="72">
+      <c r="A99" s="66">
         <v>46230</v>
       </c>
-      <c r="B99" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="68" t="s">
+      <c r="B99" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="72"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="68" t="s">
+      <c r="A100" s="66"/>
+      <c r="B100" s="67"/>
+      <c r="C100" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="68"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="67"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="72">
+      <c r="A101" s="66">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="78" t="s">
+      <c r="C101" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="78"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="78"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="72"/>
+      <c r="A102" s="66"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="78" t="s">
+      <c r="C102" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="78"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="78"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="76" t="s">
+      <c r="A103" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="77" t="s">
+      <c r="B103" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="81"/>
+      <c r="F103" s="81"/>
+      <c r="G103" s="81"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
-      <c r="B104" s="68"/>
-      <c r="C104" s="68" t="s">
+      <c r="A104" s="91"/>
+      <c r="B104" s="67"/>
+      <c r="C104" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="67"/>
+      <c r="G104" s="67"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68" t="s">
+      <c r="A105" s="91"/>
+      <c r="B105" s="67"/>
+      <c r="C105" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
+      <c r="D105" s="67"/>
+      <c r="E105" s="67"/>
+      <c r="F105" s="67"/>
+      <c r="G105" s="67"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
-      <c r="B106" s="68"/>
-      <c r="C106" s="68" t="s">
+      <c r="A106" s="91"/>
+      <c r="B106" s="67"/>
+      <c r="C106" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="68"/>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
+      <c r="D106" s="67"/>
+      <c r="E106" s="67"/>
+      <c r="F106" s="67"/>
+      <c r="G106" s="67"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
-      <c r="B107" s="68"/>
-      <c r="C107" s="68" t="s">
+      <c r="A107" s="91"/>
+      <c r="B107" s="67"/>
+      <c r="C107" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
+      <c r="D107" s="67"/>
+      <c r="E107" s="67"/>
+      <c r="F107" s="67"/>
+      <c r="G107" s="67"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="72">
+      <c r="A108" s="66">
         <v>46234</v>
       </c>
-      <c r="B108" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
+      <c r="D108" s="67"/>
+      <c r="E108" s="67"/>
+      <c r="F108" s="67"/>
+      <c r="G108" s="67"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="72"/>
-      <c r="B109" s="68"/>
-      <c r="C109" s="68" t="s">
+      <c r="A109" s="66"/>
+      <c r="B109" s="67"/>
+      <c r="C109" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
+      <c r="D109" s="67"/>
+      <c r="E109" s="67"/>
+      <c r="F109" s="67"/>
+      <c r="G109" s="67"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2851,6 +2857,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2875,129 +3004,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3015,15 +3021,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46235</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3956,7 +3962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -4287,52 +4293,108 @@
       <c r="G30" s="50"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="62">
+      <c r="A31" s="11">
         <v>46279</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="52" t="s">
         <v>167</v>
       </c>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="54"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="A32" s="46"/>
+      <c r="B32" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="24" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="10" t="s">
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="10" t="s">
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="94"/>
+      <c r="G33" s="51"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="25" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="10" t="s">
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="51"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="25" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="10" t="s">
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="94"/>
+      <c r="G35" s="51"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="46"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="25" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="10" t="s">
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="94"/>
+      <c r="G36" s="51"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="25" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C38" s="10" t="s">
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="94"/>
+      <c r="G37" s="51"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="26" t="s">
         <v>168</v>
+      </c>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="50"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="62">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BF9E0B-5565-45B5-ABC7-090CB821ADC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD61C0B-D9FA-4763-A573-1C71E8E39436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="173">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -541,6 +541,15 @@
   </si>
   <si>
     <t>Nhận BH Đại lý Ngọc Hoàn</t>
+  </si>
+  <si>
+    <t>Trả BH SEA 1 VNSH02 ID: 003200B1A2 (A. Bảo)</t>
+  </si>
+  <si>
+    <t>Trả BH Nam Định</t>
+  </si>
+  <si>
+    <t>Trả BH Nam Anh</t>
   </si>
 </sst>
 </file>
@@ -764,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -917,7 +926,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -932,9 +956,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -944,20 +965,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -965,6 +980,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -974,9 +1007,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -985,30 +1015,6 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1338,15 +1344,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="71">
+      <c r="A1" s="62">
         <v>46174</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1355,16 +1361,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="66"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="71">
         <v>46202</v>
       </c>
       <c r="B3" s="67" t="s">
@@ -1379,7 +1385,7 @@
       <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="67"/>
       <c r="C4" s="67" t="s">
         <v>0</v>
@@ -1390,7 +1396,7 @@
       <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="67"/>
       <c r="C5" s="67" t="s">
         <v>3</v>
@@ -1401,7 +1407,7 @@
       <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="67" t="s">
         <v>4</v>
       </c>
@@ -1414,7 +1420,7 @@
       <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="67"/>
       <c r="C7" s="67" t="s">
         <v>10</v>
@@ -1425,7 +1431,7 @@
       <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="66"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="67"/>
       <c r="C8" s="67" t="s">
         <v>9</v>
@@ -1436,65 +1442,65 @@
       <c r="G8" s="67"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="66">
+      <c r="A9" s="71">
         <v>46203</v>
       </c>
       <c r="B9" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="74"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="67"/>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
+      <c r="A11" s="71"/>
       <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="70"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="66"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="70"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="66"/>
+      <c r="A13" s="71"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="70"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1504,6 +1510,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1514,14 +1528,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1539,15 +1545,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="87">
         <v>46204</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1556,16 +1562,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="71">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1580,20 +1586,20 @@
       <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="67"/>
       <c r="C5" s="67" t="s">
         <v>17</v>
@@ -1604,7 +1610,7 @@
       <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="67"/>
       <c r="C6" s="67" t="s">
         <v>18</v>
@@ -1615,93 +1621,93 @@
       <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="82">
+      <c r="A7" s="89">
         <v>46205</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="70"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="74"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="63" t="s">
+      <c r="A8" s="90"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="70"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="63" t="s">
+      <c r="A9" s="90"/>
+      <c r="B9" s="79"/>
+      <c r="C9" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="70"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
+      <c r="A11" s="90"/>
       <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="70"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
+      <c r="A12" s="90"/>
       <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="70"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
+      <c r="A13" s="91"/>
       <c r="B13" s="67"/>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="70"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="80">
         <v>46206</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="78" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1713,64 +1719,64 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="87"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="68" t="s">
+      <c r="A15" s="83"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="74"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="68" t="s">
+      <c r="A16" s="83"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="74"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="87"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="68" t="s">
+      <c r="A17" s="83"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="74"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="87"/>
-      <c r="B18" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="68" t="s">
+      <c r="A18" s="83"/>
+      <c r="B18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="74"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="68" t="s">
+      <c r="A19" s="81"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="70"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="74"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="89">
+      <c r="A20" s="84">
         <v>46209</v>
       </c>
       <c r="B20" s="67" t="s">
@@ -1785,7 +1791,7 @@
       <c r="G20" s="67"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="89"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="67"/>
       <c r="C21" s="67" t="s">
         <v>34</v>
@@ -1796,7 +1802,7 @@
       <c r="G21" s="67"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="89"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="67"/>
       <c r="C22" s="67" t="s">
         <v>15</v>
@@ -1807,7 +1813,7 @@
       <c r="G22" s="67"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="89"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="67" t="s">
         <v>4</v>
       </c>
@@ -1820,128 +1826,128 @@
       <c r="G23" s="67"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="89"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="67"/>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="74"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="89"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="67"/>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="74"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="89"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="67"/>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="74"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="89"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="67"/>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="70"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="74"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="89"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="67"/>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="70"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="74"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="89"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="67"/>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="74"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="89"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="67"/>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="70"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="74"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="67"/>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="74"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="67"/>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="74"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
+      <c r="A33" s="84"/>
       <c r="B33" s="67"/>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="74"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="89"/>
+      <c r="A34" s="84"/>
       <c r="B34" s="67"/>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="74"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="85">
+      <c r="A35" s="82">
         <v>46210</v>
       </c>
       <c r="B35" s="67" t="s">
@@ -1956,7 +1962,7 @@
       <c r="G35" s="67"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
+      <c r="A36" s="82"/>
       <c r="B36" s="67"/>
       <c r="C36" s="67" t="s">
         <v>27</v>
@@ -1967,7 +1973,7 @@
       <c r="G36" s="67"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
+      <c r="A37" s="82"/>
       <c r="B37" s="67"/>
       <c r="C37" s="67" t="s">
         <v>47</v>
@@ -1978,7 +1984,7 @@
       <c r="G37" s="67"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
+      <c r="A38" s="82"/>
       <c r="B38" s="67" t="s">
         <v>4</v>
       </c>
@@ -1991,7 +1997,7 @@
       <c r="G38" s="67"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="85"/>
+      <c r="A39" s="82"/>
       <c r="B39" s="67"/>
       <c r="C39" s="67" t="s">
         <v>53</v>
@@ -2002,7 +2008,7 @@
       <c r="G39" s="67"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
+      <c r="A40" s="82"/>
       <c r="B40" s="67"/>
       <c r="C40" s="67" t="s">
         <v>48</v>
@@ -2013,7 +2019,7 @@
       <c r="G40" s="67"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
+      <c r="A41" s="82"/>
       <c r="B41" s="67"/>
       <c r="C41" s="67" t="s">
         <v>49</v>
@@ -2024,7 +2030,7 @@
       <c r="G41" s="67"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
+      <c r="A42" s="82"/>
       <c r="B42" s="67"/>
       <c r="C42" s="67" t="s">
         <v>50</v>
@@ -2035,7 +2041,7 @@
       <c r="G42" s="67"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
+      <c r="A43" s="82"/>
       <c r="B43" s="67"/>
       <c r="C43" s="67" t="s">
         <v>51</v>
@@ -2046,15 +2052,15 @@
       <c r="G43" s="67"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
+      <c r="A44" s="82"/>
       <c r="B44" s="67"/>
-      <c r="C44" s="68" t="s">
+      <c r="C44" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="73"/>
+      <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2087,66 +2093,66 @@
       <c r="G46" s="67"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="86">
+      <c r="A47" s="80">
         <v>46213</v>
       </c>
-      <c r="B47" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="68" t="s">
+      <c r="B47" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="70"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="74"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="87"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="68" t="s">
+      <c r="A48" s="83"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="70"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="74"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="68" t="s">
+      <c r="A49" s="83"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="70"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="74"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="68" t="s">
+      <c r="A50" s="83"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="70"/>
+      <c r="D50" s="73"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="74"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="88"/>
-      <c r="B51" s="77"/>
-      <c r="C51" s="68" t="s">
+      <c r="A51" s="81"/>
+      <c r="B51" s="79"/>
+      <c r="C51" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="70"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="74"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="66">
+      <c r="A52" s="71">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2161,7 +2167,7 @@
       <c r="G52" s="67"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="71"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
@@ -2174,123 +2180,123 @@
       <c r="G53" s="67"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="66">
+      <c r="A54" s="71">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="69"/>
-      <c r="E54" s="69"/>
-      <c r="F54" s="69"/>
-      <c r="G54" s="70"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="74"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="66"/>
+      <c r="A55" s="71"/>
       <c r="B55" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="90" t="s">
+      <c r="C55" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
+      <c r="D55" s="85"/>
+      <c r="E55" s="85"/>
+      <c r="F55" s="85"/>
+      <c r="G55" s="85"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="66"/>
+      <c r="A56" s="71"/>
       <c r="B56" s="67"/>
-      <c r="C56" s="90" t="s">
+      <c r="C56" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="90"/>
+      <c r="D56" s="85"/>
+      <c r="E56" s="85"/>
+      <c r="F56" s="85"/>
+      <c r="G56" s="85"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="66"/>
+      <c r="A57" s="71"/>
       <c r="B57" s="67"/>
-      <c r="C57" s="90" t="s">
+      <c r="C57" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="90"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
+      <c r="D57" s="85"/>
+      <c r="E57" s="85"/>
+      <c r="F57" s="85"/>
+      <c r="G57" s="85"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="66"/>
+      <c r="A58" s="71"/>
       <c r="B58" s="67"/>
-      <c r="C58" s="90" t="s">
+      <c r="C58" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="90"/>
+      <c r="D58" s="85"/>
+      <c r="E58" s="85"/>
+      <c r="F58" s="85"/>
+      <c r="G58" s="85"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="66"/>
+      <c r="A59" s="71"/>
       <c r="B59" s="67"/>
-      <c r="C59" s="90" t="s">
+      <c r="C59" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
+      <c r="D59" s="85"/>
+      <c r="E59" s="85"/>
+      <c r="F59" s="85"/>
+      <c r="G59" s="85"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="66"/>
+      <c r="A60" s="71"/>
       <c r="B60" s="67"/>
-      <c r="C60" s="90" t="s">
+      <c r="C60" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
+      <c r="D60" s="85"/>
+      <c r="E60" s="85"/>
+      <c r="F60" s="85"/>
+      <c r="G60" s="85"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
+      <c r="A61" s="71"/>
       <c r="B61" s="67"/>
-      <c r="C61" s="90" t="s">
+      <c r="C61" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="90"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
+      <c r="D61" s="85"/>
+      <c r="E61" s="85"/>
+      <c r="F61" s="85"/>
+      <c r="G61" s="85"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="66"/>
+      <c r="A62" s="71"/>
       <c r="B62" s="67"/>
-      <c r="C62" s="90" t="s">
+      <c r="C62" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="90"/>
+      <c r="D62" s="85"/>
+      <c r="E62" s="85"/>
+      <c r="F62" s="85"/>
+      <c r="G62" s="85"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
+      <c r="A63" s="71"/>
       <c r="B63" s="67"/>
-      <c r="C63" s="90" t="s">
+      <c r="C63" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="90"/>
-      <c r="E63" s="90"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="90"/>
+      <c r="D63" s="85"/>
+      <c r="E63" s="85"/>
+      <c r="F63" s="85"/>
+      <c r="G63" s="85"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="66">
+      <c r="A64" s="71">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -2305,7 +2311,7 @@
       <c r="G64" s="67"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
+      <c r="A65" s="71"/>
       <c r="B65" s="67" t="s">
         <v>4</v>
       </c>
@@ -2318,7 +2324,7 @@
       <c r="G65" s="67"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
+      <c r="A66" s="71"/>
       <c r="B66" s="67"/>
       <c r="C66" s="67" t="s">
         <v>74</v>
@@ -2344,7 +2350,7 @@
       <c r="G67" s="67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="66">
+      <c r="A68" s="71">
         <v>46220</v>
       </c>
       <c r="B68" s="67" t="s">
@@ -2359,7 +2365,7 @@
       <c r="G68" s="67"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
+      <c r="A69" s="71"/>
       <c r="B69" s="67"/>
       <c r="C69" s="67" t="s">
         <v>77</v>
@@ -2370,129 +2376,129 @@
       <c r="G69" s="67"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="66">
+      <c r="A70" s="71">
         <v>46223</v>
       </c>
       <c r="B70" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="68" t="s">
+      <c r="C70" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="70"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="73"/>
+      <c r="F70" s="73"/>
+      <c r="G70" s="74"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
+      <c r="A71" s="71"/>
       <c r="B71" s="67"/>
-      <c r="C71" s="68" t="s">
+      <c r="C71" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="70"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="73"/>
+      <c r="F71" s="73"/>
+      <c r="G71" s="74"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
+      <c r="A72" s="71"/>
       <c r="B72" s="67"/>
-      <c r="C72" s="68" t="s">
+      <c r="C72" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="70"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="73"/>
+      <c r="F72" s="73"/>
+      <c r="G72" s="74"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
+      <c r="A73" s="71"/>
       <c r="B73" s="67"/>
-      <c r="C73" s="68" t="s">
+      <c r="C73" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="69"/>
-      <c r="F73" s="69"/>
-      <c r="G73" s="70"/>
+      <c r="D73" s="73"/>
+      <c r="E73" s="73"/>
+      <c r="F73" s="73"/>
+      <c r="G73" s="74"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
+      <c r="A74" s="71"/>
       <c r="B74" s="67"/>
-      <c r="C74" s="68" t="s">
+      <c r="C74" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="70"/>
+      <c r="D74" s="73"/>
+      <c r="E74" s="73"/>
+      <c r="F74" s="73"/>
+      <c r="G74" s="74"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
+      <c r="A75" s="71"/>
       <c r="B75" s="67"/>
-      <c r="C75" s="68" t="s">
+      <c r="C75" s="72" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="70"/>
+      <c r="D75" s="73"/>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="74"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
+      <c r="A76" s="71"/>
       <c r="B76" s="67"/>
-      <c r="C76" s="68" t="s">
+      <c r="C76" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="69"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="70"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="73"/>
+      <c r="G76" s="74"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="66"/>
+      <c r="A77" s="71"/>
       <c r="B77" s="67"/>
-      <c r="C77" s="63" t="s">
+      <c r="C77" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="65"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="69"/>
+      <c r="F77" s="69"/>
+      <c r="G77" s="70"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="66"/>
+      <c r="A78" s="71"/>
       <c r="B78" s="67"/>
-      <c r="C78" s="63" t="s">
+      <c r="C78" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="65"/>
+      <c r="D78" s="69"/>
+      <c r="E78" s="69"/>
+      <c r="F78" s="69"/>
+      <c r="G78" s="70"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
+      <c r="A79" s="71"/>
       <c r="B79" s="67"/>
-      <c r="C79" s="63" t="s">
+      <c r="C79" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="65"/>
+      <c r="D79" s="69"/>
+      <c r="E79" s="69"/>
+      <c r="F79" s="69"/>
+      <c r="G79" s="70"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
+      <c r="A80" s="71"/>
       <c r="B80" s="67"/>
-      <c r="C80" s="63" t="s">
+      <c r="C80" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="65"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="69"/>
+      <c r="F80" s="69"/>
+      <c r="G80" s="70"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2510,7 +2516,7 @@
       <c r="G81" s="67"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="66">
+      <c r="A82" s="71">
         <v>46225</v>
       </c>
       <c r="B82" s="67" t="s">
@@ -2525,7 +2531,7 @@
       <c r="G82" s="67"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="66"/>
+      <c r="A83" s="71"/>
       <c r="B83" s="67"/>
       <c r="C83" s="67" t="s">
         <v>90</v>
@@ -2536,7 +2542,7 @@
       <c r="G83" s="67"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
+      <c r="A84" s="71"/>
       <c r="B84" s="67"/>
       <c r="C84" s="67" t="s">
         <v>93</v>
@@ -2547,7 +2553,7 @@
       <c r="G84" s="67"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
+      <c r="A85" s="71"/>
       <c r="B85" s="67" t="s">
         <v>4</v>
       </c>
@@ -2560,7 +2566,7 @@
       <c r="G85" s="67"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
+      <c r="A86" s="71"/>
       <c r="B86" s="67"/>
       <c r="C86" s="67" t="s">
         <v>72</v>
@@ -2571,7 +2577,7 @@
       <c r="G86" s="67"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="66"/>
+      <c r="A87" s="71"/>
       <c r="B87" s="67"/>
       <c r="C87" s="67" t="s">
         <v>89</v>
@@ -2582,7 +2588,7 @@
       <c r="G87" s="67"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="66"/>
+      <c r="A88" s="71"/>
       <c r="B88" s="67"/>
       <c r="C88" s="67" t="s">
         <v>35</v>
@@ -2593,18 +2599,18 @@
       <c r="G88" s="67"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="66"/>
+      <c r="A89" s="71"/>
       <c r="B89" s="67"/>
-      <c r="C89" s="68" t="s">
+      <c r="C89" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="70"/>
+      <c r="D89" s="73"/>
+      <c r="E89" s="73"/>
+      <c r="F89" s="73"/>
+      <c r="G89" s="74"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="66"/>
+      <c r="A90" s="71"/>
       <c r="B90" s="67"/>
       <c r="C90" s="67" t="s">
         <v>92</v>
@@ -2615,10 +2621,10 @@
       <c r="G90" s="67"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="86">
+      <c r="A91" s="80">
         <v>46227</v>
       </c>
-      <c r="B91" s="76" t="s">
+      <c r="B91" s="78" t="s">
         <v>5</v>
       </c>
       <c r="C91" s="67" t="s">
@@ -2630,18 +2636,18 @@
       <c r="G91" s="67"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="88"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="68" t="s">
+      <c r="A92" s="81"/>
+      <c r="B92" s="79"/>
+      <c r="C92" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="69"/>
-      <c r="E92" s="69"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="70"/>
+      <c r="D92" s="73"/>
+      <c r="E92" s="73"/>
+      <c r="F92" s="73"/>
+      <c r="G92" s="74"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="66">
+      <c r="A93" s="71">
         <v>46228</v>
       </c>
       <c r="B93" s="67" t="s">
@@ -2656,7 +2662,7 @@
       <c r="G93" s="67"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="67"/>
       <c r="C94" s="67" t="s">
         <v>97</v>
@@ -2667,7 +2673,7 @@
       <c r="G94" s="67"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="66"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="67"/>
       <c r="C95" s="67" t="s">
         <v>98</v>
@@ -2678,7 +2684,7 @@
       <c r="G95" s="67"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="66"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="67"/>
       <c r="C96" s="67" t="s">
         <v>99</v>
@@ -2689,7 +2695,7 @@
       <c r="G96" s="67"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="66"/>
+      <c r="A97" s="71"/>
       <c r="B97" s="67"/>
       <c r="C97" s="67" t="s">
         <v>100</v>
@@ -2700,7 +2706,7 @@
       <c r="G97" s="67"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="66"/>
+      <c r="A98" s="71"/>
       <c r="B98" s="67"/>
       <c r="C98" s="67" t="s">
         <v>101</v>
@@ -2711,7 +2717,7 @@
       <c r="G98" s="67"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="66">
+      <c r="A99" s="71">
         <v>46230</v>
       </c>
       <c r="B99" s="67" t="s">
@@ -2726,7 +2732,7 @@
       <c r="G99" s="67"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="66"/>
+      <c r="A100" s="71"/>
       <c r="B100" s="67"/>
       <c r="C100" s="67" t="s">
         <v>39</v>
@@ -2737,50 +2743,50 @@
       <c r="G100" s="67"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="66">
+      <c r="A101" s="71">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="92" t="s">
+      <c r="C101" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="92"/>
-      <c r="E101" s="92"/>
-      <c r="F101" s="92"/>
-      <c r="G101" s="92"/>
+      <c r="D101" s="77"/>
+      <c r="E101" s="77"/>
+      <c r="F101" s="77"/>
+      <c r="G101" s="77"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="66"/>
+      <c r="A102" s="71"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="92" t="s">
+      <c r="C102" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="92"/>
-      <c r="E102" s="92"/>
-      <c r="F102" s="92"/>
-      <c r="G102" s="92"/>
+      <c r="D102" s="77"/>
+      <c r="E102" s="77"/>
+      <c r="F102" s="77"/>
+      <c r="G102" s="77"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="91" t="s">
+      <c r="A103" s="75" t="s">
         <v>105</v>
       </c>
       <c r="B103" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="81" t="s">
+      <c r="C103" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="81"/>
-      <c r="E103" s="81"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="81"/>
+      <c r="D103" s="76"/>
+      <c r="E103" s="76"/>
+      <c r="F103" s="76"/>
+      <c r="G103" s="76"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="91"/>
+      <c r="A104" s="75"/>
       <c r="B104" s="67"/>
       <c r="C104" s="67" t="s">
         <v>86</v>
@@ -2791,7 +2797,7 @@
       <c r="G104" s="67"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="91"/>
+      <c r="A105" s="75"/>
       <c r="B105" s="67"/>
       <c r="C105" s="67" t="s">
         <v>60</v>
@@ -2802,7 +2808,7 @@
       <c r="G105" s="67"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="91"/>
+      <c r="A106" s="75"/>
       <c r="B106" s="67"/>
       <c r="C106" s="67" t="s">
         <v>50</v>
@@ -2813,7 +2819,7 @@
       <c r="G106" s="67"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="91"/>
+      <c r="A107" s="75"/>
       <c r="B107" s="67"/>
       <c r="C107" s="67" t="s">
         <v>107</v>
@@ -2824,7 +2830,7 @@
       <c r="G107" s="67"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="66">
+      <c r="A108" s="71">
         <v>46234</v>
       </c>
       <c r="B108" s="67" t="s">
@@ -2839,7 +2845,7 @@
       <c r="G108" s="67"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="66"/>
+      <c r="A109" s="71"/>
       <c r="B109" s="67"/>
       <c r="C109" s="67" t="s">
         <v>39</v>
@@ -2857,68 +2863,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2943,67 +2948,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3021,15 +3027,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="87">
         <v>46235</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3962,7 +3968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -3971,15 +3977,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="92">
         <v>46266</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4326,9 +4332,6 @@
       <c r="C33" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94"/>
       <c r="G33" s="51"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -4337,9 +4340,6 @@
       <c r="C34" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
       <c r="G34" s="51"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -4348,9 +4348,6 @@
       <c r="C35" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="D35" s="94"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="94"/>
       <c r="G35" s="51"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -4359,9 +4356,6 @@
       <c r="C36" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="94"/>
-      <c r="E36" s="94"/>
-      <c r="F36" s="94"/>
       <c r="G36" s="51"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -4370,32 +4364,96 @@
       <c r="C37" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="94"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
       <c r="G37" s="51"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="45"/>
       <c r="B38" s="45"/>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="50"/>
+      <c r="D38" s="93"/>
+      <c r="E38" s="93"/>
+      <c r="F38" s="93"/>
+      <c r="G38" s="51"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="62">
+      <c r="A39" s="6">
         <v>46280</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="10" t="s">
+      <c r="B39" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="52" t="s">
         <v>169</v>
       </c>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="54"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>46282</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="54"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="11">
+        <v>46283</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="48"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" s="93"/>
+      <c r="E42" s="93"/>
+      <c r="F42" s="93"/>
+      <c r="G42" s="51"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="46"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" s="93"/>
+      <c r="E43" s="93"/>
+      <c r="F43" s="93"/>
+      <c r="G43" s="51"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="45"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD61C0B-D9FA-4763-A573-1C71E8E39436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D80F23-1BC1-40C0-A778-9EC9F06B1BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="173">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -926,6 +926,30 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -941,80 +965,56 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1344,15 +1344,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="62">
+      <c r="A1" s="70">
         <v>46174</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1361,146 +1361,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="66"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="71">
+      <c r="A3" s="65">
         <v>46202</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="65"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
-      <c r="B6" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="71"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67" t="s">
+      <c r="A7" s="65"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
+      <c r="A8" s="65"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="71">
+      <c r="A9" s="65">
         <v>46203</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="74"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="69"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="71"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="68" t="s">
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="70"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="64"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="71"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="68" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="70"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="64"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="68" t="s">
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="70"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="64"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="71"/>
+      <c r="A13" s="65"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="70"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="64"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1510,14 +1510,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1528,6 +1520,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1545,15 +1545,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="87">
+      <c r="A1" s="78">
         <v>46204</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1562,152 +1562,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="71">
+      <c r="A3" s="65">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="76" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="65"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="89">
+      <c r="A7" s="81">
         <v>46205</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="74"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="90"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="82"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="70"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="64"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="90"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="68" t="s">
+      <c r="A9" s="82"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="64"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="90"/>
-      <c r="B10" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="68" t="s">
+      <c r="A10" s="82"/>
+      <c r="B10" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="70"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="64"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="90"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="68" t="s">
+      <c r="A11" s="82"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="70"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="64"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="90"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="68" t="s">
+      <c r="A12" s="82"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="70"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="64"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="91"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="68" t="s">
+      <c r="A13" s="83"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="70"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="64"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="80">
+      <c r="A14" s="85">
         <v>46206</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="75" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1719,348 +1719,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="83"/>
-      <c r="B15" s="86"/>
-      <c r="C15" s="72" t="s">
+      <c r="A15" s="86"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="74"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="69"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="83"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="72" t="s">
+      <c r="A16" s="86"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="74"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="69"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="83"/>
-      <c r="B17" s="79"/>
-      <c r="C17" s="72" t="s">
+      <c r="A17" s="86"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="74"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="69"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="83"/>
-      <c r="B18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="72" t="s">
+      <c r="A18" s="86"/>
+      <c r="B18" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="74"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="69"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="81"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="72" t="s">
+      <c r="A19" s="87"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="74"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="69"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="84">
+      <c r="A20" s="88">
         <v>46209</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="84"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67" t="s">
+      <c r="A21" s="88"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67" t="s">
+      <c r="A22" s="88"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
-      <c r="B23" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="67" t="s">
+      <c r="A23" s="88"/>
+      <c r="B23" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="72" t="s">
+      <c r="A24" s="88"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="74"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="69"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="72" t="s">
+      <c r="A25" s="88"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="74"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="69"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="72" t="s">
+      <c r="A26" s="88"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="74"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="69"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="72" t="s">
+      <c r="A27" s="88"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="74"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="69"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="72" t="s">
+      <c r="A28" s="88"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="74"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="72" t="s">
+      <c r="A29" s="88"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="74"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="69"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="72" t="s">
+      <c r="A30" s="88"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="74"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="69"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="72" t="s">
+      <c r="A31" s="88"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="74"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="69"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="84"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="72" t="s">
+      <c r="A32" s="88"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="74"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="69"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="84"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="72" t="s">
+      <c r="A33" s="88"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="74"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="69"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="84"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="72" t="s">
+      <c r="A34" s="88"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="74"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="69"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="82">
+      <c r="A35" s="84">
         <v>46210</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="82"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67" t="s">
+      <c r="A36" s="84"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="82"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67" t="s">
+      <c r="A37" s="84"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="82"/>
-      <c r="B38" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="A38" s="84"/>
+      <c r="B38" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="82"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67" t="s">
+      <c r="A39" s="84"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="82"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67" t="s">
+      <c r="A40" s="84"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="82"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67" t="s">
+      <c r="A41" s="84"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="82"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67" t="s">
+      <c r="A42" s="84"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="82"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67" t="s">
+      <c r="A43" s="84"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="82"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="72" t="s">
+      <c r="A44" s="84"/>
+      <c r="B44" s="66"/>
+      <c r="C44" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
-      <c r="F44" s="73"/>
-      <c r="G44" s="74"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2069,13 +2069,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="C45" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="66"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2084,255 +2084,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="66"/>
+      <c r="G46" s="66"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="80">
+      <c r="A47" s="85">
         <v>46213</v>
       </c>
-      <c r="B47" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="72" t="s">
+      <c r="B47" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="73"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="74"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="69"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="83"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="72" t="s">
+      <c r="A48" s="86"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="74"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="68"/>
+      <c r="G48" s="69"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="83"/>
-      <c r="B49" s="86"/>
-      <c r="C49" s="72" t="s">
+      <c r="A49" s="86"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="73"/>
-      <c r="G49" s="74"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="68"/>
+      <c r="G49" s="69"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="83"/>
-      <c r="B50" s="86"/>
-      <c r="C50" s="72" t="s">
+      <c r="A50" s="86"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="73"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="73"/>
-      <c r="G50" s="74"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="68"/>
+      <c r="G50" s="69"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="81"/>
-      <c r="B51" s="79"/>
-      <c r="C51" s="72" t="s">
+      <c r="A51" s="87"/>
+      <c r="B51" s="76"/>
+      <c r="C51" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="73"/>
-      <c r="E51" s="73"/>
-      <c r="F51" s="73"/>
-      <c r="G51" s="74"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
+      <c r="F51" s="68"/>
+      <c r="G51" s="69"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="71">
+      <c r="A52" s="65">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="C52" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="66"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="71"/>
+      <c r="A53" s="65"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="66"/>
+      <c r="G53" s="66"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="71">
+      <c r="A54" s="65">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="72" t="s">
+      <c r="C54" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="73"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="74"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="68"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="69"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="71"/>
-      <c r="B55" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="85" t="s">
+      <c r="A55" s="65"/>
+      <c r="B55" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="85"/>
-      <c r="E55" s="85"/>
-      <c r="F55" s="85"/>
-      <c r="G55" s="85"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="71"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="85" t="s">
+      <c r="A56" s="65"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="85"/>
+      <c r="D56" s="89"/>
+      <c r="E56" s="89"/>
+      <c r="F56" s="89"/>
+      <c r="G56" s="89"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="71"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="85" t="s">
+      <c r="A57" s="65"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="85"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="85"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="89"/>
+      <c r="F57" s="89"/>
+      <c r="G57" s="89"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="71"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="85" t="s">
+      <c r="A58" s="65"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="85"/>
-      <c r="E58" s="85"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="85"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="89"/>
+      <c r="F58" s="89"/>
+      <c r="G58" s="89"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="71"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="85" t="s">
+      <c r="A59" s="65"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="85"/>
-      <c r="E59" s="85"/>
-      <c r="F59" s="85"/>
-      <c r="G59" s="85"/>
+      <c r="D59" s="89"/>
+      <c r="E59" s="89"/>
+      <c r="F59" s="89"/>
+      <c r="G59" s="89"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="71"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="85" t="s">
+      <c r="A60" s="65"/>
+      <c r="B60" s="66"/>
+      <c r="C60" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="85"/>
-      <c r="E60" s="85"/>
-      <c r="F60" s="85"/>
-      <c r="G60" s="85"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="71"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="85" t="s">
+      <c r="A61" s="65"/>
+      <c r="B61" s="66"/>
+      <c r="C61" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="85"/>
-      <c r="E61" s="85"/>
-      <c r="F61" s="85"/>
-      <c r="G61" s="85"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="89"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="71"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="85" t="s">
+      <c r="A62" s="65"/>
+      <c r="B62" s="66"/>
+      <c r="C62" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="85"/>
-      <c r="E62" s="85"/>
-      <c r="F62" s="85"/>
-      <c r="G62" s="85"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="89"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="71"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="85" t="s">
+      <c r="A63" s="65"/>
+      <c r="B63" s="66"/>
+      <c r="C63" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="85"/>
-      <c r="E63" s="85"/>
-      <c r="F63" s="85"/>
-      <c r="G63" s="85"/>
+      <c r="D63" s="89"/>
+      <c r="E63" s="89"/>
+      <c r="F63" s="89"/>
+      <c r="G63" s="89"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="71">
+      <c r="A64" s="65">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="67" t="s">
+      <c r="C64" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
+      <c r="D64" s="66"/>
+      <c r="E64" s="66"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="66"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="71"/>
-      <c r="B65" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="67" t="s">
+      <c r="A65" s="65"/>
+      <c r="B65" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
+      <c r="D65" s="66"/>
+      <c r="E65" s="66"/>
+      <c r="F65" s="66"/>
+      <c r="G65" s="66"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="71"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67" t="s">
+      <c r="A66" s="65"/>
+      <c r="B66" s="66"/>
+      <c r="C66" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
+      <c r="D66" s="66"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="66"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2341,164 +2341,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="67" t="s">
+      <c r="C67" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="66"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="71">
+      <c r="A68" s="65">
         <v>46220</v>
       </c>
-      <c r="B68" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="67" t="s">
+      <c r="B68" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="66"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="71"/>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="A69" s="65"/>
+      <c r="B69" s="66"/>
+      <c r="C69" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="66"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="71">
+      <c r="A70" s="65">
         <v>46223</v>
       </c>
-      <c r="B70" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="72" t="s">
+      <c r="B70" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="73"/>
-      <c r="E70" s="73"/>
-      <c r="F70" s="73"/>
-      <c r="G70" s="74"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="68"/>
+      <c r="F70" s="68"/>
+      <c r="G70" s="69"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="71"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="72" t="s">
+      <c r="A71" s="65"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="73"/>
-      <c r="E71" s="73"/>
-      <c r="F71" s="73"/>
-      <c r="G71" s="74"/>
+      <c r="D71" s="68"/>
+      <c r="E71" s="68"/>
+      <c r="F71" s="68"/>
+      <c r="G71" s="69"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="71"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="72" t="s">
+      <c r="A72" s="65"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="73"/>
-      <c r="E72" s="73"/>
-      <c r="F72" s="73"/>
-      <c r="G72" s="74"/>
+      <c r="D72" s="68"/>
+      <c r="E72" s="68"/>
+      <c r="F72" s="68"/>
+      <c r="G72" s="69"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="71"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="72" t="s">
+      <c r="A73" s="65"/>
+      <c r="B73" s="66"/>
+      <c r="C73" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="73"/>
-      <c r="E73" s="73"/>
-      <c r="F73" s="73"/>
-      <c r="G73" s="74"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="68"/>
+      <c r="F73" s="68"/>
+      <c r="G73" s="69"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="71"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="72" t="s">
+      <c r="A74" s="65"/>
+      <c r="B74" s="66"/>
+      <c r="C74" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="73"/>
-      <c r="E74" s="73"/>
-      <c r="F74" s="73"/>
-      <c r="G74" s="74"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="68"/>
+      <c r="F74" s="68"/>
+      <c r="G74" s="69"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="71"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="72" t="s">
+      <c r="A75" s="65"/>
+      <c r="B75" s="66"/>
+      <c r="C75" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="73"/>
-      <c r="E75" s="73"/>
-      <c r="F75" s="73"/>
-      <c r="G75" s="74"/>
+      <c r="D75" s="68"/>
+      <c r="E75" s="68"/>
+      <c r="F75" s="68"/>
+      <c r="G75" s="69"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="71"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="72" t="s">
+      <c r="A76" s="65"/>
+      <c r="B76" s="66"/>
+      <c r="C76" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="74"/>
+      <c r="D76" s="68"/>
+      <c r="E76" s="68"/>
+      <c r="F76" s="68"/>
+      <c r="G76" s="69"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="71"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="68" t="s">
+      <c r="A77" s="65"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="69"/>
-      <c r="E77" s="69"/>
-      <c r="F77" s="69"/>
-      <c r="G77" s="70"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="63"/>
+      <c r="F77" s="63"/>
+      <c r="G77" s="64"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="71"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="68" t="s">
+      <c r="A78" s="65"/>
+      <c r="B78" s="66"/>
+      <c r="C78" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="69"/>
-      <c r="E78" s="69"/>
-      <c r="F78" s="69"/>
-      <c r="G78" s="70"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="63"/>
+      <c r="F78" s="63"/>
+      <c r="G78" s="64"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="71"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="68" t="s">
+      <c r="A79" s="65"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="69"/>
-      <c r="E79" s="69"/>
-      <c r="F79" s="69"/>
-      <c r="G79" s="70"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="63"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="64"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="71"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="68" t="s">
+      <c r="A80" s="65"/>
+      <c r="B80" s="66"/>
+      <c r="C80" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="69"/>
-      <c r="E80" s="69"/>
-      <c r="F80" s="69"/>
-      <c r="G80" s="70"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="64"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2507,353 +2507,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="67" t="s">
+      <c r="C81" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
+      <c r="D81" s="66"/>
+      <c r="E81" s="66"/>
+      <c r="F81" s="66"/>
+      <c r="G81" s="66"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="71">
+      <c r="A82" s="65">
         <v>46225</v>
       </c>
-      <c r="B82" s="67" t="s">
+      <c r="B82" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
+      <c r="D82" s="66"/>
+      <c r="E82" s="66"/>
+      <c r="F82" s="66"/>
+      <c r="G82" s="66"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="71"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="67" t="s">
+      <c r="A83" s="65"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="67"/>
+      <c r="D83" s="66"/>
+      <c r="E83" s="66"/>
+      <c r="F83" s="66"/>
+      <c r="G83" s="66"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="71"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="67" t="s">
+      <c r="A84" s="65"/>
+      <c r="B84" s="66"/>
+      <c r="C84" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="67"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="67"/>
+      <c r="D84" s="66"/>
+      <c r="E84" s="66"/>
+      <c r="F84" s="66"/>
+      <c r="G84" s="66"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="71"/>
-      <c r="B85" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="67" t="s">
+      <c r="A85" s="65"/>
+      <c r="B85" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="67"/>
+      <c r="D85" s="66"/>
+      <c r="E85" s="66"/>
+      <c r="F85" s="66"/>
+      <c r="G85" s="66"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="71"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67" t="s">
+      <c r="A86" s="65"/>
+      <c r="B86" s="66"/>
+      <c r="C86" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="67"/>
+      <c r="D86" s="66"/>
+      <c r="E86" s="66"/>
+      <c r="F86" s="66"/>
+      <c r="G86" s="66"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="71"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67" t="s">
+      <c r="A87" s="65"/>
+      <c r="B87" s="66"/>
+      <c r="C87" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
+      <c r="D87" s="66"/>
+      <c r="E87" s="66"/>
+      <c r="F87" s="66"/>
+      <c r="G87" s="66"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="71"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="67" t="s">
+      <c r="A88" s="65"/>
+      <c r="B88" s="66"/>
+      <c r="C88" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="67"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
+      <c r="D88" s="66"/>
+      <c r="E88" s="66"/>
+      <c r="F88" s="66"/>
+      <c r="G88" s="66"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="71"/>
-      <c r="B89" s="67"/>
-      <c r="C89" s="72" t="s">
+      <c r="A89" s="65"/>
+      <c r="B89" s="66"/>
+      <c r="C89" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="73"/>
-      <c r="E89" s="73"/>
-      <c r="F89" s="73"/>
-      <c r="G89" s="74"/>
+      <c r="D89" s="68"/>
+      <c r="E89" s="68"/>
+      <c r="F89" s="68"/>
+      <c r="G89" s="69"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="71"/>
-      <c r="B90" s="67"/>
-      <c r="C90" s="67" t="s">
+      <c r="A90" s="65"/>
+      <c r="B90" s="66"/>
+      <c r="C90" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
+      <c r="D90" s="66"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="66"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="80">
+      <c r="A91" s="85">
         <v>46227</v>
       </c>
-      <c r="B91" s="78" t="s">
+      <c r="B91" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
+      <c r="D91" s="66"/>
+      <c r="E91" s="66"/>
+      <c r="F91" s="66"/>
+      <c r="G91" s="66"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="81"/>
-      <c r="B92" s="79"/>
-      <c r="C92" s="72" t="s">
+      <c r="A92" s="87"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="73"/>
-      <c r="E92" s="73"/>
-      <c r="F92" s="73"/>
-      <c r="G92" s="74"/>
+      <c r="D92" s="68"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="68"/>
+      <c r="G92" s="69"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="71">
+      <c r="A93" s="65">
         <v>46228</v>
       </c>
-      <c r="B93" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="67" t="s">
+      <c r="B93" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="67"/>
+      <c r="D93" s="66"/>
+      <c r="E93" s="66"/>
+      <c r="F93" s="66"/>
+      <c r="G93" s="66"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="71"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="67" t="s">
+      <c r="A94" s="65"/>
+      <c r="B94" s="66"/>
+      <c r="C94" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="67"/>
+      <c r="D94" s="66"/>
+      <c r="E94" s="66"/>
+      <c r="F94" s="66"/>
+      <c r="G94" s="66"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="71"/>
-      <c r="B95" s="67"/>
-      <c r="C95" s="67" t="s">
+      <c r="A95" s="65"/>
+      <c r="B95" s="66"/>
+      <c r="C95" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="67"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="66"/>
+      <c r="F95" s="66"/>
+      <c r="G95" s="66"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="71"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="67" t="s">
+      <c r="A96" s="65"/>
+      <c r="B96" s="66"/>
+      <c r="C96" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="67"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="67"/>
+      <c r="D96" s="66"/>
+      <c r="E96" s="66"/>
+      <c r="F96" s="66"/>
+      <c r="G96" s="66"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="71"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="67" t="s">
+      <c r="A97" s="65"/>
+      <c r="B97" s="66"/>
+      <c r="C97" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="67"/>
+      <c r="D97" s="66"/>
+      <c r="E97" s="66"/>
+      <c r="F97" s="66"/>
+      <c r="G97" s="66"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="71"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="67" t="s">
+      <c r="A98" s="65"/>
+      <c r="B98" s="66"/>
+      <c r="C98" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="67"/>
+      <c r="D98" s="66"/>
+      <c r="E98" s="66"/>
+      <c r="F98" s="66"/>
+      <c r="G98" s="66"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="71">
+      <c r="A99" s="65">
         <v>46230</v>
       </c>
-      <c r="B99" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="67" t="s">
+      <c r="B99" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
+      <c r="D99" s="66"/>
+      <c r="E99" s="66"/>
+      <c r="F99" s="66"/>
+      <c r="G99" s="66"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="71"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="67" t="s">
+      <c r="A100" s="65"/>
+      <c r="B100" s="66"/>
+      <c r="C100" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="67"/>
+      <c r="D100" s="66"/>
+      <c r="E100" s="66"/>
+      <c r="F100" s="66"/>
+      <c r="G100" s="66"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="71">
+      <c r="A101" s="65">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="77" t="s">
+      <c r="C101" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="77"/>
-      <c r="E101" s="77"/>
-      <c r="F101" s="77"/>
-      <c r="G101" s="77"/>
+      <c r="D101" s="91"/>
+      <c r="E101" s="91"/>
+      <c r="F101" s="91"/>
+      <c r="G101" s="91"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="71"/>
+      <c r="A102" s="65"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="77" t="s">
+      <c r="C102" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="77"/>
-      <c r="E102" s="77"/>
-      <c r="F102" s="77"/>
-      <c r="G102" s="77"/>
+      <c r="D102" s="91"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="91"/>
+      <c r="G102" s="91"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="75" t="s">
+      <c r="A103" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="76" t="s">
+      <c r="B103" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="76"/>
-      <c r="E103" s="76"/>
-      <c r="F103" s="76"/>
-      <c r="G103" s="76"/>
+      <c r="D103" s="80"/>
+      <c r="E103" s="80"/>
+      <c r="F103" s="80"/>
+      <c r="G103" s="80"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="75"/>
-      <c r="B104" s="67"/>
-      <c r="C104" s="67" t="s">
+      <c r="A104" s="90"/>
+      <c r="B104" s="66"/>
+      <c r="C104" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
+      <c r="D104" s="66"/>
+      <c r="E104" s="66"/>
+      <c r="F104" s="66"/>
+      <c r="G104" s="66"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="75"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="67" t="s">
+      <c r="A105" s="90"/>
+      <c r="B105" s="66"/>
+      <c r="C105" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="67"/>
+      <c r="D105" s="66"/>
+      <c r="E105" s="66"/>
+      <c r="F105" s="66"/>
+      <c r="G105" s="66"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="75"/>
-      <c r="B106" s="67"/>
-      <c r="C106" s="67" t="s">
+      <c r="A106" s="90"/>
+      <c r="B106" s="66"/>
+      <c r="C106" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="67"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="67"/>
+      <c r="D106" s="66"/>
+      <c r="E106" s="66"/>
+      <c r="F106" s="66"/>
+      <c r="G106" s="66"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="75"/>
-      <c r="B107" s="67"/>
-      <c r="C107" s="67" t="s">
+      <c r="A107" s="90"/>
+      <c r="B107" s="66"/>
+      <c r="C107" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="67"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="67"/>
+      <c r="D107" s="66"/>
+      <c r="E107" s="66"/>
+      <c r="F107" s="66"/>
+      <c r="G107" s="66"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="71">
+      <c r="A108" s="65">
         <v>46234</v>
       </c>
-      <c r="B108" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="67" t="s">
+      <c r="B108" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="66" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="67"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="67"/>
-      <c r="G108" s="67"/>
+      <c r="D108" s="66"/>
+      <c r="E108" s="66"/>
+      <c r="F108" s="66"/>
+      <c r="G108" s="66"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="71"/>
-      <c r="B109" s="67"/>
-      <c r="C109" s="67" t="s">
+      <c r="A109" s="65"/>
+      <c r="B109" s="66"/>
+      <c r="C109" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="67"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="67"/>
-      <c r="G109" s="67"/>
+      <c r="D109" s="66"/>
+      <c r="E109" s="66"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="66"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2863,6 +2863,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2887,129 +3010,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3027,15 +3027,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="87">
+      <c r="A1" s="78">
         <v>46235</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3968,7 +3968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -4372,9 +4372,6 @@
       <c r="C38" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="D38" s="93"/>
-      <c r="E38" s="93"/>
-      <c r="F38" s="93"/>
       <c r="G38" s="51"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -4428,9 +4425,6 @@
       <c r="C42" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="D42" s="93"/>
-      <c r="E42" s="93"/>
-      <c r="F42" s="93"/>
       <c r="G42" s="51"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -4439,9 +4433,6 @@
       <c r="C43" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="D43" s="93"/>
-      <c r="E43" s="93"/>
-      <c r="F43" s="93"/>
       <c r="G43" s="51"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -4454,6 +4445,43 @@
       <c r="E44" s="49"/>
       <c r="F44" s="49"/>
       <c r="G44" s="50"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>46284</v>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="48"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="93"/>
+      <c r="G46" s="51"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="45"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D27B2F-9896-444A-81D5-F04C2E3D6FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D80F23-1BC1-40C0-A778-9EC9F06B1BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="173">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -538,6 +538,18 @@
   </si>
   <si>
     <t>Trả BH Ngọc Hoàn (trả trước ID: VNET861385070647584, 0032001EFD)</t>
+  </si>
+  <si>
+    <t>Nhận BH Đại lý Ngọc Hoàn</t>
+  </si>
+  <si>
+    <t>Trả BH SEA 1 VNSH02 ID: 003200B1A2 (A. Bảo)</t>
+  </si>
+  <si>
+    <t>Trả BH Nam Định</t>
+  </si>
+  <si>
+    <t>Trả BH Nam Anh</t>
   </si>
 </sst>
 </file>
@@ -914,7 +926,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -932,82 +965,61 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1332,15 +1344,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="63">
+      <c r="A1" s="70">
         <v>46174</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1349,146 +1361,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="74"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="65">
         <v>46202</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="65"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68" t="s">
+      <c r="A7" s="65"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="65"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72">
+      <c r="A9" s="65">
         <v>46203</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="69"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="64"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="64"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="64"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="65"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="64"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1498,14 +1510,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1516,6 +1520,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1533,15 +1545,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="78">
         <v>46204</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1550,152 +1562,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="65">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="77" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="65"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="81">
         <v>46205</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="69" t="s">
+      <c r="A8" s="82"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="71"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="64"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="82"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="64"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
-      <c r="B10" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="82"/>
+      <c r="B10" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="64"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="91"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="82"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="64"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="82"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="64"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69" t="s">
+      <c r="A13" s="83"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="64"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="81">
+      <c r="A14" s="85">
         <v>46206</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="75" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1707,348 +1719,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="73" t="s">
+      <c r="A15" s="86"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="69"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="84"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="73" t="s">
+      <c r="A16" s="86"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="69"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="73" t="s">
+      <c r="A17" s="86"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="69"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="84"/>
-      <c r="B18" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="73" t="s">
+      <c r="A18" s="86"/>
+      <c r="B18" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="75"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="69"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="73" t="s">
+      <c r="A19" s="87"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="69"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="88">
         <v>46209</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68" t="s">
+      <c r="A21" s="88"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68" t="s">
+      <c r="A22" s="88"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="68" t="s">
+      <c r="A23" s="88"/>
+      <c r="B23" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="73" t="s">
+      <c r="A24" s="88"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="75"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="69"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="73" t="s">
+      <c r="A25" s="88"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="75"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="69"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="73" t="s">
+      <c r="A26" s="88"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="69"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="73" t="s">
+      <c r="A27" s="88"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="75"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="69"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="73" t="s">
+      <c r="A28" s="88"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="75"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="73" t="s">
+      <c r="A29" s="88"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="69"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="73" t="s">
+      <c r="A30" s="88"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="69"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="73" t="s">
+      <c r="A31" s="88"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="69"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="73" t="s">
+      <c r="A32" s="88"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="69"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="73" t="s">
+      <c r="A33" s="88"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="69"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="73" t="s">
+      <c r="A34" s="88"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="69"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="83">
+      <c r="A35" s="84">
         <v>46210</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68" t="s">
+      <c r="A36" s="84"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68" t="s">
+      <c r="A37" s="84"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
-      <c r="B38" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="68" t="s">
+      <c r="A38" s="84"/>
+      <c r="B38" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68" t="s">
+      <c r="A39" s="84"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68" t="s">
+      <c r="A40" s="84"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68" t="s">
+      <c r="A41" s="84"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68" t="s">
+      <c r="A42" s="84"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68" t="s">
+      <c r="A43" s="84"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="73" t="s">
+      <c r="A44" s="84"/>
+      <c r="B44" s="66"/>
+      <c r="C44" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="75"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2057,13 +2069,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="66"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2072,255 +2084,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="66"/>
+      <c r="G46" s="66"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="81">
+      <c r="A47" s="85">
         <v>46213</v>
       </c>
-      <c r="B47" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="73" t="s">
+      <c r="B47" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="75"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="69"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="84"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="73" t="s">
+      <c r="A48" s="86"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="75"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="68"/>
+      <c r="G48" s="69"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="84"/>
-      <c r="B49" s="87"/>
-      <c r="C49" s="73" t="s">
+      <c r="A49" s="86"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="75"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="68"/>
+      <c r="G49" s="69"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="87"/>
-      <c r="C50" s="73" t="s">
+      <c r="A50" s="86"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="68"/>
+      <c r="G50" s="69"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="73" t="s">
+      <c r="A51" s="87"/>
+      <c r="B51" s="76"/>
+      <c r="C51" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="75"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
+      <c r="F51" s="68"/>
+      <c r="G51" s="69"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="72">
+      <c r="A52" s="65">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="66"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="65"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="66"/>
+      <c r="G53" s="66"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="72">
+      <c r="A54" s="65">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="75"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="68"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="69"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
-      <c r="B55" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="86" t="s">
+      <c r="A55" s="65"/>
+      <c r="B55" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="86" t="s">
+      <c r="A56" s="65"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
+      <c r="D56" s="89"/>
+      <c r="E56" s="89"/>
+      <c r="F56" s="89"/>
+      <c r="G56" s="89"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="86" t="s">
+      <c r="A57" s="65"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="89"/>
+      <c r="F57" s="89"/>
+      <c r="G57" s="89"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="86" t="s">
+      <c r="A58" s="65"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="89"/>
+      <c r="F58" s="89"/>
+      <c r="G58" s="89"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="86" t="s">
+      <c r="A59" s="65"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
+      <c r="D59" s="89"/>
+      <c r="E59" s="89"/>
+      <c r="F59" s="89"/>
+      <c r="G59" s="89"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="86" t="s">
+      <c r="A60" s="65"/>
+      <c r="B60" s="66"/>
+      <c r="C60" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="86" t="s">
+      <c r="A61" s="65"/>
+      <c r="B61" s="66"/>
+      <c r="C61" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="86"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="89"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="86" t="s">
+      <c r="A62" s="65"/>
+      <c r="B62" s="66"/>
+      <c r="C62" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="89"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="86" t="s">
+      <c r="A63" s="65"/>
+      <c r="B63" s="66"/>
+      <c r="C63" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
+      <c r="D63" s="89"/>
+      <c r="E63" s="89"/>
+      <c r="F63" s="89"/>
+      <c r="G63" s="89"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="72">
+      <c r="A64" s="65">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
+      <c r="D64" s="66"/>
+      <c r="E64" s="66"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="66"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
-      <c r="B65" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="68" t="s">
+      <c r="A65" s="65"/>
+      <c r="B65" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
+      <c r="D65" s="66"/>
+      <c r="E65" s="66"/>
+      <c r="F65" s="66"/>
+      <c r="G65" s="66"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68" t="s">
+      <c r="A66" s="65"/>
+      <c r="B66" s="66"/>
+      <c r="C66" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
+      <c r="D66" s="66"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="66"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2329,164 +2341,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="66"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="72">
+      <c r="A68" s="65">
         <v>46220</v>
       </c>
-      <c r="B68" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="68" t="s">
+      <c r="B68" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="66"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68" t="s">
+      <c r="A69" s="65"/>
+      <c r="B69" s="66"/>
+      <c r="C69" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="66"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="72">
+      <c r="A70" s="65">
         <v>46223</v>
       </c>
-      <c r="B70" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="73" t="s">
+      <c r="B70" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="75"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="68"/>
+      <c r="F70" s="68"/>
+      <c r="G70" s="69"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="73" t="s">
+      <c r="A71" s="65"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="75"/>
+      <c r="D71" s="68"/>
+      <c r="E71" s="68"/>
+      <c r="F71" s="68"/>
+      <c r="G71" s="69"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="73" t="s">
+      <c r="A72" s="65"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="75"/>
+      <c r="D72" s="68"/>
+      <c r="E72" s="68"/>
+      <c r="F72" s="68"/>
+      <c r="G72" s="69"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="73" t="s">
+      <c r="A73" s="65"/>
+      <c r="B73" s="66"/>
+      <c r="C73" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="75"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="68"/>
+      <c r="F73" s="68"/>
+      <c r="G73" s="69"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="73" t="s">
+      <c r="A74" s="65"/>
+      <c r="B74" s="66"/>
+      <c r="C74" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="75"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="68"/>
+      <c r="F74" s="68"/>
+      <c r="G74" s="69"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="73" t="s">
+      <c r="A75" s="65"/>
+      <c r="B75" s="66"/>
+      <c r="C75" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="75"/>
+      <c r="D75" s="68"/>
+      <c r="E75" s="68"/>
+      <c r="F75" s="68"/>
+      <c r="G75" s="69"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="73" t="s">
+      <c r="A76" s="65"/>
+      <c r="B76" s="66"/>
+      <c r="C76" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="75"/>
+      <c r="D76" s="68"/>
+      <c r="E76" s="68"/>
+      <c r="F76" s="68"/>
+      <c r="G76" s="69"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="69" t="s">
+      <c r="A77" s="65"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="63"/>
+      <c r="F77" s="63"/>
+      <c r="G77" s="64"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="69" t="s">
+      <c r="A78" s="65"/>
+      <c r="B78" s="66"/>
+      <c r="C78" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="71"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="63"/>
+      <c r="F78" s="63"/>
+      <c r="G78" s="64"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="72"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="69" t="s">
+      <c r="A79" s="65"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
-      <c r="F79" s="70"/>
-      <c r="G79" s="71"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="63"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="64"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="69" t="s">
+      <c r="A80" s="65"/>
+      <c r="B80" s="66"/>
+      <c r="C80" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="71"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="64"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2495,353 +2507,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="68" t="s">
+      <c r="C81" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
+      <c r="D81" s="66"/>
+      <c r="E81" s="66"/>
+      <c r="F81" s="66"/>
+      <c r="G81" s="66"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="72">
+      <c r="A82" s="65">
         <v>46225</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
+      <c r="D82" s="66"/>
+      <c r="E82" s="66"/>
+      <c r="F82" s="66"/>
+      <c r="G82" s="66"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68" t="s">
+      <c r="A83" s="65"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
+      <c r="D83" s="66"/>
+      <c r="E83" s="66"/>
+      <c r="F83" s="66"/>
+      <c r="G83" s="66"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68" t="s">
+      <c r="A84" s="65"/>
+      <c r="B84" s="66"/>
+      <c r="C84" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
+      <c r="D84" s="66"/>
+      <c r="E84" s="66"/>
+      <c r="F84" s="66"/>
+      <c r="G84" s="66"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
-      <c r="B85" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="68" t="s">
+      <c r="A85" s="65"/>
+      <c r="B85" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
+      <c r="D85" s="66"/>
+      <c r="E85" s="66"/>
+      <c r="F85" s="66"/>
+      <c r="G85" s="66"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68" t="s">
+      <c r="A86" s="65"/>
+      <c r="B86" s="66"/>
+      <c r="C86" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
+      <c r="D86" s="66"/>
+      <c r="E86" s="66"/>
+      <c r="F86" s="66"/>
+      <c r="G86" s="66"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68" t="s">
+      <c r="A87" s="65"/>
+      <c r="B87" s="66"/>
+      <c r="C87" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
+      <c r="D87" s="66"/>
+      <c r="E87" s="66"/>
+      <c r="F87" s="66"/>
+      <c r="G87" s="66"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68" t="s">
+      <c r="A88" s="65"/>
+      <c r="B88" s="66"/>
+      <c r="C88" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
+      <c r="D88" s="66"/>
+      <c r="E88" s="66"/>
+      <c r="F88" s="66"/>
+      <c r="G88" s="66"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
-      <c r="B89" s="68"/>
-      <c r="C89" s="73" t="s">
+      <c r="A89" s="65"/>
+      <c r="B89" s="66"/>
+      <c r="C89" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="74"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="75"/>
+      <c r="D89" s="68"/>
+      <c r="E89" s="68"/>
+      <c r="F89" s="68"/>
+      <c r="G89" s="69"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="72"/>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68" t="s">
+      <c r="A90" s="65"/>
+      <c r="B90" s="66"/>
+      <c r="C90" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
+      <c r="D90" s="66"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="66"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="81">
+      <c r="A91" s="85">
         <v>46227</v>
       </c>
-      <c r="B91" s="79" t="s">
+      <c r="B91" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
+      <c r="D91" s="66"/>
+      <c r="E91" s="66"/>
+      <c r="F91" s="66"/>
+      <c r="G91" s="66"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="82"/>
-      <c r="B92" s="80"/>
-      <c r="C92" s="73" t="s">
+      <c r="A92" s="87"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="75"/>
+      <c r="D92" s="68"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="68"/>
+      <c r="G92" s="69"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="72">
+      <c r="A93" s="65">
         <v>46228</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="68" t="s">
+      <c r="B93" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
+      <c r="D93" s="66"/>
+      <c r="E93" s="66"/>
+      <c r="F93" s="66"/>
+      <c r="G93" s="66"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68" t="s">
+      <c r="A94" s="65"/>
+      <c r="B94" s="66"/>
+      <c r="C94" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
+      <c r="D94" s="66"/>
+      <c r="E94" s="66"/>
+      <c r="F94" s="66"/>
+      <c r="G94" s="66"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="72"/>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68" t="s">
+      <c r="A95" s="65"/>
+      <c r="B95" s="66"/>
+      <c r="C95" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="66"/>
+      <c r="F95" s="66"/>
+      <c r="G95" s="66"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="A96" s="65"/>
+      <c r="B96" s="66"/>
+      <c r="C96" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
+      <c r="D96" s="66"/>
+      <c r="E96" s="66"/>
+      <c r="F96" s="66"/>
+      <c r="G96" s="66"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="72"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="68" t="s">
+      <c r="A97" s="65"/>
+      <c r="B97" s="66"/>
+      <c r="C97" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="68"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
+      <c r="D97" s="66"/>
+      <c r="E97" s="66"/>
+      <c r="F97" s="66"/>
+      <c r="G97" s="66"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="72"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="68" t="s">
+      <c r="A98" s="65"/>
+      <c r="B98" s="66"/>
+      <c r="C98" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
+      <c r="D98" s="66"/>
+      <c r="E98" s="66"/>
+      <c r="F98" s="66"/>
+      <c r="G98" s="66"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="72">
+      <c r="A99" s="65">
         <v>46230</v>
       </c>
-      <c r="B99" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="68" t="s">
+      <c r="B99" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
+      <c r="D99" s="66"/>
+      <c r="E99" s="66"/>
+      <c r="F99" s="66"/>
+      <c r="G99" s="66"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="72"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="68" t="s">
+      <c r="A100" s="65"/>
+      <c r="B100" s="66"/>
+      <c r="C100" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="68"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
+      <c r="D100" s="66"/>
+      <c r="E100" s="66"/>
+      <c r="F100" s="66"/>
+      <c r="G100" s="66"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="72">
+      <c r="A101" s="65">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="78" t="s">
+      <c r="C101" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="78"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="78"/>
+      <c r="D101" s="91"/>
+      <c r="E101" s="91"/>
+      <c r="F101" s="91"/>
+      <c r="G101" s="91"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="72"/>
+      <c r="A102" s="65"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="78" t="s">
+      <c r="C102" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="78"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="78"/>
+      <c r="D102" s="91"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="91"/>
+      <c r="G102" s="91"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="76" t="s">
+      <c r="A103" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="77" t="s">
+      <c r="B103" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
+      <c r="D103" s="80"/>
+      <c r="E103" s="80"/>
+      <c r="F103" s="80"/>
+      <c r="G103" s="80"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
-      <c r="B104" s="68"/>
-      <c r="C104" s="68" t="s">
+      <c r="A104" s="90"/>
+      <c r="B104" s="66"/>
+      <c r="C104" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
+      <c r="D104" s="66"/>
+      <c r="E104" s="66"/>
+      <c r="F104" s="66"/>
+      <c r="G104" s="66"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68" t="s">
+      <c r="A105" s="90"/>
+      <c r="B105" s="66"/>
+      <c r="C105" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
+      <c r="D105" s="66"/>
+      <c r="E105" s="66"/>
+      <c r="F105" s="66"/>
+      <c r="G105" s="66"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
-      <c r="B106" s="68"/>
-      <c r="C106" s="68" t="s">
+      <c r="A106" s="90"/>
+      <c r="B106" s="66"/>
+      <c r="C106" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="68"/>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
+      <c r="D106" s="66"/>
+      <c r="E106" s="66"/>
+      <c r="F106" s="66"/>
+      <c r="G106" s="66"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
-      <c r="B107" s="68"/>
-      <c r="C107" s="68" t="s">
+      <c r="A107" s="90"/>
+      <c r="B107" s="66"/>
+      <c r="C107" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
+      <c r="D107" s="66"/>
+      <c r="E107" s="66"/>
+      <c r="F107" s="66"/>
+      <c r="G107" s="66"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="72">
+      <c r="A108" s="65">
         <v>46234</v>
       </c>
-      <c r="B108" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="66" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
+      <c r="D108" s="66"/>
+      <c r="E108" s="66"/>
+      <c r="F108" s="66"/>
+      <c r="G108" s="66"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="72"/>
-      <c r="B109" s="68"/>
-      <c r="C109" s="68" t="s">
+      <c r="A109" s="65"/>
+      <c r="B109" s="66"/>
+      <c r="C109" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
+      <c r="D109" s="66"/>
+      <c r="E109" s="66"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="66"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2851,6 +2863,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2875,129 +3010,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3015,15 +3027,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="78">
         <v>46235</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3956,7 +3968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -3965,15 +3977,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="92">
         <v>46266</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4287,53 +4299,189 @@
       <c r="G30" s="50"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="62">
+      <c r="A31" s="11">
         <v>46279</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="52" t="s">
         <v>167</v>
       </c>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="54"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="A32" s="46"/>
+      <c r="B32" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="24" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="10" t="s">
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="10" t="s">
+      <c r="G33" s="51"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="25" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="10" t="s">
+      <c r="G34" s="51"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="25" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="10" t="s">
+      <c r="G35" s="51"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="46"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="25" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="10" t="s">
+      <c r="G36" s="51"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="25" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C38" s="10" t="s">
+      <c r="G37" s="51"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="25" t="s">
         <v>168</v>
       </c>
+      <c r="G38" s="51"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="54"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>46282</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="54"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="11">
+        <v>46283</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="48"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="G42" s="51"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="46"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="G43" s="51"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="45"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="50"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>46284</v>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="48"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="93"/>
+      <c r="G46" s="51"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="45"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D80F23-1BC1-40C0-A778-9EC9F06B1BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EDE018-09B5-43C4-85E2-8D7288DCF56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="175">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -550,6 +550,12 @@
   </si>
   <si>
     <t>Trả BH Nam Anh</t>
+  </si>
+  <si>
+    <t>Trả BH Tuyên Hằng</t>
+  </si>
+  <si>
+    <t>Nhận BH Anh Tuấn NB</t>
   </si>
 </sst>
 </file>
@@ -773,7 +779,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -924,6 +930,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1344,15 +1353,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="70">
+      <c r="A1" s="71">
         <v>46174</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1361,146 +1370,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="75"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="65">
+      <c r="A3" s="66">
         <v>46202</v>
       </c>
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="66" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="65"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66" t="s">
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="66" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="65">
+      <c r="A9" s="66">
         <v>46203</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="70"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="62" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="62" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="62" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="65"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1545,15 +1554,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="78">
+      <c r="A1" s="79">
         <v>46204</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1562,152 +1571,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="65">
+      <c r="A3" s="66">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="80" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="81">
+      <c r="A7" s="82">
         <v>46205</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="82"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="62" t="s">
+      <c r="A8" s="83"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="65"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="82"/>
-      <c r="B9" s="76"/>
-      <c r="C9" s="62" t="s">
+      <c r="A9" s="83"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="65"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="82"/>
-      <c r="B10" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="62" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="82"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="62" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="82"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="62" t="s">
+      <c r="A12" s="83"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="83"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="62" t="s">
+      <c r="A13" s="84"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="85">
+      <c r="A14" s="86">
         <v>46206</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="76" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1719,348 +1728,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="86"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="67" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="70"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="86"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="67" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="70"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="86"/>
-      <c r="B17" s="76"/>
-      <c r="C17" s="67" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="86"/>
-      <c r="B18" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="67" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="70"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="87"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="67" t="s">
+      <c r="A19" s="88"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="70"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="88">
+      <c r="A20" s="89">
         <v>46209</v>
       </c>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="88"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="66" t="s">
+      <c r="A21" s="89"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="88"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66" t="s">
+      <c r="A22" s="89"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="88"/>
-      <c r="B23" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="66" t="s">
+      <c r="A23" s="89"/>
+      <c r="B23" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="88"/>
-      <c r="B24" s="66"/>
-      <c r="C24" s="67" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="88"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="67" t="s">
+      <c r="A25" s="89"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="70"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="88"/>
-      <c r="B26" s="66"/>
-      <c r="C26" s="67" t="s">
+      <c r="A26" s="89"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="88"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="67" t="s">
+      <c r="A27" s="89"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="88"/>
-      <c r="B28" s="66"/>
-      <c r="C28" s="67" t="s">
+      <c r="A28" s="89"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="88"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="67" t="s">
+      <c r="A29" s="89"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="88"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="67" t="s">
+      <c r="A30" s="89"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="88"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="67" t="s">
+      <c r="A31" s="89"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="88"/>
-      <c r="B32" s="66"/>
-      <c r="C32" s="67" t="s">
+      <c r="A32" s="89"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="68"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="68"/>
-      <c r="G32" s="69"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="88"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="67" t="s">
+      <c r="A33" s="89"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="69"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="88"/>
-      <c r="B34" s="66"/>
-      <c r="C34" s="67" t="s">
+      <c r="A34" s="89"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="70"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="84">
+      <c r="A35" s="85">
         <v>46210</v>
       </c>
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="84"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="66" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="66"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="84"/>
-      <c r="B37" s="66"/>
-      <c r="C37" s="66" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="66"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="66"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="84"/>
-      <c r="B38" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="66" t="s">
+      <c r="A38" s="85"/>
+      <c r="B38" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="84"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="66"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="84"/>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66" t="s">
+      <c r="A40" s="85"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="84"/>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="84"/>
-      <c r="B42" s="66"/>
-      <c r="C42" s="66" t="s">
+      <c r="A42" s="85"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="66"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="66"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="84"/>
-      <c r="B43" s="66"/>
-      <c r="C43" s="66" t="s">
+      <c r="A43" s="85"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="66"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="84"/>
-      <c r="B44" s="66"/>
-      <c r="C44" s="67" t="s">
+      <c r="A44" s="85"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="70"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2069,13 +2078,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="66"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="66"/>
-      <c r="G45" s="66"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2084,255 +2093,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="66" t="s">
+      <c r="C46" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="66"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="66"/>
-      <c r="G46" s="66"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="85">
+      <c r="A47" s="86">
         <v>46213</v>
       </c>
-      <c r="B47" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="67" t="s">
+      <c r="B47" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="69"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="86"/>
-      <c r="B48" s="77"/>
-      <c r="C48" s="67" t="s">
+      <c r="A48" s="87"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="69"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="70"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="86"/>
-      <c r="B49" s="77"/>
-      <c r="C49" s="67" t="s">
+      <c r="A49" s="87"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="69"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="70"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="86"/>
-      <c r="B50" s="77"/>
-      <c r="C50" s="67" t="s">
+      <c r="A50" s="87"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="68"/>
-      <c r="E50" s="68"/>
-      <c r="F50" s="68"/>
-      <c r="G50" s="69"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="70"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="87"/>
-      <c r="B51" s="76"/>
-      <c r="C51" s="67" t="s">
+      <c r="A51" s="88"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="68"/>
-      <c r="G51" s="69"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="70"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="65">
+      <c r="A52" s="66">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="66" t="s">
+      <c r="C52" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="66"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="66"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="65"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="66" t="s">
+      <c r="C53" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="66"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="66"/>
-      <c r="G53" s="66"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="65">
+      <c r="A54" s="66">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="67" t="s">
+      <c r="C54" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="68"/>
-      <c r="E54" s="68"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="69"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="70"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="65"/>
-      <c r="B55" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="89" t="s">
+      <c r="A55" s="66"/>
+      <c r="B55" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="89"/>
-      <c r="E55" s="89"/>
-      <c r="F55" s="89"/>
-      <c r="G55" s="89"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="65"/>
-      <c r="B56" s="66"/>
-      <c r="C56" s="89" t="s">
+      <c r="A56" s="66"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="89"/>
-      <c r="E56" s="89"/>
-      <c r="F56" s="89"/>
-      <c r="G56" s="89"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="90"/>
+      <c r="G56" s="90"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="65"/>
-      <c r="B57" s="66"/>
-      <c r="C57" s="89" t="s">
+      <c r="A57" s="66"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="89"/>
-      <c r="E57" s="89"/>
-      <c r="F57" s="89"/>
-      <c r="G57" s="89"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="65"/>
-      <c r="B58" s="66"/>
-      <c r="C58" s="89" t="s">
+      <c r="A58" s="66"/>
+      <c r="B58" s="67"/>
+      <c r="C58" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="89"/>
-      <c r="E58" s="89"/>
-      <c r="F58" s="89"/>
-      <c r="G58" s="89"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="65"/>
-      <c r="B59" s="66"/>
-      <c r="C59" s="89" t="s">
+      <c r="A59" s="66"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="89"/>
-      <c r="E59" s="89"/>
-      <c r="F59" s="89"/>
-      <c r="G59" s="89"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="65"/>
-      <c r="B60" s="66"/>
-      <c r="C60" s="89" t="s">
+      <c r="A60" s="66"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="89"/>
-      <c r="E60" s="89"/>
-      <c r="F60" s="89"/>
-      <c r="G60" s="89"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="65"/>
-      <c r="B61" s="66"/>
-      <c r="C61" s="89" t="s">
+      <c r="A61" s="66"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="89"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="89"/>
-      <c r="G61" s="89"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="90"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="65"/>
-      <c r="B62" s="66"/>
-      <c r="C62" s="89" t="s">
+      <c r="A62" s="66"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="89"/>
-      <c r="E62" s="89"/>
-      <c r="F62" s="89"/>
-      <c r="G62" s="89"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="90"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="65"/>
-      <c r="B63" s="66"/>
-      <c r="C63" s="89" t="s">
+      <c r="A63" s="66"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="89"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="89"/>
-      <c r="G63" s="89"/>
+      <c r="D63" s="90"/>
+      <c r="E63" s="90"/>
+      <c r="F63" s="90"/>
+      <c r="G63" s="90"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="65">
+      <c r="A64" s="66">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="66" t="s">
+      <c r="C64" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="66"/>
-      <c r="E64" s="66"/>
-      <c r="F64" s="66"/>
-      <c r="G64" s="66"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="67"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="65"/>
-      <c r="B65" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="66" t="s">
+      <c r="A65" s="66"/>
+      <c r="B65" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="66"/>
-      <c r="E65" s="66"/>
-      <c r="F65" s="66"/>
-      <c r="G65" s="66"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="65"/>
-      <c r="B66" s="66"/>
-      <c r="C66" s="66" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="66"/>
-      <c r="E66" s="66"/>
-      <c r="F66" s="66"/>
-      <c r="G66" s="66"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2341,164 +2350,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="66"/>
-      <c r="E67" s="66"/>
-      <c r="F67" s="66"/>
-      <c r="G67" s="66"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="65">
+      <c r="A68" s="66">
         <v>46220</v>
       </c>
-      <c r="B68" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="66" t="s">
+      <c r="B68" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="66"/>
-      <c r="E68" s="66"/>
-      <c r="F68" s="66"/>
-      <c r="G68" s="66"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="65"/>
-      <c r="B69" s="66"/>
-      <c r="C69" s="66" t="s">
+      <c r="A69" s="66"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="66"/>
-      <c r="E69" s="66"/>
-      <c r="F69" s="66"/>
-      <c r="G69" s="66"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="65">
+      <c r="A70" s="66">
         <v>46223</v>
       </c>
-      <c r="B70" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="67" t="s">
+      <c r="B70" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="68"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="69"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="70"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="65"/>
-      <c r="B71" s="66"/>
-      <c r="C71" s="67" t="s">
+      <c r="A71" s="66"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="68"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="69"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="70"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="65"/>
-      <c r="B72" s="66"/>
-      <c r="C72" s="67" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="68"/>
-      <c r="E72" s="68"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="69"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="70"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="65"/>
-      <c r="B73" s="66"/>
-      <c r="C73" s="67" t="s">
+      <c r="A73" s="66"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="68"/>
-      <c r="E73" s="68"/>
-      <c r="F73" s="68"/>
-      <c r="G73" s="69"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="69"/>
+      <c r="G73" s="70"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="65"/>
-      <c r="B74" s="66"/>
-      <c r="C74" s="67" t="s">
+      <c r="A74" s="66"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="68"/>
-      <c r="E74" s="68"/>
-      <c r="F74" s="68"/>
-      <c r="G74" s="69"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="70"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="65"/>
-      <c r="B75" s="66"/>
-      <c r="C75" s="67" t="s">
+      <c r="A75" s="66"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="68"/>
-      <c r="E75" s="68"/>
-      <c r="F75" s="68"/>
-      <c r="G75" s="69"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="69"/>
+      <c r="G75" s="70"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="65"/>
-      <c r="B76" s="66"/>
-      <c r="C76" s="67" t="s">
+      <c r="A76" s="66"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="68"/>
-      <c r="E76" s="68"/>
-      <c r="F76" s="68"/>
-      <c r="G76" s="69"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="70"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="65"/>
-      <c r="B77" s="66"/>
-      <c r="C77" s="62" t="s">
+      <c r="A77" s="66"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="63"/>
-      <c r="E77" s="63"/>
-      <c r="F77" s="63"/>
-      <c r="G77" s="64"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="65"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="65"/>
-      <c r="B78" s="66"/>
-      <c r="C78" s="62" t="s">
+      <c r="A78" s="66"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="63"/>
-      <c r="E78" s="63"/>
-      <c r="F78" s="63"/>
-      <c r="G78" s="64"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="65"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="65"/>
-      <c r="B79" s="66"/>
-      <c r="C79" s="62" t="s">
+      <c r="A79" s="66"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="63"/>
-      <c r="E79" s="63"/>
-      <c r="F79" s="63"/>
-      <c r="G79" s="64"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="65"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="65"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="62" t="s">
+      <c r="A80" s="66"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="63"/>
-      <c r="E80" s="63"/>
-      <c r="F80" s="63"/>
-      <c r="G80" s="64"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="65"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2507,353 +2516,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="66" t="s">
+      <c r="C81" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="66"/>
-      <c r="E81" s="66"/>
-      <c r="F81" s="66"/>
-      <c r="G81" s="66"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="65">
+      <c r="A82" s="66">
         <v>46225</v>
       </c>
-      <c r="B82" s="66" t="s">
+      <c r="B82" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="66" t="s">
+      <c r="C82" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="66"/>
-      <c r="E82" s="66"/>
-      <c r="F82" s="66"/>
-      <c r="G82" s="66"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="67"/>
+      <c r="G82" s="67"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="65"/>
-      <c r="B83" s="66"/>
-      <c r="C83" s="66" t="s">
+      <c r="A83" s="66"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="66"/>
-      <c r="E83" s="66"/>
-      <c r="F83" s="66"/>
-      <c r="G83" s="66"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="67"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="67"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="65"/>
-      <c r="B84" s="66"/>
-      <c r="C84" s="66" t="s">
+      <c r="A84" s="66"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="66"/>
-      <c r="E84" s="66"/>
-      <c r="F84" s="66"/>
-      <c r="G84" s="66"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="67"/>
+      <c r="F84" s="67"/>
+      <c r="G84" s="67"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="65"/>
-      <c r="B85" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="66" t="s">
+      <c r="A85" s="66"/>
+      <c r="B85" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="66"/>
-      <c r="E85" s="66"/>
-      <c r="F85" s="66"/>
-      <c r="G85" s="66"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="67"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="65"/>
-      <c r="B86" s="66"/>
-      <c r="C86" s="66" t="s">
+      <c r="A86" s="66"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="66"/>
-      <c r="E86" s="66"/>
-      <c r="F86" s="66"/>
-      <c r="G86" s="66"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="67"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="65"/>
-      <c r="B87" s="66"/>
-      <c r="C87" s="66" t="s">
+      <c r="A87" s="66"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="66"/>
-      <c r="E87" s="66"/>
-      <c r="F87" s="66"/>
-      <c r="G87" s="66"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="67"/>
+      <c r="G87" s="67"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="65"/>
-      <c r="B88" s="66"/>
-      <c r="C88" s="66" t="s">
+      <c r="A88" s="66"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="66"/>
-      <c r="E88" s="66"/>
-      <c r="F88" s="66"/>
-      <c r="G88" s="66"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="67"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="65"/>
-      <c r="B89" s="66"/>
-      <c r="C89" s="67" t="s">
+      <c r="A89" s="66"/>
+      <c r="B89" s="67"/>
+      <c r="C89" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="68"/>
-      <c r="E89" s="68"/>
-      <c r="F89" s="68"/>
-      <c r="G89" s="69"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
+      <c r="F89" s="69"/>
+      <c r="G89" s="70"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="65"/>
-      <c r="B90" s="66"/>
-      <c r="C90" s="66" t="s">
+      <c r="A90" s="66"/>
+      <c r="B90" s="67"/>
+      <c r="C90" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="66"/>
-      <c r="E90" s="66"/>
-      <c r="F90" s="66"/>
-      <c r="G90" s="66"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="67"/>
+      <c r="G90" s="67"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="85">
+      <c r="A91" s="86">
         <v>46227</v>
       </c>
-      <c r="B91" s="75" t="s">
+      <c r="B91" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="66" t="s">
+      <c r="C91" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="66"/>
-      <c r="E91" s="66"/>
-      <c r="F91" s="66"/>
-      <c r="G91" s="66"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="67"/>
+      <c r="G91" s="67"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="87"/>
-      <c r="B92" s="76"/>
-      <c r="C92" s="67" t="s">
+      <c r="A92" s="88"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="68"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="69"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="70"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="65">
+      <c r="A93" s="66">
         <v>46228</v>
       </c>
-      <c r="B93" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="66" t="s">
+      <c r="B93" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="66"/>
-      <c r="E93" s="66"/>
-      <c r="F93" s="66"/>
-      <c r="G93" s="66"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="67"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="65"/>
-      <c r="B94" s="66"/>
-      <c r="C94" s="66" t="s">
+      <c r="A94" s="66"/>
+      <c r="B94" s="67"/>
+      <c r="C94" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="66"/>
-      <c r="E94" s="66"/>
-      <c r="F94" s="66"/>
-      <c r="G94" s="66"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="67"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="65"/>
-      <c r="B95" s="66"/>
-      <c r="C95" s="66" t="s">
+      <c r="A95" s="66"/>
+      <c r="B95" s="67"/>
+      <c r="C95" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="66"/>
-      <c r="E95" s="66"/>
-      <c r="F95" s="66"/>
-      <c r="G95" s="66"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
+      <c r="F95" s="67"/>
+      <c r="G95" s="67"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="65"/>
-      <c r="B96" s="66"/>
-      <c r="C96" s="66" t="s">
+      <c r="A96" s="66"/>
+      <c r="B96" s="67"/>
+      <c r="C96" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="66"/>
-      <c r="E96" s="66"/>
-      <c r="F96" s="66"/>
-      <c r="G96" s="66"/>
+      <c r="D96" s="67"/>
+      <c r="E96" s="67"/>
+      <c r="F96" s="67"/>
+      <c r="G96" s="67"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="65"/>
-      <c r="B97" s="66"/>
-      <c r="C97" s="66" t="s">
+      <c r="A97" s="66"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="66"/>
-      <c r="E97" s="66"/>
-      <c r="F97" s="66"/>
-      <c r="G97" s="66"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="67"/>
+      <c r="G97" s="67"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="65"/>
-      <c r="B98" s="66"/>
-      <c r="C98" s="66" t="s">
+      <c r="A98" s="66"/>
+      <c r="B98" s="67"/>
+      <c r="C98" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="66"/>
-      <c r="E98" s="66"/>
-      <c r="F98" s="66"/>
-      <c r="G98" s="66"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="67"/>
+      <c r="G98" s="67"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="65">
+      <c r="A99" s="66">
         <v>46230</v>
       </c>
-      <c r="B99" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="66" t="s">
+      <c r="B99" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="66"/>
-      <c r="E99" s="66"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="66"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="65"/>
-      <c r="B100" s="66"/>
-      <c r="C100" s="66" t="s">
+      <c r="A100" s="66"/>
+      <c r="B100" s="67"/>
+      <c r="C100" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="66"/>
-      <c r="E100" s="66"/>
-      <c r="F100" s="66"/>
-      <c r="G100" s="66"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="67"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="65">
+      <c r="A101" s="66">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="91" t="s">
+      <c r="C101" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="91"/>
-      <c r="E101" s="91"/>
-      <c r="F101" s="91"/>
-      <c r="G101" s="91"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="65"/>
+      <c r="A102" s="66"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="91" t="s">
+      <c r="C102" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="91"/>
-      <c r="E102" s="91"/>
-      <c r="F102" s="91"/>
-      <c r="G102" s="91"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="90" t="s">
+      <c r="A103" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="80" t="s">
+      <c r="B103" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="80"/>
-      <c r="E103" s="80"/>
-      <c r="F103" s="80"/>
-      <c r="G103" s="80"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="81"/>
+      <c r="F103" s="81"/>
+      <c r="G103" s="81"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="90"/>
-      <c r="B104" s="66"/>
-      <c r="C104" s="66" t="s">
+      <c r="A104" s="91"/>
+      <c r="B104" s="67"/>
+      <c r="C104" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="66"/>
-      <c r="E104" s="66"/>
-      <c r="F104" s="66"/>
-      <c r="G104" s="66"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="67"/>
+      <c r="G104" s="67"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="90"/>
-      <c r="B105" s="66"/>
-      <c r="C105" s="66" t="s">
+      <c r="A105" s="91"/>
+      <c r="B105" s="67"/>
+      <c r="C105" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="66"/>
-      <c r="E105" s="66"/>
-      <c r="F105" s="66"/>
-      <c r="G105" s="66"/>
+      <c r="D105" s="67"/>
+      <c r="E105" s="67"/>
+      <c r="F105" s="67"/>
+      <c r="G105" s="67"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="90"/>
-      <c r="B106" s="66"/>
-      <c r="C106" s="66" t="s">
+      <c r="A106" s="91"/>
+      <c r="B106" s="67"/>
+      <c r="C106" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="66"/>
-      <c r="E106" s="66"/>
-      <c r="F106" s="66"/>
-      <c r="G106" s="66"/>
+      <c r="D106" s="67"/>
+      <c r="E106" s="67"/>
+      <c r="F106" s="67"/>
+      <c r="G106" s="67"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="90"/>
-      <c r="B107" s="66"/>
-      <c r="C107" s="66" t="s">
+      <c r="A107" s="91"/>
+      <c r="B107" s="67"/>
+      <c r="C107" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="66"/>
-      <c r="E107" s="66"/>
-      <c r="F107" s="66"/>
-      <c r="G107" s="66"/>
+      <c r="D107" s="67"/>
+      <c r="E107" s="67"/>
+      <c r="F107" s="67"/>
+      <c r="G107" s="67"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="65">
+      <c r="A108" s="66">
         <v>46234</v>
       </c>
-      <c r="B108" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="66" t="s">
+      <c r="B108" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="66"/>
-      <c r="E108" s="66"/>
-      <c r="F108" s="66"/>
-      <c r="G108" s="66"/>
+      <c r="D108" s="67"/>
+      <c r="E108" s="67"/>
+      <c r="F108" s="67"/>
+      <c r="G108" s="67"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="65"/>
-      <c r="B109" s="66"/>
-      <c r="C109" s="66" t="s">
+      <c r="A109" s="66"/>
+      <c r="B109" s="67"/>
+      <c r="C109" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="66"/>
-      <c r="E109" s="66"/>
-      <c r="F109" s="66"/>
-      <c r="G109" s="66"/>
+      <c r="D109" s="67"/>
+      <c r="E109" s="67"/>
+      <c r="F109" s="67"/>
+      <c r="G109" s="67"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -3027,15 +3036,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="78">
+      <c r="A1" s="79">
         <v>46235</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3968,7 +3977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -3977,15 +3986,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="92">
+      <c r="A1" s="93">
         <v>46266</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4467,21 +4476,157 @@
       <c r="C46" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D46" s="93"/>
-      <c r="E46" s="93"/>
-      <c r="F46" s="93"/>
       <c r="G46" s="51"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="45"/>
       <c r="B47" s="45"/>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="50"/>
+      <c r="D47" s="94"/>
+      <c r="E47" s="94"/>
+      <c r="F47" s="94"/>
+      <c r="G47" s="51"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="62">
+        <v>46286</v>
+      </c>
+      <c r="B48" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="54"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="94"/>
+      <c r="E49" s="94"/>
+      <c r="F49" s="94"/>
+      <c r="G49" s="51"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="25"/>
+      <c r="C50" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="94"/>
+      <c r="E50" s="94"/>
+      <c r="F50" s="94"/>
+      <c r="G50" s="51"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="46"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D51" s="94"/>
+      <c r="E51" s="94"/>
+      <c r="F51" s="94"/>
+      <c r="G51" s="51"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="46"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D52" s="94"/>
+      <c r="E52" s="94"/>
+      <c r="F52" s="94"/>
+      <c r="G52" s="51"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="46"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" s="94"/>
+      <c r="E53" s="94"/>
+      <c r="F53" s="94"/>
+      <c r="G53" s="51"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="46"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="94"/>
+      <c r="E54" s="94"/>
+      <c r="F54" s="94"/>
+      <c r="G54" s="51"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="46"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="94"/>
+      <c r="E55" s="94"/>
+      <c r="F55" s="94"/>
+      <c r="G55" s="51"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="46"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D56" s="94"/>
+      <c r="E56" s="94"/>
+      <c r="F56" s="94"/>
+      <c r="G56" s="51"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="46"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" s="94"/>
+      <c r="E57" s="94"/>
+      <c r="F57" s="94"/>
+      <c r="G57" s="51"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="46"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58" s="94"/>
+      <c r="E58" s="94"/>
+      <c r="F58" s="94"/>
+      <c r="G58" s="51"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="45"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EDE018-09B5-43C4-85E2-8D7288DCF56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA41205-1F69-4F52-8030-B5EADD0EDC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="176">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -556,6 +556,9 @@
   </si>
   <si>
     <t>Nhận BH Anh Tuấn NB</t>
+  </si>
+  <si>
+    <t>Nhận BH Nguyễn Nam</t>
   </si>
 </sst>
 </file>
@@ -935,6 +938,24 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -947,9 +968,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -959,20 +977,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -980,6 +992,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -989,9 +1019,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1001,34 +1028,10 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1353,15 +1356,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="71">
+      <c r="A1" s="63">
         <v>46174</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1370,146 +1373,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46202</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67" t="s">
+      <c r="A7" s="72"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="66"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="66">
+      <c r="A9" s="72">
         <v>46203</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="66"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="66"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1519,6 +1522,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1529,14 +1540,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1554,15 +1557,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46204</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1571,152 +1574,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="82">
+      <c r="A7" s="90">
         <v>46205</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="70"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="75"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="63" t="s">
+      <c r="A8" s="91"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="63" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
-      <c r="B10" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="63" t="s">
+      <c r="A13" s="92"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="81">
         <v>46206</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1728,348 +1731,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="87"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="68" t="s">
+      <c r="A15" s="84"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="75"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="68" t="s">
+      <c r="A16" s="84"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="75"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="87"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="68" t="s">
+      <c r="A17" s="84"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="75"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="87"/>
-      <c r="B18" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="68" t="s">
+      <c r="A18" s="84"/>
+      <c r="B18" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="75"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="68" t="s">
+      <c r="A19" s="82"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="70"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="75"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="89">
+      <c r="A20" s="85">
         <v>46209</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="89"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67" t="s">
+      <c r="A21" s="85"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="89"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67" t="s">
+      <c r="A22" s="85"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="89"/>
-      <c r="B23" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="67" t="s">
+      <c r="A23" s="85"/>
+      <c r="B23" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="89"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="68" t="s">
+      <c r="A24" s="85"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="75"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="89"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="68" t="s">
+      <c r="A25" s="85"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="75"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="89"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="68" t="s">
+      <c r="A26" s="85"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="75"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="89"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="68" t="s">
+      <c r="A27" s="85"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="70"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="75"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="89"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="68" t="s">
+      <c r="A28" s="85"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="70"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="75"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="89"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="68" t="s">
+      <c r="A29" s="85"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="75"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="89"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="68" t="s">
+      <c r="A30" s="85"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="70"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="75"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="68" t="s">
+      <c r="A31" s="85"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="68" t="s">
+      <c r="A32" s="85"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="68" t="s">
+      <c r="A33" s="85"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="89"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="68" t="s">
+      <c r="A34" s="85"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="85">
+      <c r="A35" s="83">
         <v>46210</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67" t="s">
+      <c r="A36" s="83"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67" t="s">
+      <c r="A37" s="83"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
-      <c r="B38" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="A38" s="83"/>
+      <c r="B38" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="85"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67" t="s">
+      <c r="A39" s="83"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67" t="s">
+      <c r="A40" s="83"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67" t="s">
+      <c r="A41" s="83"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67" t="s">
+      <c r="A42" s="83"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67" t="s">
+      <c r="A43" s="83"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="68" t="s">
+      <c r="A44" s="83"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="75"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2078,13 +2081,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="C45" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2093,255 +2096,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="86">
+      <c r="A47" s="81">
         <v>46213</v>
       </c>
-      <c r="B47" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="68" t="s">
+      <c r="B47" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="70"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="75"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="87"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="68" t="s">
+      <c r="A48" s="84"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="70"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="75"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="68" t="s">
+      <c r="A49" s="84"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="70"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="75"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="68" t="s">
+      <c r="A50" s="84"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="70"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="75"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="88"/>
-      <c r="B51" s="77"/>
-      <c r="C51" s="68" t="s">
+      <c r="A51" s="82"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="70"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="75"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="66">
+      <c r="A52" s="72">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="C52" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="68"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="72"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="68"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="66">
+      <c r="A54" s="72">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="69"/>
-      <c r="E54" s="69"/>
-      <c r="F54" s="69"/>
-      <c r="G54" s="70"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="75"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="66"/>
-      <c r="B55" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="90" t="s">
+      <c r="A55" s="72"/>
+      <c r="B55" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="66"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="90" t="s">
+      <c r="A56" s="72"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="90"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
+      <c r="F56" s="86"/>
+      <c r="G56" s="86"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="66"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="90" t="s">
+      <c r="A57" s="72"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="90"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="66"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="90" t="s">
+      <c r="A58" s="72"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="90"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="66"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="90" t="s">
+      <c r="A59" s="72"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="86"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="66"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="90" t="s">
+      <c r="A60" s="72"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
+      <c r="D60" s="86"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="86"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="90" t="s">
+      <c r="A61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="90"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="66"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="90" t="s">
+      <c r="A62" s="72"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="90"/>
+      <c r="D62" s="86"/>
+      <c r="E62" s="86"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="86"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="90" t="s">
+      <c r="A63" s="72"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="90"/>
-      <c r="E63" s="90"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="90"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="86"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="86"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="66">
+      <c r="A64" s="72">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="67" t="s">
+      <c r="C64" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="68"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
-      <c r="B65" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="67" t="s">
+      <c r="A65" s="72"/>
+      <c r="B65" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="68"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67" t="s">
+      <c r="A66" s="72"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="68"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2350,164 +2353,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="67" t="s">
+      <c r="C67" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="66">
+      <c r="A68" s="72">
         <v>46220</v>
       </c>
-      <c r="B68" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="67" t="s">
+      <c r="B68" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="A69" s="72"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="66">
+      <c r="A70" s="72">
         <v>46223</v>
       </c>
-      <c r="B70" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="68" t="s">
+      <c r="B70" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="70"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="75"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="68" t="s">
+      <c r="A71" s="72"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="70"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="75"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="68" t="s">
+      <c r="A72" s="72"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="70"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="75"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="68" t="s">
+      <c r="A73" s="72"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="69"/>
-      <c r="F73" s="69"/>
-      <c r="G73" s="70"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="75"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="68" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="70"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="75"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="68" t="s">
+      <c r="A75" s="72"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="70"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="75"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="68" t="s">
+      <c r="A76" s="72"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="69"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="70"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="75"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="66"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="63" t="s">
+      <c r="A77" s="72"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="65"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="71"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="66"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="63" t="s">
+      <c r="A78" s="72"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="65"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="71"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="63" t="s">
+      <c r="A79" s="72"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="65"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="71"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="63" t="s">
+      <c r="A80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="65"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="71"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2516,353 +2519,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="67" t="s">
+      <c r="C81" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="68"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="66">
+      <c r="A82" s="72">
         <v>46225</v>
       </c>
-      <c r="B82" s="67" t="s">
+      <c r="B82" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="68"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="66"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="67" t="s">
+      <c r="A83" s="72"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="67"/>
+      <c r="D83" s="68"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="68"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="67" t="s">
+      <c r="A84" s="72"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="67"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="67"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="68"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
-      <c r="B85" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="67" t="s">
+      <c r="A85" s="72"/>
+      <c r="B85" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="67"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67" t="s">
+      <c r="A86" s="72"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="67"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="68"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="66"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67" t="s">
+      <c r="A87" s="72"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="66"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="67" t="s">
+      <c r="A88" s="72"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="67"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
+      <c r="D88" s="68"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="66"/>
-      <c r="B89" s="67"/>
-      <c r="C89" s="68" t="s">
+      <c r="A89" s="72"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="70"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="74"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="75"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="66"/>
-      <c r="B90" s="67"/>
-      <c r="C90" s="67" t="s">
+      <c r="A90" s="72"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
+      <c r="D90" s="68"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="68"/>
+      <c r="G90" s="68"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="86">
+      <c r="A91" s="81">
         <v>46227</v>
       </c>
-      <c r="B91" s="76" t="s">
+      <c r="B91" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="88"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="68" t="s">
+      <c r="A92" s="82"/>
+      <c r="B92" s="80"/>
+      <c r="C92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="69"/>
-      <c r="E92" s="69"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="70"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="74"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="75"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="66">
+      <c r="A93" s="72">
         <v>46228</v>
       </c>
-      <c r="B93" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="67" t="s">
+      <c r="B93" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="67"/>
+      <c r="D93" s="68"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="68"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="67" t="s">
+      <c r="A94" s="72"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="67"/>
+      <c r="D94" s="68"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="68"/>
+      <c r="G94" s="68"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="66"/>
-      <c r="B95" s="67"/>
-      <c r="C95" s="67" t="s">
+      <c r="A95" s="72"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="67"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="68"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="66"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="67" t="s">
+      <c r="A96" s="72"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="67"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="67"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="66"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="67" t="s">
+      <c r="A97" s="72"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="67"/>
+      <c r="D97" s="68"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="68"/>
+      <c r="G97" s="68"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="66"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="67" t="s">
+      <c r="A98" s="72"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="67"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="66">
+      <c r="A99" s="72">
         <v>46230</v>
       </c>
-      <c r="B99" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="67" t="s">
+      <c r="B99" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="66"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="67" t="s">
+      <c r="A100" s="72"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="67"/>
+      <c r="D100" s="68"/>
+      <c r="E100" s="68"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="68"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="66">
+      <c r="A101" s="72">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="92" t="s">
+      <c r="C101" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="92"/>
-      <c r="E101" s="92"/>
-      <c r="F101" s="92"/>
-      <c r="G101" s="92"/>
+      <c r="D101" s="78"/>
+      <c r="E101" s="78"/>
+      <c r="F101" s="78"/>
+      <c r="G101" s="78"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="66"/>
+      <c r="A102" s="72"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="92" t="s">
+      <c r="C102" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="92"/>
-      <c r="E102" s="92"/>
-      <c r="F102" s="92"/>
-      <c r="G102" s="92"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="78"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="91" t="s">
+      <c r="A103" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="81" t="s">
+      <c r="B103" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="81"/>
-      <c r="E103" s="81"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="81"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="91"/>
-      <c r="B104" s="67"/>
-      <c r="C104" s="67" t="s">
+      <c r="A104" s="76"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="91"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="67" t="s">
+      <c r="A105" s="76"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="67"/>
+      <c r="D105" s="68"/>
+      <c r="E105" s="68"/>
+      <c r="F105" s="68"/>
+      <c r="G105" s="68"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="91"/>
-      <c r="B106" s="67"/>
-      <c r="C106" s="67" t="s">
+      <c r="A106" s="76"/>
+      <c r="B106" s="68"/>
+      <c r="C106" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="67"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="67"/>
+      <c r="D106" s="68"/>
+      <c r="E106" s="68"/>
+      <c r="F106" s="68"/>
+      <c r="G106" s="68"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="91"/>
-      <c r="B107" s="67"/>
-      <c r="C107" s="67" t="s">
+      <c r="A107" s="76"/>
+      <c r="B107" s="68"/>
+      <c r="C107" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="67"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="67"/>
+      <c r="D107" s="68"/>
+      <c r="E107" s="68"/>
+      <c r="F107" s="68"/>
+      <c r="G107" s="68"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="66">
+      <c r="A108" s="72">
         <v>46234</v>
       </c>
-      <c r="B108" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="67" t="s">
+      <c r="B108" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="67"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="67"/>
-      <c r="G108" s="67"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="66"/>
-      <c r="B109" s="67"/>
-      <c r="C109" s="67" t="s">
+      <c r="A109" s="72"/>
+      <c r="B109" s="68"/>
+      <c r="C109" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="67"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="67"/>
-      <c r="G109" s="67"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="68"/>
+      <c r="F109" s="68"/>
+      <c r="G109" s="68"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2872,68 +2875,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2958,67 +2960,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3036,15 +3039,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46235</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3977,7 +3980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -4484,9 +4487,6 @@
       <c r="C47" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="94"/>
-      <c r="E47" s="94"/>
-      <c r="F47" s="94"/>
       <c r="G47" s="51"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -4514,9 +4514,6 @@
       <c r="C49" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D49" s="94"/>
-      <c r="E49" s="94"/>
-      <c r="F49" s="94"/>
       <c r="G49" s="51"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -4524,9 +4521,6 @@
       <c r="C50" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="D50" s="94"/>
-      <c r="E50" s="94"/>
-      <c r="F50" s="94"/>
       <c r="G50" s="51"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -4535,9 +4529,6 @@
       <c r="C51" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="D51" s="94"/>
-      <c r="E51" s="94"/>
-      <c r="F51" s="94"/>
       <c r="G51" s="51"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -4546,9 +4537,6 @@
       <c r="C52" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="D52" s="94"/>
-      <c r="E52" s="94"/>
-      <c r="F52" s="94"/>
       <c r="G52" s="51"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -4557,9 +4545,6 @@
       <c r="C53" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="D53" s="94"/>
-      <c r="E53" s="94"/>
-      <c r="F53" s="94"/>
       <c r="G53" s="51"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -4568,9 +4553,6 @@
       <c r="C54" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="94"/>
-      <c r="E54" s="94"/>
-      <c r="F54" s="94"/>
       <c r="G54" s="51"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -4579,9 +4561,6 @@
       <c r="C55" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D55" s="94"/>
-      <c r="E55" s="94"/>
-      <c r="F55" s="94"/>
       <c r="G55" s="51"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -4590,9 +4569,6 @@
       <c r="C56" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="D56" s="94"/>
-      <c r="E56" s="94"/>
-      <c r="F56" s="94"/>
       <c r="G56" s="51"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -4601,9 +4577,6 @@
       <c r="C57" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="D57" s="94"/>
-      <c r="E57" s="94"/>
-      <c r="F57" s="94"/>
       <c r="G57" s="51"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -4612,9 +4585,6 @@
       <c r="C58" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="94"/>
-      <c r="E58" s="94"/>
-      <c r="F58" s="94"/>
       <c r="G58" s="51"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -4627,6 +4597,22 @@
       <c r="E59" s="49"/>
       <c r="F59" s="49"/>
       <c r="G59" s="50"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="94">
+        <v>46289</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C61" s="10" t="s">
+        <v>174</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA41205-1F69-4F52-8030-B5EADD0EDC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B675634-A159-4EB5-A4D5-CB8896EAD1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="180">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -559,6 +559,18 @@
   </si>
   <si>
     <t>Nhận BH Nguyễn Nam</t>
+  </si>
+  <si>
+    <t>Nhận BH Anh Thái Quy Nhơn</t>
+  </si>
+  <si>
+    <t>Nhận BH Đức Đoàn</t>
+  </si>
+  <si>
+    <t>Trả BH Anh Tuấn NB (VNSH01 ID: 00BD000F3D)</t>
+  </si>
+  <si>
+    <t>Trả kho 49 Mắt CAM (20 đã thay lens, 29 lỗi)</t>
   </si>
 </sst>
 </file>
@@ -938,6 +950,30 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -953,85 +989,61 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1356,15 +1368,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="63">
+      <c r="A1" s="71">
         <v>46174</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1373,146 +1385,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="75"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46202</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68" t="s">
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72">
+      <c r="A9" s="66">
         <v>46203</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="70"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1522,14 +1534,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1540,6 +1544,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1557,15 +1569,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46204</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1574,152 +1586,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="77" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="82">
         <v>46205</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="69" t="s">
+      <c r="A8" s="83"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="71"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="65"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="83"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="65"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
-      <c r="B10" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="91"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="83"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69" t="s">
+      <c r="A13" s="84"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="81">
+      <c r="A14" s="86">
         <v>46206</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="76" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1731,348 +1743,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="73" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="70"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="84"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="73" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="70"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="73" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="84"/>
-      <c r="B18" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="73" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="75"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="70"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="73" t="s">
+      <c r="A19" s="88"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="70"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="89">
         <v>46209</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68" t="s">
+      <c r="A21" s="89"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68" t="s">
+      <c r="A22" s="89"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="68" t="s">
+      <c r="A23" s="89"/>
+      <c r="B23" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="73" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="75"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="73" t="s">
+      <c r="A25" s="89"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="75"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="70"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="73" t="s">
+      <c r="A26" s="89"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="73" t="s">
+      <c r="A27" s="89"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="75"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="73" t="s">
+      <c r="A28" s="89"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="75"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="73" t="s">
+      <c r="A29" s="89"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="73" t="s">
+      <c r="A30" s="89"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="73" t="s">
+      <c r="A31" s="89"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="73" t="s">
+      <c r="A32" s="89"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="73" t="s">
+      <c r="A33" s="89"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="73" t="s">
+      <c r="A34" s="89"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="70"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="83">
+      <c r="A35" s="85">
         <v>46210</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
-      <c r="B38" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="68" t="s">
+      <c r="A38" s="85"/>
+      <c r="B38" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68" t="s">
+      <c r="A40" s="85"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68" t="s">
+      <c r="A42" s="85"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68" t="s">
+      <c r="A43" s="85"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="73" t="s">
+      <c r="A44" s="85"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="75"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="70"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2081,13 +2093,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2096,255 +2108,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="81">
+      <c r="A47" s="86">
         <v>46213</v>
       </c>
-      <c r="B47" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="73" t="s">
+      <c r="B47" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="75"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="84"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="73" t="s">
+      <c r="A48" s="87"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="75"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="70"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="84"/>
-      <c r="B49" s="87"/>
-      <c r="C49" s="73" t="s">
+      <c r="A49" s="87"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="75"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="70"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="87"/>
-      <c r="C50" s="73" t="s">
+      <c r="A50" s="87"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="70"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="73" t="s">
+      <c r="A51" s="88"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="75"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="70"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="72">
+      <c r="A52" s="66">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="72">
+      <c r="A54" s="66">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="75"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="70"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
-      <c r="B55" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="86" t="s">
+      <c r="A55" s="66"/>
+      <c r="B55" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="86" t="s">
+      <c r="A56" s="66"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="90"/>
+      <c r="G56" s="90"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="86" t="s">
+      <c r="A57" s="66"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="86" t="s">
+      <c r="A58" s="66"/>
+      <c r="B58" s="67"/>
+      <c r="C58" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="86" t="s">
+      <c r="A59" s="66"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="86" t="s">
+      <c r="A60" s="66"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="86" t="s">
+      <c r="A61" s="66"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="86"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="90"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="86" t="s">
+      <c r="A62" s="66"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="90"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="86" t="s">
+      <c r="A63" s="66"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
+      <c r="D63" s="90"/>
+      <c r="E63" s="90"/>
+      <c r="F63" s="90"/>
+      <c r="G63" s="90"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="72">
+      <c r="A64" s="66">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="67"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
-      <c r="B65" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="68" t="s">
+      <c r="A65" s="66"/>
+      <c r="B65" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2353,164 +2365,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="72">
+      <c r="A68" s="66">
         <v>46220</v>
       </c>
-      <c r="B68" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="68" t="s">
+      <c r="B68" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68" t="s">
+      <c r="A69" s="66"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="72">
+      <c r="A70" s="66">
         <v>46223</v>
       </c>
-      <c r="B70" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="73" t="s">
+      <c r="B70" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="75"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="70"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="73" t="s">
+      <c r="A71" s="66"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="75"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="70"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="73" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="75"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="70"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="73" t="s">
+      <c r="A73" s="66"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="75"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="69"/>
+      <c r="G73" s="70"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="73" t="s">
+      <c r="A74" s="66"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="75"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="70"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="73" t="s">
+      <c r="A75" s="66"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="75"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="69"/>
+      <c r="G75" s="70"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="73" t="s">
+      <c r="A76" s="66"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="75"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="70"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="69" t="s">
+      <c r="A77" s="66"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="65"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="69" t="s">
+      <c r="A78" s="66"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="71"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="65"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="72"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="69" t="s">
+      <c r="A79" s="66"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
-      <c r="F79" s="70"/>
-      <c r="G79" s="71"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="65"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="69" t="s">
+      <c r="A80" s="66"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="71"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="65"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2519,353 +2531,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="68" t="s">
+      <c r="C81" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="72">
+      <c r="A82" s="66">
         <v>46225</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="67"/>
+      <c r="G82" s="67"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68" t="s">
+      <c r="A83" s="66"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="67"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="67"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68" t="s">
+      <c r="A84" s="66"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="67"/>
+      <c r="F84" s="67"/>
+      <c r="G84" s="67"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
-      <c r="B85" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="68" t="s">
+      <c r="A85" s="66"/>
+      <c r="B85" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="67"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68" t="s">
+      <c r="A86" s="66"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="67"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68" t="s">
+      <c r="A87" s="66"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="67"/>
+      <c r="G87" s="67"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68" t="s">
+      <c r="A88" s="66"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="67"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
-      <c r="B89" s="68"/>
-      <c r="C89" s="73" t="s">
+      <c r="A89" s="66"/>
+      <c r="B89" s="67"/>
+      <c r="C89" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="74"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="75"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
+      <c r="F89" s="69"/>
+      <c r="G89" s="70"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="72"/>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68" t="s">
+      <c r="A90" s="66"/>
+      <c r="B90" s="67"/>
+      <c r="C90" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="67"/>
+      <c r="G90" s="67"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="81">
+      <c r="A91" s="86">
         <v>46227</v>
       </c>
-      <c r="B91" s="79" t="s">
+      <c r="B91" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="67"/>
+      <c r="G91" s="67"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="82"/>
-      <c r="B92" s="80"/>
-      <c r="C92" s="73" t="s">
+      <c r="A92" s="88"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="75"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="70"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="72">
+      <c r="A93" s="66">
         <v>46228</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="68" t="s">
+      <c r="B93" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="67"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68" t="s">
+      <c r="A94" s="66"/>
+      <c r="B94" s="67"/>
+      <c r="C94" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="67"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="72"/>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68" t="s">
+      <c r="A95" s="66"/>
+      <c r="B95" s="67"/>
+      <c r="C95" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
+      <c r="F95" s="67"/>
+      <c r="G95" s="67"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="A96" s="66"/>
+      <c r="B96" s="67"/>
+      <c r="C96" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
+      <c r="D96" s="67"/>
+      <c r="E96" s="67"/>
+      <c r="F96" s="67"/>
+      <c r="G96" s="67"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="72"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="68" t="s">
+      <c r="A97" s="66"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="68"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="67"/>
+      <c r="G97" s="67"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="72"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="68" t="s">
+      <c r="A98" s="66"/>
+      <c r="B98" s="67"/>
+      <c r="C98" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="67"/>
+      <c r="G98" s="67"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="72">
+      <c r="A99" s="66">
         <v>46230</v>
       </c>
-      <c r="B99" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="68" t="s">
+      <c r="B99" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="72"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="68" t="s">
+      <c r="A100" s="66"/>
+      <c r="B100" s="67"/>
+      <c r="C100" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="68"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="67"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="72">
+      <c r="A101" s="66">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="78" t="s">
+      <c r="C101" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="78"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="78"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="72"/>
+      <c r="A102" s="66"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="78" t="s">
+      <c r="C102" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="78"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="78"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="76" t="s">
+      <c r="A103" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="77" t="s">
+      <c r="B103" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="81"/>
+      <c r="F103" s="81"/>
+      <c r="G103" s="81"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
-      <c r="B104" s="68"/>
-      <c r="C104" s="68" t="s">
+      <c r="A104" s="91"/>
+      <c r="B104" s="67"/>
+      <c r="C104" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="67"/>
+      <c r="G104" s="67"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68" t="s">
+      <c r="A105" s="91"/>
+      <c r="B105" s="67"/>
+      <c r="C105" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
+      <c r="D105" s="67"/>
+      <c r="E105" s="67"/>
+      <c r="F105" s="67"/>
+      <c r="G105" s="67"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
-      <c r="B106" s="68"/>
-      <c r="C106" s="68" t="s">
+      <c r="A106" s="91"/>
+      <c r="B106" s="67"/>
+      <c r="C106" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="68"/>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
+      <c r="D106" s="67"/>
+      <c r="E106" s="67"/>
+      <c r="F106" s="67"/>
+      <c r="G106" s="67"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
-      <c r="B107" s="68"/>
-      <c r="C107" s="68" t="s">
+      <c r="A107" s="91"/>
+      <c r="B107" s="67"/>
+      <c r="C107" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
+      <c r="D107" s="67"/>
+      <c r="E107" s="67"/>
+      <c r="F107" s="67"/>
+      <c r="G107" s="67"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="72">
+      <c r="A108" s="66">
         <v>46234</v>
       </c>
-      <c r="B108" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
+      <c r="D108" s="67"/>
+      <c r="E108" s="67"/>
+      <c r="F108" s="67"/>
+      <c r="G108" s="67"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="72"/>
-      <c r="B109" s="68"/>
-      <c r="C109" s="68" t="s">
+      <c r="A109" s="66"/>
+      <c r="B109" s="67"/>
+      <c r="C109" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
+      <c r="D109" s="67"/>
+      <c r="E109" s="67"/>
+      <c r="F109" s="67"/>
+      <c r="G109" s="67"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2875,6 +2887,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2899,129 +3034,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3039,15 +3051,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46235</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3980,7 +3992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -4588,7 +4600,7 @@
       <c r="G58" s="51"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="45"/>
+      <c r="A59" s="46"/>
       <c r="B59" s="26"/>
       <c r="C59" s="26" t="s">
         <v>39</v>
@@ -4599,20 +4611,109 @@
       <c r="G59" s="50"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="94">
+      <c r="A60" s="11">
         <v>46289</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C60" s="10" t="s">
+      <c r="B60" s="94" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="94"/>
+      <c r="E60" s="94"/>
+      <c r="F60" s="94"/>
+      <c r="G60" s="51"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="13"/>
+      <c r="B61" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" s="24" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C61" s="10" t="s">
+      <c r="D61" s="47"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="48"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="46"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="25" t="s">
         <v>174</v>
       </c>
+      <c r="D62" s="94"/>
+      <c r="E62" s="94"/>
+      <c r="F62" s="94"/>
+      <c r="G62" s="51"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="46"/>
+      <c r="B63" s="51"/>
+      <c r="C63" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="D63" s="94"/>
+      <c r="E63" s="94"/>
+      <c r="F63" s="94"/>
+      <c r="G63" s="51"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="46"/>
+      <c r="B64" s="51"/>
+      <c r="C64" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="D64" s="94"/>
+      <c r="E64" s="94"/>
+      <c r="F64" s="94"/>
+      <c r="G64" s="51"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="46"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="D65" s="94"/>
+      <c r="E65" s="94"/>
+      <c r="F65" s="94"/>
+      <c r="G65" s="51"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="46"/>
+      <c r="B66" s="51"/>
+      <c r="C66" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D66" s="94"/>
+      <c r="E66" s="94"/>
+      <c r="F66" s="94"/>
+      <c r="G66" s="51"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="46"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" s="94"/>
+      <c r="E67" s="94"/>
+      <c r="F67" s="94"/>
+      <c r="G67" s="51"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="45"/>
+      <c r="B68" s="50"/>
+      <c r="C68" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D68" s="49"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B675634-A159-4EB5-A4D5-CB8896EAD1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64768A6-D200-4B7F-A7EA-D9D86DA3B96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="181">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -571,6 +571,9 @@
   </si>
   <si>
     <t>Trả kho 49 Mắt CAM (20 đã thay lens, 29 lỗi)</t>
+  </si>
+  <si>
+    <t>Nhận 23 LE-2G nâng cấp LE-4G từ KT. Kho</t>
   </si>
 </sst>
 </file>
@@ -950,6 +953,24 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -962,9 +983,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -974,20 +992,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -995,6 +1007,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1004,9 +1034,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1015,30 +1042,6 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1368,15 +1371,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="71">
+      <c r="A1" s="63">
         <v>46174</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1385,146 +1388,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46202</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67" t="s">
+      <c r="A7" s="72"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="66"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="66">
+      <c r="A9" s="72">
         <v>46203</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="66"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="66"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1534,6 +1537,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1544,14 +1555,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1569,15 +1572,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46204</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1586,152 +1589,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="82">
+      <c r="A7" s="90">
         <v>46205</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="70"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="75"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="63" t="s">
+      <c r="A8" s="91"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="63" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
-      <c r="B10" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="63" t="s">
+      <c r="A13" s="92"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="81">
         <v>46206</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1743,348 +1746,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="87"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="68" t="s">
+      <c r="A15" s="84"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="75"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="68" t="s">
+      <c r="A16" s="84"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="75"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="87"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="68" t="s">
+      <c r="A17" s="84"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="75"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="87"/>
-      <c r="B18" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="68" t="s">
+      <c r="A18" s="84"/>
+      <c r="B18" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="75"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="68" t="s">
+      <c r="A19" s="82"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="70"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="75"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="89">
+      <c r="A20" s="85">
         <v>46209</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="89"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67" t="s">
+      <c r="A21" s="85"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="89"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67" t="s">
+      <c r="A22" s="85"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="89"/>
-      <c r="B23" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="67" t="s">
+      <c r="A23" s="85"/>
+      <c r="B23" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="89"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="68" t="s">
+      <c r="A24" s="85"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="75"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="89"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="68" t="s">
+      <c r="A25" s="85"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="75"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="89"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="68" t="s">
+      <c r="A26" s="85"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="75"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="89"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="68" t="s">
+      <c r="A27" s="85"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="70"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="75"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="89"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="68" t="s">
+      <c r="A28" s="85"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="70"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="75"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="89"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="68" t="s">
+      <c r="A29" s="85"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="75"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="89"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="68" t="s">
+      <c r="A30" s="85"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="70"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="75"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="68" t="s">
+      <c r="A31" s="85"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="68" t="s">
+      <c r="A32" s="85"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="68" t="s">
+      <c r="A33" s="85"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="89"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="68" t="s">
+      <c r="A34" s="85"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="85">
+      <c r="A35" s="83">
         <v>46210</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67" t="s">
+      <c r="A36" s="83"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67" t="s">
+      <c r="A37" s="83"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
-      <c r="B38" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="A38" s="83"/>
+      <c r="B38" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="85"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67" t="s">
+      <c r="A39" s="83"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67" t="s">
+      <c r="A40" s="83"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67" t="s">
+      <c r="A41" s="83"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67" t="s">
+      <c r="A42" s="83"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67" t="s">
+      <c r="A43" s="83"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="68" t="s">
+      <c r="A44" s="83"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="75"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2093,13 +2096,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="C45" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2108,255 +2111,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="86">
+      <c r="A47" s="81">
         <v>46213</v>
       </c>
-      <c r="B47" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="68" t="s">
+      <c r="B47" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="70"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="75"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="87"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="68" t="s">
+      <c r="A48" s="84"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="70"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="75"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="68" t="s">
+      <c r="A49" s="84"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="70"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="75"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="68" t="s">
+      <c r="A50" s="84"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="70"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="75"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="88"/>
-      <c r="B51" s="77"/>
-      <c r="C51" s="68" t="s">
+      <c r="A51" s="82"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="70"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="75"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="66">
+      <c r="A52" s="72">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="C52" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="68"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="72"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="68"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="66">
+      <c r="A54" s="72">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="69"/>
-      <c r="E54" s="69"/>
-      <c r="F54" s="69"/>
-      <c r="G54" s="70"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="75"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="66"/>
-      <c r="B55" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="90" t="s">
+      <c r="A55" s="72"/>
+      <c r="B55" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="66"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="90" t="s">
+      <c r="A56" s="72"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="90"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
+      <c r="F56" s="86"/>
+      <c r="G56" s="86"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="66"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="90" t="s">
+      <c r="A57" s="72"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="90"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="66"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="90" t="s">
+      <c r="A58" s="72"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="90"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="66"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="90" t="s">
+      <c r="A59" s="72"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="86"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="66"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="90" t="s">
+      <c r="A60" s="72"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
+      <c r="D60" s="86"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="86"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="90" t="s">
+      <c r="A61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="90"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="66"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="90" t="s">
+      <c r="A62" s="72"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="90"/>
+      <c r="D62" s="86"/>
+      <c r="E62" s="86"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="86"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="90" t="s">
+      <c r="A63" s="72"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="90"/>
-      <c r="E63" s="90"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="90"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="86"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="86"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="66">
+      <c r="A64" s="72">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="67" t="s">
+      <c r="C64" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="68"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
-      <c r="B65" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="67" t="s">
+      <c r="A65" s="72"/>
+      <c r="B65" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="68"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67" t="s">
+      <c r="A66" s="72"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="68"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2365,164 +2368,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="67" t="s">
+      <c r="C67" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="66">
+      <c r="A68" s="72">
         <v>46220</v>
       </c>
-      <c r="B68" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="67" t="s">
+      <c r="B68" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="A69" s="72"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="66">
+      <c r="A70" s="72">
         <v>46223</v>
       </c>
-      <c r="B70" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="68" t="s">
+      <c r="B70" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="70"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="75"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="68" t="s">
+      <c r="A71" s="72"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="70"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="75"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="68" t="s">
+      <c r="A72" s="72"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="70"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="75"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="68" t="s">
+      <c r="A73" s="72"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="69"/>
-      <c r="F73" s="69"/>
-      <c r="G73" s="70"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="75"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="68" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="70"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="75"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="68" t="s">
+      <c r="A75" s="72"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="70"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="75"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="68" t="s">
+      <c r="A76" s="72"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="69"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="70"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="75"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="66"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="63" t="s">
+      <c r="A77" s="72"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="65"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="71"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="66"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="63" t="s">
+      <c r="A78" s="72"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="65"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="71"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="63" t="s">
+      <c r="A79" s="72"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="65"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="71"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="63" t="s">
+      <c r="A80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="65"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="71"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2531,353 +2534,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="67" t="s">
+      <c r="C81" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="68"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="66">
+      <c r="A82" s="72">
         <v>46225</v>
       </c>
-      <c r="B82" s="67" t="s">
+      <c r="B82" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="68"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="66"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="67" t="s">
+      <c r="A83" s="72"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="67"/>
+      <c r="D83" s="68"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="68"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="67" t="s">
+      <c r="A84" s="72"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="67"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="67"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="68"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
-      <c r="B85" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="67" t="s">
+      <c r="A85" s="72"/>
+      <c r="B85" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="67"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67" t="s">
+      <c r="A86" s="72"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="67"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="68"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="66"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67" t="s">
+      <c r="A87" s="72"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="66"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="67" t="s">
+      <c r="A88" s="72"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="67"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
+      <c r="D88" s="68"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="66"/>
-      <c r="B89" s="67"/>
-      <c r="C89" s="68" t="s">
+      <c r="A89" s="72"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="70"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="74"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="75"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="66"/>
-      <c r="B90" s="67"/>
-      <c r="C90" s="67" t="s">
+      <c r="A90" s="72"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
+      <c r="D90" s="68"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="68"/>
+      <c r="G90" s="68"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="86">
+      <c r="A91" s="81">
         <v>46227</v>
       </c>
-      <c r="B91" s="76" t="s">
+      <c r="B91" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="88"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="68" t="s">
+      <c r="A92" s="82"/>
+      <c r="B92" s="80"/>
+      <c r="C92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="69"/>
-      <c r="E92" s="69"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="70"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="74"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="75"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="66">
+      <c r="A93" s="72">
         <v>46228</v>
       </c>
-      <c r="B93" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="67" t="s">
+      <c r="B93" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="67"/>
+      <c r="D93" s="68"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="68"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="67" t="s">
+      <c r="A94" s="72"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="67"/>
+      <c r="D94" s="68"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="68"/>
+      <c r="G94" s="68"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="66"/>
-      <c r="B95" s="67"/>
-      <c r="C95" s="67" t="s">
+      <c r="A95" s="72"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="67"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="68"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="66"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="67" t="s">
+      <c r="A96" s="72"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="67"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="67"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="66"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="67" t="s">
+      <c r="A97" s="72"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="67"/>
+      <c r="D97" s="68"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="68"/>
+      <c r="G97" s="68"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="66"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="67" t="s">
+      <c r="A98" s="72"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="67"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="66">
+      <c r="A99" s="72">
         <v>46230</v>
       </c>
-      <c r="B99" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="67" t="s">
+      <c r="B99" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="66"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="67" t="s">
+      <c r="A100" s="72"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="67"/>
+      <c r="D100" s="68"/>
+      <c r="E100" s="68"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="68"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="66">
+      <c r="A101" s="72">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="92" t="s">
+      <c r="C101" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="92"/>
-      <c r="E101" s="92"/>
-      <c r="F101" s="92"/>
-      <c r="G101" s="92"/>
+      <c r="D101" s="78"/>
+      <c r="E101" s="78"/>
+      <c r="F101" s="78"/>
+      <c r="G101" s="78"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="66"/>
+      <c r="A102" s="72"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="92" t="s">
+      <c r="C102" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="92"/>
-      <c r="E102" s="92"/>
-      <c r="F102" s="92"/>
-      <c r="G102" s="92"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="78"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="91" t="s">
+      <c r="A103" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="81" t="s">
+      <c r="B103" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="81"/>
-      <c r="E103" s="81"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="81"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="91"/>
-      <c r="B104" s="67"/>
-      <c r="C104" s="67" t="s">
+      <c r="A104" s="76"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="91"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="67" t="s">
+      <c r="A105" s="76"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="67"/>
+      <c r="D105" s="68"/>
+      <c r="E105" s="68"/>
+      <c r="F105" s="68"/>
+      <c r="G105" s="68"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="91"/>
-      <c r="B106" s="67"/>
-      <c r="C106" s="67" t="s">
+      <c r="A106" s="76"/>
+      <c r="B106" s="68"/>
+      <c r="C106" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="67"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="67"/>
+      <c r="D106" s="68"/>
+      <c r="E106" s="68"/>
+      <c r="F106" s="68"/>
+      <c r="G106" s="68"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="91"/>
-      <c r="B107" s="67"/>
-      <c r="C107" s="67" t="s">
+      <c r="A107" s="76"/>
+      <c r="B107" s="68"/>
+      <c r="C107" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="67"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="67"/>
+      <c r="D107" s="68"/>
+      <c r="E107" s="68"/>
+      <c r="F107" s="68"/>
+      <c r="G107" s="68"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="66">
+      <c r="A108" s="72">
         <v>46234</v>
       </c>
-      <c r="B108" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="67" t="s">
+      <c r="B108" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="67"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="67"/>
-      <c r="G108" s="67"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="66"/>
-      <c r="B109" s="67"/>
-      <c r="C109" s="67" t="s">
+      <c r="A109" s="72"/>
+      <c r="B109" s="68"/>
+      <c r="C109" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="67"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="67"/>
-      <c r="G109" s="67"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="68"/>
+      <c r="F109" s="68"/>
+      <c r="G109" s="68"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2887,68 +2890,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2973,67 +2975,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3051,15 +3054,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46235</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3992,7 +3995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -4614,15 +4617,12 @@
       <c r="A60" s="11">
         <v>46289</v>
       </c>
-      <c r="B60" s="94" t="s">
+      <c r="B60" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C60" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="D60" s="94"/>
-      <c r="E60" s="94"/>
-      <c r="F60" s="94"/>
       <c r="G60" s="51"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -4644,9 +4644,6 @@
       <c r="C62" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="94"/>
-      <c r="E62" s="94"/>
-      <c r="F62" s="94"/>
       <c r="G62" s="51"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -4655,9 +4652,6 @@
       <c r="C63" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="D63" s="94"/>
-      <c r="E63" s="94"/>
-      <c r="F63" s="94"/>
       <c r="G63" s="51"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -4666,9 +4660,6 @@
       <c r="C64" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="D64" s="94"/>
-      <c r="E64" s="94"/>
-      <c r="F64" s="94"/>
       <c r="G64" s="51"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4677,9 +4668,6 @@
       <c r="C65" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="D65" s="94"/>
-      <c r="E65" s="94"/>
-      <c r="F65" s="94"/>
       <c r="G65" s="51"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -4688,9 +4676,6 @@
       <c r="C66" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D66" s="94"/>
-      <c r="E66" s="94"/>
-      <c r="F66" s="94"/>
       <c r="G66" s="51"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -4699,9 +4684,6 @@
       <c r="C67" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="D67" s="94"/>
-      <c r="E67" s="94"/>
-      <c r="F67" s="94"/>
       <c r="G67" s="51"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -4714,6 +4696,45 @@
       <c r="E68" s="49"/>
       <c r="F68" s="49"/>
       <c r="G68" s="50"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="11">
+        <v>46198</v>
+      </c>
+      <c r="B69" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="48"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="46"/>
+      <c r="B70" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" s="94"/>
+      <c r="E70" s="94"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="51"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="45"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64768A6-D200-4B7F-A7EA-D9D86DA3B96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F4C051-01B7-4D26-99E9-DD9BC1652952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="181">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -797,7 +797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -953,6 +953,30 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -968,85 +992,58 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1371,15 +1368,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="63">
+      <c r="A1" s="71">
         <v>46174</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1388,146 +1385,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="75"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46202</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68" t="s">
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72">
+      <c r="A9" s="66">
         <v>46203</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="70"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1537,14 +1534,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1555,6 +1544,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1572,15 +1569,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46204</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1589,152 +1586,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="77" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="82">
         <v>46205</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="69" t="s">
+      <c r="A8" s="83"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="71"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="65"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="83"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="65"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
-      <c r="B10" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="91"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="83"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69" t="s">
+      <c r="A13" s="84"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="81">
+      <c r="A14" s="86">
         <v>46206</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="76" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1746,348 +1743,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="73" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="70"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="84"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="73" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="70"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="73" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="84"/>
-      <c r="B18" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="73" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="75"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="70"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="73" t="s">
+      <c r="A19" s="88"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="70"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="89">
         <v>46209</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68" t="s">
+      <c r="A21" s="89"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68" t="s">
+      <c r="A22" s="89"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="68" t="s">
+      <c r="A23" s="89"/>
+      <c r="B23" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="73" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="75"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="73" t="s">
+      <c r="A25" s="89"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="75"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="70"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="73" t="s">
+      <c r="A26" s="89"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="73" t="s">
+      <c r="A27" s="89"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="75"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="73" t="s">
+      <c r="A28" s="89"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="75"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="73" t="s">
+      <c r="A29" s="89"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="73" t="s">
+      <c r="A30" s="89"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="73" t="s">
+      <c r="A31" s="89"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="73" t="s">
+      <c r="A32" s="89"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="73" t="s">
+      <c r="A33" s="89"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="73" t="s">
+      <c r="A34" s="89"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="70"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="83">
+      <c r="A35" s="85">
         <v>46210</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
-      <c r="B38" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="68" t="s">
+      <c r="A38" s="85"/>
+      <c r="B38" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68" t="s">
+      <c r="A40" s="85"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68" t="s">
+      <c r="A42" s="85"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68" t="s">
+      <c r="A43" s="85"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="73" t="s">
+      <c r="A44" s="85"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="75"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="70"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2096,13 +2093,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2111,255 +2108,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="81">
+      <c r="A47" s="86">
         <v>46213</v>
       </c>
-      <c r="B47" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="73" t="s">
+      <c r="B47" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="75"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="84"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="73" t="s">
+      <c r="A48" s="87"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="75"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="70"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="84"/>
-      <c r="B49" s="87"/>
-      <c r="C49" s="73" t="s">
+      <c r="A49" s="87"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="75"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="70"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="87"/>
-      <c r="C50" s="73" t="s">
+      <c r="A50" s="87"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="70"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="73" t="s">
+      <c r="A51" s="88"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="75"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="70"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="72">
+      <c r="A52" s="66">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="72">
+      <c r="A54" s="66">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="75"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="70"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
-      <c r="B55" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="86" t="s">
+      <c r="A55" s="66"/>
+      <c r="B55" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="86" t="s">
+      <c r="A56" s="66"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="90"/>
+      <c r="G56" s="90"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="86" t="s">
+      <c r="A57" s="66"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="86" t="s">
+      <c r="A58" s="66"/>
+      <c r="B58" s="67"/>
+      <c r="C58" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="86" t="s">
+      <c r="A59" s="66"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="86" t="s">
+      <c r="A60" s="66"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="86" t="s">
+      <c r="A61" s="66"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="86"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="90"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="86" t="s">
+      <c r="A62" s="66"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="90"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="86" t="s">
+      <c r="A63" s="66"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
+      <c r="D63" s="90"/>
+      <c r="E63" s="90"/>
+      <c r="F63" s="90"/>
+      <c r="G63" s="90"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="72">
+      <c r="A64" s="66">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="67"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
-      <c r="B65" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="68" t="s">
+      <c r="A65" s="66"/>
+      <c r="B65" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2368,164 +2365,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="72">
+      <c r="A68" s="66">
         <v>46220</v>
       </c>
-      <c r="B68" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="68" t="s">
+      <c r="B68" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68" t="s">
+      <c r="A69" s="66"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="72">
+      <c r="A70" s="66">
         <v>46223</v>
       </c>
-      <c r="B70" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="73" t="s">
+      <c r="B70" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="75"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="70"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="73" t="s">
+      <c r="A71" s="66"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="75"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="70"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="73" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="75"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="70"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="73" t="s">
+      <c r="A73" s="66"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="75"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="69"/>
+      <c r="G73" s="70"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="73" t="s">
+      <c r="A74" s="66"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="75"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="70"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="73" t="s">
+      <c r="A75" s="66"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="75"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="69"/>
+      <c r="G75" s="70"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="73" t="s">
+      <c r="A76" s="66"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="75"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="70"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="69" t="s">
+      <c r="A77" s="66"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="65"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="69" t="s">
+      <c r="A78" s="66"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="71"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="65"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="72"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="69" t="s">
+      <c r="A79" s="66"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
-      <c r="F79" s="70"/>
-      <c r="G79" s="71"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="65"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="69" t="s">
+      <c r="A80" s="66"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="71"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="65"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2534,353 +2531,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="68" t="s">
+      <c r="C81" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="72">
+      <c r="A82" s="66">
         <v>46225</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="67"/>
+      <c r="G82" s="67"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68" t="s">
+      <c r="A83" s="66"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="67"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="67"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68" t="s">
+      <c r="A84" s="66"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="67"/>
+      <c r="F84" s="67"/>
+      <c r="G84" s="67"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
-      <c r="B85" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="68" t="s">
+      <c r="A85" s="66"/>
+      <c r="B85" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="67"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68" t="s">
+      <c r="A86" s="66"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="67"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68" t="s">
+      <c r="A87" s="66"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="67"/>
+      <c r="G87" s="67"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68" t="s">
+      <c r="A88" s="66"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="67"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
-      <c r="B89" s="68"/>
-      <c r="C89" s="73" t="s">
+      <c r="A89" s="66"/>
+      <c r="B89" s="67"/>
+      <c r="C89" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="74"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="75"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
+      <c r="F89" s="69"/>
+      <c r="G89" s="70"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="72"/>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68" t="s">
+      <c r="A90" s="66"/>
+      <c r="B90" s="67"/>
+      <c r="C90" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="67"/>
+      <c r="G90" s="67"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="81">
+      <c r="A91" s="86">
         <v>46227</v>
       </c>
-      <c r="B91" s="79" t="s">
+      <c r="B91" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="67"/>
+      <c r="G91" s="67"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="82"/>
-      <c r="B92" s="80"/>
-      <c r="C92" s="73" t="s">
+      <c r="A92" s="88"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="75"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="70"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="72">
+      <c r="A93" s="66">
         <v>46228</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="68" t="s">
+      <c r="B93" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="67"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68" t="s">
+      <c r="A94" s="66"/>
+      <c r="B94" s="67"/>
+      <c r="C94" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="67"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="72"/>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68" t="s">
+      <c r="A95" s="66"/>
+      <c r="B95" s="67"/>
+      <c r="C95" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
+      <c r="F95" s="67"/>
+      <c r="G95" s="67"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="A96" s="66"/>
+      <c r="B96" s="67"/>
+      <c r="C96" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
+      <c r="D96" s="67"/>
+      <c r="E96" s="67"/>
+      <c r="F96" s="67"/>
+      <c r="G96" s="67"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="72"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="68" t="s">
+      <c r="A97" s="66"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="68"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="67"/>
+      <c r="G97" s="67"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="72"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="68" t="s">
+      <c r="A98" s="66"/>
+      <c r="B98" s="67"/>
+      <c r="C98" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="67"/>
+      <c r="G98" s="67"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="72">
+      <c r="A99" s="66">
         <v>46230</v>
       </c>
-      <c r="B99" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="68" t="s">
+      <c r="B99" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="72"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="68" t="s">
+      <c r="A100" s="66"/>
+      <c r="B100" s="67"/>
+      <c r="C100" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="68"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="67"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="72">
+      <c r="A101" s="66">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="78" t="s">
+      <c r="C101" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="78"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="78"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="72"/>
+      <c r="A102" s="66"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="78" t="s">
+      <c r="C102" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="78"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="78"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="76" t="s">
+      <c r="A103" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="77" t="s">
+      <c r="B103" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="81"/>
+      <c r="F103" s="81"/>
+      <c r="G103" s="81"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
-      <c r="B104" s="68"/>
-      <c r="C104" s="68" t="s">
+      <c r="A104" s="91"/>
+      <c r="B104" s="67"/>
+      <c r="C104" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="67"/>
+      <c r="G104" s="67"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68" t="s">
+      <c r="A105" s="91"/>
+      <c r="B105" s="67"/>
+      <c r="C105" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
+      <c r="D105" s="67"/>
+      <c r="E105" s="67"/>
+      <c r="F105" s="67"/>
+      <c r="G105" s="67"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
-      <c r="B106" s="68"/>
-      <c r="C106" s="68" t="s">
+      <c r="A106" s="91"/>
+      <c r="B106" s="67"/>
+      <c r="C106" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="68"/>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
+      <c r="D106" s="67"/>
+      <c r="E106" s="67"/>
+      <c r="F106" s="67"/>
+      <c r="G106" s="67"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
-      <c r="B107" s="68"/>
-      <c r="C107" s="68" t="s">
+      <c r="A107" s="91"/>
+      <c r="B107" s="67"/>
+      <c r="C107" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
+      <c r="D107" s="67"/>
+      <c r="E107" s="67"/>
+      <c r="F107" s="67"/>
+      <c r="G107" s="67"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="72">
+      <c r="A108" s="66">
         <v>46234</v>
       </c>
-      <c r="B108" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
+      <c r="D108" s="67"/>
+      <c r="E108" s="67"/>
+      <c r="F108" s="67"/>
+      <c r="G108" s="67"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="72"/>
-      <c r="B109" s="68"/>
-      <c r="C109" s="68" t="s">
+      <c r="A109" s="66"/>
+      <c r="B109" s="67"/>
+      <c r="C109" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
+      <c r="D109" s="67"/>
+      <c r="E109" s="67"/>
+      <c r="F109" s="67"/>
+      <c r="G109" s="67"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2890,6 +2887,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2914,129 +3034,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3054,15 +3051,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46235</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3995,7 +3992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -4720,13 +4717,10 @@
       <c r="C70" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="D70" s="94"/>
-      <c r="E70" s="94"/>
-      <c r="F70" s="94"/>
       <c r="G70" s="51"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="45"/>
+      <c r="A71" s="46"/>
       <c r="B71" s="45"/>
       <c r="C71" s="26" t="s">
         <v>72</v>
@@ -4735,6 +4729,32 @@
       <c r="E71" s="49"/>
       <c r="F71" s="49"/>
       <c r="G71" s="50"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B72" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="47"/>
+      <c r="E72" s="47"/>
+      <c r="F72" s="47"/>
+      <c r="G72" s="48"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="45"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="49"/>
+      <c r="G73" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F4C051-01B7-4D26-99E9-DD9BC1652952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC150D38-7159-494A-A193-618A70646869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="182">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -574,6 +574,9 @@
   </si>
   <si>
     <t>Nhận 23 LE-2G nâng cấp LE-4G từ KT. Kho</t>
+  </si>
+  <si>
+    <t>Nhận 24 mạch LE2G=&gt;4G Anh Tuấn BG</t>
   </si>
 </sst>
 </file>
@@ -797,7 +800,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -953,6 +956,24 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -965,9 +986,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -977,20 +995,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -998,6 +1010,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1007,9 +1037,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1019,31 +1046,10 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1368,15 +1374,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="71">
+      <c r="A1" s="63">
         <v>46174</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1385,146 +1391,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46202</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67" t="s">
+      <c r="A7" s="72"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="66"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="66">
+      <c r="A9" s="72">
         <v>46203</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="66"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="66"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1534,6 +1540,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1544,14 +1558,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1569,15 +1575,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46204</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1586,152 +1592,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="82">
+      <c r="A7" s="90">
         <v>46205</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="70"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="75"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="63" t="s">
+      <c r="A8" s="91"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="63" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
-      <c r="B10" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="63" t="s">
+      <c r="A13" s="92"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="81">
         <v>46206</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1743,348 +1749,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="87"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="68" t="s">
+      <c r="A15" s="84"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="75"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="68" t="s">
+      <c r="A16" s="84"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="75"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="87"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="68" t="s">
+      <c r="A17" s="84"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="75"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="87"/>
-      <c r="B18" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="68" t="s">
+      <c r="A18" s="84"/>
+      <c r="B18" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="75"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="68" t="s">
+      <c r="A19" s="82"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="70"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="75"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="89">
+      <c r="A20" s="85">
         <v>46209</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="89"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67" t="s">
+      <c r="A21" s="85"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="89"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67" t="s">
+      <c r="A22" s="85"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="89"/>
-      <c r="B23" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="67" t="s">
+      <c r="A23" s="85"/>
+      <c r="B23" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="89"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="68" t="s">
+      <c r="A24" s="85"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="75"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="89"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="68" t="s">
+      <c r="A25" s="85"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="75"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="89"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="68" t="s">
+      <c r="A26" s="85"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="75"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="89"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="68" t="s">
+      <c r="A27" s="85"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="70"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="75"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="89"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="68" t="s">
+      <c r="A28" s="85"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="70"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="75"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="89"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="68" t="s">
+      <c r="A29" s="85"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="75"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="89"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="68" t="s">
+      <c r="A30" s="85"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="70"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="75"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="68" t="s">
+      <c r="A31" s="85"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="68" t="s">
+      <c r="A32" s="85"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="68" t="s">
+      <c r="A33" s="85"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="89"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="68" t="s">
+      <c r="A34" s="85"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="85">
+      <c r="A35" s="83">
         <v>46210</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67" t="s">
+      <c r="A36" s="83"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67" t="s">
+      <c r="A37" s="83"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
-      <c r="B38" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="A38" s="83"/>
+      <c r="B38" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="85"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67" t="s">
+      <c r="A39" s="83"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67" t="s">
+      <c r="A40" s="83"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67" t="s">
+      <c r="A41" s="83"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67" t="s">
+      <c r="A42" s="83"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67" t="s">
+      <c r="A43" s="83"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="68" t="s">
+      <c r="A44" s="83"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="75"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2093,13 +2099,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="C45" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2108,255 +2114,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="86">
+      <c r="A47" s="81">
         <v>46213</v>
       </c>
-      <c r="B47" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="68" t="s">
+      <c r="B47" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="70"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="75"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="87"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="68" t="s">
+      <c r="A48" s="84"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="70"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="75"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="68" t="s">
+      <c r="A49" s="84"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="70"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="75"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="68" t="s">
+      <c r="A50" s="84"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="70"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="75"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="88"/>
-      <c r="B51" s="77"/>
-      <c r="C51" s="68" t="s">
+      <c r="A51" s="82"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="70"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="75"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="66">
+      <c r="A52" s="72">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="C52" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="68"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="72"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="68"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="66">
+      <c r="A54" s="72">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="69"/>
-      <c r="E54" s="69"/>
-      <c r="F54" s="69"/>
-      <c r="G54" s="70"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="75"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="66"/>
-      <c r="B55" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="90" t="s">
+      <c r="A55" s="72"/>
+      <c r="B55" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="66"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="90" t="s">
+      <c r="A56" s="72"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="90"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
+      <c r="F56" s="86"/>
+      <c r="G56" s="86"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="66"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="90" t="s">
+      <c r="A57" s="72"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="90"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="66"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="90" t="s">
+      <c r="A58" s="72"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="90"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="66"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="90" t="s">
+      <c r="A59" s="72"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="86"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="66"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="90" t="s">
+      <c r="A60" s="72"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
+      <c r="D60" s="86"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="86"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="90" t="s">
+      <c r="A61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="90"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="66"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="90" t="s">
+      <c r="A62" s="72"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="90"/>
+      <c r="D62" s="86"/>
+      <c r="E62" s="86"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="86"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="90" t="s">
+      <c r="A63" s="72"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="90"/>
-      <c r="E63" s="90"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="90"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="86"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="86"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="66">
+      <c r="A64" s="72">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="67" t="s">
+      <c r="C64" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="68"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
-      <c r="B65" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="67" t="s">
+      <c r="A65" s="72"/>
+      <c r="B65" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="68"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67" t="s">
+      <c r="A66" s="72"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="68"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2365,164 +2371,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="67" t="s">
+      <c r="C67" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="66">
+      <c r="A68" s="72">
         <v>46220</v>
       </c>
-      <c r="B68" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="67" t="s">
+      <c r="B68" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="A69" s="72"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="66">
+      <c r="A70" s="72">
         <v>46223</v>
       </c>
-      <c r="B70" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="68" t="s">
+      <c r="B70" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="70"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="75"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="68" t="s">
+      <c r="A71" s="72"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="70"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="75"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="68" t="s">
+      <c r="A72" s="72"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="70"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="75"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="68" t="s">
+      <c r="A73" s="72"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="69"/>
-      <c r="F73" s="69"/>
-      <c r="G73" s="70"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="75"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="68" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="70"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="75"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="68" t="s">
+      <c r="A75" s="72"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="70"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="75"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="68" t="s">
+      <c r="A76" s="72"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="69"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="70"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="75"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="66"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="63" t="s">
+      <c r="A77" s="72"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="65"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="71"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="66"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="63" t="s">
+      <c r="A78" s="72"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="65"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="71"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="63" t="s">
+      <c r="A79" s="72"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="65"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="71"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="63" t="s">
+      <c r="A80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="65"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="71"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2531,353 +2537,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="67" t="s">
+      <c r="C81" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="68"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="66">
+      <c r="A82" s="72">
         <v>46225</v>
       </c>
-      <c r="B82" s="67" t="s">
+      <c r="B82" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="68"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="66"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="67" t="s">
+      <c r="A83" s="72"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="67"/>
+      <c r="D83" s="68"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="68"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="67" t="s">
+      <c r="A84" s="72"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="67"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="67"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="68"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
-      <c r="B85" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="67" t="s">
+      <c r="A85" s="72"/>
+      <c r="B85" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="67"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67" t="s">
+      <c r="A86" s="72"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="67"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="68"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="66"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67" t="s">
+      <c r="A87" s="72"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="66"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="67" t="s">
+      <c r="A88" s="72"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="67"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
+      <c r="D88" s="68"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="66"/>
-      <c r="B89" s="67"/>
-      <c r="C89" s="68" t="s">
+      <c r="A89" s="72"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="70"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="74"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="75"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="66"/>
-      <c r="B90" s="67"/>
-      <c r="C90" s="67" t="s">
+      <c r="A90" s="72"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
+      <c r="D90" s="68"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="68"/>
+      <c r="G90" s="68"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="86">
+      <c r="A91" s="81">
         <v>46227</v>
       </c>
-      <c r="B91" s="76" t="s">
+      <c r="B91" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="88"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="68" t="s">
+      <c r="A92" s="82"/>
+      <c r="B92" s="80"/>
+      <c r="C92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="69"/>
-      <c r="E92" s="69"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="70"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="74"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="75"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="66">
+      <c r="A93" s="72">
         <v>46228</v>
       </c>
-      <c r="B93" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="67" t="s">
+      <c r="B93" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="67"/>
+      <c r="D93" s="68"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="68"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="67" t="s">
+      <c r="A94" s="72"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="67"/>
+      <c r="D94" s="68"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="68"/>
+      <c r="G94" s="68"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="66"/>
-      <c r="B95" s="67"/>
-      <c r="C95" s="67" t="s">
+      <c r="A95" s="72"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="67"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="68"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="66"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="67" t="s">
+      <c r="A96" s="72"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="67"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="67"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="66"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="67" t="s">
+      <c r="A97" s="72"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="67"/>
+      <c r="D97" s="68"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="68"/>
+      <c r="G97" s="68"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="66"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="67" t="s">
+      <c r="A98" s="72"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="67"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="66">
+      <c r="A99" s="72">
         <v>46230</v>
       </c>
-      <c r="B99" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="67" t="s">
+      <c r="B99" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="66"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="67" t="s">
+      <c r="A100" s="72"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="67"/>
+      <c r="D100" s="68"/>
+      <c r="E100" s="68"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="68"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="66">
+      <c r="A101" s="72">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="92" t="s">
+      <c r="C101" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="92"/>
-      <c r="E101" s="92"/>
-      <c r="F101" s="92"/>
-      <c r="G101" s="92"/>
+      <c r="D101" s="78"/>
+      <c r="E101" s="78"/>
+      <c r="F101" s="78"/>
+      <c r="G101" s="78"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="66"/>
+      <c r="A102" s="72"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="92" t="s">
+      <c r="C102" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="92"/>
-      <c r="E102" s="92"/>
-      <c r="F102" s="92"/>
-      <c r="G102" s="92"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="78"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="91" t="s">
+      <c r="A103" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="81" t="s">
+      <c r="B103" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="81"/>
-      <c r="E103" s="81"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="81"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="91"/>
-      <c r="B104" s="67"/>
-      <c r="C104" s="67" t="s">
+      <c r="A104" s="76"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="91"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="67" t="s">
+      <c r="A105" s="76"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="67"/>
+      <c r="D105" s="68"/>
+      <c r="E105" s="68"/>
+      <c r="F105" s="68"/>
+      <c r="G105" s="68"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="91"/>
-      <c r="B106" s="67"/>
-      <c r="C106" s="67" t="s">
+      <c r="A106" s="76"/>
+      <c r="B106" s="68"/>
+      <c r="C106" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="67"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="67"/>
+      <c r="D106" s="68"/>
+      <c r="E106" s="68"/>
+      <c r="F106" s="68"/>
+      <c r="G106" s="68"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="91"/>
-      <c r="B107" s="67"/>
-      <c r="C107" s="67" t="s">
+      <c r="A107" s="76"/>
+      <c r="B107" s="68"/>
+      <c r="C107" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="67"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="67"/>
+      <c r="D107" s="68"/>
+      <c r="E107" s="68"/>
+      <c r="F107" s="68"/>
+      <c r="G107" s="68"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="66">
+      <c r="A108" s="72">
         <v>46234</v>
       </c>
-      <c r="B108" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="67" t="s">
+      <c r="B108" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="67"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="67"/>
-      <c r="G108" s="67"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="66"/>
-      <c r="B109" s="67"/>
-      <c r="C109" s="67" t="s">
+      <c r="A109" s="72"/>
+      <c r="B109" s="68"/>
+      <c r="C109" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="67"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="67"/>
-      <c r="G109" s="67"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="68"/>
+      <c r="F109" s="68"/>
+      <c r="G109" s="68"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2887,68 +2893,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2973,67 +2978,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3051,15 +3057,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46235</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3992,7 +3998,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -4756,6 +4762,67 @@
       <c r="F73" s="49"/>
       <c r="G73" s="50"/>
     </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B74" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="D74" s="47"/>
+      <c r="E74" s="47"/>
+      <c r="F74" s="47"/>
+      <c r="G74" s="48"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="46"/>
+      <c r="B75" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" s="94"/>
+      <c r="E75" s="94"/>
+      <c r="F75" s="94"/>
+      <c r="G75" s="51"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="46"/>
+      <c r="B76" s="46"/>
+      <c r="C76" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="94"/>
+      <c r="E76" s="94"/>
+      <c r="F76" s="94"/>
+      <c r="G76" s="51"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="46"/>
+      <c r="B77" s="46"/>
+      <c r="C77" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="94"/>
+      <c r="E77" s="94"/>
+      <c r="F77" s="94"/>
+      <c r="G77" s="51"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="45"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="50"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC150D38-7159-494A-A193-618A70646869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7C7CAE-0D1C-43B5-944F-EF426A1C12B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="183">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -577,6 +577,9 @@
   </si>
   <si>
     <t>Nhận 24 mạch LE2G=&gt;4G Anh Tuấn BG</t>
+  </si>
+  <si>
+    <t>Nhận 21 mắt cam kiểm tra từ kho</t>
   </si>
 </sst>
 </file>
@@ -956,6 +959,30 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -971,80 +998,56 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1374,15 +1377,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="63">
+      <c r="A1" s="71">
         <v>46174</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1391,146 +1394,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="75"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46202</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68" t="s">
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72">
+      <c r="A9" s="66">
         <v>46203</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="70"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1540,14 +1543,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1558,6 +1553,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1575,15 +1578,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46204</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1592,152 +1595,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="77" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="82">
         <v>46205</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="69" t="s">
+      <c r="A8" s="83"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="71"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="65"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="83"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="65"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
-      <c r="B10" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="91"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="83"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69" t="s">
+      <c r="A13" s="84"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="81">
+      <c r="A14" s="86">
         <v>46206</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="76" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1749,348 +1752,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="73" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="70"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="84"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="73" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="70"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="73" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="84"/>
-      <c r="B18" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="73" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="75"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="70"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="73" t="s">
+      <c r="A19" s="88"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="70"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="89">
         <v>46209</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68" t="s">
+      <c r="A21" s="89"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68" t="s">
+      <c r="A22" s="89"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="68" t="s">
+      <c r="A23" s="89"/>
+      <c r="B23" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="73" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="75"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="73" t="s">
+      <c r="A25" s="89"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="75"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="70"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="73" t="s">
+      <c r="A26" s="89"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="73" t="s">
+      <c r="A27" s="89"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="75"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="73" t="s">
+      <c r="A28" s="89"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="75"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="73" t="s">
+      <c r="A29" s="89"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="73" t="s">
+      <c r="A30" s="89"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="73" t="s">
+      <c r="A31" s="89"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="73" t="s">
+      <c r="A32" s="89"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="73" t="s">
+      <c r="A33" s="89"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="73" t="s">
+      <c r="A34" s="89"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="70"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="83">
+      <c r="A35" s="85">
         <v>46210</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
-      <c r="B38" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="68" t="s">
+      <c r="A38" s="85"/>
+      <c r="B38" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68" t="s">
+      <c r="A40" s="85"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68" t="s">
+      <c r="A42" s="85"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68" t="s">
+      <c r="A43" s="85"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="73" t="s">
+      <c r="A44" s="85"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="75"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="70"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2099,13 +2102,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2114,255 +2117,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="81">
+      <c r="A47" s="86">
         <v>46213</v>
       </c>
-      <c r="B47" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="73" t="s">
+      <c r="B47" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="75"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="84"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="73" t="s">
+      <c r="A48" s="87"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="75"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="70"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="84"/>
-      <c r="B49" s="87"/>
-      <c r="C49" s="73" t="s">
+      <c r="A49" s="87"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="75"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="70"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="87"/>
-      <c r="C50" s="73" t="s">
+      <c r="A50" s="87"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="70"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="73" t="s">
+      <c r="A51" s="88"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="75"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="70"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="72">
+      <c r="A52" s="66">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="72">
+      <c r="A54" s="66">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="75"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="70"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
-      <c r="B55" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="86" t="s">
+      <c r="A55" s="66"/>
+      <c r="B55" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="86" t="s">
+      <c r="A56" s="66"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="90"/>
+      <c r="G56" s="90"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="86" t="s">
+      <c r="A57" s="66"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="86" t="s">
+      <c r="A58" s="66"/>
+      <c r="B58" s="67"/>
+      <c r="C58" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="86" t="s">
+      <c r="A59" s="66"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="86" t="s">
+      <c r="A60" s="66"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="86" t="s">
+      <c r="A61" s="66"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="86"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="90"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="86" t="s">
+      <c r="A62" s="66"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="90"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="86" t="s">
+      <c r="A63" s="66"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
+      <c r="D63" s="90"/>
+      <c r="E63" s="90"/>
+      <c r="F63" s="90"/>
+      <c r="G63" s="90"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="72">
+      <c r="A64" s="66">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="67"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
-      <c r="B65" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="68" t="s">
+      <c r="A65" s="66"/>
+      <c r="B65" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2371,164 +2374,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="72">
+      <c r="A68" s="66">
         <v>46220</v>
       </c>
-      <c r="B68" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="68" t="s">
+      <c r="B68" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68" t="s">
+      <c r="A69" s="66"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="72">
+      <c r="A70" s="66">
         <v>46223</v>
       </c>
-      <c r="B70" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="73" t="s">
+      <c r="B70" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="75"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="70"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="73" t="s">
+      <c r="A71" s="66"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="75"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="70"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="73" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="75"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="70"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="73" t="s">
+      <c r="A73" s="66"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="75"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="69"/>
+      <c r="G73" s="70"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="73" t="s">
+      <c r="A74" s="66"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="75"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="70"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="73" t="s">
+      <c r="A75" s="66"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="75"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="69"/>
+      <c r="G75" s="70"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="73" t="s">
+      <c r="A76" s="66"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="75"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="70"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="69" t="s">
+      <c r="A77" s="66"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="65"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="69" t="s">
+      <c r="A78" s="66"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="71"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="65"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="72"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="69" t="s">
+      <c r="A79" s="66"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
-      <c r="F79" s="70"/>
-      <c r="G79" s="71"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="65"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="69" t="s">
+      <c r="A80" s="66"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="71"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="65"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2537,353 +2540,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="68" t="s">
+      <c r="C81" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="72">
+      <c r="A82" s="66">
         <v>46225</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="67"/>
+      <c r="G82" s="67"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68" t="s">
+      <c r="A83" s="66"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="67"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="67"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68" t="s">
+      <c r="A84" s="66"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="67"/>
+      <c r="F84" s="67"/>
+      <c r="G84" s="67"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
-      <c r="B85" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="68" t="s">
+      <c r="A85" s="66"/>
+      <c r="B85" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="67"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68" t="s">
+      <c r="A86" s="66"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="67"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68" t="s">
+      <c r="A87" s="66"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="67"/>
+      <c r="G87" s="67"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68" t="s">
+      <c r="A88" s="66"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="67"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
-      <c r="B89" s="68"/>
-      <c r="C89" s="73" t="s">
+      <c r="A89" s="66"/>
+      <c r="B89" s="67"/>
+      <c r="C89" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="74"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="75"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
+      <c r="F89" s="69"/>
+      <c r="G89" s="70"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="72"/>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68" t="s">
+      <c r="A90" s="66"/>
+      <c r="B90" s="67"/>
+      <c r="C90" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="67"/>
+      <c r="G90" s="67"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="81">
+      <c r="A91" s="86">
         <v>46227</v>
       </c>
-      <c r="B91" s="79" t="s">
+      <c r="B91" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="67"/>
+      <c r="G91" s="67"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="82"/>
-      <c r="B92" s="80"/>
-      <c r="C92" s="73" t="s">
+      <c r="A92" s="88"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="75"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="70"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="72">
+      <c r="A93" s="66">
         <v>46228</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="68" t="s">
+      <c r="B93" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="67"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68" t="s">
+      <c r="A94" s="66"/>
+      <c r="B94" s="67"/>
+      <c r="C94" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="67"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="72"/>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68" t="s">
+      <c r="A95" s="66"/>
+      <c r="B95" s="67"/>
+      <c r="C95" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
+      <c r="F95" s="67"/>
+      <c r="G95" s="67"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="A96" s="66"/>
+      <c r="B96" s="67"/>
+      <c r="C96" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
+      <c r="D96" s="67"/>
+      <c r="E96" s="67"/>
+      <c r="F96" s="67"/>
+      <c r="G96" s="67"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="72"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="68" t="s">
+      <c r="A97" s="66"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="68"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="67"/>
+      <c r="G97" s="67"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="72"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="68" t="s">
+      <c r="A98" s="66"/>
+      <c r="B98" s="67"/>
+      <c r="C98" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="67"/>
+      <c r="G98" s="67"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="72">
+      <c r="A99" s="66">
         <v>46230</v>
       </c>
-      <c r="B99" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="68" t="s">
+      <c r="B99" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="72"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="68" t="s">
+      <c r="A100" s="66"/>
+      <c r="B100" s="67"/>
+      <c r="C100" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="68"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="67"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="72">
+      <c r="A101" s="66">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="78" t="s">
+      <c r="C101" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="78"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="78"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="72"/>
+      <c r="A102" s="66"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="78" t="s">
+      <c r="C102" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="78"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="78"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="76" t="s">
+      <c r="A103" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="77" t="s">
+      <c r="B103" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="81"/>
+      <c r="F103" s="81"/>
+      <c r="G103" s="81"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
-      <c r="B104" s="68"/>
-      <c r="C104" s="68" t="s">
+      <c r="A104" s="91"/>
+      <c r="B104" s="67"/>
+      <c r="C104" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="67"/>
+      <c r="G104" s="67"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68" t="s">
+      <c r="A105" s="91"/>
+      <c r="B105" s="67"/>
+      <c r="C105" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
+      <c r="D105" s="67"/>
+      <c r="E105" s="67"/>
+      <c r="F105" s="67"/>
+      <c r="G105" s="67"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
-      <c r="B106" s="68"/>
-      <c r="C106" s="68" t="s">
+      <c r="A106" s="91"/>
+      <c r="B106" s="67"/>
+      <c r="C106" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="68"/>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
+      <c r="D106" s="67"/>
+      <c r="E106" s="67"/>
+      <c r="F106" s="67"/>
+      <c r="G106" s="67"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
-      <c r="B107" s="68"/>
-      <c r="C107" s="68" t="s">
+      <c r="A107" s="91"/>
+      <c r="B107" s="67"/>
+      <c r="C107" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
+      <c r="D107" s="67"/>
+      <c r="E107" s="67"/>
+      <c r="F107" s="67"/>
+      <c r="G107" s="67"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="72">
+      <c r="A108" s="66">
         <v>46234</v>
       </c>
-      <c r="B108" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
+      <c r="D108" s="67"/>
+      <c r="E108" s="67"/>
+      <c r="F108" s="67"/>
+      <c r="G108" s="67"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="72"/>
-      <c r="B109" s="68"/>
-      <c r="C109" s="68" t="s">
+      <c r="A109" s="66"/>
+      <c r="B109" s="67"/>
+      <c r="C109" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
+      <c r="D109" s="67"/>
+      <c r="E109" s="67"/>
+      <c r="F109" s="67"/>
+      <c r="G109" s="67"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2893,6 +2896,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2917,129 +3043,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3057,15 +3060,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46235</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3998,7 +4001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F794F4-B843-4D59-B697-A1CBEF2779DC}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -4763,14 +4766,14 @@
       <c r="G73" s="50"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="11">
+      <c r="A74" s="13">
         <v>46294</v>
       </c>
-      <c r="B74" s="52" t="s">
+      <c r="B74" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="24" t="s">
-        <v>181</v>
+      <c r="C74" s="47" t="s">
+        <v>182</v>
       </c>
       <c r="D74" s="47"/>
       <c r="E74" s="47"/>
@@ -4778,34 +4781,34 @@
       <c r="G74" s="48"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="46"/>
-      <c r="B75" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" s="94"/>
-      <c r="E75" s="94"/>
-      <c r="F75" s="94"/>
-      <c r="G75" s="51"/>
+      <c r="A75" s="13"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="50"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="46"/>
-      <c r="B76" s="46"/>
-      <c r="C76" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D76" s="94"/>
-      <c r="E76" s="94"/>
-      <c r="F76" s="94"/>
-      <c r="G76" s="51"/>
+      <c r="B76" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D76" s="47"/>
+      <c r="E76" s="47"/>
+      <c r="F76" s="47"/>
+      <c r="G76" s="48"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="46"/>
       <c r="B77" s="46"/>
       <c r="C77" s="25" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="D77" s="94"/>
       <c r="E77" s="94"/>
@@ -4813,15 +4816,48 @@
       <c r="G77" s="51"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="45"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="26" t="s">
+      <c r="A78" s="46"/>
+      <c r="B78" s="46"/>
+      <c r="C78" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="94"/>
+      <c r="E78" s="94"/>
+      <c r="F78" s="94"/>
+      <c r="G78" s="51"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="46"/>
+      <c r="B79" s="46"/>
+      <c r="C79" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79" s="94"/>
+      <c r="E79" s="94"/>
+      <c r="F79" s="94"/>
+      <c r="G79" s="51"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="46"/>
+      <c r="B80" s="46"/>
+      <c r="C80" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D80" s="94"/>
+      <c r="E80" s="94"/>
+      <c r="F80" s="94"/>
+      <c r="G80" s="51"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="45"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="50"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7C7CAE-0D1C-43B5-944F-EF426A1C12B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733F1157-0C18-4144-BF68-27D628009DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
     <sheet name="07-2026" sheetId="2" r:id="rId2"/>
     <sheet name="08-2026" sheetId="3" r:id="rId3"/>
     <sheet name="09-2026" sheetId="4" r:id="rId4"/>
+    <sheet name="10-2026" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'6-2026'!$A$2:$G$8</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="184">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -580,6 +581,9 @@
   </si>
   <si>
     <t>Nhận 21 mắt cam kiểm tra từ kho</t>
+  </si>
+  <si>
+    <t>Nhận linh kiện dư VNSH03 (Chưa kiểm đếm)</t>
   </si>
 </sst>
 </file>
@@ -959,6 +963,24 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -971,9 +993,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -983,20 +1002,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1004,6 +1017,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1013,9 +1044,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1024,30 +1052,6 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1377,15 +1381,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="71">
+      <c r="A1" s="63">
         <v>46174</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1394,146 +1398,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46202</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67" t="s">
+      <c r="A7" s="72"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="66"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="66">
+      <c r="A9" s="72">
         <v>46203</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="66"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="66"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1543,6 +1547,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1553,14 +1565,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1578,15 +1582,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46204</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1595,152 +1599,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="82">
+      <c r="A7" s="90">
         <v>46205</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="70"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="75"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="63" t="s">
+      <c r="A8" s="91"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="63" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
-      <c r="B10" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="63" t="s">
+      <c r="A13" s="92"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="81">
         <v>46206</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1752,348 +1756,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="87"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="68" t="s">
+      <c r="A15" s="84"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="75"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="68" t="s">
+      <c r="A16" s="84"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="75"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="87"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="68" t="s">
+      <c r="A17" s="84"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="75"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="87"/>
-      <c r="B18" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="68" t="s">
+      <c r="A18" s="84"/>
+      <c r="B18" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="75"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="68" t="s">
+      <c r="A19" s="82"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="70"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="75"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="89">
+      <c r="A20" s="85">
         <v>46209</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="89"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67" t="s">
+      <c r="A21" s="85"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="89"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67" t="s">
+      <c r="A22" s="85"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="89"/>
-      <c r="B23" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="67" t="s">
+      <c r="A23" s="85"/>
+      <c r="B23" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="89"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="68" t="s">
+      <c r="A24" s="85"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="75"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="89"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="68" t="s">
+      <c r="A25" s="85"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="75"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="89"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="68" t="s">
+      <c r="A26" s="85"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="75"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="89"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="68" t="s">
+      <c r="A27" s="85"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="70"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="75"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="89"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="68" t="s">
+      <c r="A28" s="85"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="70"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="75"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="89"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="68" t="s">
+      <c r="A29" s="85"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="75"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="89"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="68" t="s">
+      <c r="A30" s="85"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="70"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="75"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="68" t="s">
+      <c r="A31" s="85"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="68" t="s">
+      <c r="A32" s="85"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="68" t="s">
+      <c r="A33" s="85"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="89"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="68" t="s">
+      <c r="A34" s="85"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="85">
+      <c r="A35" s="83">
         <v>46210</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67" t="s">
+      <c r="A36" s="83"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67" t="s">
+      <c r="A37" s="83"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
-      <c r="B38" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="A38" s="83"/>
+      <c r="B38" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="85"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67" t="s">
+      <c r="A39" s="83"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67" t="s">
+      <c r="A40" s="83"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67" t="s">
+      <c r="A41" s="83"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67" t="s">
+      <c r="A42" s="83"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67" t="s">
+      <c r="A43" s="83"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="68" t="s">
+      <c r="A44" s="83"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="75"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2102,13 +2106,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="C45" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2117,255 +2121,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="86">
+      <c r="A47" s="81">
         <v>46213</v>
       </c>
-      <c r="B47" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="68" t="s">
+      <c r="B47" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="70"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="75"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="87"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="68" t="s">
+      <c r="A48" s="84"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="70"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="75"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="68" t="s">
+      <c r="A49" s="84"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="70"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="75"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="68" t="s">
+      <c r="A50" s="84"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="70"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="75"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="88"/>
-      <c r="B51" s="77"/>
-      <c r="C51" s="68" t="s">
+      <c r="A51" s="82"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="70"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="75"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="66">
+      <c r="A52" s="72">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="C52" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="68"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="72"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="68"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="66">
+      <c r="A54" s="72">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="69"/>
-      <c r="E54" s="69"/>
-      <c r="F54" s="69"/>
-      <c r="G54" s="70"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="75"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="66"/>
-      <c r="B55" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="90" t="s">
+      <c r="A55" s="72"/>
+      <c r="B55" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="66"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="90" t="s">
+      <c r="A56" s="72"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="90"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
+      <c r="F56" s="86"/>
+      <c r="G56" s="86"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="66"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="90" t="s">
+      <c r="A57" s="72"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="90"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="66"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="90" t="s">
+      <c r="A58" s="72"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="90"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="66"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="90" t="s">
+      <c r="A59" s="72"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="86"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="66"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="90" t="s">
+      <c r="A60" s="72"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
+      <c r="D60" s="86"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="86"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="90" t="s">
+      <c r="A61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="90"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="66"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="90" t="s">
+      <c r="A62" s="72"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="90"/>
+      <c r="D62" s="86"/>
+      <c r="E62" s="86"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="86"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="90" t="s">
+      <c r="A63" s="72"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="90"/>
-      <c r="E63" s="90"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="90"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="86"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="86"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="66">
+      <c r="A64" s="72">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="67" t="s">
+      <c r="C64" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="68"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
-      <c r="B65" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="67" t="s">
+      <c r="A65" s="72"/>
+      <c r="B65" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="68"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67" t="s">
+      <c r="A66" s="72"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="68"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2374,164 +2378,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="67" t="s">
+      <c r="C67" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="66">
+      <c r="A68" s="72">
         <v>46220</v>
       </c>
-      <c r="B68" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="67" t="s">
+      <c r="B68" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="A69" s="72"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="66">
+      <c r="A70" s="72">
         <v>46223</v>
       </c>
-      <c r="B70" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="68" t="s">
+      <c r="B70" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="70"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="75"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="68" t="s">
+      <c r="A71" s="72"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="70"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="75"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="68" t="s">
+      <c r="A72" s="72"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="70"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="75"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="68" t="s">
+      <c r="A73" s="72"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="69"/>
-      <c r="F73" s="69"/>
-      <c r="G73" s="70"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="75"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="68" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="70"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="75"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="68" t="s">
+      <c r="A75" s="72"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="70"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="75"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="68" t="s">
+      <c r="A76" s="72"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="69"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="70"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="75"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="66"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="63" t="s">
+      <c r="A77" s="72"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="65"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="71"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="66"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="63" t="s">
+      <c r="A78" s="72"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="65"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="71"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="63" t="s">
+      <c r="A79" s="72"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="65"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="71"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="63" t="s">
+      <c r="A80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="65"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="71"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2540,353 +2544,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="67" t="s">
+      <c r="C81" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="68"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="66">
+      <c r="A82" s="72">
         <v>46225</v>
       </c>
-      <c r="B82" s="67" t="s">
+      <c r="B82" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="68"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="66"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="67" t="s">
+      <c r="A83" s="72"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="67"/>
+      <c r="D83" s="68"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="68"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="67" t="s">
+      <c r="A84" s="72"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="67"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="67"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="68"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
-      <c r="B85" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="67" t="s">
+      <c r="A85" s="72"/>
+      <c r="B85" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="67"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67" t="s">
+      <c r="A86" s="72"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="67"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="68"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="66"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67" t="s">
+      <c r="A87" s="72"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="66"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="67" t="s">
+      <c r="A88" s="72"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="67"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
+      <c r="D88" s="68"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="66"/>
-      <c r="B89" s="67"/>
-      <c r="C89" s="68" t="s">
+      <c r="A89" s="72"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="70"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="74"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="75"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="66"/>
-      <c r="B90" s="67"/>
-      <c r="C90" s="67" t="s">
+      <c r="A90" s="72"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
+      <c r="D90" s="68"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="68"/>
+      <c r="G90" s="68"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="86">
+      <c r="A91" s="81">
         <v>46227</v>
       </c>
-      <c r="B91" s="76" t="s">
+      <c r="B91" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="88"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="68" t="s">
+      <c r="A92" s="82"/>
+      <c r="B92" s="80"/>
+      <c r="C92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="69"/>
-      <c r="E92" s="69"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="70"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="74"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="75"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="66">
+      <c r="A93" s="72">
         <v>46228</v>
       </c>
-      <c r="B93" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="67" t="s">
+      <c r="B93" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="67"/>
+      <c r="D93" s="68"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="68"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="67" t="s">
+      <c r="A94" s="72"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="67"/>
+      <c r="D94" s="68"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="68"/>
+      <c r="G94" s="68"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="66"/>
-      <c r="B95" s="67"/>
-      <c r="C95" s="67" t="s">
+      <c r="A95" s="72"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="67"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="68"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="66"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="67" t="s">
+      <c r="A96" s="72"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="67"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="67"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="66"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="67" t="s">
+      <c r="A97" s="72"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="67"/>
+      <c r="D97" s="68"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="68"/>
+      <c r="G97" s="68"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="66"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="67" t="s">
+      <c r="A98" s="72"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="67"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="66">
+      <c r="A99" s="72">
         <v>46230</v>
       </c>
-      <c r="B99" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="67" t="s">
+      <c r="B99" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="66"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="67" t="s">
+      <c r="A100" s="72"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="67"/>
+      <c r="D100" s="68"/>
+      <c r="E100" s="68"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="68"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="66">
+      <c r="A101" s="72">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="92" t="s">
+      <c r="C101" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="92"/>
-      <c r="E101" s="92"/>
-      <c r="F101" s="92"/>
-      <c r="G101" s="92"/>
+      <c r="D101" s="78"/>
+      <c r="E101" s="78"/>
+      <c r="F101" s="78"/>
+      <c r="G101" s="78"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="66"/>
+      <c r="A102" s="72"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="92" t="s">
+      <c r="C102" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="92"/>
-      <c r="E102" s="92"/>
-      <c r="F102" s="92"/>
-      <c r="G102" s="92"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="78"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="91" t="s">
+      <c r="A103" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="81" t="s">
+      <c r="B103" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="81"/>
-      <c r="E103" s="81"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="81"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="91"/>
-      <c r="B104" s="67"/>
-      <c r="C104" s="67" t="s">
+      <c r="A104" s="76"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="91"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="67" t="s">
+      <c r="A105" s="76"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="67"/>
+      <c r="D105" s="68"/>
+      <c r="E105" s="68"/>
+      <c r="F105" s="68"/>
+      <c r="G105" s="68"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="91"/>
-      <c r="B106" s="67"/>
-      <c r="C106" s="67" t="s">
+      <c r="A106" s="76"/>
+      <c r="B106" s="68"/>
+      <c r="C106" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="67"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="67"/>
+      <c r="D106" s="68"/>
+      <c r="E106" s="68"/>
+      <c r="F106" s="68"/>
+      <c r="G106" s="68"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="91"/>
-      <c r="B107" s="67"/>
-      <c r="C107" s="67" t="s">
+      <c r="A107" s="76"/>
+      <c r="B107" s="68"/>
+      <c r="C107" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="67"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="67"/>
+      <c r="D107" s="68"/>
+      <c r="E107" s="68"/>
+      <c r="F107" s="68"/>
+      <c r="G107" s="68"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="66">
+      <c r="A108" s="72">
         <v>46234</v>
       </c>
-      <c r="B108" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="67" t="s">
+      <c r="B108" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="67"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="67"/>
-      <c r="G108" s="67"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="66"/>
-      <c r="B109" s="67"/>
-      <c r="C109" s="67" t="s">
+      <c r="A109" s="72"/>
+      <c r="B109" s="68"/>
+      <c r="C109" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="67"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="67"/>
-      <c r="G109" s="67"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="68"/>
+      <c r="F109" s="68"/>
+      <c r="G109" s="68"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2896,68 +2900,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2982,67 +2985,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3060,15 +3064,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46235</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4810,9 +4814,6 @@
       <c r="C77" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="94"/>
-      <c r="E77" s="94"/>
-      <c r="F77" s="94"/>
       <c r="G77" s="51"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4821,9 +4822,6 @@
       <c r="C78" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="D78" s="94"/>
-      <c r="E78" s="94"/>
-      <c r="F78" s="94"/>
       <c r="G78" s="51"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4832,9 +4830,6 @@
       <c r="C79" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D79" s="94"/>
-      <c r="E79" s="94"/>
-      <c r="F79" s="94"/>
       <c r="G79" s="51"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4843,9 +4838,6 @@
       <c r="C80" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="D80" s="94"/>
-      <c r="E80" s="94"/>
-      <c r="F80" s="94"/>
       <c r="G80" s="51"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4858,6 +4850,87 @@
       <c r="E81" s="49"/>
       <c r="F81" s="49"/>
       <c r="G81" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="93">
+        <v>46296</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="61"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>46298</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="46"/>
+      <c r="B4" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="94" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="51"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733F1157-0C18-4144-BF68-27D628009DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B638C2B-DD6E-4861-B5F2-10121BB446AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
@@ -807,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -963,6 +963,30 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -978,85 +1002,58 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1381,15 +1378,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="63">
+      <c r="A1" s="71">
         <v>46174</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1398,146 +1395,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="75"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46202</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68" t="s">
+      <c r="A7" s="66"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72">
+      <c r="A9" s="66">
         <v>46203</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="70"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1547,14 +1544,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1565,6 +1554,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1582,15 +1579,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46204</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1599,152 +1596,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="66">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="77" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="82">
         <v>46205</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="69" t="s">
+      <c r="A8" s="83"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="71"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="65"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="83"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="65"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
-      <c r="B10" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="69" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="91"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="83"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69" t="s">
+      <c r="A13" s="84"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="81">
+      <c r="A14" s="86">
         <v>46206</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="76" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1756,348 +1753,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="73" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="70"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="84"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="73" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="70"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="73" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="84"/>
-      <c r="B18" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="73" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="75"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="70"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="73" t="s">
+      <c r="A19" s="88"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="70"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="89">
         <v>46209</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68" t="s">
+      <c r="A21" s="89"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68" t="s">
+      <c r="A22" s="89"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
-      <c r="B23" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="68" t="s">
+      <c r="A23" s="89"/>
+      <c r="B23" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="73" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="75"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="73" t="s">
+      <c r="A25" s="89"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="75"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="70"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="73" t="s">
+      <c r="A26" s="89"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="73" t="s">
+      <c r="A27" s="89"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="75"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="73" t="s">
+      <c r="A28" s="89"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="75"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="73" t="s">
+      <c r="A29" s="89"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="73" t="s">
+      <c r="A30" s="89"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="73" t="s">
+      <c r="A31" s="89"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="73" t="s">
+      <c r="A32" s="89"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="70"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="73" t="s">
+      <c r="A33" s="89"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="70"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="73" t="s">
+      <c r="A34" s="89"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="70"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="83">
+      <c r="A35" s="85">
         <v>46210</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
-      <c r="B38" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="68" t="s">
+      <c r="A38" s="85"/>
+      <c r="B38" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68" t="s">
+      <c r="A40" s="85"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68" t="s">
+      <c r="A42" s="85"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68" t="s">
+      <c r="A43" s="85"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="73" t="s">
+      <c r="A44" s="85"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="75"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="70"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2106,13 +2103,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2121,255 +2118,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="81">
+      <c r="A47" s="86">
         <v>46213</v>
       </c>
-      <c r="B47" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="73" t="s">
+      <c r="B47" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="75"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="84"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="73" t="s">
+      <c r="A48" s="87"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="75"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="70"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="84"/>
-      <c r="B49" s="87"/>
-      <c r="C49" s="73" t="s">
+      <c r="A49" s="87"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="75"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="70"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="87"/>
-      <c r="C50" s="73" t="s">
+      <c r="A50" s="87"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="70"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="73" t="s">
+      <c r="A51" s="88"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="75"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="70"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="72">
+      <c r="A52" s="66">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="72">
+      <c r="A54" s="66">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="75"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="70"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
-      <c r="B55" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="86" t="s">
+      <c r="A55" s="66"/>
+      <c r="B55" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="86" t="s">
+      <c r="A56" s="66"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="90"/>
+      <c r="G56" s="90"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="86" t="s">
+      <c r="A57" s="66"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="86" t="s">
+      <c r="A58" s="66"/>
+      <c r="B58" s="67"/>
+      <c r="C58" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="86" t="s">
+      <c r="A59" s="66"/>
+      <c r="B59" s="67"/>
+      <c r="C59" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="86" t="s">
+      <c r="A60" s="66"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="86" t="s">
+      <c r="A61" s="66"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="86"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="90"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="86" t="s">
+      <c r="A62" s="66"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="90"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="86" t="s">
+      <c r="A63" s="66"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
+      <c r="D63" s="90"/>
+      <c r="E63" s="90"/>
+      <c r="F63" s="90"/>
+      <c r="G63" s="90"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="72">
+      <c r="A64" s="66">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="67"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
-      <c r="B65" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="68" t="s">
+      <c r="A65" s="66"/>
+      <c r="B65" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2378,164 +2375,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="72">
+      <c r="A68" s="66">
         <v>46220</v>
       </c>
-      <c r="B68" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="68" t="s">
+      <c r="B68" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68" t="s">
+      <c r="A69" s="66"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="72">
+      <c r="A70" s="66">
         <v>46223</v>
       </c>
-      <c r="B70" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="73" t="s">
+      <c r="B70" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="75"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="70"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="73" t="s">
+      <c r="A71" s="66"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="75"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="70"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="73" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="75"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="70"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="73" t="s">
+      <c r="A73" s="66"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="75"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="69"/>
+      <c r="G73" s="70"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="73" t="s">
+      <c r="A74" s="66"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="75"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="70"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="73" t="s">
+      <c r="A75" s="66"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="75"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="69"/>
+      <c r="G75" s="70"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="73" t="s">
+      <c r="A76" s="66"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="75"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="70"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="69" t="s">
+      <c r="A77" s="66"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="65"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="69" t="s">
+      <c r="A78" s="66"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="71"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="65"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="72"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="69" t="s">
+      <c r="A79" s="66"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
-      <c r="F79" s="70"/>
-      <c r="G79" s="71"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="65"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="69" t="s">
+      <c r="A80" s="66"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="71"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="65"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2544,353 +2541,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="68" t="s">
+      <c r="C81" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="72">
+      <c r="A82" s="66">
         <v>46225</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="67"/>
+      <c r="G82" s="67"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68" t="s">
+      <c r="A83" s="66"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="67"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="67"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68" t="s">
+      <c r="A84" s="66"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="67"/>
+      <c r="F84" s="67"/>
+      <c r="G84" s="67"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
-      <c r="B85" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="68" t="s">
+      <c r="A85" s="66"/>
+      <c r="B85" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="67"/>
+      <c r="G85" s="67"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68" t="s">
+      <c r="A86" s="66"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="67"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68" t="s">
+      <c r="A87" s="66"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="67"/>
+      <c r="G87" s="67"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68" t="s">
+      <c r="A88" s="66"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="67"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
-      <c r="B89" s="68"/>
-      <c r="C89" s="73" t="s">
+      <c r="A89" s="66"/>
+      <c r="B89" s="67"/>
+      <c r="C89" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="74"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="75"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
+      <c r="F89" s="69"/>
+      <c r="G89" s="70"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="72"/>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68" t="s">
+      <c r="A90" s="66"/>
+      <c r="B90" s="67"/>
+      <c r="C90" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="67"/>
+      <c r="G90" s="67"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="81">
+      <c r="A91" s="86">
         <v>46227</v>
       </c>
-      <c r="B91" s="79" t="s">
+      <c r="B91" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="67"/>
+      <c r="G91" s="67"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="82"/>
-      <c r="B92" s="80"/>
-      <c r="C92" s="73" t="s">
+      <c r="A92" s="88"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="75"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="70"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="72">
+      <c r="A93" s="66">
         <v>46228</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="68" t="s">
+      <c r="B93" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="67"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68" t="s">
+      <c r="A94" s="66"/>
+      <c r="B94" s="67"/>
+      <c r="C94" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="67"/>
+      <c r="G94" s="67"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="72"/>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68" t="s">
+      <c r="A95" s="66"/>
+      <c r="B95" s="67"/>
+      <c r="C95" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
+      <c r="F95" s="67"/>
+      <c r="G95" s="67"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="A96" s="66"/>
+      <c r="B96" s="67"/>
+      <c r="C96" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
+      <c r="D96" s="67"/>
+      <c r="E96" s="67"/>
+      <c r="F96" s="67"/>
+      <c r="G96" s="67"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="72"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="68" t="s">
+      <c r="A97" s="66"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="68"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="67"/>
+      <c r="G97" s="67"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="72"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="68" t="s">
+      <c r="A98" s="66"/>
+      <c r="B98" s="67"/>
+      <c r="C98" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="67"/>
+      <c r="G98" s="67"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="72">
+      <c r="A99" s="66">
         <v>46230</v>
       </c>
-      <c r="B99" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="68" t="s">
+      <c r="B99" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="67"/>
+      <c r="G99" s="67"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="72"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="68" t="s">
+      <c r="A100" s="66"/>
+      <c r="B100" s="67"/>
+      <c r="C100" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="68"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
+      <c r="D100" s="67"/>
+      <c r="E100" s="67"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="67"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="72">
+      <c r="A101" s="66">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="78" t="s">
+      <c r="C101" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="78"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="78"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="72"/>
+      <c r="A102" s="66"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="78" t="s">
+      <c r="C102" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="78"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="78"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="76" t="s">
+      <c r="A103" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="77" t="s">
+      <c r="B103" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="81"/>
+      <c r="F103" s="81"/>
+      <c r="G103" s="81"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
-      <c r="B104" s="68"/>
-      <c r="C104" s="68" t="s">
+      <c r="A104" s="91"/>
+      <c r="B104" s="67"/>
+      <c r="C104" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="67"/>
+      <c r="G104" s="67"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68" t="s">
+      <c r="A105" s="91"/>
+      <c r="B105" s="67"/>
+      <c r="C105" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
+      <c r="D105" s="67"/>
+      <c r="E105" s="67"/>
+      <c r="F105" s="67"/>
+      <c r="G105" s="67"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
-      <c r="B106" s="68"/>
-      <c r="C106" s="68" t="s">
+      <c r="A106" s="91"/>
+      <c r="B106" s="67"/>
+      <c r="C106" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="68"/>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
+      <c r="D106" s="67"/>
+      <c r="E106" s="67"/>
+      <c r="F106" s="67"/>
+      <c r="G106" s="67"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
-      <c r="B107" s="68"/>
-      <c r="C107" s="68" t="s">
+      <c r="A107" s="91"/>
+      <c r="B107" s="67"/>
+      <c r="C107" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
+      <c r="D107" s="67"/>
+      <c r="E107" s="67"/>
+      <c r="F107" s="67"/>
+      <c r="G107" s="67"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="72">
+      <c r="A108" s="66">
         <v>46234</v>
       </c>
-      <c r="B108" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
+      <c r="D108" s="67"/>
+      <c r="E108" s="67"/>
+      <c r="F108" s="67"/>
+      <c r="G108" s="67"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="72"/>
-      <c r="B109" s="68"/>
-      <c r="C109" s="68" t="s">
+      <c r="A109" s="66"/>
+      <c r="B109" s="67"/>
+      <c r="C109" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
+      <c r="D109" s="67"/>
+      <c r="E109" s="67"/>
+      <c r="F109" s="67"/>
+      <c r="G109" s="67"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2900,6 +2897,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2924,129 +3044,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3064,15 +3061,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="79">
         <v>46235</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4913,12 +4910,12 @@
       <c r="B4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="51"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B638C2B-DD6E-4861-B5F2-10121BB446AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1501EC5C-5A6D-4A8D-BCEA-10F62E288F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="186">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -584,6 +584,12 @@
   </si>
   <si>
     <t>Nhận linh kiện dư VNSH03 (Chưa kiểm đếm)</t>
+  </si>
+  <si>
+    <t>Nhận BH Kho VNET</t>
+  </si>
+  <si>
+    <t>Xuất kho 458 vỏ hộp RFID (old) không có ốc chưa làm phiếu</t>
   </si>
 </sst>
 </file>
@@ -807,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1054,6 +1060,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4858,7 +4874,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.140625" customWidth="1"/>
@@ -4929,6 +4945,35 @@
       <c r="F5" s="49"/>
       <c r="G5" s="50"/>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="97"/>
+      <c r="B6" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="94">
+        <v>46300</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="96" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" s="96" t="s">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1501EC5C-5A6D-4A8D-BCEA-10F62E288F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621C9CA6-10CF-4F2F-9BD1-6E58B2DC7E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView xWindow="6900" yWindow="690" windowWidth="21600" windowHeight="11835" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="187">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -590,6 +590,9 @@
   </si>
   <si>
     <t>Xuất kho 458 vỏ hộp RFID (old) không có ốc chưa làm phiếu</t>
+  </si>
+  <si>
+    <t>Nhập kho 20 LE nâng cấp 2G=4G</t>
   </si>
 </sst>
 </file>
@@ -813,7 +816,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -969,6 +972,24 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -981,9 +1002,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -993,20 +1011,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1014,6 +1026,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1023,9 +1053,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1035,43 +1062,10 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1394,15 +1388,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="71">
+      <c r="A1" s="63">
         <v>46174</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1411,146 +1405,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46202</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67" t="s">
+      <c r="A7" s="72"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="66"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="66">
+      <c r="A9" s="72">
         <v>46203</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="70"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="66"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="66"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1560,6 +1554,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1570,14 +1572,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1595,15 +1589,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46204</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1612,152 +1606,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="72">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="66"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="82">
+      <c r="A7" s="90">
         <v>46205</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="70"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="75"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="63" t="s">
+      <c r="A8" s="91"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="63" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
-      <c r="B10" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="63" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="63" t="s">
+      <c r="A13" s="92"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="81">
         <v>46206</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1769,348 +1763,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="87"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="68" t="s">
+      <c r="A15" s="84"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="75"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="68" t="s">
+      <c r="A16" s="84"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="75"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="87"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="68" t="s">
+      <c r="A17" s="84"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="75"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="87"/>
-      <c r="B18" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="68" t="s">
+      <c r="A18" s="84"/>
+      <c r="B18" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="75"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="68" t="s">
+      <c r="A19" s="82"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="70"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="75"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="89">
+      <c r="A20" s="85">
         <v>46209</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="89"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67" t="s">
+      <c r="A21" s="85"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="89"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67" t="s">
+      <c r="A22" s="85"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="89"/>
-      <c r="B23" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="67" t="s">
+      <c r="A23" s="85"/>
+      <c r="B23" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="89"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="68" t="s">
+      <c r="A24" s="85"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="75"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="89"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="68" t="s">
+      <c r="A25" s="85"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="75"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="89"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="68" t="s">
+      <c r="A26" s="85"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="75"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="89"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="68" t="s">
+      <c r="A27" s="85"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="70"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="75"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="89"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="68" t="s">
+      <c r="A28" s="85"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="70"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="75"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="89"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="68" t="s">
+      <c r="A29" s="85"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="75"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="89"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="68" t="s">
+      <c r="A30" s="85"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="70"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="75"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="68" t="s">
+      <c r="A31" s="85"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="75"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="68" t="s">
+      <c r="A32" s="85"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="70"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="68" t="s">
+      <c r="A33" s="85"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="70"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="89"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="68" t="s">
+      <c r="A34" s="85"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="85">
+      <c r="A35" s="83">
         <v>46210</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67" t="s">
+      <c r="A36" s="83"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67" t="s">
+      <c r="A37" s="83"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
-      <c r="B38" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="67" t="s">
+      <c r="A38" s="83"/>
+      <c r="B38" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="85"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67" t="s">
+      <c r="A39" s="83"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67" t="s">
+      <c r="A40" s="83"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67" t="s">
+      <c r="A41" s="83"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67" t="s">
+      <c r="A42" s="83"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67" t="s">
+      <c r="A43" s="83"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="68" t="s">
+      <c r="A44" s="83"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="70"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="75"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2119,13 +2113,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="C45" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2134,255 +2128,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="86">
+      <c r="A47" s="81">
         <v>46213</v>
       </c>
-      <c r="B47" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="68" t="s">
+      <c r="B47" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="70"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="75"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="87"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="68" t="s">
+      <c r="A48" s="84"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="70"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="75"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="68" t="s">
+      <c r="A49" s="84"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="70"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="75"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="68" t="s">
+      <c r="A50" s="84"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="70"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="75"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="88"/>
-      <c r="B51" s="77"/>
-      <c r="C51" s="68" t="s">
+      <c r="A51" s="82"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="69"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="70"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="75"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="66">
+      <c r="A52" s="72">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="C52" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="68"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="72"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="68"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="66">
+      <c r="A54" s="72">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="69"/>
-      <c r="E54" s="69"/>
-      <c r="F54" s="69"/>
-      <c r="G54" s="70"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="75"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="66"/>
-      <c r="B55" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="90" t="s">
+      <c r="A55" s="72"/>
+      <c r="B55" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="66"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="90" t="s">
+      <c r="A56" s="72"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="90"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
+      <c r="F56" s="86"/>
+      <c r="G56" s="86"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="66"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="90" t="s">
+      <c r="A57" s="72"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="90"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="66"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="90" t="s">
+      <c r="A58" s="72"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="90"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="66"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="90" t="s">
+      <c r="A59" s="72"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="86"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="66"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="90" t="s">
+      <c r="A60" s="72"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
+      <c r="D60" s="86"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="86"/>
+      <c r="G60" s="86"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="90" t="s">
+      <c r="A61" s="72"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="90"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="86"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="66"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="90" t="s">
+      <c r="A62" s="72"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="90"/>
+      <c r="D62" s="86"/>
+      <c r="E62" s="86"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="86"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="90" t="s">
+      <c r="A63" s="72"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="90"/>
-      <c r="E63" s="90"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="90"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="86"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="86"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="66">
+      <c r="A64" s="72">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="67" t="s">
+      <c r="C64" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="68"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
-      <c r="B65" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="67" t="s">
+      <c r="A65" s="72"/>
+      <c r="B65" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="68"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67" t="s">
+      <c r="A66" s="72"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="68"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2391,164 +2385,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="67" t="s">
+      <c r="C67" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="66">
+      <c r="A68" s="72">
         <v>46220</v>
       </c>
-      <c r="B68" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="67" t="s">
+      <c r="B68" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="A69" s="72"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="66">
+      <c r="A70" s="72">
         <v>46223</v>
       </c>
-      <c r="B70" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="68" t="s">
+      <c r="B70" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="70"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="75"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="68" t="s">
+      <c r="A71" s="72"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="70"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="75"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="68" t="s">
+      <c r="A72" s="72"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="70"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="75"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="68" t="s">
+      <c r="A73" s="72"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="69"/>
-      <c r="F73" s="69"/>
-      <c r="G73" s="70"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="75"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="68" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="70"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="75"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="68" t="s">
+      <c r="A75" s="72"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="70"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="75"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="68" t="s">
+      <c r="A76" s="72"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="69"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="70"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="75"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="66"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="63" t="s">
+      <c r="A77" s="72"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="65"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="71"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="66"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="63" t="s">
+      <c r="A78" s="72"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="65"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="71"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="63" t="s">
+      <c r="A79" s="72"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="65"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="71"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="63" t="s">
+      <c r="A80" s="72"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="65"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="71"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2557,353 +2551,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="67" t="s">
+      <c r="C81" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="68"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="66">
+      <c r="A82" s="72">
         <v>46225</v>
       </c>
-      <c r="B82" s="67" t="s">
+      <c r="B82" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="68"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="66"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="67" t="s">
+      <c r="A83" s="72"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="67"/>
+      <c r="D83" s="68"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="68"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="67" t="s">
+      <c r="A84" s="72"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="67"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="67"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="68"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
-      <c r="B85" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="67" t="s">
+      <c r="A85" s="72"/>
+      <c r="B85" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="67"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67" t="s">
+      <c r="A86" s="72"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="67"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="68"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="66"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67" t="s">
+      <c r="A87" s="72"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="68" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="66"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="67" t="s">
+      <c r="A88" s="72"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="67"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
+      <c r="D88" s="68"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="66"/>
-      <c r="B89" s="67"/>
-      <c r="C89" s="68" t="s">
+      <c r="A89" s="72"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="70"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="74"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="75"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="66"/>
-      <c r="B90" s="67"/>
-      <c r="C90" s="67" t="s">
+      <c r="A90" s="72"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
+      <c r="D90" s="68"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="68"/>
+      <c r="G90" s="68"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="86">
+      <c r="A91" s="81">
         <v>46227</v>
       </c>
-      <c r="B91" s="76" t="s">
+      <c r="B91" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="88"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="68" t="s">
+      <c r="A92" s="82"/>
+      <c r="B92" s="80"/>
+      <c r="C92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="69"/>
-      <c r="E92" s="69"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="70"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="74"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="75"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="66">
+      <c r="A93" s="72">
         <v>46228</v>
       </c>
-      <c r="B93" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="67" t="s">
+      <c r="B93" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="67"/>
+      <c r="D93" s="68"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="68"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
-      <c r="B94" s="67"/>
-      <c r="C94" s="67" t="s">
+      <c r="A94" s="72"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="67"/>
+      <c r="D94" s="68"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="68"/>
+      <c r="G94" s="68"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="66"/>
-      <c r="B95" s="67"/>
-      <c r="C95" s="67" t="s">
+      <c r="A95" s="72"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="67"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="68"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="66"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="67" t="s">
+      <c r="A96" s="72"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="67"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="67"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="66"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="67" t="s">
+      <c r="A97" s="72"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="67"/>
+      <c r="D97" s="68"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="68"/>
+      <c r="G97" s="68"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="66"/>
-      <c r="B98" s="67"/>
-      <c r="C98" s="67" t="s">
+      <c r="A98" s="72"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="67"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="66">
+      <c r="A99" s="72">
         <v>46230</v>
       </c>
-      <c r="B99" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="67" t="s">
+      <c r="B99" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="66"/>
-      <c r="B100" s="67"/>
-      <c r="C100" s="67" t="s">
+      <c r="A100" s="72"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="67"/>
+      <c r="D100" s="68"/>
+      <c r="E100" s="68"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="68"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="66">
+      <c r="A101" s="72">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="92" t="s">
+      <c r="C101" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="92"/>
-      <c r="E101" s="92"/>
-      <c r="F101" s="92"/>
-      <c r="G101" s="92"/>
+      <c r="D101" s="78"/>
+      <c r="E101" s="78"/>
+      <c r="F101" s="78"/>
+      <c r="G101" s="78"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="66"/>
+      <c r="A102" s="72"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="92" t="s">
+      <c r="C102" s="78" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="92"/>
-      <c r="E102" s="92"/>
-      <c r="F102" s="92"/>
-      <c r="G102" s="92"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="78"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="91" t="s">
+      <c r="A103" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="81" t="s">
+      <c r="B103" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="81"/>
-      <c r="E103" s="81"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="81"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="91"/>
-      <c r="B104" s="67"/>
-      <c r="C104" s="67" t="s">
+      <c r="A104" s="76"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="91"/>
-      <c r="B105" s="67"/>
-      <c r="C105" s="67" t="s">
+      <c r="A105" s="76"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="67"/>
+      <c r="D105" s="68"/>
+      <c r="E105" s="68"/>
+      <c r="F105" s="68"/>
+      <c r="G105" s="68"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="91"/>
-      <c r="B106" s="67"/>
-      <c r="C106" s="67" t="s">
+      <c r="A106" s="76"/>
+      <c r="B106" s="68"/>
+      <c r="C106" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="67"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="67"/>
+      <c r="D106" s="68"/>
+      <c r="E106" s="68"/>
+      <c r="F106" s="68"/>
+      <c r="G106" s="68"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="91"/>
-      <c r="B107" s="67"/>
-      <c r="C107" s="67" t="s">
+      <c r="A107" s="76"/>
+      <c r="B107" s="68"/>
+      <c r="C107" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="67"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="67"/>
+      <c r="D107" s="68"/>
+      <c r="E107" s="68"/>
+      <c r="F107" s="68"/>
+      <c r="G107" s="68"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="66">
+      <c r="A108" s="72">
         <v>46234</v>
       </c>
-      <c r="B108" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="67" t="s">
+      <c r="B108" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="67"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="67"/>
-      <c r="G108" s="67"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="66"/>
-      <c r="B109" s="67"/>
-      <c r="C109" s="67" t="s">
+      <c r="A109" s="72"/>
+      <c r="B109" s="68"/>
+      <c r="C109" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="67"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="67"/>
-      <c r="G109" s="67"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="68"/>
+      <c r="F109" s="68"/>
+      <c r="G109" s="68"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2913,68 +2907,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2999,67 +2992,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3077,15 +3071,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="79">
+      <c r="A1" s="88">
         <v>46235</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4874,10 +4868,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4946,33 +4942,54 @@
       <c r="G5" s="50"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="97"/>
-      <c r="B6" s="46" t="s">
+      <c r="A6" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="97" t="s">
+      <c r="C6" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="48"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="46"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="94">
-        <v>46300</v>
-      </c>
-      <c r="B7" s="95" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="96" t="s">
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="50"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="94"/>
+      <c r="B8" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C8" s="96" t="s">
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="35"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="26" t="s">
         <v>184</v>
       </c>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621C9CA6-10CF-4F2F-9BD1-6E58B2DC7E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DC7CE6-4F93-4516-B48B-467FFB5BBD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="690" windowWidth="21600" windowHeight="11835" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="189">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -593,6 +593,12 @@
   </si>
   <si>
     <t>Nhập kho 20 LE nâng cấp 2G=4G</t>
+  </si>
+  <si>
+    <t>Xuất kho 2000 Tem LE, 1000 vỏ nhôm (vỏ nhôm đã giao qua gia công VNSH03 từ trước)</t>
+  </si>
+  <si>
+    <t>Nhận BH Lắp Đặt</t>
   </si>
 </sst>
 </file>
@@ -816,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -972,6 +978,31 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -987,85 +1018,69 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1388,15 +1403,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="63">
+      <c r="A1" s="72">
         <v>46174</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1405,16 +1420,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="76"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="67">
         <v>46202</v>
       </c>
       <c r="B3" s="68" t="s">
@@ -1429,7 +1444,7 @@
       <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="67"/>
       <c r="B4" s="68"/>
       <c r="C4" s="68" t="s">
         <v>0</v>
@@ -1440,7 +1455,7 @@
       <c r="G4" s="68"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="67"/>
       <c r="B5" s="68"/>
       <c r="C5" s="68" t="s">
         <v>3</v>
@@ -1451,7 +1466,7 @@
       <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="68" t="s">
         <v>4</v>
       </c>
@@ -1464,7 +1479,7 @@
       <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="67"/>
       <c r="B7" s="68"/>
       <c r="C7" s="68" t="s">
         <v>10</v>
@@ -1475,7 +1490,7 @@
       <c r="G7" s="68"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="68"/>
       <c r="C8" s="68" t="s">
         <v>9</v>
@@ -1486,65 +1501,65 @@
       <c r="G8" s="68"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72">
+      <c r="A9" s="67">
         <v>46203</v>
       </c>
       <c r="B9" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="68"/>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
+      <c r="A11" s="67"/>
       <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="66"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="66"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1554,14 +1569,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1572,6 +1579,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1589,15 +1604,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="80">
         <v>46204</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1606,16 +1621,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72">
+      <c r="A3" s="67">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1630,20 +1645,20 @@
       <c r="G3" s="68"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
+      <c r="A4" s="67"/>
       <c r="B4" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="77" t="s">
+      <c r="C4" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="67"/>
       <c r="B5" s="68"/>
       <c r="C5" s="68" t="s">
         <v>17</v>
@@ -1654,7 +1669,7 @@
       <c r="G5" s="68"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="68"/>
       <c r="C6" s="68" t="s">
         <v>18</v>
@@ -1665,93 +1680,93 @@
       <c r="G6" s="68"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="83">
         <v>46205</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="71"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="69" t="s">
+      <c r="A8" s="84"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="71"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="69" t="s">
+      <c r="A9" s="84"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
+      <c r="A10" s="84"/>
       <c r="B10" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="91"/>
+      <c r="A11" s="84"/>
       <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="66"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
+      <c r="A12" s="84"/>
       <c r="B12" s="68"/>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="66"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="66"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="81">
+      <c r="A14" s="87">
         <v>46206</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="77" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1763,64 +1778,64 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="84"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="73" t="s">
+      <c r="A15" s="88"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="71"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="84"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="73" t="s">
+      <c r="A16" s="88"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="71"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="84"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="73" t="s">
+      <c r="A17" s="88"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="71"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="84"/>
-      <c r="B18" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="73" t="s">
+      <c r="A18" s="88"/>
+      <c r="B18" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="75"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="71"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="73" t="s">
+      <c r="A19" s="89"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="71"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="90">
         <v>46209</v>
       </c>
       <c r="B20" s="68" t="s">
@@ -1835,7 +1850,7 @@
       <c r="G20" s="68"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
+      <c r="A21" s="90"/>
       <c r="B21" s="68"/>
       <c r="C21" s="68" t="s">
         <v>34</v>
@@ -1846,7 +1861,7 @@
       <c r="G21" s="68"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
+      <c r="A22" s="90"/>
       <c r="B22" s="68"/>
       <c r="C22" s="68" t="s">
         <v>15</v>
@@ -1857,7 +1872,7 @@
       <c r="G22" s="68"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
+      <c r="A23" s="90"/>
       <c r="B23" s="68" t="s">
         <v>4</v>
       </c>
@@ -1870,128 +1885,128 @@
       <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
+      <c r="A24" s="90"/>
       <c r="B24" s="68"/>
-      <c r="C24" s="73" t="s">
+      <c r="C24" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="75"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="71"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
+      <c r="A25" s="90"/>
       <c r="B25" s="68"/>
-      <c r="C25" s="73" t="s">
+      <c r="C25" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="75"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="71"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
+      <c r="A26" s="90"/>
       <c r="B26" s="68"/>
-      <c r="C26" s="73" t="s">
+      <c r="C26" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="71"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
+      <c r="A27" s="90"/>
       <c r="B27" s="68"/>
-      <c r="C27" s="73" t="s">
+      <c r="C27" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="75"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="71"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="68"/>
-      <c r="C28" s="73" t="s">
+      <c r="C28" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="75"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="71"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
+      <c r="A29" s="90"/>
       <c r="B29" s="68"/>
-      <c r="C29" s="73" t="s">
+      <c r="C29" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="71"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
+      <c r="A30" s="90"/>
       <c r="B30" s="68"/>
-      <c r="C30" s="73" t="s">
+      <c r="C30" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="71"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
+      <c r="A31" s="90"/>
       <c r="B31" s="68"/>
-      <c r="C31" s="73" t="s">
+      <c r="C31" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="71"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="68"/>
-      <c r="C32" s="73" t="s">
+      <c r="C32" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="71"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
+      <c r="A33" s="90"/>
       <c r="B33" s="68"/>
-      <c r="C33" s="73" t="s">
+      <c r="C33" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="71"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="68"/>
-      <c r="C34" s="73" t="s">
+      <c r="C34" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="71"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="83">
+      <c r="A35" s="86">
         <v>46210</v>
       </c>
       <c r="B35" s="68" t="s">
@@ -2006,7 +2021,7 @@
       <c r="G35" s="68"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
+      <c r="A36" s="86"/>
       <c r="B36" s="68"/>
       <c r="C36" s="68" t="s">
         <v>27</v>
@@ -2017,7 +2032,7 @@
       <c r="G36" s="68"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
+      <c r="A37" s="86"/>
       <c r="B37" s="68"/>
       <c r="C37" s="68" t="s">
         <v>47</v>
@@ -2028,7 +2043,7 @@
       <c r="G37" s="68"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
+      <c r="A38" s="86"/>
       <c r="B38" s="68" t="s">
         <v>4</v>
       </c>
@@ -2041,7 +2056,7 @@
       <c r="G38" s="68"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
+      <c r="A39" s="86"/>
       <c r="B39" s="68"/>
       <c r="C39" s="68" t="s">
         <v>53</v>
@@ -2052,7 +2067,7 @@
       <c r="G39" s="68"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
+      <c r="A40" s="86"/>
       <c r="B40" s="68"/>
       <c r="C40" s="68" t="s">
         <v>48</v>
@@ -2063,7 +2078,7 @@
       <c r="G40" s="68"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
+      <c r="A41" s="86"/>
       <c r="B41" s="68"/>
       <c r="C41" s="68" t="s">
         <v>49</v>
@@ -2074,7 +2089,7 @@
       <c r="G41" s="68"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
+      <c r="A42" s="86"/>
       <c r="B42" s="68"/>
       <c r="C42" s="68" t="s">
         <v>50</v>
@@ -2085,7 +2100,7 @@
       <c r="G42" s="68"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
+      <c r="A43" s="86"/>
       <c r="B43" s="68"/>
       <c r="C43" s="68" t="s">
         <v>51</v>
@@ -2096,15 +2111,15 @@
       <c r="G43" s="68"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
+      <c r="A44" s="86"/>
       <c r="B44" s="68"/>
-      <c r="C44" s="73" t="s">
+      <c r="C44" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="75"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="71"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2137,66 +2152,66 @@
       <c r="G46" s="68"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="81">
+      <c r="A47" s="87">
         <v>46213</v>
       </c>
-      <c r="B47" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="73" t="s">
+      <c r="B47" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="75"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="71"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="84"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="73" t="s">
+      <c r="A48" s="88"/>
+      <c r="B48" s="79"/>
+      <c r="C48" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="75"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="71"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="84"/>
-      <c r="B49" s="87"/>
-      <c r="C49" s="73" t="s">
+      <c r="A49" s="88"/>
+      <c r="B49" s="79"/>
+      <c r="C49" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="75"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="71"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="87"/>
-      <c r="C50" s="73" t="s">
+      <c r="A50" s="88"/>
+      <c r="B50" s="79"/>
+      <c r="C50" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="75"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="71"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="73" t="s">
+      <c r="A51" s="89"/>
+      <c r="B51" s="78"/>
+      <c r="C51" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="75"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="71"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="72">
+      <c r="A52" s="67">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2211,7 +2226,7 @@
       <c r="G52" s="68"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="67"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
@@ -2224,123 +2239,123 @@
       <c r="G53" s="68"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="72">
+      <c r="A54" s="67">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="75"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="71"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
+      <c r="A55" s="67"/>
       <c r="B55" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="86" t="s">
+      <c r="C55" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
+      <c r="D55" s="91"/>
+      <c r="E55" s="91"/>
+      <c r="F55" s="91"/>
+      <c r="G55" s="91"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
+      <c r="A56" s="67"/>
       <c r="B56" s="68"/>
-      <c r="C56" s="86" t="s">
+      <c r="C56" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
+      <c r="D56" s="91"/>
+      <c r="E56" s="91"/>
+      <c r="F56" s="91"/>
+      <c r="G56" s="91"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
+      <c r="A57" s="67"/>
       <c r="B57" s="68"/>
-      <c r="C57" s="86" t="s">
+      <c r="C57" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
+      <c r="D57" s="91"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="91"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
+      <c r="A58" s="67"/>
       <c r="B58" s="68"/>
-      <c r="C58" s="86" t="s">
+      <c r="C58" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
+      <c r="D58" s="91"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="91"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
+      <c r="A59" s="67"/>
       <c r="B59" s="68"/>
-      <c r="C59" s="86" t="s">
+      <c r="C59" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
+      <c r="D59" s="91"/>
+      <c r="E59" s="91"/>
+      <c r="F59" s="91"/>
+      <c r="G59" s="91"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
+      <c r="A60" s="67"/>
       <c r="B60" s="68"/>
-      <c r="C60" s="86" t="s">
+      <c r="C60" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
+      <c r="D60" s="91"/>
+      <c r="E60" s="91"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="91"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
+      <c r="A61" s="67"/>
       <c r="B61" s="68"/>
-      <c r="C61" s="86" t="s">
+      <c r="C61" s="91" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="86"/>
+      <c r="D61" s="91"/>
+      <c r="E61" s="91"/>
+      <c r="F61" s="91"/>
+      <c r="G61" s="91"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
+      <c r="A62" s="67"/>
       <c r="B62" s="68"/>
-      <c r="C62" s="86" t="s">
+      <c r="C62" s="91" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
+      <c r="D62" s="91"/>
+      <c r="E62" s="91"/>
+      <c r="F62" s="91"/>
+      <c r="G62" s="91"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
+      <c r="A63" s="67"/>
       <c r="B63" s="68"/>
-      <c r="C63" s="86" t="s">
+      <c r="C63" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="86"/>
-      <c r="E63" s="86"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
+      <c r="F63" s="91"/>
+      <c r="G63" s="91"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="72">
+      <c r="A64" s="67">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -2355,7 +2370,7 @@
       <c r="G64" s="68"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
+      <c r="A65" s="67"/>
       <c r="B65" s="68" t="s">
         <v>4</v>
       </c>
@@ -2368,7 +2383,7 @@
       <c r="G65" s="68"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
+      <c r="A66" s="67"/>
       <c r="B66" s="68"/>
       <c r="C66" s="68" t="s">
         <v>74</v>
@@ -2394,7 +2409,7 @@
       <c r="G67" s="68"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="72">
+      <c r="A68" s="67">
         <v>46220</v>
       </c>
       <c r="B68" s="68" t="s">
@@ -2409,7 +2424,7 @@
       <c r="G68" s="68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
+      <c r="A69" s="67"/>
       <c r="B69" s="68"/>
       <c r="C69" s="68" t="s">
         <v>77</v>
@@ -2420,129 +2435,129 @@
       <c r="G69" s="68"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="72">
+      <c r="A70" s="67">
         <v>46223</v>
       </c>
       <c r="B70" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="73" t="s">
+      <c r="C70" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="75"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="70"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="71"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
+      <c r="A71" s="67"/>
       <c r="B71" s="68"/>
-      <c r="C71" s="73" t="s">
+      <c r="C71" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="75"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="71"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
+      <c r="A72" s="67"/>
       <c r="B72" s="68"/>
-      <c r="C72" s="73" t="s">
+      <c r="C72" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="75"/>
+      <c r="D72" s="70"/>
+      <c r="E72" s="70"/>
+      <c r="F72" s="70"/>
+      <c r="G72" s="71"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
+      <c r="A73" s="67"/>
       <c r="B73" s="68"/>
-      <c r="C73" s="73" t="s">
+      <c r="C73" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="75"/>
+      <c r="D73" s="70"/>
+      <c r="E73" s="70"/>
+      <c r="F73" s="70"/>
+      <c r="G73" s="71"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
+      <c r="A74" s="67"/>
       <c r="B74" s="68"/>
-      <c r="C74" s="73" t="s">
+      <c r="C74" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="75"/>
+      <c r="D74" s="70"/>
+      <c r="E74" s="70"/>
+      <c r="F74" s="70"/>
+      <c r="G74" s="71"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
+      <c r="A75" s="67"/>
       <c r="B75" s="68"/>
-      <c r="C75" s="73" t="s">
+      <c r="C75" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="75"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="71"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
+      <c r="A76" s="67"/>
       <c r="B76" s="68"/>
-      <c r="C76" s="73" t="s">
+      <c r="C76" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="75"/>
+      <c r="D76" s="70"/>
+      <c r="E76" s="70"/>
+      <c r="F76" s="70"/>
+      <c r="G76" s="71"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
+      <c r="A77" s="67"/>
       <c r="B77" s="68"/>
-      <c r="C77" s="69" t="s">
+      <c r="C77" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
+      <c r="D77" s="65"/>
+      <c r="E77" s="65"/>
+      <c r="F77" s="65"/>
+      <c r="G77" s="66"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
+      <c r="A78" s="67"/>
       <c r="B78" s="68"/>
-      <c r="C78" s="69" t="s">
+      <c r="C78" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="71"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="66"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="72"/>
+      <c r="A79" s="67"/>
       <c r="B79" s="68"/>
-      <c r="C79" s="69" t="s">
+      <c r="C79" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
-      <c r="F79" s="70"/>
-      <c r="G79" s="71"/>
+      <c r="D79" s="65"/>
+      <c r="E79" s="65"/>
+      <c r="F79" s="65"/>
+      <c r="G79" s="66"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
+      <c r="A80" s="67"/>
       <c r="B80" s="68"/>
-      <c r="C80" s="69" t="s">
+      <c r="C80" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="70"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="71"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="66"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2560,7 +2575,7 @@
       <c r="G81" s="68"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="72">
+      <c r="A82" s="67">
         <v>46225</v>
       </c>
       <c r="B82" s="68" t="s">
@@ -2575,7 +2590,7 @@
       <c r="G82" s="68"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
+      <c r="A83" s="67"/>
       <c r="B83" s="68"/>
       <c r="C83" s="68" t="s">
         <v>90</v>
@@ -2586,7 +2601,7 @@
       <c r="G83" s="68"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
+      <c r="A84" s="67"/>
       <c r="B84" s="68"/>
       <c r="C84" s="68" t="s">
         <v>93</v>
@@ -2597,7 +2612,7 @@
       <c r="G84" s="68"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
+      <c r="A85" s="67"/>
       <c r="B85" s="68" t="s">
         <v>4</v>
       </c>
@@ -2610,7 +2625,7 @@
       <c r="G85" s="68"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
+      <c r="A86" s="67"/>
       <c r="B86" s="68"/>
       <c r="C86" s="68" t="s">
         <v>72</v>
@@ -2621,7 +2636,7 @@
       <c r="G86" s="68"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
+      <c r="A87" s="67"/>
       <c r="B87" s="68"/>
       <c r="C87" s="68" t="s">
         <v>89</v>
@@ -2632,7 +2647,7 @@
       <c r="G87" s="68"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
+      <c r="A88" s="67"/>
       <c r="B88" s="68"/>
       <c r="C88" s="68" t="s">
         <v>35</v>
@@ -2643,18 +2658,18 @@
       <c r="G88" s="68"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
+      <c r="A89" s="67"/>
       <c r="B89" s="68"/>
-      <c r="C89" s="73" t="s">
+      <c r="C89" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="74"/>
-      <c r="E89" s="74"/>
-      <c r="F89" s="74"/>
-      <c r="G89" s="75"/>
+      <c r="D89" s="70"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="70"/>
+      <c r="G89" s="71"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="72"/>
+      <c r="A90" s="67"/>
       <c r="B90" s="68"/>
       <c r="C90" s="68" t="s">
         <v>92</v>
@@ -2665,10 +2680,10 @@
       <c r="G90" s="68"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="81">
+      <c r="A91" s="87">
         <v>46227</v>
       </c>
-      <c r="B91" s="79" t="s">
+      <c r="B91" s="77" t="s">
         <v>5</v>
       </c>
       <c r="C91" s="68" t="s">
@@ -2680,18 +2695,18 @@
       <c r="G91" s="68"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="82"/>
-      <c r="B92" s="80"/>
-      <c r="C92" s="73" t="s">
+      <c r="A92" s="89"/>
+      <c r="B92" s="78"/>
+      <c r="C92" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="75"/>
+      <c r="D92" s="70"/>
+      <c r="E92" s="70"/>
+      <c r="F92" s="70"/>
+      <c r="G92" s="71"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="72">
+      <c r="A93" s="67">
         <v>46228</v>
       </c>
       <c r="B93" s="68" t="s">
@@ -2706,7 +2721,7 @@
       <c r="G93" s="68"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
+      <c r="A94" s="67"/>
       <c r="B94" s="68"/>
       <c r="C94" s="68" t="s">
         <v>97</v>
@@ -2717,7 +2732,7 @@
       <c r="G94" s="68"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="72"/>
+      <c r="A95" s="67"/>
       <c r="B95" s="68"/>
       <c r="C95" s="68" t="s">
         <v>98</v>
@@ -2728,7 +2743,7 @@
       <c r="G95" s="68"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
+      <c r="A96" s="67"/>
       <c r="B96" s="68"/>
       <c r="C96" s="68" t="s">
         <v>99</v>
@@ -2739,7 +2754,7 @@
       <c r="G96" s="68"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="72"/>
+      <c r="A97" s="67"/>
       <c r="B97" s="68"/>
       <c r="C97" s="68" t="s">
         <v>100</v>
@@ -2750,7 +2765,7 @@
       <c r="G97" s="68"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="72"/>
+      <c r="A98" s="67"/>
       <c r="B98" s="68"/>
       <c r="C98" s="68" t="s">
         <v>101</v>
@@ -2761,7 +2776,7 @@
       <c r="G98" s="68"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="72">
+      <c r="A99" s="67">
         <v>46230</v>
       </c>
       <c r="B99" s="68" t="s">
@@ -2776,7 +2791,7 @@
       <c r="G99" s="68"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="72"/>
+      <c r="A100" s="67"/>
       <c r="B100" s="68"/>
       <c r="C100" s="68" t="s">
         <v>39</v>
@@ -2787,50 +2802,50 @@
       <c r="G100" s="68"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="72">
+      <c r="A101" s="67">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="78" t="s">
+      <c r="C101" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="78"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="78"/>
+      <c r="D101" s="93"/>
+      <c r="E101" s="93"/>
+      <c r="F101" s="93"/>
+      <c r="G101" s="93"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="72"/>
+      <c r="A102" s="67"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="78" t="s">
+      <c r="C102" s="93" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="78"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="78"/>
+      <c r="D102" s="93"/>
+      <c r="E102" s="93"/>
+      <c r="F102" s="93"/>
+      <c r="G102" s="93"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="76" t="s">
+      <c r="A103" s="92" t="s">
         <v>105</v>
       </c>
       <c r="B103" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="77" t="s">
+      <c r="C103" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
+      <c r="D103" s="82"/>
+      <c r="E103" s="82"/>
+      <c r="F103" s="82"/>
+      <c r="G103" s="82"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
+      <c r="A104" s="92"/>
       <c r="B104" s="68"/>
       <c r="C104" s="68" t="s">
         <v>86</v>
@@ -2841,7 +2856,7 @@
       <c r="G104" s="68"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
+      <c r="A105" s="92"/>
       <c r="B105" s="68"/>
       <c r="C105" s="68" t="s">
         <v>60</v>
@@ -2852,7 +2867,7 @@
       <c r="G105" s="68"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
+      <c r="A106" s="92"/>
       <c r="B106" s="68"/>
       <c r="C106" s="68" t="s">
         <v>50</v>
@@ -2863,7 +2878,7 @@
       <c r="G106" s="68"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
+      <c r="A107" s="92"/>
       <c r="B107" s="68"/>
       <c r="C107" s="68" t="s">
         <v>107</v>
@@ -2874,7 +2889,7 @@
       <c r="G107" s="68"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="72">
+      <c r="A108" s="67">
         <v>46234</v>
       </c>
       <c r="B108" s="68" t="s">
@@ -2889,7 +2904,7 @@
       <c r="G108" s="68"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="72"/>
+      <c r="A109" s="67"/>
       <c r="B109" s="68"/>
       <c r="C109" s="68" t="s">
         <v>39</v>
@@ -2907,6 +2922,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2931,129 +3069,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3071,15 +3086,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="88">
+      <c r="A1" s="80">
         <v>46235</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4021,15 +4036,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="94">
         <v>46266</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4868,7 +4883,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4877,15 +4892,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="94">
         <v>46296</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4968,7 +4983,7 @@
       <c r="G7" s="50"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="94"/>
+      <c r="A8" s="63"/>
       <c r="B8" s="44" t="s">
         <v>4</v>
       </c>
@@ -4981,7 +4996,7 @@
       <c r="G8" s="35"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="42"/>
+      <c r="A9" s="41"/>
       <c r="B9" s="42"/>
       <c r="C9" s="26" t="s">
         <v>184</v>
@@ -4990,6 +5005,34 @@
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
       <c r="G9" s="40"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>46301</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="96" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="54"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="98"/>
+      <c r="B11" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="96" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="95"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DC7CE6-4F93-4516-B48B-467FFB5BBD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114767ED-9E08-47E6-A7D3-3B39B1EED21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="190">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -599,6 +599,9 @@
   </si>
   <si>
     <t>Nhận BH Lắp Đặt</t>
+  </si>
+  <si>
+    <t>Trả BH KhoVNET</t>
   </si>
 </sst>
 </file>
@@ -822,7 +825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -979,6 +982,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -991,9 +1015,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1003,20 +1024,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1024,6 +1039,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1033,9 +1066,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1045,40 +1075,19 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1403,15 +1412,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="72">
+      <c r="A1" s="67">
         <v>46174</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1420,146 +1429,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="76"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="71"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="67">
+      <c r="A3" s="76">
         <v>46202</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68" t="s">
+      <c r="A4" s="76"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="67"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="76"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="76"/>
+      <c r="B6" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68" t="s">
+      <c r="A7" s="76"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="67"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68" t="s">
+      <c r="A8" s="76"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="67">
+      <c r="A9" s="76">
         <v>46203</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="79"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="67"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="64" t="s">
+      <c r="A10" s="76"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="66"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="75"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="67"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="64" t="s">
+      <c r="A11" s="76"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="66"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="75"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="67"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="64" t="s">
+      <c r="A12" s="76"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="66"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="75"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="67"/>
+      <c r="A13" s="76"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="64" t="s">
+      <c r="C13" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="66"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="75"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1569,6 +1578,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1579,14 +1596,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1604,15 +1613,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="80">
+      <c r="A1" s="92">
         <v>46204</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1621,152 +1630,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="67">
+      <c r="A3" s="76">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="82" t="s">
+      <c r="A4" s="76"/>
+      <c r="B4" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="67"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68" t="s">
+      <c r="A5" s="76"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="76"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="83">
+      <c r="A7" s="94">
         <v>46205</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="71"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="79"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="84"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="64" t="s">
+      <c r="A8" s="95"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="66"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="75"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="84"/>
-      <c r="B9" s="78"/>
-      <c r="C9" s="64" t="s">
+      <c r="A9" s="95"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="66"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="84"/>
-      <c r="B10" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="64" t="s">
+      <c r="A10" s="95"/>
+      <c r="B10" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="66"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="75"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="84"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="64" t="s">
+      <c r="A11" s="95"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="66"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="75"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="84"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="64" t="s">
+      <c r="A12" s="95"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="66"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="75"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="85"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="64" t="s">
+      <c r="A13" s="96"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="66"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="75"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="87">
+      <c r="A14" s="85">
         <v>46206</v>
       </c>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="83" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1779,347 +1788,347 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="88"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="69" t="s">
+      <c r="B15" s="91"/>
+      <c r="C15" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="71"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="79"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="88"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="69" t="s">
+      <c r="B16" s="91"/>
+      <c r="C16" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="71"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="79"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="88"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="69" t="s">
+      <c r="B17" s="84"/>
+      <c r="C17" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="71"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="79"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="88"/>
-      <c r="B18" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="69" t="s">
+      <c r="B18" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="71"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="79"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="89"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="69" t="s">
+      <c r="A19" s="86"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="71"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="79"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="90">
+      <c r="A20" s="89">
         <v>46209</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="90"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68" t="s">
+      <c r="A21" s="89"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="90"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68" t="s">
+      <c r="A22" s="89"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="90"/>
-      <c r="B23" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="68" t="s">
+      <c r="A23" s="89"/>
+      <c r="B23" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="90"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="69" t="s">
+      <c r="A24" s="89"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="71"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="79"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="90"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="69" t="s">
+      <c r="A25" s="89"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="71"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="78"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="79"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="90"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="69" t="s">
+      <c r="A26" s="89"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="71"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="79"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="90"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="69" t="s">
+      <c r="A27" s="89"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="71"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="79"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="90"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="69" t="s">
+      <c r="A28" s="89"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="71"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="78"/>
+      <c r="G28" s="79"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="90"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="69" t="s">
+      <c r="A29" s="89"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="71"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="79"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="90"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="69" t="s">
+      <c r="A30" s="89"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="71"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="79"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="90"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="69" t="s">
+      <c r="A31" s="89"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="71"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="79"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="90"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="69" t="s">
+      <c r="A32" s="89"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="71"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="79"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="90"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="69" t="s">
+      <c r="A33" s="89"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="71"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="79"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="90"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="69" t="s">
+      <c r="A34" s="89"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="71"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="79"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="86">
+      <c r="A35" s="87">
         <v>46210</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="86"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68" t="s">
+      <c r="A36" s="87"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="86"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68" t="s">
+      <c r="A37" s="87"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="72"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="86"/>
-      <c r="B38" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="68" t="s">
+      <c r="A38" s="87"/>
+      <c r="B38" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="72"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="86"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68" t="s">
+      <c r="A39" s="87"/>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="72"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="86"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68" t="s">
+      <c r="A40" s="87"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="86"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68" t="s">
+      <c r="A41" s="87"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="72"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="86"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68" t="s">
+      <c r="A42" s="87"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="86"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68" t="s">
+      <c r="A43" s="87"/>
+      <c r="B43" s="72"/>
+      <c r="C43" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="72"/>
+      <c r="G43" s="72"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="86"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="69" t="s">
+      <c r="A44" s="87"/>
+      <c r="B44" s="72"/>
+      <c r="C44" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="71"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="79"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2128,13 +2137,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
+      <c r="D45" s="72"/>
+      <c r="E45" s="72"/>
+      <c r="F45" s="72"/>
+      <c r="G45" s="72"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2143,255 +2152,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
+      <c r="G46" s="72"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="87">
+      <c r="A47" s="85">
         <v>46213</v>
       </c>
-      <c r="B47" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="69" t="s">
+      <c r="B47" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="71"/>
+      <c r="D47" s="78"/>
+      <c r="E47" s="78"/>
+      <c r="F47" s="78"/>
+      <c r="G47" s="79"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="88"/>
-      <c r="B48" s="79"/>
-      <c r="C48" s="69" t="s">
+      <c r="B48" s="91"/>
+      <c r="C48" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="71"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="79"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="88"/>
-      <c r="B49" s="79"/>
-      <c r="C49" s="69" t="s">
+      <c r="B49" s="91"/>
+      <c r="C49" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="71"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="78"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="79"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="88"/>
-      <c r="B50" s="79"/>
-      <c r="C50" s="69" t="s">
+      <c r="B50" s="91"/>
+      <c r="C50" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="71"/>
+      <c r="D50" s="78"/>
+      <c r="E50" s="78"/>
+      <c r="F50" s="78"/>
+      <c r="G50" s="79"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="89"/>
-      <c r="B51" s="78"/>
-      <c r="C51" s="69" t="s">
+      <c r="A51" s="86"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="70"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="71"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="78"/>
+      <c r="G51" s="79"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="67">
+      <c r="A52" s="76">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
+      <c r="D52" s="72"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="72"/>
+      <c r="G52" s="72"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="67"/>
+      <c r="A53" s="76"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="72"/>
+      <c r="G53" s="72"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="67">
+      <c r="A54" s="76">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="69" t="s">
+      <c r="C54" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="71"/>
+      <c r="D54" s="78"/>
+      <c r="E54" s="78"/>
+      <c r="F54" s="78"/>
+      <c r="G54" s="79"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="67"/>
-      <c r="B55" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="91" t="s">
+      <c r="A55" s="76"/>
+      <c r="B55" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="91"/>
-      <c r="E55" s="91"/>
-      <c r="F55" s="91"/>
-      <c r="G55" s="91"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="67"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="91" t="s">
+      <c r="A56" s="76"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="91"/>
-      <c r="E56" s="91"/>
-      <c r="F56" s="91"/>
-      <c r="G56" s="91"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="90"/>
+      <c r="G56" s="90"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="67"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="91" t="s">
+      <c r="A57" s="76"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="91"/>
-      <c r="E57" s="91"/>
-      <c r="F57" s="91"/>
-      <c r="G57" s="91"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="67"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="91" t="s">
+      <c r="A58" s="76"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="91"/>
-      <c r="E58" s="91"/>
-      <c r="F58" s="91"/>
-      <c r="G58" s="91"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="67"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="91" t="s">
+      <c r="A59" s="76"/>
+      <c r="B59" s="72"/>
+      <c r="C59" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="91"/>
-      <c r="E59" s="91"/>
-      <c r="F59" s="91"/>
-      <c r="G59" s="91"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="67"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="91" t="s">
+      <c r="A60" s="76"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="91"/>
-      <c r="E60" s="91"/>
-      <c r="F60" s="91"/>
-      <c r="G60" s="91"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="67"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="91" t="s">
+      <c r="A61" s="76"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="91"/>
-      <c r="E61" s="91"/>
-      <c r="F61" s="91"/>
-      <c r="G61" s="91"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="90"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="67"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="91" t="s">
+      <c r="A62" s="76"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="91"/>
-      <c r="E62" s="91"/>
-      <c r="F62" s="91"/>
-      <c r="G62" s="91"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="90"/>
+      <c r="G62" s="90"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="67"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="91" t="s">
+      <c r="A63" s="76"/>
+      <c r="B63" s="72"/>
+      <c r="C63" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="91"/>
-      <c r="E63" s="91"/>
-      <c r="F63" s="91"/>
-      <c r="G63" s="91"/>
+      <c r="D63" s="90"/>
+      <c r="E63" s="90"/>
+      <c r="F63" s="90"/>
+      <c r="G63" s="90"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="67">
+      <c r="A64" s="76">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
+      <c r="D64" s="72"/>
+      <c r="E64" s="72"/>
+      <c r="F64" s="72"/>
+      <c r="G64" s="72"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="67"/>
-      <c r="B65" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="68" t="s">
+      <c r="A65" s="76"/>
+      <c r="B65" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
+      <c r="D65" s="72"/>
+      <c r="E65" s="72"/>
+      <c r="F65" s="72"/>
+      <c r="G65" s="72"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="67"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68" t="s">
+      <c r="A66" s="76"/>
+      <c r="B66" s="72"/>
+      <c r="C66" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
+      <c r="D66" s="72"/>
+      <c r="E66" s="72"/>
+      <c r="F66" s="72"/>
+      <c r="G66" s="72"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2400,164 +2409,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
+      <c r="D67" s="72"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="72"/>
+      <c r="G67" s="72"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="67">
+      <c r="A68" s="76">
         <v>46220</v>
       </c>
-      <c r="B68" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="68" t="s">
+      <c r="B68" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
+      <c r="G68" s="72"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="67"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68" t="s">
+      <c r="A69" s="76"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
+      <c r="G69" s="72"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="67">
+      <c r="A70" s="76">
         <v>46223</v>
       </c>
-      <c r="B70" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="69" t="s">
+      <c r="B70" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="70"/>
-      <c r="E70" s="70"/>
-      <c r="F70" s="70"/>
-      <c r="G70" s="71"/>
+      <c r="D70" s="78"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="79"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="67"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="69" t="s">
+      <c r="A71" s="76"/>
+      <c r="B71" s="72"/>
+      <c r="C71" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="70"/>
-      <c r="E71" s="70"/>
-      <c r="F71" s="70"/>
-      <c r="G71" s="71"/>
+      <c r="D71" s="78"/>
+      <c r="E71" s="78"/>
+      <c r="F71" s="78"/>
+      <c r="G71" s="79"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="67"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="69" t="s">
+      <c r="A72" s="76"/>
+      <c r="B72" s="72"/>
+      <c r="C72" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="70"/>
-      <c r="E72" s="70"/>
-      <c r="F72" s="70"/>
-      <c r="G72" s="71"/>
+      <c r="D72" s="78"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="78"/>
+      <c r="G72" s="79"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="67"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="69" t="s">
+      <c r="A73" s="76"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="70"/>
-      <c r="E73" s="70"/>
-      <c r="F73" s="70"/>
-      <c r="G73" s="71"/>
+      <c r="D73" s="78"/>
+      <c r="E73" s="78"/>
+      <c r="F73" s="78"/>
+      <c r="G73" s="79"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="67"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="69" t="s">
+      <c r="A74" s="76"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="70"/>
-      <c r="E74" s="70"/>
-      <c r="F74" s="70"/>
-      <c r="G74" s="71"/>
+      <c r="D74" s="78"/>
+      <c r="E74" s="78"/>
+      <c r="F74" s="78"/>
+      <c r="G74" s="79"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="67"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="69" t="s">
+      <c r="A75" s="76"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="70"/>
-      <c r="E75" s="70"/>
-      <c r="F75" s="70"/>
-      <c r="G75" s="71"/>
+      <c r="D75" s="78"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="78"/>
+      <c r="G75" s="79"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="67"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="69" t="s">
+      <c r="A76" s="76"/>
+      <c r="B76" s="72"/>
+      <c r="C76" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="70"/>
-      <c r="E76" s="70"/>
-      <c r="F76" s="70"/>
-      <c r="G76" s="71"/>
+      <c r="D76" s="78"/>
+      <c r="E76" s="78"/>
+      <c r="F76" s="78"/>
+      <c r="G76" s="79"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="67"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="64" t="s">
+      <c r="A77" s="76"/>
+      <c r="B77" s="72"/>
+      <c r="C77" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="65"/>
-      <c r="E77" s="65"/>
-      <c r="F77" s="65"/>
-      <c r="G77" s="66"/>
+      <c r="D77" s="74"/>
+      <c r="E77" s="74"/>
+      <c r="F77" s="74"/>
+      <c r="G77" s="75"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="67"/>
-      <c r="B78" s="68"/>
-      <c r="C78" s="64" t="s">
+      <c r="A78" s="76"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="65"/>
-      <c r="E78" s="65"/>
-      <c r="F78" s="65"/>
-      <c r="G78" s="66"/>
+      <c r="D78" s="74"/>
+      <c r="E78" s="74"/>
+      <c r="F78" s="74"/>
+      <c r="G78" s="75"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="67"/>
-      <c r="B79" s="68"/>
-      <c r="C79" s="64" t="s">
+      <c r="A79" s="76"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="65"/>
-      <c r="E79" s="65"/>
-      <c r="F79" s="65"/>
-      <c r="G79" s="66"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="74"/>
+      <c r="F79" s="74"/>
+      <c r="G79" s="75"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="67"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="64" t="s">
+      <c r="A80" s="76"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="73" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="65"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="66"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
+      <c r="F80" s="74"/>
+      <c r="G80" s="75"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2566,353 +2575,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="68" t="s">
+      <c r="C81" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
+      <c r="D81" s="72"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="72"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="67">
+      <c r="A82" s="76">
         <v>46225</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="68" t="s">
+      <c r="C82" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
+      <c r="D82" s="72"/>
+      <c r="E82" s="72"/>
+      <c r="F82" s="72"/>
+      <c r="G82" s="72"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="67"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68" t="s">
+      <c r="A83" s="76"/>
+      <c r="B83" s="72"/>
+      <c r="C83" s="72" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
+      <c r="D83" s="72"/>
+      <c r="E83" s="72"/>
+      <c r="F83" s="72"/>
+      <c r="G83" s="72"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="67"/>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68" t="s">
+      <c r="A84" s="76"/>
+      <c r="B84" s="72"/>
+      <c r="C84" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
+      <c r="D84" s="72"/>
+      <c r="E84" s="72"/>
+      <c r="F84" s="72"/>
+      <c r="G84" s="72"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="67"/>
-      <c r="B85" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="68" t="s">
+      <c r="A85" s="76"/>
+      <c r="B85" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
+      <c r="D85" s="72"/>
+      <c r="E85" s="72"/>
+      <c r="F85" s="72"/>
+      <c r="G85" s="72"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="67"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68" t="s">
+      <c r="A86" s="76"/>
+      <c r="B86" s="72"/>
+      <c r="C86" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
+      <c r="D86" s="72"/>
+      <c r="E86" s="72"/>
+      <c r="F86" s="72"/>
+      <c r="G86" s="72"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="67"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68" t="s">
+      <c r="A87" s="76"/>
+      <c r="B87" s="72"/>
+      <c r="C87" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
+      <c r="D87" s="72"/>
+      <c r="E87" s="72"/>
+      <c r="F87" s="72"/>
+      <c r="G87" s="72"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="67"/>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68" t="s">
+      <c r="A88" s="76"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="72"/>
+      <c r="G88" s="72"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="67"/>
-      <c r="B89" s="68"/>
-      <c r="C89" s="69" t="s">
+      <c r="A89" s="76"/>
+      <c r="B89" s="72"/>
+      <c r="C89" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="70"/>
-      <c r="E89" s="70"/>
-      <c r="F89" s="70"/>
-      <c r="G89" s="71"/>
+      <c r="D89" s="78"/>
+      <c r="E89" s="78"/>
+      <c r="F89" s="78"/>
+      <c r="G89" s="79"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="67"/>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68" t="s">
+      <c r="A90" s="76"/>
+      <c r="B90" s="72"/>
+      <c r="C90" s="72" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
+      <c r="D90" s="72"/>
+      <c r="E90" s="72"/>
+      <c r="F90" s="72"/>
+      <c r="G90" s="72"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="87">
+      <c r="A91" s="85">
         <v>46227</v>
       </c>
-      <c r="B91" s="77" t="s">
+      <c r="B91" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="68" t="s">
+      <c r="C91" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
+      <c r="G91" s="72"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="89"/>
-      <c r="B92" s="78"/>
-      <c r="C92" s="69" t="s">
+      <c r="A92" s="86"/>
+      <c r="B92" s="84"/>
+      <c r="C92" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="70"/>
-      <c r="E92" s="70"/>
-      <c r="F92" s="70"/>
-      <c r="G92" s="71"/>
+      <c r="D92" s="78"/>
+      <c r="E92" s="78"/>
+      <c r="F92" s="78"/>
+      <c r="G92" s="79"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="67">
+      <c r="A93" s="76">
         <v>46228</v>
       </c>
-      <c r="B93" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="68" t="s">
+      <c r="B93" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
+      <c r="F93" s="72"/>
+      <c r="G93" s="72"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="67"/>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68" t="s">
+      <c r="A94" s="76"/>
+      <c r="B94" s="72"/>
+      <c r="C94" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="67"/>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68" t="s">
+      <c r="A95" s="76"/>
+      <c r="B95" s="72"/>
+      <c r="C95" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
+      <c r="F95" s="72"/>
+      <c r="G95" s="72"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="67"/>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="A96" s="76"/>
+      <c r="B96" s="72"/>
+      <c r="C96" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
+      <c r="D96" s="72"/>
+      <c r="E96" s="72"/>
+      <c r="F96" s="72"/>
+      <c r="G96" s="72"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="67"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="68" t="s">
+      <c r="A97" s="76"/>
+      <c r="B97" s="72"/>
+      <c r="C97" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="68"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
+      <c r="D97" s="72"/>
+      <c r="E97" s="72"/>
+      <c r="F97" s="72"/>
+      <c r="G97" s="72"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="67"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="68" t="s">
+      <c r="A98" s="76"/>
+      <c r="B98" s="72"/>
+      <c r="C98" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
+      <c r="D98" s="72"/>
+      <c r="E98" s="72"/>
+      <c r="F98" s="72"/>
+      <c r="G98" s="72"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="67">
+      <c r="A99" s="76">
         <v>46230</v>
       </c>
-      <c r="B99" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="68" t="s">
+      <c r="B99" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="72"/>
+      <c r="G99" s="72"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="67"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="68" t="s">
+      <c r="A100" s="76"/>
+      <c r="B100" s="72"/>
+      <c r="C100" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="68"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
+      <c r="D100" s="72"/>
+      <c r="E100" s="72"/>
+      <c r="F100" s="72"/>
+      <c r="G100" s="72"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="67">
+      <c r="A101" s="76">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="93" t="s">
+      <c r="C101" s="82" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="93"/>
-      <c r="E101" s="93"/>
-      <c r="F101" s="93"/>
-      <c r="G101" s="93"/>
+      <c r="D101" s="82"/>
+      <c r="E101" s="82"/>
+      <c r="F101" s="82"/>
+      <c r="G101" s="82"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="67"/>
+      <c r="A102" s="76"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="93" t="s">
+      <c r="C102" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="93"/>
-      <c r="E102" s="93"/>
-      <c r="F102" s="93"/>
-      <c r="G102" s="93"/>
+      <c r="D102" s="82"/>
+      <c r="E102" s="82"/>
+      <c r="F102" s="82"/>
+      <c r="G102" s="82"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="92" t="s">
+      <c r="A103" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="82" t="s">
+      <c r="B103" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="82"/>
-      <c r="E103" s="82"/>
-      <c r="F103" s="82"/>
-      <c r="G103" s="82"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="81"/>
+      <c r="F103" s="81"/>
+      <c r="G103" s="81"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="92"/>
-      <c r="B104" s="68"/>
-      <c r="C104" s="68" t="s">
+      <c r="A104" s="80"/>
+      <c r="B104" s="72"/>
+      <c r="C104" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
+      <c r="D104" s="72"/>
+      <c r="E104" s="72"/>
+      <c r="F104" s="72"/>
+      <c r="G104" s="72"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="92"/>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68" t="s">
+      <c r="A105" s="80"/>
+      <c r="B105" s="72"/>
+      <c r="C105" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
+      <c r="D105" s="72"/>
+      <c r="E105" s="72"/>
+      <c r="F105" s="72"/>
+      <c r="G105" s="72"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="92"/>
-      <c r="B106" s="68"/>
-      <c r="C106" s="68" t="s">
+      <c r="A106" s="80"/>
+      <c r="B106" s="72"/>
+      <c r="C106" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="68"/>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
+      <c r="D106" s="72"/>
+      <c r="E106" s="72"/>
+      <c r="F106" s="72"/>
+      <c r="G106" s="72"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="92"/>
-      <c r="B107" s="68"/>
-      <c r="C107" s="68" t="s">
+      <c r="A107" s="80"/>
+      <c r="B107" s="72"/>
+      <c r="C107" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
+      <c r="D107" s="72"/>
+      <c r="E107" s="72"/>
+      <c r="F107" s="72"/>
+      <c r="G107" s="72"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="67">
+      <c r="A108" s="76">
         <v>46234</v>
       </c>
-      <c r="B108" s="68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
+      <c r="D108" s="72"/>
+      <c r="E108" s="72"/>
+      <c r="F108" s="72"/>
+      <c r="G108" s="72"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="67"/>
-      <c r="B109" s="68"/>
-      <c r="C109" s="68" t="s">
+      <c r="A109" s="76"/>
+      <c r="B109" s="72"/>
+      <c r="C109" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
+      <c r="D109" s="72"/>
+      <c r="E109" s="72"/>
+      <c r="F109" s="72"/>
+      <c r="G109" s="72"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2922,68 +2931,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -3008,67 +3016,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3086,15 +3095,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="80">
+      <c r="A1" s="92">
         <v>46235</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4036,15 +4045,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="94">
+      <c r="A1" s="97">
         <v>46266</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4883,7 +4892,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4892,15 +4901,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="94">
+      <c r="A1" s="97">
         <v>46296</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -5013,7 +5022,7 @@
       <c r="B10" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="96" t="s">
+      <c r="C10" s="52" t="s">
         <v>187</v>
       </c>
       <c r="D10" s="53"/>
@@ -5022,17 +5031,65 @@
       <c r="G10" s="54"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="96" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="52" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="97"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="100">
+        <v>46302</v>
+      </c>
+      <c r="B12" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="99" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="101"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="99" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="101"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="99" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="101"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="99" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="101"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114767ED-9E08-47E6-A7D3-3B39B1EED21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B97D361-6DB9-4E1F-BB5F-B66BF03A515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="194">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -602,6 +602,18 @@
   </si>
   <si>
     <t>Trả BH KhoVNET</t>
+  </si>
+  <si>
+    <t>Nhận 1 SIM Viettel Lực KD. Test Thành Tâm Nha Trang</t>
+  </si>
+  <si>
+    <t>Nhập kho 17 LE(UPG)</t>
+  </si>
+  <si>
+    <t>Trả BH Lắp Đặt</t>
+  </si>
+  <si>
+    <t>Nhận 39 Vỏ RFID(Old) + ốc (tổng 498 chưa làm phiếu)</t>
   </si>
 </sst>
 </file>
@@ -825,7 +837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -985,6 +997,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1000,94 +1054,58 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1412,15 +1430,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="67">
+      <c r="A1" s="85">
         <v>46174</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1429,146 +1447,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="71"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="76">
+      <c r="A3" s="80">
         <v>46202</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="76"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="76"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="72" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="76"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72" t="s">
+      <c r="A7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="76"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72" t="s">
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="76">
+      <c r="A9" s="80">
         <v>46203</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="77" t="s">
+      <c r="C9" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="79"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="73" t="s">
+      <c r="A10" s="80"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="75"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="76"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="73" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="75"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="79"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="76"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="73" t="s">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="75"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="79"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="76"/>
+      <c r="A13" s="80"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="75"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="79"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1578,14 +1596,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1596,6 +1606,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1613,15 +1631,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="92">
+      <c r="A1" s="93">
         <v>46204</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1630,152 +1648,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="76">
+      <c r="A3" s="80">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76"/>
-      <c r="B4" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="76"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="94">
+      <c r="A7" s="96">
         <v>46205</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="77" t="s">
+      <c r="C7" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="79"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="84"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="95"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="73" t="s">
+      <c r="A8" s="97"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="75"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="79"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="95"/>
-      <c r="B9" s="84"/>
-      <c r="C9" s="73" t="s">
+      <c r="A9" s="97"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="79"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="95"/>
-      <c r="B10" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="73" t="s">
+      <c r="A10" s="97"/>
+      <c r="B10" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="75"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="95"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="73" t="s">
+      <c r="A11" s="97"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="75"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="79"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="95"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="73" t="s">
+      <c r="A12" s="97"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="75"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="79"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="96"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="73" t="s">
+      <c r="A13" s="98"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="75"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="79"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="85">
+      <c r="A14" s="100">
         <v>46206</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1787,348 +1805,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="88"/>
-      <c r="B15" s="91"/>
-      <c r="C15" s="77" t="s">
+      <c r="A15" s="101"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="84"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="88"/>
-      <c r="B16" s="91"/>
-      <c r="C16" s="77" t="s">
+      <c r="A16" s="101"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="79"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="84"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="88"/>
-      <c r="B17" s="84"/>
-      <c r="C17" s="77" t="s">
+      <c r="A17" s="101"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="79"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="84"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="88"/>
-      <c r="B18" s="83" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="77" t="s">
+      <c r="A18" s="101"/>
+      <c r="B18" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="79"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="84"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="86"/>
-      <c r="B19" s="84"/>
-      <c r="C19" s="77" t="s">
+      <c r="A19" s="102"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="79"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="84"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="89">
+      <c r="A20" s="103">
         <v>46209</v>
       </c>
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="89"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72" t="s">
+      <c r="A21" s="103"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="89"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72" t="s">
+      <c r="A22" s="103"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="89"/>
-      <c r="B23" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="72" t="s">
+      <c r="A23" s="103"/>
+      <c r="B23" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="89"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="77" t="s">
+      <c r="A24" s="103"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="79"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="84"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="89"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="77" t="s">
+      <c r="A25" s="103"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="79"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="84"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="89"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="77" t="s">
+      <c r="A26" s="103"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="79"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="84"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="89"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="77" t="s">
+      <c r="A27" s="103"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="79"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="84"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="89"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="77" t="s">
+      <c r="A28" s="103"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="79"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="84"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="89"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="77" t="s">
+      <c r="A29" s="103"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="79"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="84"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="89"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="77" t="s">
+      <c r="A30" s="103"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="79"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="84"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="89"/>
-      <c r="B31" s="72"/>
-      <c r="C31" s="77" t="s">
+      <c r="A31" s="103"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="79"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="84"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="89"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="77" t="s">
+      <c r="A32" s="103"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="79"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="84"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="89"/>
-      <c r="B33" s="72"/>
-      <c r="C33" s="77" t="s">
+      <c r="A33" s="103"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="79"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="84"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="89"/>
-      <c r="B34" s="72"/>
-      <c r="C34" s="77" t="s">
+      <c r="A34" s="103"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="79"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="84"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="87">
+      <c r="A35" s="99">
         <v>46210</v>
       </c>
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="72" t="s">
+      <c r="C35" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="87"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72" t="s">
+      <c r="A36" s="99"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="87"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="72" t="s">
+      <c r="A37" s="99"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="87"/>
-      <c r="B38" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="72" t="s">
+      <c r="A38" s="99"/>
+      <c r="B38" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="72"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="87"/>
-      <c r="B39" s="72"/>
-      <c r="C39" s="72" t="s">
+      <c r="A39" s="99"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="72"/>
-      <c r="E39" s="72"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="72"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="87"/>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72" t="s">
+      <c r="A40" s="99"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="87"/>
-      <c r="B41" s="72"/>
-      <c r="C41" s="72" t="s">
+      <c r="A41" s="99"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="72"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="72"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="87"/>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72" t="s">
+      <c r="A42" s="99"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="87"/>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72" t="s">
+      <c r="A43" s="99"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="72"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="72"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="87"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="77" t="s">
+      <c r="A44" s="99"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="78"/>
-      <c r="E44" s="78"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="79"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="84"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2137,13 +2155,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="72" t="s">
+      <c r="C45" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="72"/>
-      <c r="E45" s="72"/>
-      <c r="F45" s="72"/>
-      <c r="G45" s="72"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2152,255 +2170,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="72" t="s">
+      <c r="C46" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
-      <c r="G46" s="72"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="85">
+      <c r="A47" s="100">
         <v>46213</v>
       </c>
-      <c r="B47" s="83" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="77" t="s">
+      <c r="B47" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="78"/>
-      <c r="E47" s="78"/>
-      <c r="F47" s="78"/>
-      <c r="G47" s="79"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="84"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="88"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="77" t="s">
+      <c r="A48" s="101"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="79"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="84"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="88"/>
-      <c r="B49" s="91"/>
-      <c r="C49" s="77" t="s">
+      <c r="A49" s="101"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="78"/>
-      <c r="E49" s="78"/>
-      <c r="F49" s="78"/>
-      <c r="G49" s="79"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="84"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="88"/>
-      <c r="B50" s="91"/>
-      <c r="C50" s="77" t="s">
+      <c r="A50" s="101"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="78"/>
-      <c r="E50" s="78"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="79"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="84"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="86"/>
-      <c r="B51" s="84"/>
-      <c r="C51" s="77" t="s">
+      <c r="A51" s="102"/>
+      <c r="B51" s="91"/>
+      <c r="C51" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="78"/>
-      <c r="E51" s="78"/>
-      <c r="F51" s="78"/>
-      <c r="G51" s="79"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="84"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="76">
+      <c r="A52" s="80">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="72" t="s">
+      <c r="C52" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="72"/>
-      <c r="E52" s="72"/>
-      <c r="F52" s="72"/>
-      <c r="G52" s="72"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="76"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="72" t="s">
+      <c r="C53" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="72"/>
-      <c r="G53" s="72"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="76">
+      <c r="A54" s="80">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="77" t="s">
+      <c r="C54" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="78"/>
-      <c r="E54" s="78"/>
-      <c r="F54" s="78"/>
-      <c r="G54" s="79"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="83"/>
+      <c r="G54" s="84"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="76"/>
-      <c r="B55" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="90" t="s">
+      <c r="A55" s="80"/>
+      <c r="B55" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="104"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="76"/>
-      <c r="B56" s="72"/>
-      <c r="C56" s="90" t="s">
+      <c r="A56" s="80"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="90"/>
+      <c r="D56" s="104"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="104"/>
+      <c r="G56" s="104"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="76"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="90" t="s">
+      <c r="A57" s="80"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="90"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="104"/>
+      <c r="G57" s="104"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="76"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="90" t="s">
+      <c r="A58" s="80"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="90"/>
+      <c r="D58" s="104"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="104"/>
+      <c r="G58" s="104"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="76"/>
-      <c r="B59" s="72"/>
-      <c r="C59" s="90" t="s">
+      <c r="A59" s="80"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
+      <c r="D59" s="104"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="104"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="76"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="90" t="s">
+      <c r="A60" s="80"/>
+      <c r="B60" s="81"/>
+      <c r="C60" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="76"/>
-      <c r="B61" s="72"/>
-      <c r="C61" s="90" t="s">
+      <c r="A61" s="80"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="90"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="104"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="76"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="90" t="s">
+      <c r="A62" s="80"/>
+      <c r="B62" s="81"/>
+      <c r="C62" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="90"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="90"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="76"/>
-      <c r="B63" s="72"/>
-      <c r="C63" s="90" t="s">
+      <c r="A63" s="80"/>
+      <c r="B63" s="81"/>
+      <c r="C63" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="90"/>
-      <c r="E63" s="90"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="90"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="76">
+      <c r="A64" s="80">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="72" t="s">
+      <c r="C64" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="72"/>
-      <c r="E64" s="72"/>
-      <c r="F64" s="72"/>
-      <c r="G64" s="72"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="81"/>
+      <c r="F64" s="81"/>
+      <c r="G64" s="81"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="76"/>
-      <c r="B65" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="72" t="s">
+      <c r="A65" s="80"/>
+      <c r="B65" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="72"/>
-      <c r="E65" s="72"/>
-      <c r="F65" s="72"/>
-      <c r="G65" s="72"/>
+      <c r="D65" s="81"/>
+      <c r="E65" s="81"/>
+      <c r="F65" s="81"/>
+      <c r="G65" s="81"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="76"/>
-      <c r="B66" s="72"/>
-      <c r="C66" s="72" t="s">
+      <c r="A66" s="80"/>
+      <c r="B66" s="81"/>
+      <c r="C66" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="72"/>
-      <c r="E66" s="72"/>
-      <c r="F66" s="72"/>
-      <c r="G66" s="72"/>
+      <c r="D66" s="81"/>
+      <c r="E66" s="81"/>
+      <c r="F66" s="81"/>
+      <c r="G66" s="81"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2409,164 +2427,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="72" t="s">
+      <c r="C67" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
-      <c r="G67" s="72"/>
+      <c r="D67" s="81"/>
+      <c r="E67" s="81"/>
+      <c r="F67" s="81"/>
+      <c r="G67" s="81"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="76">
+      <c r="A68" s="80">
         <v>46220</v>
       </c>
-      <c r="B68" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="72" t="s">
+      <c r="B68" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
-      <c r="G68" s="72"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="76"/>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72" t="s">
+      <c r="A69" s="80"/>
+      <c r="B69" s="81"/>
+      <c r="C69" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="72"/>
+      <c r="D69" s="81"/>
+      <c r="E69" s="81"/>
+      <c r="F69" s="81"/>
+      <c r="G69" s="81"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="76">
+      <c r="A70" s="80">
         <v>46223</v>
       </c>
-      <c r="B70" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="77" t="s">
+      <c r="B70" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="78"/>
-      <c r="E70" s="78"/>
-      <c r="F70" s="78"/>
-      <c r="G70" s="79"/>
+      <c r="D70" s="83"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="83"/>
+      <c r="G70" s="84"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="76"/>
-      <c r="B71" s="72"/>
-      <c r="C71" s="77" t="s">
+      <c r="A71" s="80"/>
+      <c r="B71" s="81"/>
+      <c r="C71" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="78"/>
-      <c r="E71" s="78"/>
-      <c r="F71" s="78"/>
-      <c r="G71" s="79"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="83"/>
+      <c r="G71" s="84"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="76"/>
-      <c r="B72" s="72"/>
-      <c r="C72" s="77" t="s">
+      <c r="A72" s="80"/>
+      <c r="B72" s="81"/>
+      <c r="C72" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
-      <c r="F72" s="78"/>
-      <c r="G72" s="79"/>
+      <c r="D72" s="83"/>
+      <c r="E72" s="83"/>
+      <c r="F72" s="83"/>
+      <c r="G72" s="84"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="76"/>
-      <c r="B73" s="72"/>
-      <c r="C73" s="77" t="s">
+      <c r="A73" s="80"/>
+      <c r="B73" s="81"/>
+      <c r="C73" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="78"/>
-      <c r="E73" s="78"/>
-      <c r="F73" s="78"/>
-      <c r="G73" s="79"/>
+      <c r="D73" s="83"/>
+      <c r="E73" s="83"/>
+      <c r="F73" s="83"/>
+      <c r="G73" s="84"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="76"/>
-      <c r="B74" s="72"/>
-      <c r="C74" s="77" t="s">
+      <c r="A74" s="80"/>
+      <c r="B74" s="81"/>
+      <c r="C74" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="78"/>
-      <c r="E74" s="78"/>
-      <c r="F74" s="78"/>
-      <c r="G74" s="79"/>
+      <c r="D74" s="83"/>
+      <c r="E74" s="83"/>
+      <c r="F74" s="83"/>
+      <c r="G74" s="84"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="76"/>
-      <c r="B75" s="72"/>
-      <c r="C75" s="77" t="s">
+      <c r="A75" s="80"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="78"/>
-      <c r="E75" s="78"/>
-      <c r="F75" s="78"/>
-      <c r="G75" s="79"/>
+      <c r="D75" s="83"/>
+      <c r="E75" s="83"/>
+      <c r="F75" s="83"/>
+      <c r="G75" s="84"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="76"/>
-      <c r="B76" s="72"/>
-      <c r="C76" s="77" t="s">
+      <c r="A76" s="80"/>
+      <c r="B76" s="81"/>
+      <c r="C76" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="78"/>
-      <c r="E76" s="78"/>
-      <c r="F76" s="78"/>
-      <c r="G76" s="79"/>
+      <c r="D76" s="83"/>
+      <c r="E76" s="83"/>
+      <c r="F76" s="83"/>
+      <c r="G76" s="84"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="76"/>
-      <c r="B77" s="72"/>
-      <c r="C77" s="73" t="s">
+      <c r="A77" s="80"/>
+      <c r="B77" s="81"/>
+      <c r="C77" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="74"/>
-      <c r="E77" s="74"/>
-      <c r="F77" s="74"/>
-      <c r="G77" s="75"/>
+      <c r="D77" s="78"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="78"/>
+      <c r="G77" s="79"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="76"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="73" t="s">
+      <c r="A78" s="80"/>
+      <c r="B78" s="81"/>
+      <c r="C78" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="74"/>
-      <c r="E78" s="74"/>
-      <c r="F78" s="74"/>
-      <c r="G78" s="75"/>
+      <c r="D78" s="78"/>
+      <c r="E78" s="78"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="79"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="76"/>
-      <c r="B79" s="72"/>
-      <c r="C79" s="73" t="s">
+      <c r="A79" s="80"/>
+      <c r="B79" s="81"/>
+      <c r="C79" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="74"/>
-      <c r="E79" s="74"/>
-      <c r="F79" s="74"/>
-      <c r="G79" s="75"/>
+      <c r="D79" s="78"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="78"/>
+      <c r="G79" s="79"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="76"/>
-      <c r="B80" s="72"/>
-      <c r="C80" s="73" t="s">
+      <c r="A80" s="80"/>
+      <c r="B80" s="81"/>
+      <c r="C80" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
-      <c r="F80" s="74"/>
-      <c r="G80" s="75"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="79"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2575,353 +2593,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="72" t="s">
+      <c r="C81" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="72"/>
-      <c r="E81" s="72"/>
-      <c r="F81" s="72"/>
-      <c r="G81" s="72"/>
+      <c r="D81" s="81"/>
+      <c r="E81" s="81"/>
+      <c r="F81" s="81"/>
+      <c r="G81" s="81"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="76">
+      <c r="A82" s="80">
         <v>46225</v>
       </c>
-      <c r="B82" s="72" t="s">
+      <c r="B82" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="72" t="s">
+      <c r="C82" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="72"/>
-      <c r="E82" s="72"/>
-      <c r="F82" s="72"/>
-      <c r="G82" s="72"/>
+      <c r="D82" s="81"/>
+      <c r="E82" s="81"/>
+      <c r="F82" s="81"/>
+      <c r="G82" s="81"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="76"/>
-      <c r="B83" s="72"/>
-      <c r="C83" s="72" t="s">
+      <c r="A83" s="80"/>
+      <c r="B83" s="81"/>
+      <c r="C83" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="72"/>
-      <c r="E83" s="72"/>
-      <c r="F83" s="72"/>
-      <c r="G83" s="72"/>
+      <c r="D83" s="81"/>
+      <c r="E83" s="81"/>
+      <c r="F83" s="81"/>
+      <c r="G83" s="81"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="76"/>
-      <c r="B84" s="72"/>
-      <c r="C84" s="72" t="s">
+      <c r="A84" s="80"/>
+      <c r="B84" s="81"/>
+      <c r="C84" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="72"/>
-      <c r="E84" s="72"/>
-      <c r="F84" s="72"/>
-      <c r="G84" s="72"/>
+      <c r="D84" s="81"/>
+      <c r="E84" s="81"/>
+      <c r="F84" s="81"/>
+      <c r="G84" s="81"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="76"/>
-      <c r="B85" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="72" t="s">
+      <c r="A85" s="80"/>
+      <c r="B85" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="72"/>
-      <c r="E85" s="72"/>
-      <c r="F85" s="72"/>
-      <c r="G85" s="72"/>
+      <c r="D85" s="81"/>
+      <c r="E85" s="81"/>
+      <c r="F85" s="81"/>
+      <c r="G85" s="81"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="76"/>
-      <c r="B86" s="72"/>
-      <c r="C86" s="72" t="s">
+      <c r="A86" s="80"/>
+      <c r="B86" s="81"/>
+      <c r="C86" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="72"/>
-      <c r="E86" s="72"/>
-      <c r="F86" s="72"/>
-      <c r="G86" s="72"/>
+      <c r="D86" s="81"/>
+      <c r="E86" s="81"/>
+      <c r="F86" s="81"/>
+      <c r="G86" s="81"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="76"/>
-      <c r="B87" s="72"/>
-      <c r="C87" s="72" t="s">
+      <c r="A87" s="80"/>
+      <c r="B87" s="81"/>
+      <c r="C87" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="72"/>
-      <c r="E87" s="72"/>
-      <c r="F87" s="72"/>
-      <c r="G87" s="72"/>
+      <c r="D87" s="81"/>
+      <c r="E87" s="81"/>
+      <c r="F87" s="81"/>
+      <c r="G87" s="81"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="76"/>
-      <c r="B88" s="72"/>
-      <c r="C88" s="72" t="s">
+      <c r="A88" s="80"/>
+      <c r="B88" s="81"/>
+      <c r="C88" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="72"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="72"/>
-      <c r="G88" s="72"/>
+      <c r="D88" s="81"/>
+      <c r="E88" s="81"/>
+      <c r="F88" s="81"/>
+      <c r="G88" s="81"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="76"/>
-      <c r="B89" s="72"/>
-      <c r="C89" s="77" t="s">
+      <c r="A89" s="80"/>
+      <c r="B89" s="81"/>
+      <c r="C89" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="78"/>
-      <c r="E89" s="78"/>
-      <c r="F89" s="78"/>
-      <c r="G89" s="79"/>
+      <c r="D89" s="83"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="83"/>
+      <c r="G89" s="84"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="76"/>
-      <c r="B90" s="72"/>
-      <c r="C90" s="72" t="s">
+      <c r="A90" s="80"/>
+      <c r="B90" s="81"/>
+      <c r="C90" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="72"/>
-      <c r="E90" s="72"/>
-      <c r="F90" s="72"/>
-      <c r="G90" s="72"/>
+      <c r="D90" s="81"/>
+      <c r="E90" s="81"/>
+      <c r="F90" s="81"/>
+      <c r="G90" s="81"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="85">
+      <c r="A91" s="100">
         <v>46227</v>
       </c>
-      <c r="B91" s="83" t="s">
+      <c r="B91" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="72" t="s">
+      <c r="C91" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="72"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
-      <c r="G91" s="72"/>
+      <c r="D91" s="81"/>
+      <c r="E91" s="81"/>
+      <c r="F91" s="81"/>
+      <c r="G91" s="81"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="86"/>
-      <c r="B92" s="84"/>
-      <c r="C92" s="77" t="s">
+      <c r="A92" s="102"/>
+      <c r="B92" s="91"/>
+      <c r="C92" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="78"/>
-      <c r="E92" s="78"/>
-      <c r="F92" s="78"/>
-      <c r="G92" s="79"/>
+      <c r="D92" s="83"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="83"/>
+      <c r="G92" s="84"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="76">
+      <c r="A93" s="80">
         <v>46228</v>
       </c>
-      <c r="B93" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="72" t="s">
+      <c r="B93" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="72"/>
-      <c r="E93" s="72"/>
-      <c r="F93" s="72"/>
-      <c r="G93" s="72"/>
+      <c r="D93" s="81"/>
+      <c r="E93" s="81"/>
+      <c r="F93" s="81"/>
+      <c r="G93" s="81"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="76"/>
-      <c r="B94" s="72"/>
-      <c r="C94" s="72" t="s">
+      <c r="A94" s="80"/>
+      <c r="B94" s="81"/>
+      <c r="C94" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="72"/>
-      <c r="E94" s="72"/>
-      <c r="F94" s="72"/>
-      <c r="G94" s="72"/>
+      <c r="D94" s="81"/>
+      <c r="E94" s="81"/>
+      <c r="F94" s="81"/>
+      <c r="G94" s="81"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="76"/>
-      <c r="B95" s="72"/>
-      <c r="C95" s="72" t="s">
+      <c r="A95" s="80"/>
+      <c r="B95" s="81"/>
+      <c r="C95" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="72"/>
-      <c r="E95" s="72"/>
-      <c r="F95" s="72"/>
-      <c r="G95" s="72"/>
+      <c r="D95" s="81"/>
+      <c r="E95" s="81"/>
+      <c r="F95" s="81"/>
+      <c r="G95" s="81"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="76"/>
-      <c r="B96" s="72"/>
-      <c r="C96" s="72" t="s">
+      <c r="A96" s="80"/>
+      <c r="B96" s="81"/>
+      <c r="C96" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="72"/>
-      <c r="E96" s="72"/>
-      <c r="F96" s="72"/>
-      <c r="G96" s="72"/>
+      <c r="D96" s="81"/>
+      <c r="E96" s="81"/>
+      <c r="F96" s="81"/>
+      <c r="G96" s="81"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="76"/>
-      <c r="B97" s="72"/>
-      <c r="C97" s="72" t="s">
+      <c r="A97" s="80"/>
+      <c r="B97" s="81"/>
+      <c r="C97" s="81" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="72"/>
-      <c r="E97" s="72"/>
-      <c r="F97" s="72"/>
-      <c r="G97" s="72"/>
+      <c r="D97" s="81"/>
+      <c r="E97" s="81"/>
+      <c r="F97" s="81"/>
+      <c r="G97" s="81"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="76"/>
-      <c r="B98" s="72"/>
-      <c r="C98" s="72" t="s">
+      <c r="A98" s="80"/>
+      <c r="B98" s="81"/>
+      <c r="C98" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="72"/>
-      <c r="E98" s="72"/>
-      <c r="F98" s="72"/>
-      <c r="G98" s="72"/>
+      <c r="D98" s="81"/>
+      <c r="E98" s="81"/>
+      <c r="F98" s="81"/>
+      <c r="G98" s="81"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="76">
+      <c r="A99" s="80">
         <v>46230</v>
       </c>
-      <c r="B99" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="72" t="s">
+      <c r="B99" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="72"/>
-      <c r="E99" s="72"/>
-      <c r="F99" s="72"/>
-      <c r="G99" s="72"/>
+      <c r="D99" s="81"/>
+      <c r="E99" s="81"/>
+      <c r="F99" s="81"/>
+      <c r="G99" s="81"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="76"/>
-      <c r="B100" s="72"/>
-      <c r="C100" s="72" t="s">
+      <c r="A100" s="80"/>
+      <c r="B100" s="81"/>
+      <c r="C100" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="72"/>
-      <c r="E100" s="72"/>
-      <c r="F100" s="72"/>
-      <c r="G100" s="72"/>
+      <c r="D100" s="81"/>
+      <c r="E100" s="81"/>
+      <c r="F100" s="81"/>
+      <c r="G100" s="81"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="76">
+      <c r="A101" s="80">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="82" t="s">
+      <c r="C101" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="82"/>
-      <c r="E101" s="82"/>
-      <c r="F101" s="82"/>
-      <c r="G101" s="82"/>
+      <c r="D101" s="106"/>
+      <c r="E101" s="106"/>
+      <c r="F101" s="106"/>
+      <c r="G101" s="106"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="76"/>
+      <c r="A102" s="80"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="82" t="s">
+      <c r="C102" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="82"/>
-      <c r="E102" s="82"/>
-      <c r="F102" s="82"/>
-      <c r="G102" s="82"/>
+      <c r="D102" s="106"/>
+      <c r="E102" s="106"/>
+      <c r="F102" s="106"/>
+      <c r="G102" s="106"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="80" t="s">
+      <c r="A103" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="81" t="s">
+      <c r="B103" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="81"/>
-      <c r="E103" s="81"/>
-      <c r="F103" s="81"/>
-      <c r="G103" s="81"/>
+      <c r="D103" s="95"/>
+      <c r="E103" s="95"/>
+      <c r="F103" s="95"/>
+      <c r="G103" s="95"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="80"/>
-      <c r="B104" s="72"/>
-      <c r="C104" s="72" t="s">
+      <c r="A104" s="105"/>
+      <c r="B104" s="81"/>
+      <c r="C104" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="72"/>
-      <c r="E104" s="72"/>
-      <c r="F104" s="72"/>
-      <c r="G104" s="72"/>
+      <c r="D104" s="81"/>
+      <c r="E104" s="81"/>
+      <c r="F104" s="81"/>
+      <c r="G104" s="81"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="80"/>
-      <c r="B105" s="72"/>
-      <c r="C105" s="72" t="s">
+      <c r="A105" s="105"/>
+      <c r="B105" s="81"/>
+      <c r="C105" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="72"/>
-      <c r="E105" s="72"/>
-      <c r="F105" s="72"/>
-      <c r="G105" s="72"/>
+      <c r="D105" s="81"/>
+      <c r="E105" s="81"/>
+      <c r="F105" s="81"/>
+      <c r="G105" s="81"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="80"/>
-      <c r="B106" s="72"/>
-      <c r="C106" s="72" t="s">
+      <c r="A106" s="105"/>
+      <c r="B106" s="81"/>
+      <c r="C106" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="72"/>
-      <c r="E106" s="72"/>
-      <c r="F106" s="72"/>
-      <c r="G106" s="72"/>
+      <c r="D106" s="81"/>
+      <c r="E106" s="81"/>
+      <c r="F106" s="81"/>
+      <c r="G106" s="81"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="80"/>
-      <c r="B107" s="72"/>
-      <c r="C107" s="72" t="s">
+      <c r="A107" s="105"/>
+      <c r="B107" s="81"/>
+      <c r="C107" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="72"/>
-      <c r="E107" s="72"/>
-      <c r="F107" s="72"/>
-      <c r="G107" s="72"/>
+      <c r="D107" s="81"/>
+      <c r="E107" s="81"/>
+      <c r="F107" s="81"/>
+      <c r="G107" s="81"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="76">
+      <c r="A108" s="80">
         <v>46234</v>
       </c>
-      <c r="B108" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="72" t="s">
+      <c r="B108" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="72"/>
-      <c r="E108" s="72"/>
-      <c r="F108" s="72"/>
-      <c r="G108" s="72"/>
+      <c r="D108" s="81"/>
+      <c r="E108" s="81"/>
+      <c r="F108" s="81"/>
+      <c r="G108" s="81"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="76"/>
-      <c r="B109" s="72"/>
-      <c r="C109" s="72" t="s">
+      <c r="A109" s="80"/>
+      <c r="B109" s="81"/>
+      <c r="C109" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="72"/>
-      <c r="E109" s="72"/>
-      <c r="F109" s="72"/>
-      <c r="G109" s="72"/>
+      <c r="D109" s="81"/>
+      <c r="E109" s="81"/>
+      <c r="F109" s="81"/>
+      <c r="G109" s="81"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2931,6 +2949,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2955,129 +3096,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3095,15 +3113,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="92">
+      <c r="A1" s="93">
         <v>46235</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4045,15 +4063,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="97">
+      <c r="A1" s="107">
         <v>46266</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4892,7 +4910,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4901,15 +4919,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="97">
+      <c r="A1" s="107">
         <v>46296</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -5044,57 +5062,137 @@
       <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="100">
+      <c r="A12" s="11">
         <v>46302</v>
       </c>
-      <c r="B12" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="99" t="s">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="76"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="75"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="76"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" s="71"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="76"/>
+      <c r="B15" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="101"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="99" t="s">
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="70"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="25"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="101"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="99" t="s">
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="70"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="101"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="101"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="99" t="s">
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="25"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="70"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="36"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="71"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="38"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="73"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>46303</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B97D361-6DB9-4E1F-BB5F-B66BF03A515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC61FC0-2798-4FAC-9CA8-77637011A78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="198">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -614,6 +614,18 @@
   </si>
   <si>
     <t>Nhận 39 Vỏ RFID(Old) + ốc (tổng 498 chưa làm phiếu)</t>
+  </si>
+  <si>
+    <t>Trả 2 VNSH03 hàn thêm M2</t>
+  </si>
+  <si>
+    <t>Nhập kho 10 VNSH03</t>
+  </si>
+  <si>
+    <t>Xuất kho phụ kiện VNSH03 trừ dần đi</t>
+  </si>
+  <si>
+    <t>Nhận 96 VNSH03, lấy 100 vỏ carton, 100 dây nguồn LE, 100 anten GSM, 100 anten GPS, 200m dây nguồn VNSH03</t>
   </si>
 </sst>
 </file>
@@ -837,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1015,6 +1027,24 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1027,9 +1057,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1039,20 +1066,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1060,6 +1081,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1069,9 +1108,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1081,31 +1117,16 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1430,15 +1451,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="85">
+      <c r="A1" s="77">
         <v>46174</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1447,146 +1468,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="81"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="80">
+      <c r="A3" s="86">
         <v>46202</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="86"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="80"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81" t="s">
+      <c r="A5" s="86"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="81" t="s">
+      <c r="A6" s="86"/>
+      <c r="B6" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="80"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81" t="s">
+      <c r="A7" s="86"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="80"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81" t="s">
+      <c r="A8" s="86"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="80">
+      <c r="A9" s="86">
         <v>46203</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="84"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="89"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="80"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="77" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="85"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="77" t="s">
+      <c r="A11" s="86"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="79"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="85"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="77" t="s">
+      <c r="A12" s="86"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="85"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="80"/>
+      <c r="A13" s="86"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="85"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1596,6 +1617,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1606,14 +1635,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1631,15 +1652,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="102">
         <v>46204</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1648,152 +1669,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="80">
+      <c r="A3" s="86">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="95" t="s">
+      <c r="A4" s="86"/>
+      <c r="B4" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="80"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81" t="s">
+      <c r="A5" s="86"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81" t="s">
+      <c r="A6" s="86"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="96">
+      <c r="A7" s="104">
         <v>46205</v>
       </c>
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="84"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="97"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="77" t="s">
+      <c r="A8" s="105"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="79"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="85"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="97"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="77" t="s">
+      <c r="A9" s="105"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="79"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="85"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="97"/>
-      <c r="B10" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="77" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="85"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="97"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="77" t="s">
+      <c r="A11" s="105"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="79"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="85"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="97"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="77" t="s">
+      <c r="A12" s="105"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="85"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="98"/>
-      <c r="B13" s="81"/>
-      <c r="C13" s="77" t="s">
+      <c r="A13" s="106"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="85"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="100">
+      <c r="A14" s="95">
         <v>46206</v>
       </c>
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="93" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1805,348 +1826,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="101"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="82" t="s">
+      <c r="A15" s="98"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="84"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="89"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="101"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="82" t="s">
+      <c r="A16" s="98"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="84"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="89"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="101"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="82" t="s">
+      <c r="A17" s="98"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="84"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="89"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="101"/>
-      <c r="B18" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="82" t="s">
+      <c r="A18" s="98"/>
+      <c r="B18" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="84"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="89"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="102"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="82" t="s">
+      <c r="A19" s="96"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="84"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="89"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="103">
+      <c r="A20" s="99">
         <v>46209</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="81" t="s">
+      <c r="C20" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="103"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="81" t="s">
+      <c r="A21" s="99"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="103"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="81" t="s">
+      <c r="A22" s="99"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="103"/>
-      <c r="B23" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="81" t="s">
+      <c r="A23" s="99"/>
+      <c r="B23" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="103"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="82" t="s">
+      <c r="A24" s="99"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="84"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="89"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="103"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="82" t="s">
+      <c r="A25" s="99"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="84"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="89"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="103"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="82" t="s">
+      <c r="A26" s="99"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="84"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="89"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="103"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="82" t="s">
+      <c r="A27" s="99"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="84"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="89"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="103"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="82" t="s">
+      <c r="A28" s="99"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="84"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="89"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="103"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="82" t="s">
+      <c r="A29" s="99"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="84"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="89"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="103"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="82" t="s">
+      <c r="A30" s="99"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="84"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="89"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="103"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="82" t="s">
+      <c r="A31" s="99"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="84"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="89"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="103"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="82" t="s">
+      <c r="A32" s="99"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="84"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="89"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="103"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="82" t="s">
+      <c r="A33" s="99"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="84"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="89"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="103"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="82" t="s">
+      <c r="A34" s="99"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="84"/>
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="89"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="99">
+      <c r="A35" s="97">
         <v>46210</v>
       </c>
-      <c r="B35" s="81" t="s">
+      <c r="B35" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="99"/>
-      <c r="B36" s="81"/>
-      <c r="C36" s="81" t="s">
+      <c r="A36" s="97"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="99"/>
-      <c r="B37" s="81"/>
-      <c r="C37" s="81" t="s">
+      <c r="A37" s="97"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="99"/>
-      <c r="B38" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="81" t="s">
+      <c r="A38" s="97"/>
+      <c r="B38" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="99"/>
-      <c r="B39" s="81"/>
-      <c r="C39" s="81" t="s">
+      <c r="A39" s="97"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="99"/>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81" t="s">
+      <c r="A40" s="97"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="99"/>
-      <c r="B41" s="81"/>
-      <c r="C41" s="81" t="s">
+      <c r="A41" s="97"/>
+      <c r="B41" s="82"/>
+      <c r="C41" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="99"/>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81" t="s">
+      <c r="A42" s="97"/>
+      <c r="B42" s="82"/>
+      <c r="C42" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="82"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="99"/>
-      <c r="B43" s="81"/>
-      <c r="C43" s="81" t="s">
+      <c r="A43" s="97"/>
+      <c r="B43" s="82"/>
+      <c r="C43" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="82"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="99"/>
-      <c r="B44" s="81"/>
-      <c r="C44" s="82" t="s">
+      <c r="A44" s="97"/>
+      <c r="B44" s="82"/>
+      <c r="C44" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="84"/>
+      <c r="D44" s="88"/>
+      <c r="E44" s="88"/>
+      <c r="F44" s="88"/>
+      <c r="G44" s="89"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2155,13 +2176,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="81" t="s">
+      <c r="C45" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="82"/>
+      <c r="F45" s="82"/>
+      <c r="G45" s="82"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2170,255 +2191,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="81" t="s">
+      <c r="C46" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="81"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="82"/>
+      <c r="G46" s="82"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="100">
+      <c r="A47" s="95">
         <v>46213</v>
       </c>
-      <c r="B47" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="82" t="s">
+      <c r="B47" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="84"/>
+      <c r="D47" s="88"/>
+      <c r="E47" s="88"/>
+      <c r="F47" s="88"/>
+      <c r="G47" s="89"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="101"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="82" t="s">
+      <c r="A48" s="98"/>
+      <c r="B48" s="101"/>
+      <c r="C48" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="84"/>
+      <c r="D48" s="88"/>
+      <c r="E48" s="88"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="89"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="101"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="82" t="s">
+      <c r="A49" s="98"/>
+      <c r="B49" s="101"/>
+      <c r="C49" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="84"/>
+      <c r="D49" s="88"/>
+      <c r="E49" s="88"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="89"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="101"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="82" t="s">
+      <c r="A50" s="98"/>
+      <c r="B50" s="101"/>
+      <c r="C50" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="84"/>
+      <c r="D50" s="88"/>
+      <c r="E50" s="88"/>
+      <c r="F50" s="88"/>
+      <c r="G50" s="89"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="102"/>
-      <c r="B51" s="91"/>
-      <c r="C51" s="82" t="s">
+      <c r="A51" s="96"/>
+      <c r="B51" s="94"/>
+      <c r="C51" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="84"/>
+      <c r="D51" s="88"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="89"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="80">
+      <c r="A52" s="86">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="81" t="s">
+      <c r="C52" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="82"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="82"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="82"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="80">
+      <c r="A54" s="86">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="82" t="s">
+      <c r="C54" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="84"/>
+      <c r="D54" s="88"/>
+      <c r="E54" s="88"/>
+      <c r="F54" s="88"/>
+      <c r="G54" s="89"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="80"/>
-      <c r="B55" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="104" t="s">
+      <c r="A55" s="86"/>
+      <c r="B55" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="104"/>
-      <c r="E55" s="104"/>
-      <c r="F55" s="104"/>
-      <c r="G55" s="104"/>
+      <c r="D55" s="100"/>
+      <c r="E55" s="100"/>
+      <c r="F55" s="100"/>
+      <c r="G55" s="100"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="80"/>
-      <c r="B56" s="81"/>
-      <c r="C56" s="104" t="s">
+      <c r="A56" s="86"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="104"/>
-      <c r="E56" s="104"/>
-      <c r="F56" s="104"/>
-      <c r="G56" s="104"/>
+      <c r="D56" s="100"/>
+      <c r="E56" s="100"/>
+      <c r="F56" s="100"/>
+      <c r="G56" s="100"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="80"/>
-      <c r="B57" s="81"/>
-      <c r="C57" s="104" t="s">
+      <c r="A57" s="86"/>
+      <c r="B57" s="82"/>
+      <c r="C57" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="104"/>
-      <c r="E57" s="104"/>
-      <c r="F57" s="104"/>
-      <c r="G57" s="104"/>
+      <c r="D57" s="100"/>
+      <c r="E57" s="100"/>
+      <c r="F57" s="100"/>
+      <c r="G57" s="100"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="80"/>
-      <c r="B58" s="81"/>
-      <c r="C58" s="104" t="s">
+      <c r="A58" s="86"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="104"/>
-      <c r="E58" s="104"/>
-      <c r="F58" s="104"/>
-      <c r="G58" s="104"/>
+      <c r="D58" s="100"/>
+      <c r="E58" s="100"/>
+      <c r="F58" s="100"/>
+      <c r="G58" s="100"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="80"/>
-      <c r="B59" s="81"/>
-      <c r="C59" s="104" t="s">
+      <c r="A59" s="86"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="100" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="104"/>
-      <c r="E59" s="104"/>
-      <c r="F59" s="104"/>
-      <c r="G59" s="104"/>
+      <c r="D59" s="100"/>
+      <c r="E59" s="100"/>
+      <c r="F59" s="100"/>
+      <c r="G59" s="100"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="80"/>
-      <c r="B60" s="81"/>
-      <c r="C60" s="104" t="s">
+      <c r="A60" s="86"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
+      <c r="D60" s="100"/>
+      <c r="E60" s="100"/>
+      <c r="F60" s="100"/>
+      <c r="G60" s="100"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="80"/>
-      <c r="B61" s="81"/>
-      <c r="C61" s="104" t="s">
+      <c r="A61" s="86"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="104"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="104"/>
-      <c r="G61" s="104"/>
+      <c r="D61" s="100"/>
+      <c r="E61" s="100"/>
+      <c r="F61" s="100"/>
+      <c r="G61" s="100"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="80"/>
-      <c r="B62" s="81"/>
-      <c r="C62" s="104" t="s">
+      <c r="A62" s="86"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
+      <c r="D62" s="100"/>
+      <c r="E62" s="100"/>
+      <c r="F62" s="100"/>
+      <c r="G62" s="100"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="80"/>
-      <c r="B63" s="81"/>
-      <c r="C63" s="104" t="s">
+      <c r="A63" s="86"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="104"/>
-      <c r="E63" s="104"/>
-      <c r="F63" s="104"/>
-      <c r="G63" s="104"/>
+      <c r="D63" s="100"/>
+      <c r="E63" s="100"/>
+      <c r="F63" s="100"/>
+      <c r="G63" s="100"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="80">
+      <c r="A64" s="86">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="81" t="s">
+      <c r="C64" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="81"/>
-      <c r="E64" s="81"/>
-      <c r="F64" s="81"/>
-      <c r="G64" s="81"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="82"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="82"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="80"/>
-      <c r="B65" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="81" t="s">
+      <c r="A65" s="86"/>
+      <c r="B65" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="81"/>
-      <c r="E65" s="81"/>
-      <c r="F65" s="81"/>
-      <c r="G65" s="81"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="82"/>
+      <c r="F65" s="82"/>
+      <c r="G65" s="82"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="80"/>
-      <c r="B66" s="81"/>
-      <c r="C66" s="81" t="s">
+      <c r="A66" s="86"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="81"/>
-      <c r="E66" s="81"/>
-      <c r="F66" s="81"/>
-      <c r="G66" s="81"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="82"/>
+      <c r="F66" s="82"/>
+      <c r="G66" s="82"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2427,164 +2448,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="81" t="s">
+      <c r="C67" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="81"/>
-      <c r="E67" s="81"/>
-      <c r="F67" s="81"/>
-      <c r="G67" s="81"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="82"/>
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="80">
+      <c r="A68" s="86">
         <v>46220</v>
       </c>
-      <c r="B68" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="81" t="s">
+      <c r="B68" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="81"/>
-      <c r="E68" s="81"/>
-      <c r="F68" s="81"/>
-      <c r="G68" s="81"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="80"/>
-      <c r="B69" s="81"/>
-      <c r="C69" s="81" t="s">
+      <c r="A69" s="86"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="81"/>
-      <c r="E69" s="81"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="81"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="82"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="80">
+      <c r="A70" s="86">
         <v>46223</v>
       </c>
-      <c r="B70" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="82" t="s">
+      <c r="B70" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="83"/>
-      <c r="E70" s="83"/>
-      <c r="F70" s="83"/>
-      <c r="G70" s="84"/>
+      <c r="D70" s="88"/>
+      <c r="E70" s="88"/>
+      <c r="F70" s="88"/>
+      <c r="G70" s="89"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="80"/>
-      <c r="B71" s="81"/>
-      <c r="C71" s="82" t="s">
+      <c r="A71" s="86"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="83"/>
-      <c r="E71" s="83"/>
-      <c r="F71" s="83"/>
-      <c r="G71" s="84"/>
+      <c r="D71" s="88"/>
+      <c r="E71" s="88"/>
+      <c r="F71" s="88"/>
+      <c r="G71" s="89"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="80"/>
-      <c r="B72" s="81"/>
-      <c r="C72" s="82" t="s">
+      <c r="A72" s="86"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="83"/>
-      <c r="E72" s="83"/>
-      <c r="F72" s="83"/>
-      <c r="G72" s="84"/>
+      <c r="D72" s="88"/>
+      <c r="E72" s="88"/>
+      <c r="F72" s="88"/>
+      <c r="G72" s="89"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="80"/>
-      <c r="B73" s="81"/>
-      <c r="C73" s="82" t="s">
+      <c r="A73" s="86"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="83"/>
-      <c r="E73" s="83"/>
-      <c r="F73" s="83"/>
-      <c r="G73" s="84"/>
+      <c r="D73" s="88"/>
+      <c r="E73" s="88"/>
+      <c r="F73" s="88"/>
+      <c r="G73" s="89"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="80"/>
-      <c r="B74" s="81"/>
-      <c r="C74" s="82" t="s">
+      <c r="A74" s="86"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="83"/>
-      <c r="E74" s="83"/>
-      <c r="F74" s="83"/>
-      <c r="G74" s="84"/>
+      <c r="D74" s="88"/>
+      <c r="E74" s="88"/>
+      <c r="F74" s="88"/>
+      <c r="G74" s="89"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="80"/>
-      <c r="B75" s="81"/>
-      <c r="C75" s="82" t="s">
+      <c r="A75" s="86"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="83"/>
-      <c r="G75" s="84"/>
+      <c r="D75" s="88"/>
+      <c r="E75" s="88"/>
+      <c r="F75" s="88"/>
+      <c r="G75" s="89"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="80"/>
-      <c r="B76" s="81"/>
-      <c r="C76" s="82" t="s">
+      <c r="A76" s="86"/>
+      <c r="B76" s="82"/>
+      <c r="C76" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="83"/>
-      <c r="E76" s="83"/>
-      <c r="F76" s="83"/>
-      <c r="G76" s="84"/>
+      <c r="D76" s="88"/>
+      <c r="E76" s="88"/>
+      <c r="F76" s="88"/>
+      <c r="G76" s="89"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="80"/>
-      <c r="B77" s="81"/>
-      <c r="C77" s="77" t="s">
+      <c r="A77" s="86"/>
+      <c r="B77" s="82"/>
+      <c r="C77" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="78"/>
-      <c r="E77" s="78"/>
-      <c r="F77" s="78"/>
-      <c r="G77" s="79"/>
+      <c r="D77" s="84"/>
+      <c r="E77" s="84"/>
+      <c r="F77" s="84"/>
+      <c r="G77" s="85"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="80"/>
-      <c r="B78" s="81"/>
-      <c r="C78" s="77" t="s">
+      <c r="A78" s="86"/>
+      <c r="B78" s="82"/>
+      <c r="C78" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="78"/>
-      <c r="E78" s="78"/>
-      <c r="F78" s="78"/>
-      <c r="G78" s="79"/>
+      <c r="D78" s="84"/>
+      <c r="E78" s="84"/>
+      <c r="F78" s="84"/>
+      <c r="G78" s="85"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="80"/>
-      <c r="B79" s="81"/>
-      <c r="C79" s="77" t="s">
+      <c r="A79" s="86"/>
+      <c r="B79" s="82"/>
+      <c r="C79" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="78"/>
-      <c r="E79" s="78"/>
-      <c r="F79" s="78"/>
-      <c r="G79" s="79"/>
+      <c r="D79" s="84"/>
+      <c r="E79" s="84"/>
+      <c r="F79" s="84"/>
+      <c r="G79" s="85"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="80"/>
-      <c r="B80" s="81"/>
-      <c r="C80" s="77" t="s">
+      <c r="A80" s="86"/>
+      <c r="B80" s="82"/>
+      <c r="C80" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="78"/>
-      <c r="E80" s="78"/>
-      <c r="F80" s="78"/>
-      <c r="G80" s="79"/>
+      <c r="D80" s="84"/>
+      <c r="E80" s="84"/>
+      <c r="F80" s="84"/>
+      <c r="G80" s="85"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2593,353 +2614,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="81" t="s">
+      <c r="C81" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="81"/>
-      <c r="E81" s="81"/>
-      <c r="F81" s="81"/>
-      <c r="G81" s="81"/>
+      <c r="D81" s="82"/>
+      <c r="E81" s="82"/>
+      <c r="F81" s="82"/>
+      <c r="G81" s="82"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="80">
+      <c r="A82" s="86">
         <v>46225</v>
       </c>
-      <c r="B82" s="81" t="s">
+      <c r="B82" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="81" t="s">
+      <c r="C82" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="81"/>
-      <c r="E82" s="81"/>
-      <c r="F82" s="81"/>
-      <c r="G82" s="81"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="82"/>
+      <c r="F82" s="82"/>
+      <c r="G82" s="82"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="80"/>
-      <c r="B83" s="81"/>
-      <c r="C83" s="81" t="s">
+      <c r="A83" s="86"/>
+      <c r="B83" s="82"/>
+      <c r="C83" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="81"/>
-      <c r="E83" s="81"/>
-      <c r="F83" s="81"/>
-      <c r="G83" s="81"/>
+      <c r="D83" s="82"/>
+      <c r="E83" s="82"/>
+      <c r="F83" s="82"/>
+      <c r="G83" s="82"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="80"/>
-      <c r="B84" s="81"/>
-      <c r="C84" s="81" t="s">
+      <c r="A84" s="86"/>
+      <c r="B84" s="82"/>
+      <c r="C84" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="81"/>
-      <c r="E84" s="81"/>
-      <c r="F84" s="81"/>
-      <c r="G84" s="81"/>
+      <c r="D84" s="82"/>
+      <c r="E84" s="82"/>
+      <c r="F84" s="82"/>
+      <c r="G84" s="82"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="80"/>
-      <c r="B85" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="81" t="s">
+      <c r="A85" s="86"/>
+      <c r="B85" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="81"/>
-      <c r="E85" s="81"/>
-      <c r="F85" s="81"/>
-      <c r="G85" s="81"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="82"/>
+      <c r="F85" s="82"/>
+      <c r="G85" s="82"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="80"/>
-      <c r="B86" s="81"/>
-      <c r="C86" s="81" t="s">
+      <c r="A86" s="86"/>
+      <c r="B86" s="82"/>
+      <c r="C86" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="81"/>
-      <c r="E86" s="81"/>
-      <c r="F86" s="81"/>
-      <c r="G86" s="81"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="82"/>
+      <c r="F86" s="82"/>
+      <c r="G86" s="82"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="80"/>
-      <c r="B87" s="81"/>
-      <c r="C87" s="81" t="s">
+      <c r="A87" s="86"/>
+      <c r="B87" s="82"/>
+      <c r="C87" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="81"/>
-      <c r="E87" s="81"/>
-      <c r="F87" s="81"/>
-      <c r="G87" s="81"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="82"/>
+      <c r="F87" s="82"/>
+      <c r="G87" s="82"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="80"/>
-      <c r="B88" s="81"/>
-      <c r="C88" s="81" t="s">
+      <c r="A88" s="86"/>
+      <c r="B88" s="82"/>
+      <c r="C88" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="81"/>
-      <c r="E88" s="81"/>
-      <c r="F88" s="81"/>
-      <c r="G88" s="81"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="82"/>
+      <c r="F88" s="82"/>
+      <c r="G88" s="82"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="80"/>
-      <c r="B89" s="81"/>
-      <c r="C89" s="82" t="s">
+      <c r="A89" s="86"/>
+      <c r="B89" s="82"/>
+      <c r="C89" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="83"/>
-      <c r="E89" s="83"/>
-      <c r="F89" s="83"/>
-      <c r="G89" s="84"/>
+      <c r="D89" s="88"/>
+      <c r="E89" s="88"/>
+      <c r="F89" s="88"/>
+      <c r="G89" s="89"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="80"/>
-      <c r="B90" s="81"/>
-      <c r="C90" s="81" t="s">
+      <c r="A90" s="86"/>
+      <c r="B90" s="82"/>
+      <c r="C90" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="81"/>
-      <c r="E90" s="81"/>
-      <c r="F90" s="81"/>
-      <c r="G90" s="81"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="82"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="82"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="100">
+      <c r="A91" s="95">
         <v>46227</v>
       </c>
-      <c r="B91" s="90" t="s">
+      <c r="B91" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="81" t="s">
+      <c r="C91" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="81"/>
-      <c r="E91" s="81"/>
-      <c r="F91" s="81"/>
-      <c r="G91" s="81"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="82"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="102"/>
-      <c r="B92" s="91"/>
-      <c r="C92" s="82" t="s">
+      <c r="A92" s="96"/>
+      <c r="B92" s="94"/>
+      <c r="C92" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="83"/>
-      <c r="E92" s="83"/>
-      <c r="F92" s="83"/>
-      <c r="G92" s="84"/>
+      <c r="D92" s="88"/>
+      <c r="E92" s="88"/>
+      <c r="F92" s="88"/>
+      <c r="G92" s="89"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="80">
+      <c r="A93" s="86">
         <v>46228</v>
       </c>
-      <c r="B93" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="81" t="s">
+      <c r="B93" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="81"/>
-      <c r="E93" s="81"/>
-      <c r="F93" s="81"/>
-      <c r="G93" s="81"/>
+      <c r="D93" s="82"/>
+      <c r="E93" s="82"/>
+      <c r="F93" s="82"/>
+      <c r="G93" s="82"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="80"/>
-      <c r="B94" s="81"/>
-      <c r="C94" s="81" t="s">
+      <c r="A94" s="86"/>
+      <c r="B94" s="82"/>
+      <c r="C94" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="81"/>
-      <c r="E94" s="81"/>
-      <c r="F94" s="81"/>
-      <c r="G94" s="81"/>
+      <c r="D94" s="82"/>
+      <c r="E94" s="82"/>
+      <c r="F94" s="82"/>
+      <c r="G94" s="82"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="80"/>
-      <c r="B95" s="81"/>
-      <c r="C95" s="81" t="s">
+      <c r="A95" s="86"/>
+      <c r="B95" s="82"/>
+      <c r="C95" s="82" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="81"/>
-      <c r="E95" s="81"/>
-      <c r="F95" s="81"/>
-      <c r="G95" s="81"/>
+      <c r="D95" s="82"/>
+      <c r="E95" s="82"/>
+      <c r="F95" s="82"/>
+      <c r="G95" s="82"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="80"/>
-      <c r="B96" s="81"/>
-      <c r="C96" s="81" t="s">
+      <c r="A96" s="86"/>
+      <c r="B96" s="82"/>
+      <c r="C96" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="81"/>
-      <c r="E96" s="81"/>
-      <c r="F96" s="81"/>
-      <c r="G96" s="81"/>
+      <c r="D96" s="82"/>
+      <c r="E96" s="82"/>
+      <c r="F96" s="82"/>
+      <c r="G96" s="82"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="80"/>
-      <c r="B97" s="81"/>
-      <c r="C97" s="81" t="s">
+      <c r="A97" s="86"/>
+      <c r="B97" s="82"/>
+      <c r="C97" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="81"/>
-      <c r="E97" s="81"/>
-      <c r="F97" s="81"/>
-      <c r="G97" s="81"/>
+      <c r="D97" s="82"/>
+      <c r="E97" s="82"/>
+      <c r="F97" s="82"/>
+      <c r="G97" s="82"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="80"/>
-      <c r="B98" s="81"/>
-      <c r="C98" s="81" t="s">
+      <c r="A98" s="86"/>
+      <c r="B98" s="82"/>
+      <c r="C98" s="82" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="81"/>
-      <c r="E98" s="81"/>
-      <c r="F98" s="81"/>
-      <c r="G98" s="81"/>
+      <c r="D98" s="82"/>
+      <c r="E98" s="82"/>
+      <c r="F98" s="82"/>
+      <c r="G98" s="82"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="80">
+      <c r="A99" s="86">
         <v>46230</v>
       </c>
-      <c r="B99" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="81" t="s">
+      <c r="B99" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="81"/>
-      <c r="E99" s="81"/>
-      <c r="F99" s="81"/>
-      <c r="G99" s="81"/>
+      <c r="D99" s="82"/>
+      <c r="E99" s="82"/>
+      <c r="F99" s="82"/>
+      <c r="G99" s="82"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="80"/>
-      <c r="B100" s="81"/>
-      <c r="C100" s="81" t="s">
+      <c r="A100" s="86"/>
+      <c r="B100" s="82"/>
+      <c r="C100" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="81"/>
-      <c r="E100" s="81"/>
-      <c r="F100" s="81"/>
-      <c r="G100" s="81"/>
+      <c r="D100" s="82"/>
+      <c r="E100" s="82"/>
+      <c r="F100" s="82"/>
+      <c r="G100" s="82"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="80">
+      <c r="A101" s="86">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="106" t="s">
+      <c r="C101" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="106"/>
-      <c r="E101" s="106"/>
-      <c r="F101" s="106"/>
-      <c r="G101" s="106"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="80"/>
+      <c r="A102" s="86"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="106" t="s">
+      <c r="C102" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="106"/>
-      <c r="E102" s="106"/>
-      <c r="F102" s="106"/>
-      <c r="G102" s="106"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="105" t="s">
+      <c r="A103" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="95" t="s">
+      <c r="B103" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="95"/>
-      <c r="E103" s="95"/>
-      <c r="F103" s="95"/>
-      <c r="G103" s="95"/>
+      <c r="D103" s="91"/>
+      <c r="E103" s="91"/>
+      <c r="F103" s="91"/>
+      <c r="G103" s="91"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="105"/>
-      <c r="B104" s="81"/>
-      <c r="C104" s="81" t="s">
+      <c r="A104" s="90"/>
+      <c r="B104" s="82"/>
+      <c r="C104" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="81"/>
-      <c r="E104" s="81"/>
-      <c r="F104" s="81"/>
-      <c r="G104" s="81"/>
+      <c r="D104" s="82"/>
+      <c r="E104" s="82"/>
+      <c r="F104" s="82"/>
+      <c r="G104" s="82"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="105"/>
-      <c r="B105" s="81"/>
-      <c r="C105" s="81" t="s">
+      <c r="A105" s="90"/>
+      <c r="B105" s="82"/>
+      <c r="C105" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="81"/>
-      <c r="E105" s="81"/>
-      <c r="F105" s="81"/>
-      <c r="G105" s="81"/>
+      <c r="D105" s="82"/>
+      <c r="E105" s="82"/>
+      <c r="F105" s="82"/>
+      <c r="G105" s="82"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="105"/>
-      <c r="B106" s="81"/>
-      <c r="C106" s="81" t="s">
+      <c r="A106" s="90"/>
+      <c r="B106" s="82"/>
+      <c r="C106" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="81"/>
-      <c r="E106" s="81"/>
-      <c r="F106" s="81"/>
-      <c r="G106" s="81"/>
+      <c r="D106" s="82"/>
+      <c r="E106" s="82"/>
+      <c r="F106" s="82"/>
+      <c r="G106" s="82"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="105"/>
-      <c r="B107" s="81"/>
-      <c r="C107" s="81" t="s">
+      <c r="A107" s="90"/>
+      <c r="B107" s="82"/>
+      <c r="C107" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="81"/>
-      <c r="E107" s="81"/>
-      <c r="F107" s="81"/>
-      <c r="G107" s="81"/>
+      <c r="D107" s="82"/>
+      <c r="E107" s="82"/>
+      <c r="F107" s="82"/>
+      <c r="G107" s="82"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="80">
+      <c r="A108" s="86">
         <v>46234</v>
       </c>
-      <c r="B108" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="81" t="s">
+      <c r="B108" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="81"/>
-      <c r="E108" s="81"/>
-      <c r="F108" s="81"/>
-      <c r="G108" s="81"/>
+      <c r="D108" s="82"/>
+      <c r="E108" s="82"/>
+      <c r="F108" s="82"/>
+      <c r="G108" s="82"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="80"/>
-      <c r="B109" s="81"/>
-      <c r="C109" s="81" t="s">
+      <c r="A109" s="86"/>
+      <c r="B109" s="82"/>
+      <c r="C109" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="81"/>
-      <c r="E109" s="81"/>
-      <c r="F109" s="81"/>
-      <c r="G109" s="81"/>
+      <c r="D109" s="82"/>
+      <c r="E109" s="82"/>
+      <c r="F109" s="82"/>
+      <c r="G109" s="82"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2949,68 +2970,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -3035,67 +3055,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3113,15 +3134,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="102">
         <v>46235</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4910,7 +4931,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -5176,17 +5197,65 @@
       <c r="G21" s="32"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="26" t="s">
+      <c r="A22" s="13"/>
+      <c r="B22" s="109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="50"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="109"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="51"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>46307</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="48"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="108" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="51"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="46"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="108" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="51"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="45"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="110" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC61FC0-2798-4FAC-9CA8-77637011A78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC255FC-8954-436D-A0E2-6C9FADD9C3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="201">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -626,6 +626,15 @@
   </si>
   <si>
     <t>Nhận 96 VNSH03, lấy 100 vỏ carton, 100 dây nguồn LE, 100 anten GSM, 100 anten GPS, 200m dây nguồn VNSH03</t>
+  </si>
+  <si>
+    <t>Nhập kho</t>
+  </si>
+  <si>
+    <t>Nhận hàn ổ cứng 4 VNSH03 (A. Lực)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận BH </t>
   </si>
 </sst>
 </file>
@@ -849,7 +858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1027,6 +1036,30 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1042,91 +1075,62 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1451,15 +1455,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="77">
+      <c r="A1" s="85">
         <v>46174</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1468,146 +1472,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="81"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="86">
+      <c r="A3" s="80">
         <v>46202</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="86"/>
-      <c r="B6" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="82" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="86"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82" t="s">
+      <c r="A7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="86"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82" t="s">
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="86">
+      <c r="A9" s="80">
         <v>46203</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="89"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="86"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="83" t="s">
+      <c r="A10" s="80"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="85"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="86"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="83" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="85"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="79"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="86"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="83" t="s">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="85"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="79"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="86"/>
+      <c r="A13" s="80"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="85"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="79"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1617,14 +1621,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1635,6 +1631,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1652,15 +1656,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="102">
+      <c r="A1" s="93">
         <v>46204</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1669,152 +1673,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="86">
+      <c r="A3" s="80">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="91" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="86"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="104">
+      <c r="A7" s="96">
         <v>46205</v>
       </c>
-      <c r="B7" s="93" t="s">
+      <c r="B7" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="84"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="105"/>
-      <c r="B8" s="101"/>
-      <c r="C8" s="83" t="s">
+      <c r="A8" s="97"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="85"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="79"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="105"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="83" t="s">
+      <c r="A9" s="97"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="85"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="79"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="105"/>
-      <c r="B10" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="83" t="s">
+      <c r="A10" s="97"/>
+      <c r="B10" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="85"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="105"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="83" t="s">
+      <c r="A11" s="97"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="85"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="79"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="105"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="83" t="s">
+      <c r="A12" s="97"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="85"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="79"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="106"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="83" t="s">
+      <c r="A13" s="98"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="85"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="79"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="95">
+      <c r="A14" s="100">
         <v>46206</v>
       </c>
-      <c r="B14" s="93" t="s">
+      <c r="B14" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1826,348 +1830,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="98"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="87" t="s">
+      <c r="A15" s="101"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="89"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="84"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="98"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="87" t="s">
+      <c r="A16" s="101"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="89"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="84"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="98"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="87" t="s">
+      <c r="A17" s="101"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="89"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="84"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="98"/>
-      <c r="B18" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="87" t="s">
+      <c r="A18" s="101"/>
+      <c r="B18" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="89"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="84"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="96"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="87" t="s">
+      <c r="A19" s="102"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="89"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="84"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="99">
+      <c r="A20" s="103">
         <v>46209</v>
       </c>
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="82" t="s">
+      <c r="C20" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="99"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82" t="s">
+      <c r="A21" s="103"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="99"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82" t="s">
+      <c r="A22" s="103"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="99"/>
-      <c r="B23" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="82" t="s">
+      <c r="A23" s="103"/>
+      <c r="B23" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="82"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="99"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="87" t="s">
+      <c r="A24" s="103"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="89"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="84"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="99"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="87" t="s">
+      <c r="A25" s="103"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="89"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="84"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="99"/>
-      <c r="B26" s="82"/>
-      <c r="C26" s="87" t="s">
+      <c r="A26" s="103"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="89"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="84"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="87" t="s">
+      <c r="A27" s="103"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="89"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="84"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="99"/>
-      <c r="B28" s="82"/>
-      <c r="C28" s="87" t="s">
+      <c r="A28" s="103"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="89"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="84"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="99"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="87" t="s">
+      <c r="A29" s="103"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="89"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="84"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="99"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="87" t="s">
+      <c r="A30" s="103"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="89"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="84"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="99"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="87" t="s">
+      <c r="A31" s="103"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="89"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="84"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="99"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="87" t="s">
+      <c r="A32" s="103"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="88"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="89"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="84"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="99"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="87" t="s">
+      <c r="A33" s="103"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="89"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="84"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="99"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="87" t="s">
+      <c r="A34" s="103"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="89"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="84"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="97">
+      <c r="A35" s="99">
         <v>46210</v>
       </c>
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="82" t="s">
+      <c r="C35" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="82"/>
-      <c r="E35" s="82"/>
-      <c r="F35" s="82"/>
-      <c r="G35" s="82"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="97"/>
-      <c r="B36" s="82"/>
-      <c r="C36" s="82" t="s">
+      <c r="A36" s="99"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="82"/>
-      <c r="E36" s="82"/>
-      <c r="F36" s="82"/>
-      <c r="G36" s="82"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="97"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="82" t="s">
+      <c r="A37" s="99"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="82"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="82"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="97"/>
-      <c r="B38" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="82" t="s">
+      <c r="A38" s="99"/>
+      <c r="B38" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="82"/>
-      <c r="E38" s="82"/>
-      <c r="F38" s="82"/>
-      <c r="G38" s="82"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="97"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="82" t="s">
+      <c r="A39" s="99"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="82"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="82"/>
-      <c r="G39" s="82"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="97"/>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82" t="s">
+      <c r="A40" s="99"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="82"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="82"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="97"/>
-      <c r="B41" s="82"/>
-      <c r="C41" s="82" t="s">
+      <c r="A41" s="99"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="97"/>
-      <c r="B42" s="82"/>
-      <c r="C42" s="82" t="s">
+      <c r="A42" s="99"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="82"/>
-      <c r="E42" s="82"/>
-      <c r="F42" s="82"/>
-      <c r="G42" s="82"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="97"/>
-      <c r="B43" s="82"/>
-      <c r="C43" s="82" t="s">
+      <c r="A43" s="99"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82"/>
-      <c r="F43" s="82"/>
-      <c r="G43" s="82"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="97"/>
-      <c r="B44" s="82"/>
-      <c r="C44" s="87" t="s">
+      <c r="A44" s="99"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="88"/>
-      <c r="G44" s="89"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="84"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2176,13 +2180,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="82" t="s">
+      <c r="C45" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="82"/>
-      <c r="E45" s="82"/>
-      <c r="F45" s="82"/>
-      <c r="G45" s="82"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2191,255 +2195,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="82" t="s">
+      <c r="C46" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="82"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="82"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="95">
+      <c r="A47" s="100">
         <v>46213</v>
       </c>
-      <c r="B47" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="87" t="s">
+      <c r="B47" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="88"/>
-      <c r="E47" s="88"/>
-      <c r="F47" s="88"/>
-      <c r="G47" s="89"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="84"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="98"/>
-      <c r="B48" s="101"/>
-      <c r="C48" s="87" t="s">
+      <c r="A48" s="101"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="89"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="84"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="98"/>
-      <c r="B49" s="101"/>
-      <c r="C49" s="87" t="s">
+      <c r="A49" s="101"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="88"/>
-      <c r="E49" s="88"/>
-      <c r="F49" s="88"/>
-      <c r="G49" s="89"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="84"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="98"/>
-      <c r="B50" s="101"/>
-      <c r="C50" s="87" t="s">
+      <c r="A50" s="101"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="88"/>
-      <c r="E50" s="88"/>
-      <c r="F50" s="88"/>
-      <c r="G50" s="89"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="84"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="96"/>
-      <c r="B51" s="94"/>
-      <c r="C51" s="87" t="s">
+      <c r="A51" s="102"/>
+      <c r="B51" s="91"/>
+      <c r="C51" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="88"/>
-      <c r="E51" s="88"/>
-      <c r="F51" s="88"/>
-      <c r="G51" s="89"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="84"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="86">
+      <c r="A52" s="80">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="82" t="s">
+      <c r="C52" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="82"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="82" t="s">
+      <c r="C53" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="82"/>
-      <c r="E53" s="82"/>
-      <c r="F53" s="82"/>
-      <c r="G53" s="82"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="86">
+      <c r="A54" s="80">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="87" t="s">
+      <c r="C54" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="88"/>
-      <c r="E54" s="88"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="89"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="83"/>
+      <c r="G54" s="84"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="86"/>
-      <c r="B55" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="100" t="s">
+      <c r="A55" s="80"/>
+      <c r="B55" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="100"/>
-      <c r="E55" s="100"/>
-      <c r="F55" s="100"/>
-      <c r="G55" s="100"/>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="104"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="86"/>
-      <c r="B56" s="82"/>
-      <c r="C56" s="100" t="s">
+      <c r="A56" s="80"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="100"/>
-      <c r="E56" s="100"/>
-      <c r="F56" s="100"/>
-      <c r="G56" s="100"/>
+      <c r="D56" s="104"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="104"/>
+      <c r="G56" s="104"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="86"/>
-      <c r="B57" s="82"/>
-      <c r="C57" s="100" t="s">
+      <c r="A57" s="80"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="100"/>
-      <c r="E57" s="100"/>
-      <c r="F57" s="100"/>
-      <c r="G57" s="100"/>
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="104"/>
+      <c r="G57" s="104"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="86"/>
-      <c r="B58" s="82"/>
-      <c r="C58" s="100" t="s">
+      <c r="A58" s="80"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="100"/>
-      <c r="E58" s="100"/>
-      <c r="F58" s="100"/>
-      <c r="G58" s="100"/>
+      <c r="D58" s="104"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="104"/>
+      <c r="G58" s="104"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="86"/>
-      <c r="B59" s="82"/>
-      <c r="C59" s="100" t="s">
+      <c r="A59" s="80"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="100"/>
-      <c r="E59" s="100"/>
-      <c r="F59" s="100"/>
-      <c r="G59" s="100"/>
+      <c r="D59" s="104"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="104"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="86"/>
-      <c r="B60" s="82"/>
-      <c r="C60" s="100" t="s">
+      <c r="A60" s="80"/>
+      <c r="B60" s="81"/>
+      <c r="C60" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="100"/>
-      <c r="E60" s="100"/>
-      <c r="F60" s="100"/>
-      <c r="G60" s="100"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="86"/>
-      <c r="B61" s="82"/>
-      <c r="C61" s="100" t="s">
+      <c r="A61" s="80"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="100"/>
-      <c r="E61" s="100"/>
-      <c r="F61" s="100"/>
-      <c r="G61" s="100"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="104"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="86"/>
-      <c r="B62" s="82"/>
-      <c r="C62" s="100" t="s">
+      <c r="A62" s="80"/>
+      <c r="B62" s="81"/>
+      <c r="C62" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="100"/>
-      <c r="E62" s="100"/>
-      <c r="F62" s="100"/>
-      <c r="G62" s="100"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="86"/>
-      <c r="B63" s="82"/>
-      <c r="C63" s="100" t="s">
+      <c r="A63" s="80"/>
+      <c r="B63" s="81"/>
+      <c r="C63" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="100"/>
-      <c r="E63" s="100"/>
-      <c r="F63" s="100"/>
-      <c r="G63" s="100"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="86">
+      <c r="A64" s="80">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="82" t="s">
+      <c r="C64" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="82"/>
-      <c r="E64" s="82"/>
-      <c r="F64" s="82"/>
-      <c r="G64" s="82"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="81"/>
+      <c r="F64" s="81"/>
+      <c r="G64" s="81"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="86"/>
-      <c r="B65" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="82" t="s">
+      <c r="A65" s="80"/>
+      <c r="B65" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="82"/>
-      <c r="E65" s="82"/>
-      <c r="F65" s="82"/>
-      <c r="G65" s="82"/>
+      <c r="D65" s="81"/>
+      <c r="E65" s="81"/>
+      <c r="F65" s="81"/>
+      <c r="G65" s="81"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="86"/>
-      <c r="B66" s="82"/>
-      <c r="C66" s="82" t="s">
+      <c r="A66" s="80"/>
+      <c r="B66" s="81"/>
+      <c r="C66" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="82"/>
-      <c r="E66" s="82"/>
-      <c r="F66" s="82"/>
-      <c r="G66" s="82"/>
+      <c r="D66" s="81"/>
+      <c r="E66" s="81"/>
+      <c r="F66" s="81"/>
+      <c r="G66" s="81"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2448,164 +2452,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="82" t="s">
+      <c r="C67" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="82"/>
-      <c r="E67" s="82"/>
-      <c r="F67" s="82"/>
-      <c r="G67" s="82"/>
+      <c r="D67" s="81"/>
+      <c r="E67" s="81"/>
+      <c r="F67" s="81"/>
+      <c r="G67" s="81"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="86">
+      <c r="A68" s="80">
         <v>46220</v>
       </c>
-      <c r="B68" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="82" t="s">
+      <c r="B68" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="82"/>
-      <c r="E68" s="82"/>
-      <c r="F68" s="82"/>
-      <c r="G68" s="82"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="86"/>
-      <c r="B69" s="82"/>
-      <c r="C69" s="82" t="s">
+      <c r="A69" s="80"/>
+      <c r="B69" s="81"/>
+      <c r="C69" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
-      <c r="F69" s="82"/>
-      <c r="G69" s="82"/>
+      <c r="D69" s="81"/>
+      <c r="E69" s="81"/>
+      <c r="F69" s="81"/>
+      <c r="G69" s="81"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="86">
+      <c r="A70" s="80">
         <v>46223</v>
       </c>
-      <c r="B70" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="87" t="s">
+      <c r="B70" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="88"/>
-      <c r="E70" s="88"/>
-      <c r="F70" s="88"/>
-      <c r="G70" s="89"/>
+      <c r="D70" s="83"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="83"/>
+      <c r="G70" s="84"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="86"/>
-      <c r="B71" s="82"/>
-      <c r="C71" s="87" t="s">
+      <c r="A71" s="80"/>
+      <c r="B71" s="81"/>
+      <c r="C71" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="88"/>
-      <c r="E71" s="88"/>
-      <c r="F71" s="88"/>
-      <c r="G71" s="89"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="83"/>
+      <c r="G71" s="84"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="86"/>
-      <c r="B72" s="82"/>
-      <c r="C72" s="87" t="s">
+      <c r="A72" s="80"/>
+      <c r="B72" s="81"/>
+      <c r="C72" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="88"/>
-      <c r="E72" s="88"/>
-      <c r="F72" s="88"/>
-      <c r="G72" s="89"/>
+      <c r="D72" s="83"/>
+      <c r="E72" s="83"/>
+      <c r="F72" s="83"/>
+      <c r="G72" s="84"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="86"/>
-      <c r="B73" s="82"/>
-      <c r="C73" s="87" t="s">
+      <c r="A73" s="80"/>
+      <c r="B73" s="81"/>
+      <c r="C73" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="88"/>
-      <c r="E73" s="88"/>
-      <c r="F73" s="88"/>
-      <c r="G73" s="89"/>
+      <c r="D73" s="83"/>
+      <c r="E73" s="83"/>
+      <c r="F73" s="83"/>
+      <c r="G73" s="84"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="86"/>
-      <c r="B74" s="82"/>
-      <c r="C74" s="87" t="s">
+      <c r="A74" s="80"/>
+      <c r="B74" s="81"/>
+      <c r="C74" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="88"/>
-      <c r="E74" s="88"/>
-      <c r="F74" s="88"/>
-      <c r="G74" s="89"/>
+      <c r="D74" s="83"/>
+      <c r="E74" s="83"/>
+      <c r="F74" s="83"/>
+      <c r="G74" s="84"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="86"/>
-      <c r="B75" s="82"/>
-      <c r="C75" s="87" t="s">
+      <c r="A75" s="80"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="88"/>
-      <c r="E75" s="88"/>
-      <c r="F75" s="88"/>
-      <c r="G75" s="89"/>
+      <c r="D75" s="83"/>
+      <c r="E75" s="83"/>
+      <c r="F75" s="83"/>
+      <c r="G75" s="84"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="86"/>
-      <c r="B76" s="82"/>
-      <c r="C76" s="87" t="s">
+      <c r="A76" s="80"/>
+      <c r="B76" s="81"/>
+      <c r="C76" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="88"/>
-      <c r="E76" s="88"/>
-      <c r="F76" s="88"/>
-      <c r="G76" s="89"/>
+      <c r="D76" s="83"/>
+      <c r="E76" s="83"/>
+      <c r="F76" s="83"/>
+      <c r="G76" s="84"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="86"/>
-      <c r="B77" s="82"/>
-      <c r="C77" s="83" t="s">
+      <c r="A77" s="80"/>
+      <c r="B77" s="81"/>
+      <c r="C77" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="84"/>
-      <c r="E77" s="84"/>
-      <c r="F77" s="84"/>
-      <c r="G77" s="85"/>
+      <c r="D77" s="78"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="78"/>
+      <c r="G77" s="79"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="86"/>
-      <c r="B78" s="82"/>
-      <c r="C78" s="83" t="s">
+      <c r="A78" s="80"/>
+      <c r="B78" s="81"/>
+      <c r="C78" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="84"/>
-      <c r="E78" s="84"/>
-      <c r="F78" s="84"/>
-      <c r="G78" s="85"/>
+      <c r="D78" s="78"/>
+      <c r="E78" s="78"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="79"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="86"/>
-      <c r="B79" s="82"/>
-      <c r="C79" s="83" t="s">
+      <c r="A79" s="80"/>
+      <c r="B79" s="81"/>
+      <c r="C79" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="84"/>
-      <c r="E79" s="84"/>
-      <c r="F79" s="84"/>
-      <c r="G79" s="85"/>
+      <c r="D79" s="78"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="78"/>
+      <c r="G79" s="79"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="86"/>
-      <c r="B80" s="82"/>
-      <c r="C80" s="83" t="s">
+      <c r="A80" s="80"/>
+      <c r="B80" s="81"/>
+      <c r="C80" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="84"/>
-      <c r="E80" s="84"/>
-      <c r="F80" s="84"/>
-      <c r="G80" s="85"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="79"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2614,353 +2618,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="82" t="s">
+      <c r="C81" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="82"/>
-      <c r="E81" s="82"/>
-      <c r="F81" s="82"/>
-      <c r="G81" s="82"/>
+      <c r="D81" s="81"/>
+      <c r="E81" s="81"/>
+      <c r="F81" s="81"/>
+      <c r="G81" s="81"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="86">
+      <c r="A82" s="80">
         <v>46225</v>
       </c>
-      <c r="B82" s="82" t="s">
+      <c r="B82" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="82" t="s">
+      <c r="C82" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
+      <c r="D82" s="81"/>
+      <c r="E82" s="81"/>
+      <c r="F82" s="81"/>
+      <c r="G82" s="81"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="86"/>
-      <c r="B83" s="82"/>
-      <c r="C83" s="82" t="s">
+      <c r="A83" s="80"/>
+      <c r="B83" s="81"/>
+      <c r="C83" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="82"/>
-      <c r="E83" s="82"/>
-      <c r="F83" s="82"/>
-      <c r="G83" s="82"/>
+      <c r="D83" s="81"/>
+      <c r="E83" s="81"/>
+      <c r="F83" s="81"/>
+      <c r="G83" s="81"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="86"/>
-      <c r="B84" s="82"/>
-      <c r="C84" s="82" t="s">
+      <c r="A84" s="80"/>
+      <c r="B84" s="81"/>
+      <c r="C84" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="82"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
+      <c r="D84" s="81"/>
+      <c r="E84" s="81"/>
+      <c r="F84" s="81"/>
+      <c r="G84" s="81"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="86"/>
-      <c r="B85" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="82" t="s">
+      <c r="A85" s="80"/>
+      <c r="B85" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="82"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
+      <c r="D85" s="81"/>
+      <c r="E85" s="81"/>
+      <c r="F85" s="81"/>
+      <c r="G85" s="81"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="86"/>
-      <c r="B86" s="82"/>
-      <c r="C86" s="82" t="s">
+      <c r="A86" s="80"/>
+      <c r="B86" s="81"/>
+      <c r="C86" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="82"/>
-      <c r="E86" s="82"/>
-      <c r="F86" s="82"/>
-      <c r="G86" s="82"/>
+      <c r="D86" s="81"/>
+      <c r="E86" s="81"/>
+      <c r="F86" s="81"/>
+      <c r="G86" s="81"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="86"/>
-      <c r="B87" s="82"/>
-      <c r="C87" s="82" t="s">
+      <c r="A87" s="80"/>
+      <c r="B87" s="81"/>
+      <c r="C87" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="82"/>
-      <c r="E87" s="82"/>
-      <c r="F87" s="82"/>
-      <c r="G87" s="82"/>
+      <c r="D87" s="81"/>
+      <c r="E87" s="81"/>
+      <c r="F87" s="81"/>
+      <c r="G87" s="81"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="86"/>
-      <c r="B88" s="82"/>
-      <c r="C88" s="82" t="s">
+      <c r="A88" s="80"/>
+      <c r="B88" s="81"/>
+      <c r="C88" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="82"/>
-      <c r="E88" s="82"/>
-      <c r="F88" s="82"/>
-      <c r="G88" s="82"/>
+      <c r="D88" s="81"/>
+      <c r="E88" s="81"/>
+      <c r="F88" s="81"/>
+      <c r="G88" s="81"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="86"/>
-      <c r="B89" s="82"/>
-      <c r="C89" s="87" t="s">
+      <c r="A89" s="80"/>
+      <c r="B89" s="81"/>
+      <c r="C89" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="88"/>
-      <c r="E89" s="88"/>
-      <c r="F89" s="88"/>
-      <c r="G89" s="89"/>
+      <c r="D89" s="83"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="83"/>
+      <c r="G89" s="84"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="86"/>
-      <c r="B90" s="82"/>
-      <c r="C90" s="82" t="s">
+      <c r="A90" s="80"/>
+      <c r="B90" s="81"/>
+      <c r="C90" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
+      <c r="D90" s="81"/>
+      <c r="E90" s="81"/>
+      <c r="F90" s="81"/>
+      <c r="G90" s="81"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="95">
+      <c r="A91" s="100">
         <v>46227</v>
       </c>
-      <c r="B91" s="93" t="s">
+      <c r="B91" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="82" t="s">
+      <c r="C91" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="82"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
+      <c r="D91" s="81"/>
+      <c r="E91" s="81"/>
+      <c r="F91" s="81"/>
+      <c r="G91" s="81"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="96"/>
-      <c r="B92" s="94"/>
-      <c r="C92" s="87" t="s">
+      <c r="A92" s="102"/>
+      <c r="B92" s="91"/>
+      <c r="C92" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="88"/>
-      <c r="E92" s="88"/>
-      <c r="F92" s="88"/>
-      <c r="G92" s="89"/>
+      <c r="D92" s="83"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="83"/>
+      <c r="G92" s="84"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="86">
+      <c r="A93" s="80">
         <v>46228</v>
       </c>
-      <c r="B93" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="82" t="s">
+      <c r="B93" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="82"/>
-      <c r="E93" s="82"/>
-      <c r="F93" s="82"/>
-      <c r="G93" s="82"/>
+      <c r="D93" s="81"/>
+      <c r="E93" s="81"/>
+      <c r="F93" s="81"/>
+      <c r="G93" s="81"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="86"/>
-      <c r="B94" s="82"/>
-      <c r="C94" s="82" t="s">
+      <c r="A94" s="80"/>
+      <c r="B94" s="81"/>
+      <c r="C94" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="82"/>
-      <c r="E94" s="82"/>
-      <c r="F94" s="82"/>
-      <c r="G94" s="82"/>
+      <c r="D94" s="81"/>
+      <c r="E94" s="81"/>
+      <c r="F94" s="81"/>
+      <c r="G94" s="81"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="86"/>
-      <c r="B95" s="82"/>
-      <c r="C95" s="82" t="s">
+      <c r="A95" s="80"/>
+      <c r="B95" s="81"/>
+      <c r="C95" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="82"/>
-      <c r="E95" s="82"/>
-      <c r="F95" s="82"/>
-      <c r="G95" s="82"/>
+      <c r="D95" s="81"/>
+      <c r="E95" s="81"/>
+      <c r="F95" s="81"/>
+      <c r="G95" s="81"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="86"/>
-      <c r="B96" s="82"/>
-      <c r="C96" s="82" t="s">
+      <c r="A96" s="80"/>
+      <c r="B96" s="81"/>
+      <c r="C96" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="82"/>
-      <c r="E96" s="82"/>
-      <c r="F96" s="82"/>
-      <c r="G96" s="82"/>
+      <c r="D96" s="81"/>
+      <c r="E96" s="81"/>
+      <c r="F96" s="81"/>
+      <c r="G96" s="81"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="86"/>
-      <c r="B97" s="82"/>
-      <c r="C97" s="82" t="s">
+      <c r="A97" s="80"/>
+      <c r="B97" s="81"/>
+      <c r="C97" s="81" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="82"/>
-      <c r="E97" s="82"/>
-      <c r="F97" s="82"/>
-      <c r="G97" s="82"/>
+      <c r="D97" s="81"/>
+      <c r="E97" s="81"/>
+      <c r="F97" s="81"/>
+      <c r="G97" s="81"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="86"/>
-      <c r="B98" s="82"/>
-      <c r="C98" s="82" t="s">
+      <c r="A98" s="80"/>
+      <c r="B98" s="81"/>
+      <c r="C98" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="82"/>
-      <c r="E98" s="82"/>
-      <c r="F98" s="82"/>
-      <c r="G98" s="82"/>
+      <c r="D98" s="81"/>
+      <c r="E98" s="81"/>
+      <c r="F98" s="81"/>
+      <c r="G98" s="81"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="86">
+      <c r="A99" s="80">
         <v>46230</v>
       </c>
-      <c r="B99" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="82" t="s">
+      <c r="B99" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="82"/>
-      <c r="E99" s="82"/>
-      <c r="F99" s="82"/>
-      <c r="G99" s="82"/>
+      <c r="D99" s="81"/>
+      <c r="E99" s="81"/>
+      <c r="F99" s="81"/>
+      <c r="G99" s="81"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="86"/>
-      <c r="B100" s="82"/>
-      <c r="C100" s="82" t="s">
+      <c r="A100" s="80"/>
+      <c r="B100" s="81"/>
+      <c r="C100" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="82"/>
-      <c r="E100" s="82"/>
-      <c r="F100" s="82"/>
-      <c r="G100" s="82"/>
+      <c r="D100" s="81"/>
+      <c r="E100" s="81"/>
+      <c r="F100" s="81"/>
+      <c r="G100" s="81"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="86">
+      <c r="A101" s="80">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="92" t="s">
+      <c r="C101" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="92"/>
-      <c r="E101" s="92"/>
-      <c r="F101" s="92"/>
-      <c r="G101" s="92"/>
+      <c r="D101" s="106"/>
+      <c r="E101" s="106"/>
+      <c r="F101" s="106"/>
+      <c r="G101" s="106"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="86"/>
+      <c r="A102" s="80"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="92" t="s">
+      <c r="C102" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="92"/>
-      <c r="E102" s="92"/>
-      <c r="F102" s="92"/>
-      <c r="G102" s="92"/>
+      <c r="D102" s="106"/>
+      <c r="E102" s="106"/>
+      <c r="F102" s="106"/>
+      <c r="G102" s="106"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="90" t="s">
+      <c r="A103" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="91" t="s">
+      <c r="B103" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="91"/>
-      <c r="E103" s="91"/>
-      <c r="F103" s="91"/>
-      <c r="G103" s="91"/>
+      <c r="D103" s="95"/>
+      <c r="E103" s="95"/>
+      <c r="F103" s="95"/>
+      <c r="G103" s="95"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="90"/>
-      <c r="B104" s="82"/>
-      <c r="C104" s="82" t="s">
+      <c r="A104" s="105"/>
+      <c r="B104" s="81"/>
+      <c r="C104" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="82"/>
-      <c r="E104" s="82"/>
-      <c r="F104" s="82"/>
-      <c r="G104" s="82"/>
+      <c r="D104" s="81"/>
+      <c r="E104" s="81"/>
+      <c r="F104" s="81"/>
+      <c r="G104" s="81"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="90"/>
-      <c r="B105" s="82"/>
-      <c r="C105" s="82" t="s">
+      <c r="A105" s="105"/>
+      <c r="B105" s="81"/>
+      <c r="C105" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="82"/>
-      <c r="E105" s="82"/>
-      <c r="F105" s="82"/>
-      <c r="G105" s="82"/>
+      <c r="D105" s="81"/>
+      <c r="E105" s="81"/>
+      <c r="F105" s="81"/>
+      <c r="G105" s="81"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="90"/>
-      <c r="B106" s="82"/>
-      <c r="C106" s="82" t="s">
+      <c r="A106" s="105"/>
+      <c r="B106" s="81"/>
+      <c r="C106" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="82"/>
-      <c r="E106" s="82"/>
-      <c r="F106" s="82"/>
-      <c r="G106" s="82"/>
+      <c r="D106" s="81"/>
+      <c r="E106" s="81"/>
+      <c r="F106" s="81"/>
+      <c r="G106" s="81"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="90"/>
-      <c r="B107" s="82"/>
-      <c r="C107" s="82" t="s">
+      <c r="A107" s="105"/>
+      <c r="B107" s="81"/>
+      <c r="C107" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="82"/>
-      <c r="E107" s="82"/>
-      <c r="F107" s="82"/>
-      <c r="G107" s="82"/>
+      <c r="D107" s="81"/>
+      <c r="E107" s="81"/>
+      <c r="F107" s="81"/>
+      <c r="G107" s="81"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="86">
+      <c r="A108" s="80">
         <v>46234</v>
       </c>
-      <c r="B108" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="82" t="s">
+      <c r="B108" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="82"/>
-      <c r="E108" s="82"/>
-      <c r="F108" s="82"/>
-      <c r="G108" s="82"/>
+      <c r="D108" s="81"/>
+      <c r="E108" s="81"/>
+      <c r="F108" s="81"/>
+      <c r="G108" s="81"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="86"/>
-      <c r="B109" s="82"/>
-      <c r="C109" s="82" t="s">
+      <c r="A109" s="80"/>
+      <c r="B109" s="81"/>
+      <c r="C109" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="82"/>
-      <c r="E109" s="82"/>
-      <c r="F109" s="82"/>
-      <c r="G109" s="82"/>
+      <c r="D109" s="81"/>
+      <c r="E109" s="81"/>
+      <c r="F109" s="81"/>
+      <c r="G109" s="81"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2970,6 +2974,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2994,129 +3121,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3134,15 +3138,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="102">
+      <c r="A1" s="93">
         <v>46235</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4931,7 +4935,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -5198,15 +5202,15 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
-      <c r="B22" s="109" t="s">
+      <c r="B22" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
       <c r="G22" s="51"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -5226,36 +5230,57 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
-      <c r="B24" s="109"/>
-      <c r="C24" s="108" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
       <c r="G24" s="51"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="46"/>
-      <c r="B25" s="109"/>
-      <c r="C25" s="108" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="D25" s="109"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="109"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="51"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
       <c r="B26" s="49"/>
-      <c r="C26" s="110" t="s">
+      <c r="C26" s="26" t="s">
         <v>195</v>
       </c>
       <c r="D26" s="49"/>
       <c r="E26" s="49"/>
       <c r="F26" s="49"/>
       <c r="G26" s="50"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="108">
+        <v>46308</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="109" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C28" s="109" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C29" s="109" t="s">
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC255FC-8954-436D-A0E2-6C9FADD9C3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9114948F-B25F-4253-9C0E-5D61CD3AAD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView minimized="1" xWindow="5220" yWindow="1170" windowWidth="21600" windowHeight="11835" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="210">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -628,13 +628,40 @@
     <t>Nhận 96 VNSH03, lấy 100 vỏ carton, 100 dây nguồn LE, 100 anten GSM, 100 anten GPS, 200m dây nguồn VNSH03</t>
   </si>
   <si>
-    <t>Nhập kho</t>
-  </si>
-  <si>
-    <t>Nhận hàn ổ cứng 4 VNSH03 (A. Lực)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhận BH </t>
+    <t>Nhập kho 51 VNSH03, 100 RFID(Old), 50 RFID(New)</t>
+  </si>
+  <si>
+    <t>Hàn thêm 2 VNSH03 M2 (hàng của kho A.Thông, Quân đưa lên trả cho A. Lực)</t>
+  </si>
+  <si>
+    <t>Nhận hàn thêm 4 VNSH03 SEA M2 ( A. Lực đưa lên trả 3 cho A. Lực, 1 cho A. Bảo)</t>
+  </si>
+  <si>
+    <t>Nhận BH  SEA</t>
+  </si>
+  <si>
+    <t>Nhân BH GPS Global</t>
+  </si>
+  <si>
+    <t>Nhân BH GPS Tây Ninh</t>
+  </si>
+  <si>
+    <t>Nhập lại kho 2 VNSH03 đổi bảo hành Victory đã làm mới</t>
+  </si>
+  <si>
+    <t>Nhập kho 87 VNSH03</t>
+  </si>
+  <si>
+    <t>Nhập kho 100 RFID New</t>
+  </si>
+  <si>
+    <t>Hàn thêm 1 VNSH03 M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xuất thêm 100 Anten GPS, 100 Anten GSM, 130 dây mở rộng VNSH03 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận </t>
   </si>
 </sst>
 </file>
@@ -858,7 +885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1036,6 +1063,24 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1048,9 +1093,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1060,20 +1102,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1081,6 +1117,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1090,9 +1144,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1102,35 +1153,10 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1455,15 +1481,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="85">
+      <c r="A1" s="77">
         <v>46174</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1472,146 +1498,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="81"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="80">
+      <c r="A3" s="86">
         <v>46202</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="86"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="80"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81" t="s">
+      <c r="A5" s="86"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="81" t="s">
+      <c r="A6" s="86"/>
+      <c r="B6" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="80"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81" t="s">
+      <c r="A7" s="86"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="80"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81" t="s">
+      <c r="A8" s="86"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="80">
+      <c r="A9" s="86">
         <v>46203</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="84"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="89"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="80"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="77" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="85"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="77" t="s">
+      <c r="A11" s="86"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="79"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="85"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="77" t="s">
+      <c r="A12" s="86"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="85"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="80"/>
+      <c r="A13" s="86"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="85"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1621,6 +1647,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1631,14 +1665,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1656,15 +1682,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="102">
         <v>46204</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1673,152 +1699,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="80">
+      <c r="A3" s="86">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="95" t="s">
+      <c r="A4" s="86"/>
+      <c r="B4" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="80"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81" t="s">
+      <c r="A5" s="86"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81" t="s">
+      <c r="A6" s="86"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="96">
+      <c r="A7" s="104">
         <v>46205</v>
       </c>
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="84"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="97"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="77" t="s">
+      <c r="A8" s="105"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="79"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="85"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="97"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="77" t="s">
+      <c r="A9" s="105"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="79"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="85"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="97"/>
-      <c r="B10" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="77" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="85"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="97"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="77" t="s">
+      <c r="A11" s="105"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="79"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="85"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="97"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="77" t="s">
+      <c r="A12" s="105"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="85"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="98"/>
-      <c r="B13" s="81"/>
-      <c r="C13" s="77" t="s">
+      <c r="A13" s="106"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="85"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="100">
+      <c r="A14" s="95">
         <v>46206</v>
       </c>
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="93" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1830,348 +1856,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="101"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="82" t="s">
+      <c r="A15" s="98"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="84"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="89"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="101"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="82" t="s">
+      <c r="A16" s="98"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="84"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="89"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="101"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="82" t="s">
+      <c r="A17" s="98"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="84"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="89"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="101"/>
-      <c r="B18" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="82" t="s">
+      <c r="A18" s="98"/>
+      <c r="B18" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="84"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="89"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="102"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="82" t="s">
+      <c r="A19" s="96"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="84"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="89"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="103">
+      <c r="A20" s="99">
         <v>46209</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="81" t="s">
+      <c r="C20" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="103"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="81" t="s">
+      <c r="A21" s="99"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="103"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="81" t="s">
+      <c r="A22" s="99"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="103"/>
-      <c r="B23" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="81" t="s">
+      <c r="A23" s="99"/>
+      <c r="B23" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="103"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="82" t="s">
+      <c r="A24" s="99"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="84"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="89"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="103"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="82" t="s">
+      <c r="A25" s="99"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="84"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="89"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="103"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="82" t="s">
+      <c r="A26" s="99"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="84"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="89"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="103"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="82" t="s">
+      <c r="A27" s="99"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="84"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="89"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="103"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="82" t="s">
+      <c r="A28" s="99"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="84"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="89"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="103"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="82" t="s">
+      <c r="A29" s="99"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="84"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="89"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="103"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="82" t="s">
+      <c r="A30" s="99"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="84"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="89"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="103"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="82" t="s">
+      <c r="A31" s="99"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="84"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="89"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="103"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="82" t="s">
+      <c r="A32" s="99"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="84"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="89"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="103"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="82" t="s">
+      <c r="A33" s="99"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="84"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="89"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="103"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="82" t="s">
+      <c r="A34" s="99"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="84"/>
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="89"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="99">
+      <c r="A35" s="97">
         <v>46210</v>
       </c>
-      <c r="B35" s="81" t="s">
+      <c r="B35" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="99"/>
-      <c r="B36" s="81"/>
-      <c r="C36" s="81" t="s">
+      <c r="A36" s="97"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="99"/>
-      <c r="B37" s="81"/>
-      <c r="C37" s="81" t="s">
+      <c r="A37" s="97"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="99"/>
-      <c r="B38" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="81" t="s">
+      <c r="A38" s="97"/>
+      <c r="B38" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="99"/>
-      <c r="B39" s="81"/>
-      <c r="C39" s="81" t="s">
+      <c r="A39" s="97"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="99"/>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81" t="s">
+      <c r="A40" s="97"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="99"/>
-      <c r="B41" s="81"/>
-      <c r="C41" s="81" t="s">
+      <c r="A41" s="97"/>
+      <c r="B41" s="82"/>
+      <c r="C41" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="99"/>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81" t="s">
+      <c r="A42" s="97"/>
+      <c r="B42" s="82"/>
+      <c r="C42" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="82"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="99"/>
-      <c r="B43" s="81"/>
-      <c r="C43" s="81" t="s">
+      <c r="A43" s="97"/>
+      <c r="B43" s="82"/>
+      <c r="C43" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="82"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="99"/>
-      <c r="B44" s="81"/>
-      <c r="C44" s="82" t="s">
+      <c r="A44" s="97"/>
+      <c r="B44" s="82"/>
+      <c r="C44" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="84"/>
+      <c r="D44" s="88"/>
+      <c r="E44" s="88"/>
+      <c r="F44" s="88"/>
+      <c r="G44" s="89"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2180,13 +2206,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="81" t="s">
+      <c r="C45" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="82"/>
+      <c r="F45" s="82"/>
+      <c r="G45" s="82"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2195,255 +2221,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="81" t="s">
+      <c r="C46" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="81"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="82"/>
+      <c r="G46" s="82"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="100">
+      <c r="A47" s="95">
         <v>46213</v>
       </c>
-      <c r="B47" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="82" t="s">
+      <c r="B47" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="84"/>
+      <c r="D47" s="88"/>
+      <c r="E47" s="88"/>
+      <c r="F47" s="88"/>
+      <c r="G47" s="89"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="101"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="82" t="s">
+      <c r="A48" s="98"/>
+      <c r="B48" s="101"/>
+      <c r="C48" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="84"/>
+      <c r="D48" s="88"/>
+      <c r="E48" s="88"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="89"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="101"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="82" t="s">
+      <c r="A49" s="98"/>
+      <c r="B49" s="101"/>
+      <c r="C49" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="84"/>
+      <c r="D49" s="88"/>
+      <c r="E49" s="88"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="89"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="101"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="82" t="s">
+      <c r="A50" s="98"/>
+      <c r="B50" s="101"/>
+      <c r="C50" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="84"/>
+      <c r="D50" s="88"/>
+      <c r="E50" s="88"/>
+      <c r="F50" s="88"/>
+      <c r="G50" s="89"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="102"/>
-      <c r="B51" s="91"/>
-      <c r="C51" s="82" t="s">
+      <c r="A51" s="96"/>
+      <c r="B51" s="94"/>
+      <c r="C51" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="84"/>
+      <c r="D51" s="88"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="89"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="80">
+      <c r="A52" s="86">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="81" t="s">
+      <c r="C52" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
+      <c r="D52" s="82"/>
+      <c r="E52" s="82"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="82"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="82"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="80">
+      <c r="A54" s="86">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="82" t="s">
+      <c r="C54" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="84"/>
+      <c r="D54" s="88"/>
+      <c r="E54" s="88"/>
+      <c r="F54" s="88"/>
+      <c r="G54" s="89"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="80"/>
-      <c r="B55" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="104" t="s">
+      <c r="A55" s="86"/>
+      <c r="B55" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="104"/>
-      <c r="E55" s="104"/>
-      <c r="F55" s="104"/>
-      <c r="G55" s="104"/>
+      <c r="D55" s="100"/>
+      <c r="E55" s="100"/>
+      <c r="F55" s="100"/>
+      <c r="G55" s="100"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="80"/>
-      <c r="B56" s="81"/>
-      <c r="C56" s="104" t="s">
+      <c r="A56" s="86"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="104"/>
-      <c r="E56" s="104"/>
-      <c r="F56" s="104"/>
-      <c r="G56" s="104"/>
+      <c r="D56" s="100"/>
+      <c r="E56" s="100"/>
+      <c r="F56" s="100"/>
+      <c r="G56" s="100"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="80"/>
-      <c r="B57" s="81"/>
-      <c r="C57" s="104" t="s">
+      <c r="A57" s="86"/>
+      <c r="B57" s="82"/>
+      <c r="C57" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="104"/>
-      <c r="E57" s="104"/>
-      <c r="F57" s="104"/>
-      <c r="G57" s="104"/>
+      <c r="D57" s="100"/>
+      <c r="E57" s="100"/>
+      <c r="F57" s="100"/>
+      <c r="G57" s="100"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="80"/>
-      <c r="B58" s="81"/>
-      <c r="C58" s="104" t="s">
+      <c r="A58" s="86"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="104"/>
-      <c r="E58" s="104"/>
-      <c r="F58" s="104"/>
-      <c r="G58" s="104"/>
+      <c r="D58" s="100"/>
+      <c r="E58" s="100"/>
+      <c r="F58" s="100"/>
+      <c r="G58" s="100"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="80"/>
-      <c r="B59" s="81"/>
-      <c r="C59" s="104" t="s">
+      <c r="A59" s="86"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="100" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="104"/>
-      <c r="E59" s="104"/>
-      <c r="F59" s="104"/>
-      <c r="G59" s="104"/>
+      <c r="D59" s="100"/>
+      <c r="E59" s="100"/>
+      <c r="F59" s="100"/>
+      <c r="G59" s="100"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="80"/>
-      <c r="B60" s="81"/>
-      <c r="C60" s="104" t="s">
+      <c r="A60" s="86"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
+      <c r="D60" s="100"/>
+      <c r="E60" s="100"/>
+      <c r="F60" s="100"/>
+      <c r="G60" s="100"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="80"/>
-      <c r="B61" s="81"/>
-      <c r="C61" s="104" t="s">
+      <c r="A61" s="86"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="104"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="104"/>
-      <c r="G61" s="104"/>
+      <c r="D61" s="100"/>
+      <c r="E61" s="100"/>
+      <c r="F61" s="100"/>
+      <c r="G61" s="100"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="80"/>
-      <c r="B62" s="81"/>
-      <c r="C62" s="104" t="s">
+      <c r="A62" s="86"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
+      <c r="D62" s="100"/>
+      <c r="E62" s="100"/>
+      <c r="F62" s="100"/>
+      <c r="G62" s="100"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="80"/>
-      <c r="B63" s="81"/>
-      <c r="C63" s="104" t="s">
+      <c r="A63" s="86"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="104"/>
-      <c r="E63" s="104"/>
-      <c r="F63" s="104"/>
-      <c r="G63" s="104"/>
+      <c r="D63" s="100"/>
+      <c r="E63" s="100"/>
+      <c r="F63" s="100"/>
+      <c r="G63" s="100"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="80">
+      <c r="A64" s="86">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="81" t="s">
+      <c r="C64" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="81"/>
-      <c r="E64" s="81"/>
-      <c r="F64" s="81"/>
-      <c r="G64" s="81"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="82"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="82"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="80"/>
-      <c r="B65" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="81" t="s">
+      <c r="A65" s="86"/>
+      <c r="B65" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="81"/>
-      <c r="E65" s="81"/>
-      <c r="F65" s="81"/>
-      <c r="G65" s="81"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="82"/>
+      <c r="F65" s="82"/>
+      <c r="G65" s="82"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="80"/>
-      <c r="B66" s="81"/>
-      <c r="C66" s="81" t="s">
+      <c r="A66" s="86"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="81"/>
-      <c r="E66" s="81"/>
-      <c r="F66" s="81"/>
-      <c r="G66" s="81"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="82"/>
+      <c r="F66" s="82"/>
+      <c r="G66" s="82"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2452,164 +2478,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="81" t="s">
+      <c r="C67" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="81"/>
-      <c r="E67" s="81"/>
-      <c r="F67" s="81"/>
-      <c r="G67" s="81"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="82"/>
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="80">
+      <c r="A68" s="86">
         <v>46220</v>
       </c>
-      <c r="B68" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="81" t="s">
+      <c r="B68" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="81"/>
-      <c r="E68" s="81"/>
-      <c r="F68" s="81"/>
-      <c r="G68" s="81"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="80"/>
-      <c r="B69" s="81"/>
-      <c r="C69" s="81" t="s">
+      <c r="A69" s="86"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="81"/>
-      <c r="E69" s="81"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="81"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="82"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="80">
+      <c r="A70" s="86">
         <v>46223</v>
       </c>
-      <c r="B70" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="82" t="s">
+      <c r="B70" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="83"/>
-      <c r="E70" s="83"/>
-      <c r="F70" s="83"/>
-      <c r="G70" s="84"/>
+      <c r="D70" s="88"/>
+      <c r="E70" s="88"/>
+      <c r="F70" s="88"/>
+      <c r="G70" s="89"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="80"/>
-      <c r="B71" s="81"/>
-      <c r="C71" s="82" t="s">
+      <c r="A71" s="86"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="83"/>
-      <c r="E71" s="83"/>
-      <c r="F71" s="83"/>
-      <c r="G71" s="84"/>
+      <c r="D71" s="88"/>
+      <c r="E71" s="88"/>
+      <c r="F71" s="88"/>
+      <c r="G71" s="89"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="80"/>
-      <c r="B72" s="81"/>
-      <c r="C72" s="82" t="s">
+      <c r="A72" s="86"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="83"/>
-      <c r="E72" s="83"/>
-      <c r="F72" s="83"/>
-      <c r="G72" s="84"/>
+      <c r="D72" s="88"/>
+      <c r="E72" s="88"/>
+      <c r="F72" s="88"/>
+      <c r="G72" s="89"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="80"/>
-      <c r="B73" s="81"/>
-      <c r="C73" s="82" t="s">
+      <c r="A73" s="86"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="83"/>
-      <c r="E73" s="83"/>
-      <c r="F73" s="83"/>
-      <c r="G73" s="84"/>
+      <c r="D73" s="88"/>
+      <c r="E73" s="88"/>
+      <c r="F73" s="88"/>
+      <c r="G73" s="89"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="80"/>
-      <c r="B74" s="81"/>
-      <c r="C74" s="82" t="s">
+      <c r="A74" s="86"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="83"/>
-      <c r="E74" s="83"/>
-      <c r="F74" s="83"/>
-      <c r="G74" s="84"/>
+      <c r="D74" s="88"/>
+      <c r="E74" s="88"/>
+      <c r="F74" s="88"/>
+      <c r="G74" s="89"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="80"/>
-      <c r="B75" s="81"/>
-      <c r="C75" s="82" t="s">
+      <c r="A75" s="86"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="83"/>
-      <c r="G75" s="84"/>
+      <c r="D75" s="88"/>
+      <c r="E75" s="88"/>
+      <c r="F75" s="88"/>
+      <c r="G75" s="89"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="80"/>
-      <c r="B76" s="81"/>
-      <c r="C76" s="82" t="s">
+      <c r="A76" s="86"/>
+      <c r="B76" s="82"/>
+      <c r="C76" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="83"/>
-      <c r="E76" s="83"/>
-      <c r="F76" s="83"/>
-      <c r="G76" s="84"/>
+      <c r="D76" s="88"/>
+      <c r="E76" s="88"/>
+      <c r="F76" s="88"/>
+      <c r="G76" s="89"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="80"/>
-      <c r="B77" s="81"/>
-      <c r="C77" s="77" t="s">
+      <c r="A77" s="86"/>
+      <c r="B77" s="82"/>
+      <c r="C77" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="78"/>
-      <c r="E77" s="78"/>
-      <c r="F77" s="78"/>
-      <c r="G77" s="79"/>
+      <c r="D77" s="84"/>
+      <c r="E77" s="84"/>
+      <c r="F77" s="84"/>
+      <c r="G77" s="85"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="80"/>
-      <c r="B78" s="81"/>
-      <c r="C78" s="77" t="s">
+      <c r="A78" s="86"/>
+      <c r="B78" s="82"/>
+      <c r="C78" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="78"/>
-      <c r="E78" s="78"/>
-      <c r="F78" s="78"/>
-      <c r="G78" s="79"/>
+      <c r="D78" s="84"/>
+      <c r="E78" s="84"/>
+      <c r="F78" s="84"/>
+      <c r="G78" s="85"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="80"/>
-      <c r="B79" s="81"/>
-      <c r="C79" s="77" t="s">
+      <c r="A79" s="86"/>
+      <c r="B79" s="82"/>
+      <c r="C79" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="78"/>
-      <c r="E79" s="78"/>
-      <c r="F79" s="78"/>
-      <c r="G79" s="79"/>
+      <c r="D79" s="84"/>
+      <c r="E79" s="84"/>
+      <c r="F79" s="84"/>
+      <c r="G79" s="85"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="80"/>
-      <c r="B80" s="81"/>
-      <c r="C80" s="77" t="s">
+      <c r="A80" s="86"/>
+      <c r="B80" s="82"/>
+      <c r="C80" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="78"/>
-      <c r="E80" s="78"/>
-      <c r="F80" s="78"/>
-      <c r="G80" s="79"/>
+      <c r="D80" s="84"/>
+      <c r="E80" s="84"/>
+      <c r="F80" s="84"/>
+      <c r="G80" s="85"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2618,353 +2644,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="81" t="s">
+      <c r="C81" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="81"/>
-      <c r="E81" s="81"/>
-      <c r="F81" s="81"/>
-      <c r="G81" s="81"/>
+      <c r="D81" s="82"/>
+      <c r="E81" s="82"/>
+      <c r="F81" s="82"/>
+      <c r="G81" s="82"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="80">
+      <c r="A82" s="86">
         <v>46225</v>
       </c>
-      <c r="B82" s="81" t="s">
+      <c r="B82" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="81" t="s">
+      <c r="C82" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="81"/>
-      <c r="E82" s="81"/>
-      <c r="F82" s="81"/>
-      <c r="G82" s="81"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="82"/>
+      <c r="F82" s="82"/>
+      <c r="G82" s="82"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="80"/>
-      <c r="B83" s="81"/>
-      <c r="C83" s="81" t="s">
+      <c r="A83" s="86"/>
+      <c r="B83" s="82"/>
+      <c r="C83" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="81"/>
-      <c r="E83" s="81"/>
-      <c r="F83" s="81"/>
-      <c r="G83" s="81"/>
+      <c r="D83" s="82"/>
+      <c r="E83" s="82"/>
+      <c r="F83" s="82"/>
+      <c r="G83" s="82"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="80"/>
-      <c r="B84" s="81"/>
-      <c r="C84" s="81" t="s">
+      <c r="A84" s="86"/>
+      <c r="B84" s="82"/>
+      <c r="C84" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="81"/>
-      <c r="E84" s="81"/>
-      <c r="F84" s="81"/>
-      <c r="G84" s="81"/>
+      <c r="D84" s="82"/>
+      <c r="E84" s="82"/>
+      <c r="F84" s="82"/>
+      <c r="G84" s="82"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="80"/>
-      <c r="B85" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="81" t="s">
+      <c r="A85" s="86"/>
+      <c r="B85" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="81"/>
-      <c r="E85" s="81"/>
-      <c r="F85" s="81"/>
-      <c r="G85" s="81"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="82"/>
+      <c r="F85" s="82"/>
+      <c r="G85" s="82"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="80"/>
-      <c r="B86" s="81"/>
-      <c r="C86" s="81" t="s">
+      <c r="A86" s="86"/>
+      <c r="B86" s="82"/>
+      <c r="C86" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="81"/>
-      <c r="E86" s="81"/>
-      <c r="F86" s="81"/>
-      <c r="G86" s="81"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="82"/>
+      <c r="F86" s="82"/>
+      <c r="G86" s="82"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="80"/>
-      <c r="B87" s="81"/>
-      <c r="C87" s="81" t="s">
+      <c r="A87" s="86"/>
+      <c r="B87" s="82"/>
+      <c r="C87" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="81"/>
-      <c r="E87" s="81"/>
-      <c r="F87" s="81"/>
-      <c r="G87" s="81"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="82"/>
+      <c r="F87" s="82"/>
+      <c r="G87" s="82"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="80"/>
-      <c r="B88" s="81"/>
-      <c r="C88" s="81" t="s">
+      <c r="A88" s="86"/>
+      <c r="B88" s="82"/>
+      <c r="C88" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="81"/>
-      <c r="E88" s="81"/>
-      <c r="F88" s="81"/>
-      <c r="G88" s="81"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="82"/>
+      <c r="F88" s="82"/>
+      <c r="G88" s="82"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="80"/>
-      <c r="B89" s="81"/>
-      <c r="C89" s="82" t="s">
+      <c r="A89" s="86"/>
+      <c r="B89" s="82"/>
+      <c r="C89" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="83"/>
-      <c r="E89" s="83"/>
-      <c r="F89" s="83"/>
-      <c r="G89" s="84"/>
+      <c r="D89" s="88"/>
+      <c r="E89" s="88"/>
+      <c r="F89" s="88"/>
+      <c r="G89" s="89"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="80"/>
-      <c r="B90" s="81"/>
-      <c r="C90" s="81" t="s">
+      <c r="A90" s="86"/>
+      <c r="B90" s="82"/>
+      <c r="C90" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="81"/>
-      <c r="E90" s="81"/>
-      <c r="F90" s="81"/>
-      <c r="G90" s="81"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="82"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="82"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="100">
+      <c r="A91" s="95">
         <v>46227</v>
       </c>
-      <c r="B91" s="90" t="s">
+      <c r="B91" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="81" t="s">
+      <c r="C91" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="81"/>
-      <c r="E91" s="81"/>
-      <c r="F91" s="81"/>
-      <c r="G91" s="81"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="82"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="102"/>
-      <c r="B92" s="91"/>
-      <c r="C92" s="82" t="s">
+      <c r="A92" s="96"/>
+      <c r="B92" s="94"/>
+      <c r="C92" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="83"/>
-      <c r="E92" s="83"/>
-      <c r="F92" s="83"/>
-      <c r="G92" s="84"/>
+      <c r="D92" s="88"/>
+      <c r="E92" s="88"/>
+      <c r="F92" s="88"/>
+      <c r="G92" s="89"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="80">
+      <c r="A93" s="86">
         <v>46228</v>
       </c>
-      <c r="B93" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="81" t="s">
+      <c r="B93" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="81"/>
-      <c r="E93" s="81"/>
-      <c r="F93" s="81"/>
-      <c r="G93" s="81"/>
+      <c r="D93" s="82"/>
+      <c r="E93" s="82"/>
+      <c r="F93" s="82"/>
+      <c r="G93" s="82"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="80"/>
-      <c r="B94" s="81"/>
-      <c r="C94" s="81" t="s">
+      <c r="A94" s="86"/>
+      <c r="B94" s="82"/>
+      <c r="C94" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="81"/>
-      <c r="E94" s="81"/>
-      <c r="F94" s="81"/>
-      <c r="G94" s="81"/>
+      <c r="D94" s="82"/>
+      <c r="E94" s="82"/>
+      <c r="F94" s="82"/>
+      <c r="G94" s="82"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="80"/>
-      <c r="B95" s="81"/>
-      <c r="C95" s="81" t="s">
+      <c r="A95" s="86"/>
+      <c r="B95" s="82"/>
+      <c r="C95" s="82" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="81"/>
-      <c r="E95" s="81"/>
-      <c r="F95" s="81"/>
-      <c r="G95" s="81"/>
+      <c r="D95" s="82"/>
+      <c r="E95" s="82"/>
+      <c r="F95" s="82"/>
+      <c r="G95" s="82"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="80"/>
-      <c r="B96" s="81"/>
-      <c r="C96" s="81" t="s">
+      <c r="A96" s="86"/>
+      <c r="B96" s="82"/>
+      <c r="C96" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="81"/>
-      <c r="E96" s="81"/>
-      <c r="F96" s="81"/>
-      <c r="G96" s="81"/>
+      <c r="D96" s="82"/>
+      <c r="E96" s="82"/>
+      <c r="F96" s="82"/>
+      <c r="G96" s="82"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="80"/>
-      <c r="B97" s="81"/>
-      <c r="C97" s="81" t="s">
+      <c r="A97" s="86"/>
+      <c r="B97" s="82"/>
+      <c r="C97" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="81"/>
-      <c r="E97" s="81"/>
-      <c r="F97" s="81"/>
-      <c r="G97" s="81"/>
+      <c r="D97" s="82"/>
+      <c r="E97" s="82"/>
+      <c r="F97" s="82"/>
+      <c r="G97" s="82"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="80"/>
-      <c r="B98" s="81"/>
-      <c r="C98" s="81" t="s">
+      <c r="A98" s="86"/>
+      <c r="B98" s="82"/>
+      <c r="C98" s="82" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="81"/>
-      <c r="E98" s="81"/>
-      <c r="F98" s="81"/>
-      <c r="G98" s="81"/>
+      <c r="D98" s="82"/>
+      <c r="E98" s="82"/>
+      <c r="F98" s="82"/>
+      <c r="G98" s="82"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="80">
+      <c r="A99" s="86">
         <v>46230</v>
       </c>
-      <c r="B99" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="81" t="s">
+      <c r="B99" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="81"/>
-      <c r="E99" s="81"/>
-      <c r="F99" s="81"/>
-      <c r="G99" s="81"/>
+      <c r="D99" s="82"/>
+      <c r="E99" s="82"/>
+      <c r="F99" s="82"/>
+      <c r="G99" s="82"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="80"/>
-      <c r="B100" s="81"/>
-      <c r="C100" s="81" t="s">
+      <c r="A100" s="86"/>
+      <c r="B100" s="82"/>
+      <c r="C100" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="81"/>
-      <c r="E100" s="81"/>
-      <c r="F100" s="81"/>
-      <c r="G100" s="81"/>
+      <c r="D100" s="82"/>
+      <c r="E100" s="82"/>
+      <c r="F100" s="82"/>
+      <c r="G100" s="82"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="80">
+      <c r="A101" s="86">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="106" t="s">
+      <c r="C101" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="106"/>
-      <c r="E101" s="106"/>
-      <c r="F101" s="106"/>
-      <c r="G101" s="106"/>
+      <c r="D101" s="92"/>
+      <c r="E101" s="92"/>
+      <c r="F101" s="92"/>
+      <c r="G101" s="92"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="80"/>
+      <c r="A102" s="86"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="106" t="s">
+      <c r="C102" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="106"/>
-      <c r="E102" s="106"/>
-      <c r="F102" s="106"/>
-      <c r="G102" s="106"/>
+      <c r="D102" s="92"/>
+      <c r="E102" s="92"/>
+      <c r="F102" s="92"/>
+      <c r="G102" s="92"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="105" t="s">
+      <c r="A103" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="95" t="s">
+      <c r="B103" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="95"/>
-      <c r="E103" s="95"/>
-      <c r="F103" s="95"/>
-      <c r="G103" s="95"/>
+      <c r="D103" s="91"/>
+      <c r="E103" s="91"/>
+      <c r="F103" s="91"/>
+      <c r="G103" s="91"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="105"/>
-      <c r="B104" s="81"/>
-      <c r="C104" s="81" t="s">
+      <c r="A104" s="90"/>
+      <c r="B104" s="82"/>
+      <c r="C104" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="81"/>
-      <c r="E104" s="81"/>
-      <c r="F104" s="81"/>
-      <c r="G104" s="81"/>
+      <c r="D104" s="82"/>
+      <c r="E104" s="82"/>
+      <c r="F104" s="82"/>
+      <c r="G104" s="82"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="105"/>
-      <c r="B105" s="81"/>
-      <c r="C105" s="81" t="s">
+      <c r="A105" s="90"/>
+      <c r="B105" s="82"/>
+      <c r="C105" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="81"/>
-      <c r="E105" s="81"/>
-      <c r="F105" s="81"/>
-      <c r="G105" s="81"/>
+      <c r="D105" s="82"/>
+      <c r="E105" s="82"/>
+      <c r="F105" s="82"/>
+      <c r="G105" s="82"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="105"/>
-      <c r="B106" s="81"/>
-      <c r="C106" s="81" t="s">
+      <c r="A106" s="90"/>
+      <c r="B106" s="82"/>
+      <c r="C106" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="81"/>
-      <c r="E106" s="81"/>
-      <c r="F106" s="81"/>
-      <c r="G106" s="81"/>
+      <c r="D106" s="82"/>
+      <c r="E106" s="82"/>
+      <c r="F106" s="82"/>
+      <c r="G106" s="82"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="105"/>
-      <c r="B107" s="81"/>
-      <c r="C107" s="81" t="s">
+      <c r="A107" s="90"/>
+      <c r="B107" s="82"/>
+      <c r="C107" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="81"/>
-      <c r="E107" s="81"/>
-      <c r="F107" s="81"/>
-      <c r="G107" s="81"/>
+      <c r="D107" s="82"/>
+      <c r="E107" s="82"/>
+      <c r="F107" s="82"/>
+      <c r="G107" s="82"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="80">
+      <c r="A108" s="86">
         <v>46234</v>
       </c>
-      <c r="B108" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="81" t="s">
+      <c r="B108" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="81"/>
-      <c r="E108" s="81"/>
-      <c r="F108" s="81"/>
-      <c r="G108" s="81"/>
+      <c r="D108" s="82"/>
+      <c r="E108" s="82"/>
+      <c r="F108" s="82"/>
+      <c r="G108" s="82"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="80"/>
-      <c r="B109" s="81"/>
-      <c r="C109" s="81" t="s">
+      <c r="A109" s="86"/>
+      <c r="B109" s="82"/>
+      <c r="C109" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="81"/>
-      <c r="E109" s="81"/>
-      <c r="F109" s="81"/>
-      <c r="G109" s="81"/>
+      <c r="D109" s="82"/>
+      <c r="E109" s="82"/>
+      <c r="F109" s="82"/>
+      <c r="G109" s="82"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2974,68 +3000,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -3060,67 +3085,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3138,15 +3164,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="102">
         <v>46235</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4935,7 +4961,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -5144,7 +5170,7 @@
       <c r="F16" s="69"/>
       <c r="G16" s="70"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="67"/>
       <c r="C17" s="25" t="s">
@@ -5155,7 +5181,7 @@
       <c r="F17" s="69"/>
       <c r="G17" s="70"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
       <c r="B18" s="67"/>
       <c r="C18" s="25" t="s">
@@ -5166,7 +5192,7 @@
       <c r="F18" s="69"/>
       <c r="G18" s="70"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="36"/>
       <c r="B19" s="68"/>
       <c r="C19" s="25" t="s">
@@ -5174,7 +5200,7 @@
       </c>
       <c r="G19" s="71"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
       <c r="B20" s="66"/>
       <c r="C20" s="26" t="s">
@@ -5185,7 +5211,7 @@
       <c r="F20" s="72"/>
       <c r="G20" s="73"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>46303</v>
       </c>
@@ -5200,7 +5226,7 @@
       <c r="F21" s="31"/>
       <c r="G21" s="32"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="10" t="s">
         <v>4</v>
@@ -5213,7 +5239,7 @@
       <c r="F22" s="10"/>
       <c r="G22" s="51"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>46307</v>
       </c>
@@ -5228,7 +5254,7 @@
       <c r="F23" s="47"/>
       <c r="G23" s="48"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="10"/>
       <c r="C24" s="25" t="s">
@@ -5239,7 +5265,7 @@
       <c r="F24" s="10"/>
       <c r="G24" s="51"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="46"/>
       <c r="B25" s="10"/>
       <c r="C25" s="25" t="s">
@@ -5250,7 +5276,7 @@
       <c r="F25" s="10"/>
       <c r="G25" s="51"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
       <c r="B26" s="49"/>
       <c r="C26" s="26" t="s">
@@ -5261,26 +5287,166 @@
       <c r="F26" s="49"/>
       <c r="G26" s="50"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="108">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="46"/>
+      <c r="B27" s="108" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="51"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
         <v>46308</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" s="44"/>
+      <c r="C28" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="46"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="41"/>
+      <c r="B31" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="35"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="37"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="41"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="37"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="41"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="37"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B35" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="109" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="109" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="109" t="s">
-        <v>200</v>
-      </c>
+      <c r="C35" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="48"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="13"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="51"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="13"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="51"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="46"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="50"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9114948F-B25F-4253-9C0E-5D61CD3AAD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD7E6D4-594F-486C-BB5A-4646384D7248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5220" yWindow="1170" windowWidth="21600" windowHeight="11835" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="213">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -662,6 +662,15 @@
   </si>
   <si>
     <t xml:space="preserve">Nhận </t>
+  </si>
+  <si>
+    <t>Nhận 2 VNSH03 A. Bảo (Kho)</t>
+  </si>
+  <si>
+    <t>Trả 3 VNSH03 SEA cho Tuấn Anh</t>
+  </si>
+  <si>
+    <t>Nhận  VNSH03 + 3 ổ SSD A. Bảo (SEA)</t>
   </si>
 </sst>
 </file>
@@ -885,7 +894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1063,6 +1072,30 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1078,87 +1111,70 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1481,15 +1497,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="77">
+      <c r="A1" s="85">
         <v>46174</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1498,146 +1514,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="81"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="86">
+      <c r="A3" s="80">
         <v>46202</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="86"/>
-      <c r="B6" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="82" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="86"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82" t="s">
+      <c r="A7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="86"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82" t="s">
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="86">
+      <c r="A9" s="80">
         <v>46203</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="89"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="86"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="83" t="s">
+      <c r="A10" s="80"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="85"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="86"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="83" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="85"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="79"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="86"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="83" t="s">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="85"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="79"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="86"/>
+      <c r="A13" s="80"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="85"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="79"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1647,14 +1663,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1665,6 +1673,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1682,15 +1698,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="102">
+      <c r="A1" s="93">
         <v>46204</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1699,152 +1715,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="86">
+      <c r="A3" s="80">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="91" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="86"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="104">
+      <c r="A7" s="96">
         <v>46205</v>
       </c>
-      <c r="B7" s="93" t="s">
+      <c r="B7" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="84"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="105"/>
-      <c r="B8" s="101"/>
-      <c r="C8" s="83" t="s">
+      <c r="A8" s="97"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="85"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="79"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="105"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="83" t="s">
+      <c r="A9" s="97"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="85"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="79"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="105"/>
-      <c r="B10" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="83" t="s">
+      <c r="A10" s="97"/>
+      <c r="B10" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="85"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="105"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="83" t="s">
+      <c r="A11" s="97"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="85"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="79"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="105"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="83" t="s">
+      <c r="A12" s="97"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="85"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="79"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="106"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="83" t="s">
+      <c r="A13" s="98"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="85"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="79"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="95">
+      <c r="A14" s="100">
         <v>46206</v>
       </c>
-      <c r="B14" s="93" t="s">
+      <c r="B14" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1856,348 +1872,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="98"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="87" t="s">
+      <c r="A15" s="101"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="89"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="84"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="98"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="87" t="s">
+      <c r="A16" s="101"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="89"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="84"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="98"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="87" t="s">
+      <c r="A17" s="101"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="89"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="84"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="98"/>
-      <c r="B18" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="87" t="s">
+      <c r="A18" s="101"/>
+      <c r="B18" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="89"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="84"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="96"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="87" t="s">
+      <c r="A19" s="102"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="89"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="84"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="99">
+      <c r="A20" s="103">
         <v>46209</v>
       </c>
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="82" t="s">
+      <c r="C20" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="99"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82" t="s">
+      <c r="A21" s="103"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="99"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82" t="s">
+      <c r="A22" s="103"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="99"/>
-      <c r="B23" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="82" t="s">
+      <c r="A23" s="103"/>
+      <c r="B23" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="82"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="99"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="87" t="s">
+      <c r="A24" s="103"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="89"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="84"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="99"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="87" t="s">
+      <c r="A25" s="103"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="89"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="84"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="99"/>
-      <c r="B26" s="82"/>
-      <c r="C26" s="87" t="s">
+      <c r="A26" s="103"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="89"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="84"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="87" t="s">
+      <c r="A27" s="103"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="89"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="84"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="99"/>
-      <c r="B28" s="82"/>
-      <c r="C28" s="87" t="s">
+      <c r="A28" s="103"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="89"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="84"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="99"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="87" t="s">
+      <c r="A29" s="103"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="89"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="84"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="99"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="87" t="s">
+      <c r="A30" s="103"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="89"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="84"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="99"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="87" t="s">
+      <c r="A31" s="103"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="89"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="84"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="99"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="87" t="s">
+      <c r="A32" s="103"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="88"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="89"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="84"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="99"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="87" t="s">
+      <c r="A33" s="103"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="89"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="84"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="99"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="87" t="s">
+      <c r="A34" s="103"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="89"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="84"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="97">
+      <c r="A35" s="99">
         <v>46210</v>
       </c>
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="82" t="s">
+      <c r="C35" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="82"/>
-      <c r="E35" s="82"/>
-      <c r="F35" s="82"/>
-      <c r="G35" s="82"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="97"/>
-      <c r="B36" s="82"/>
-      <c r="C36" s="82" t="s">
+      <c r="A36" s="99"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="82"/>
-      <c r="E36" s="82"/>
-      <c r="F36" s="82"/>
-      <c r="G36" s="82"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="97"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="82" t="s">
+      <c r="A37" s="99"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="82"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="82"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="97"/>
-      <c r="B38" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="82" t="s">
+      <c r="A38" s="99"/>
+      <c r="B38" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="82"/>
-      <c r="E38" s="82"/>
-      <c r="F38" s="82"/>
-      <c r="G38" s="82"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="97"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="82" t="s">
+      <c r="A39" s="99"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="82"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="82"/>
-      <c r="G39" s="82"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="97"/>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82" t="s">
+      <c r="A40" s="99"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="82"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="82"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="97"/>
-      <c r="B41" s="82"/>
-      <c r="C41" s="82" t="s">
+      <c r="A41" s="99"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="97"/>
-      <c r="B42" s="82"/>
-      <c r="C42" s="82" t="s">
+      <c r="A42" s="99"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="82"/>
-      <c r="E42" s="82"/>
-      <c r="F42" s="82"/>
-      <c r="G42" s="82"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="97"/>
-      <c r="B43" s="82"/>
-      <c r="C43" s="82" t="s">
+      <c r="A43" s="99"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82"/>
-      <c r="F43" s="82"/>
-      <c r="G43" s="82"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="97"/>
-      <c r="B44" s="82"/>
-      <c r="C44" s="87" t="s">
+      <c r="A44" s="99"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="88"/>
-      <c r="G44" s="89"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="84"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2206,13 +2222,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="82" t="s">
+      <c r="C45" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="82"/>
-      <c r="E45" s="82"/>
-      <c r="F45" s="82"/>
-      <c r="G45" s="82"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2221,255 +2237,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="82" t="s">
+      <c r="C46" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="82"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="82"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="95">
+      <c r="A47" s="100">
         <v>46213</v>
       </c>
-      <c r="B47" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="87" t="s">
+      <c r="B47" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="88"/>
-      <c r="E47" s="88"/>
-      <c r="F47" s="88"/>
-      <c r="G47" s="89"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="84"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="98"/>
-      <c r="B48" s="101"/>
-      <c r="C48" s="87" t="s">
+      <c r="A48" s="101"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="89"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="84"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="98"/>
-      <c r="B49" s="101"/>
-      <c r="C49" s="87" t="s">
+      <c r="A49" s="101"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="88"/>
-      <c r="E49" s="88"/>
-      <c r="F49" s="88"/>
-      <c r="G49" s="89"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="84"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="98"/>
-      <c r="B50" s="101"/>
-      <c r="C50" s="87" t="s">
+      <c r="A50" s="101"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="88"/>
-      <c r="E50" s="88"/>
-      <c r="F50" s="88"/>
-      <c r="G50" s="89"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="84"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="96"/>
-      <c r="B51" s="94"/>
-      <c r="C51" s="87" t="s">
+      <c r="A51" s="102"/>
+      <c r="B51" s="91"/>
+      <c r="C51" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="88"/>
-      <c r="E51" s="88"/>
-      <c r="F51" s="88"/>
-      <c r="G51" s="89"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="84"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="86">
+      <c r="A52" s="80">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="82" t="s">
+      <c r="C52" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="82"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="82" t="s">
+      <c r="C53" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="82"/>
-      <c r="E53" s="82"/>
-      <c r="F53" s="82"/>
-      <c r="G53" s="82"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="86">
+      <c r="A54" s="80">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="87" t="s">
+      <c r="C54" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="88"/>
-      <c r="E54" s="88"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="89"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="83"/>
+      <c r="G54" s="84"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="86"/>
-      <c r="B55" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="100" t="s">
+      <c r="A55" s="80"/>
+      <c r="B55" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="100"/>
-      <c r="E55" s="100"/>
-      <c r="F55" s="100"/>
-      <c r="G55" s="100"/>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="104"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="86"/>
-      <c r="B56" s="82"/>
-      <c r="C56" s="100" t="s">
+      <c r="A56" s="80"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="100"/>
-      <c r="E56" s="100"/>
-      <c r="F56" s="100"/>
-      <c r="G56" s="100"/>
+      <c r="D56" s="104"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="104"/>
+      <c r="G56" s="104"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="86"/>
-      <c r="B57" s="82"/>
-      <c r="C57" s="100" t="s">
+      <c r="A57" s="80"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="100"/>
-      <c r="E57" s="100"/>
-      <c r="F57" s="100"/>
-      <c r="G57" s="100"/>
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="104"/>
+      <c r="G57" s="104"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="86"/>
-      <c r="B58" s="82"/>
-      <c r="C58" s="100" t="s">
+      <c r="A58" s="80"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="100"/>
-      <c r="E58" s="100"/>
-      <c r="F58" s="100"/>
-      <c r="G58" s="100"/>
+      <c r="D58" s="104"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="104"/>
+      <c r="G58" s="104"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="86"/>
-      <c r="B59" s="82"/>
-      <c r="C59" s="100" t="s">
+      <c r="A59" s="80"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="100"/>
-      <c r="E59" s="100"/>
-      <c r="F59" s="100"/>
-      <c r="G59" s="100"/>
+      <c r="D59" s="104"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="104"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="86"/>
-      <c r="B60" s="82"/>
-      <c r="C60" s="100" t="s">
+      <c r="A60" s="80"/>
+      <c r="B60" s="81"/>
+      <c r="C60" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="100"/>
-      <c r="E60" s="100"/>
-      <c r="F60" s="100"/>
-      <c r="G60" s="100"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="86"/>
-      <c r="B61" s="82"/>
-      <c r="C61" s="100" t="s">
+      <c r="A61" s="80"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="100"/>
-      <c r="E61" s="100"/>
-      <c r="F61" s="100"/>
-      <c r="G61" s="100"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="104"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="86"/>
-      <c r="B62" s="82"/>
-      <c r="C62" s="100" t="s">
+      <c r="A62" s="80"/>
+      <c r="B62" s="81"/>
+      <c r="C62" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="100"/>
-      <c r="E62" s="100"/>
-      <c r="F62" s="100"/>
-      <c r="G62" s="100"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="86"/>
-      <c r="B63" s="82"/>
-      <c r="C63" s="100" t="s">
+      <c r="A63" s="80"/>
+      <c r="B63" s="81"/>
+      <c r="C63" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="100"/>
-      <c r="E63" s="100"/>
-      <c r="F63" s="100"/>
-      <c r="G63" s="100"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="86">
+      <c r="A64" s="80">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="82" t="s">
+      <c r="C64" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="82"/>
-      <c r="E64" s="82"/>
-      <c r="F64" s="82"/>
-      <c r="G64" s="82"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="81"/>
+      <c r="F64" s="81"/>
+      <c r="G64" s="81"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="86"/>
-      <c r="B65" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="82" t="s">
+      <c r="A65" s="80"/>
+      <c r="B65" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="82"/>
-      <c r="E65" s="82"/>
-      <c r="F65" s="82"/>
-      <c r="G65" s="82"/>
+      <c r="D65" s="81"/>
+      <c r="E65" s="81"/>
+      <c r="F65" s="81"/>
+      <c r="G65" s="81"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="86"/>
-      <c r="B66" s="82"/>
-      <c r="C66" s="82" t="s">
+      <c r="A66" s="80"/>
+      <c r="B66" s="81"/>
+      <c r="C66" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="82"/>
-      <c r="E66" s="82"/>
-      <c r="F66" s="82"/>
-      <c r="G66" s="82"/>
+      <c r="D66" s="81"/>
+      <c r="E66" s="81"/>
+      <c r="F66" s="81"/>
+      <c r="G66" s="81"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2478,164 +2494,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="82" t="s">
+      <c r="C67" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="82"/>
-      <c r="E67" s="82"/>
-      <c r="F67" s="82"/>
-      <c r="G67" s="82"/>
+      <c r="D67" s="81"/>
+      <c r="E67" s="81"/>
+      <c r="F67" s="81"/>
+      <c r="G67" s="81"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="86">
+      <c r="A68" s="80">
         <v>46220</v>
       </c>
-      <c r="B68" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="82" t="s">
+      <c r="B68" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="82"/>
-      <c r="E68" s="82"/>
-      <c r="F68" s="82"/>
-      <c r="G68" s="82"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="86"/>
-      <c r="B69" s="82"/>
-      <c r="C69" s="82" t="s">
+      <c r="A69" s="80"/>
+      <c r="B69" s="81"/>
+      <c r="C69" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
-      <c r="F69" s="82"/>
-      <c r="G69" s="82"/>
+      <c r="D69" s="81"/>
+      <c r="E69" s="81"/>
+      <c r="F69" s="81"/>
+      <c r="G69" s="81"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="86">
+      <c r="A70" s="80">
         <v>46223</v>
       </c>
-      <c r="B70" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="87" t="s">
+      <c r="B70" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="88"/>
-      <c r="E70" s="88"/>
-      <c r="F70" s="88"/>
-      <c r="G70" s="89"/>
+      <c r="D70" s="83"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="83"/>
+      <c r="G70" s="84"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="86"/>
-      <c r="B71" s="82"/>
-      <c r="C71" s="87" t="s">
+      <c r="A71" s="80"/>
+      <c r="B71" s="81"/>
+      <c r="C71" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="88"/>
-      <c r="E71" s="88"/>
-      <c r="F71" s="88"/>
-      <c r="G71" s="89"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="83"/>
+      <c r="G71" s="84"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="86"/>
-      <c r="B72" s="82"/>
-      <c r="C72" s="87" t="s">
+      <c r="A72" s="80"/>
+      <c r="B72" s="81"/>
+      <c r="C72" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="88"/>
-      <c r="E72" s="88"/>
-      <c r="F72" s="88"/>
-      <c r="G72" s="89"/>
+      <c r="D72" s="83"/>
+      <c r="E72" s="83"/>
+      <c r="F72" s="83"/>
+      <c r="G72" s="84"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="86"/>
-      <c r="B73" s="82"/>
-      <c r="C73" s="87" t="s">
+      <c r="A73" s="80"/>
+      <c r="B73" s="81"/>
+      <c r="C73" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="88"/>
-      <c r="E73" s="88"/>
-      <c r="F73" s="88"/>
-      <c r="G73" s="89"/>
+      <c r="D73" s="83"/>
+      <c r="E73" s="83"/>
+      <c r="F73" s="83"/>
+      <c r="G73" s="84"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="86"/>
-      <c r="B74" s="82"/>
-      <c r="C74" s="87" t="s">
+      <c r="A74" s="80"/>
+      <c r="B74" s="81"/>
+      <c r="C74" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="88"/>
-      <c r="E74" s="88"/>
-      <c r="F74" s="88"/>
-      <c r="G74" s="89"/>
+      <c r="D74" s="83"/>
+      <c r="E74" s="83"/>
+      <c r="F74" s="83"/>
+      <c r="G74" s="84"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="86"/>
-      <c r="B75" s="82"/>
-      <c r="C75" s="87" t="s">
+      <c r="A75" s="80"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="88"/>
-      <c r="E75" s="88"/>
-      <c r="F75" s="88"/>
-      <c r="G75" s="89"/>
+      <c r="D75" s="83"/>
+      <c r="E75" s="83"/>
+      <c r="F75" s="83"/>
+      <c r="G75" s="84"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="86"/>
-      <c r="B76" s="82"/>
-      <c r="C76" s="87" t="s">
+      <c r="A76" s="80"/>
+      <c r="B76" s="81"/>
+      <c r="C76" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="88"/>
-      <c r="E76" s="88"/>
-      <c r="F76" s="88"/>
-      <c r="G76" s="89"/>
+      <c r="D76" s="83"/>
+      <c r="E76" s="83"/>
+      <c r="F76" s="83"/>
+      <c r="G76" s="84"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="86"/>
-      <c r="B77" s="82"/>
-      <c r="C77" s="83" t="s">
+      <c r="A77" s="80"/>
+      <c r="B77" s="81"/>
+      <c r="C77" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="84"/>
-      <c r="E77" s="84"/>
-      <c r="F77" s="84"/>
-      <c r="G77" s="85"/>
+      <c r="D77" s="78"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="78"/>
+      <c r="G77" s="79"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="86"/>
-      <c r="B78" s="82"/>
-      <c r="C78" s="83" t="s">
+      <c r="A78" s="80"/>
+      <c r="B78" s="81"/>
+      <c r="C78" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="84"/>
-      <c r="E78" s="84"/>
-      <c r="F78" s="84"/>
-      <c r="G78" s="85"/>
+      <c r="D78" s="78"/>
+      <c r="E78" s="78"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="79"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="86"/>
-      <c r="B79" s="82"/>
-      <c r="C79" s="83" t="s">
+      <c r="A79" s="80"/>
+      <c r="B79" s="81"/>
+      <c r="C79" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="84"/>
-      <c r="E79" s="84"/>
-      <c r="F79" s="84"/>
-      <c r="G79" s="85"/>
+      <c r="D79" s="78"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="78"/>
+      <c r="G79" s="79"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="86"/>
-      <c r="B80" s="82"/>
-      <c r="C80" s="83" t="s">
+      <c r="A80" s="80"/>
+      <c r="B80" s="81"/>
+      <c r="C80" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="84"/>
-      <c r="E80" s="84"/>
-      <c r="F80" s="84"/>
-      <c r="G80" s="85"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="79"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2644,353 +2660,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="82" t="s">
+      <c r="C81" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="82"/>
-      <c r="E81" s="82"/>
-      <c r="F81" s="82"/>
-      <c r="G81" s="82"/>
+      <c r="D81" s="81"/>
+      <c r="E81" s="81"/>
+      <c r="F81" s="81"/>
+      <c r="G81" s="81"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="86">
+      <c r="A82" s="80">
         <v>46225</v>
       </c>
-      <c r="B82" s="82" t="s">
+      <c r="B82" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="82" t="s">
+      <c r="C82" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
+      <c r="D82" s="81"/>
+      <c r="E82" s="81"/>
+      <c r="F82" s="81"/>
+      <c r="G82" s="81"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="86"/>
-      <c r="B83" s="82"/>
-      <c r="C83" s="82" t="s">
+      <c r="A83" s="80"/>
+      <c r="B83" s="81"/>
+      <c r="C83" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="82"/>
-      <c r="E83" s="82"/>
-      <c r="F83" s="82"/>
-      <c r="G83" s="82"/>
+      <c r="D83" s="81"/>
+      <c r="E83" s="81"/>
+      <c r="F83" s="81"/>
+      <c r="G83" s="81"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="86"/>
-      <c r="B84" s="82"/>
-      <c r="C84" s="82" t="s">
+      <c r="A84" s="80"/>
+      <c r="B84" s="81"/>
+      <c r="C84" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="82"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
+      <c r="D84" s="81"/>
+      <c r="E84" s="81"/>
+      <c r="F84" s="81"/>
+      <c r="G84" s="81"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="86"/>
-      <c r="B85" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="82" t="s">
+      <c r="A85" s="80"/>
+      <c r="B85" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="82"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
+      <c r="D85" s="81"/>
+      <c r="E85" s="81"/>
+      <c r="F85" s="81"/>
+      <c r="G85" s="81"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="86"/>
-      <c r="B86" s="82"/>
-      <c r="C86" s="82" t="s">
+      <c r="A86" s="80"/>
+      <c r="B86" s="81"/>
+      <c r="C86" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="82"/>
-      <c r="E86" s="82"/>
-      <c r="F86" s="82"/>
-      <c r="G86" s="82"/>
+      <c r="D86" s="81"/>
+      <c r="E86" s="81"/>
+      <c r="F86" s="81"/>
+      <c r="G86" s="81"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="86"/>
-      <c r="B87" s="82"/>
-      <c r="C87" s="82" t="s">
+      <c r="A87" s="80"/>
+      <c r="B87" s="81"/>
+      <c r="C87" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="82"/>
-      <c r="E87" s="82"/>
-      <c r="F87" s="82"/>
-      <c r="G87" s="82"/>
+      <c r="D87" s="81"/>
+      <c r="E87" s="81"/>
+      <c r="F87" s="81"/>
+      <c r="G87" s="81"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="86"/>
-      <c r="B88" s="82"/>
-      <c r="C88" s="82" t="s">
+      <c r="A88" s="80"/>
+      <c r="B88" s="81"/>
+      <c r="C88" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="82"/>
-      <c r="E88" s="82"/>
-      <c r="F88" s="82"/>
-      <c r="G88" s="82"/>
+      <c r="D88" s="81"/>
+      <c r="E88" s="81"/>
+      <c r="F88" s="81"/>
+      <c r="G88" s="81"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="86"/>
-      <c r="B89" s="82"/>
-      <c r="C89" s="87" t="s">
+      <c r="A89" s="80"/>
+      <c r="B89" s="81"/>
+      <c r="C89" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="88"/>
-      <c r="E89" s="88"/>
-      <c r="F89" s="88"/>
-      <c r="G89" s="89"/>
+      <c r="D89" s="83"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="83"/>
+      <c r="G89" s="84"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="86"/>
-      <c r="B90" s="82"/>
-      <c r="C90" s="82" t="s">
+      <c r="A90" s="80"/>
+      <c r="B90" s="81"/>
+      <c r="C90" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
+      <c r="D90" s="81"/>
+      <c r="E90" s="81"/>
+      <c r="F90" s="81"/>
+      <c r="G90" s="81"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="95">
+      <c r="A91" s="100">
         <v>46227</v>
       </c>
-      <c r="B91" s="93" t="s">
+      <c r="B91" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="82" t="s">
+      <c r="C91" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="82"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
+      <c r="D91" s="81"/>
+      <c r="E91" s="81"/>
+      <c r="F91" s="81"/>
+      <c r="G91" s="81"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="96"/>
-      <c r="B92" s="94"/>
-      <c r="C92" s="87" t="s">
+      <c r="A92" s="102"/>
+      <c r="B92" s="91"/>
+      <c r="C92" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="88"/>
-      <c r="E92" s="88"/>
-      <c r="F92" s="88"/>
-      <c r="G92" s="89"/>
+      <c r="D92" s="83"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="83"/>
+      <c r="G92" s="84"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="86">
+      <c r="A93" s="80">
         <v>46228</v>
       </c>
-      <c r="B93" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="82" t="s">
+      <c r="B93" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="82"/>
-      <c r="E93" s="82"/>
-      <c r="F93" s="82"/>
-      <c r="G93" s="82"/>
+      <c r="D93" s="81"/>
+      <c r="E93" s="81"/>
+      <c r="F93" s="81"/>
+      <c r="G93" s="81"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="86"/>
-      <c r="B94" s="82"/>
-      <c r="C94" s="82" t="s">
+      <c r="A94" s="80"/>
+      <c r="B94" s="81"/>
+      <c r="C94" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="82"/>
-      <c r="E94" s="82"/>
-      <c r="F94" s="82"/>
-      <c r="G94" s="82"/>
+      <c r="D94" s="81"/>
+      <c r="E94" s="81"/>
+      <c r="F94" s="81"/>
+      <c r="G94" s="81"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="86"/>
-      <c r="B95" s="82"/>
-      <c r="C95" s="82" t="s">
+      <c r="A95" s="80"/>
+      <c r="B95" s="81"/>
+      <c r="C95" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="82"/>
-      <c r="E95" s="82"/>
-      <c r="F95" s="82"/>
-      <c r="G95" s="82"/>
+      <c r="D95" s="81"/>
+      <c r="E95" s="81"/>
+      <c r="F95" s="81"/>
+      <c r="G95" s="81"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="86"/>
-      <c r="B96" s="82"/>
-      <c r="C96" s="82" t="s">
+      <c r="A96" s="80"/>
+      <c r="B96" s="81"/>
+      <c r="C96" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="82"/>
-      <c r="E96" s="82"/>
-      <c r="F96" s="82"/>
-      <c r="G96" s="82"/>
+      <c r="D96" s="81"/>
+      <c r="E96" s="81"/>
+      <c r="F96" s="81"/>
+      <c r="G96" s="81"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="86"/>
-      <c r="B97" s="82"/>
-      <c r="C97" s="82" t="s">
+      <c r="A97" s="80"/>
+      <c r="B97" s="81"/>
+      <c r="C97" s="81" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="82"/>
-      <c r="E97" s="82"/>
-      <c r="F97" s="82"/>
-      <c r="G97" s="82"/>
+      <c r="D97" s="81"/>
+      <c r="E97" s="81"/>
+      <c r="F97" s="81"/>
+      <c r="G97" s="81"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="86"/>
-      <c r="B98" s="82"/>
-      <c r="C98" s="82" t="s">
+      <c r="A98" s="80"/>
+      <c r="B98" s="81"/>
+      <c r="C98" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="82"/>
-      <c r="E98" s="82"/>
-      <c r="F98" s="82"/>
-      <c r="G98" s="82"/>
+      <c r="D98" s="81"/>
+      <c r="E98" s="81"/>
+      <c r="F98" s="81"/>
+      <c r="G98" s="81"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="86">
+      <c r="A99" s="80">
         <v>46230</v>
       </c>
-      <c r="B99" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="82" t="s">
+      <c r="B99" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="82"/>
-      <c r="E99" s="82"/>
-      <c r="F99" s="82"/>
-      <c r="G99" s="82"/>
+      <c r="D99" s="81"/>
+      <c r="E99" s="81"/>
+      <c r="F99" s="81"/>
+      <c r="G99" s="81"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="86"/>
-      <c r="B100" s="82"/>
-      <c r="C100" s="82" t="s">
+      <c r="A100" s="80"/>
+      <c r="B100" s="81"/>
+      <c r="C100" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="82"/>
-      <c r="E100" s="82"/>
-      <c r="F100" s="82"/>
-      <c r="G100" s="82"/>
+      <c r="D100" s="81"/>
+      <c r="E100" s="81"/>
+      <c r="F100" s="81"/>
+      <c r="G100" s="81"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="86">
+      <c r="A101" s="80">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="92" t="s">
+      <c r="C101" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="92"/>
-      <c r="E101" s="92"/>
-      <c r="F101" s="92"/>
-      <c r="G101" s="92"/>
+      <c r="D101" s="106"/>
+      <c r="E101" s="106"/>
+      <c r="F101" s="106"/>
+      <c r="G101" s="106"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="86"/>
+      <c r="A102" s="80"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="92" t="s">
+      <c r="C102" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="92"/>
-      <c r="E102" s="92"/>
-      <c r="F102" s="92"/>
-      <c r="G102" s="92"/>
+      <c r="D102" s="106"/>
+      <c r="E102" s="106"/>
+      <c r="F102" s="106"/>
+      <c r="G102" s="106"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="90" t="s">
+      <c r="A103" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="91" t="s">
+      <c r="B103" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="91"/>
-      <c r="E103" s="91"/>
-      <c r="F103" s="91"/>
-      <c r="G103" s="91"/>
+      <c r="D103" s="95"/>
+      <c r="E103" s="95"/>
+      <c r="F103" s="95"/>
+      <c r="G103" s="95"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="90"/>
-      <c r="B104" s="82"/>
-      <c r="C104" s="82" t="s">
+      <c r="A104" s="105"/>
+      <c r="B104" s="81"/>
+      <c r="C104" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="82"/>
-      <c r="E104" s="82"/>
-      <c r="F104" s="82"/>
-      <c r="G104" s="82"/>
+      <c r="D104" s="81"/>
+      <c r="E104" s="81"/>
+      <c r="F104" s="81"/>
+      <c r="G104" s="81"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="90"/>
-      <c r="B105" s="82"/>
-      <c r="C105" s="82" t="s">
+      <c r="A105" s="105"/>
+      <c r="B105" s="81"/>
+      <c r="C105" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="82"/>
-      <c r="E105" s="82"/>
-      <c r="F105" s="82"/>
-      <c r="G105" s="82"/>
+      <c r="D105" s="81"/>
+      <c r="E105" s="81"/>
+      <c r="F105" s="81"/>
+      <c r="G105" s="81"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="90"/>
-      <c r="B106" s="82"/>
-      <c r="C106" s="82" t="s">
+      <c r="A106" s="105"/>
+      <c r="B106" s="81"/>
+      <c r="C106" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="82"/>
-      <c r="E106" s="82"/>
-      <c r="F106" s="82"/>
-      <c r="G106" s="82"/>
+      <c r="D106" s="81"/>
+      <c r="E106" s="81"/>
+      <c r="F106" s="81"/>
+      <c r="G106" s="81"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="90"/>
-      <c r="B107" s="82"/>
-      <c r="C107" s="82" t="s">
+      <c r="A107" s="105"/>
+      <c r="B107" s="81"/>
+      <c r="C107" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="82"/>
-      <c r="E107" s="82"/>
-      <c r="F107" s="82"/>
-      <c r="G107" s="82"/>
+      <c r="D107" s="81"/>
+      <c r="E107" s="81"/>
+      <c r="F107" s="81"/>
+      <c r="G107" s="81"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="86">
+      <c r="A108" s="80">
         <v>46234</v>
       </c>
-      <c r="B108" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="82" t="s">
+      <c r="B108" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="82"/>
-      <c r="E108" s="82"/>
-      <c r="F108" s="82"/>
-      <c r="G108" s="82"/>
+      <c r="D108" s="81"/>
+      <c r="E108" s="81"/>
+      <c r="F108" s="81"/>
+      <c r="G108" s="81"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="86"/>
-      <c r="B109" s="82"/>
-      <c r="C109" s="82" t="s">
+      <c r="A109" s="80"/>
+      <c r="B109" s="81"/>
+      <c r="C109" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="82"/>
-      <c r="E109" s="82"/>
-      <c r="F109" s="82"/>
-      <c r="G109" s="82"/>
+      <c r="D109" s="81"/>
+      <c r="E109" s="81"/>
+      <c r="F109" s="81"/>
+      <c r="G109" s="81"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -3000,6 +3016,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -3024,129 +3163,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3164,15 +3180,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="102">
+      <c r="A1" s="93">
         <v>46235</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4961,7 +4977,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -5289,15 +5305,15 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="46"/>
-      <c r="B27" s="108" t="s">
+      <c r="B27" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="D27" s="108"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
       <c r="G27" s="51"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -5447,6 +5463,43 @@
       <c r="E39" s="53"/>
       <c r="F39" s="53"/>
       <c r="G39" s="54"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="11">
+        <v>46310</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="108" t="s">
+        <v>212</v>
+      </c>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="35"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="46"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="109" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" s="111"/>
+      <c r="E41" s="111"/>
+      <c r="F41" s="111"/>
+      <c r="G41" s="37"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="45"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="110" t="s">
+        <v>211</v>
+      </c>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD7E6D4-594F-486C-BB5A-4646384D7248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EE2733-B7F5-4458-B2CF-ADD756B27B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="214">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -671,6 +671,9 @@
   </si>
   <si>
     <t>Nhận  VNSH03 + 3 ổ SSD A. Bảo (SEA)</t>
+  </si>
+  <si>
+    <t>Lấy thêm 300 GX12-2P (tổng 500 2 lần</t>
   </si>
 </sst>
 </file>
@@ -894,7 +897,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1051,27 +1054,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1084,9 +1087,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1096,20 +1096,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1117,6 +1111,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1126,9 +1138,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1138,40 +1147,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1497,15 +1473,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="85">
+      <c r="A1" s="65">
         <v>46174</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1514,146 +1490,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="89"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="69"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="80">
+      <c r="A3" s="74">
         <v>46202</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81" t="s">
+      <c r="A4" s="74"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="80"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81" t="s">
+      <c r="A5" s="74"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="81" t="s">
+      <c r="A6" s="74"/>
+      <c r="B6" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="80"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81" t="s">
+      <c r="A7" s="74"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="80"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81" t="s">
+      <c r="A8" s="74"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="80">
+      <c r="A9" s="74">
         <v>46203</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="84"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="80"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="77" t="s">
+      <c r="A10" s="74"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="77" t="s">
+      <c r="A11" s="74"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="79"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="73"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="77" t="s">
+      <c r="A12" s="74"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="73"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="80"/>
+      <c r="A13" s="74"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="73"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1663,6 +1639,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1673,14 +1657,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1698,15 +1674,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="90">
         <v>46204</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1715,152 +1691,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="80">
+      <c r="A3" s="74">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="95" t="s">
+      <c r="A4" s="74"/>
+      <c r="B4" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="80"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81" t="s">
+      <c r="A5" s="74"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81" t="s">
+      <c r="A6" s="74"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="96">
+      <c r="A7" s="92">
         <v>46205</v>
       </c>
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="84"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="97"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="77" t="s">
+      <c r="A8" s="93"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="79"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="73"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="97"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="77" t="s">
+      <c r="A9" s="93"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="79"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="73"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="97"/>
-      <c r="B10" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="77" t="s">
+      <c r="A10" s="93"/>
+      <c r="B10" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="97"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="77" t="s">
+      <c r="A11" s="93"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="79"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="73"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="97"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="77" t="s">
+      <c r="A12" s="93"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="73"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="98"/>
-      <c r="B13" s="81"/>
-      <c r="C13" s="77" t="s">
+      <c r="A13" s="94"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="79"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="73"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="100">
+      <c r="A14" s="83">
         <v>46206</v>
       </c>
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="81" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1872,348 +1848,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="101"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="82" t="s">
+      <c r="A15" s="86"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="84"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="77"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="101"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="82" t="s">
+      <c r="A16" s="86"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="84"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="77"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="101"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="82" t="s">
+      <c r="A17" s="86"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="84"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="77"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="101"/>
-      <c r="B18" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="82" t="s">
+      <c r="A18" s="86"/>
+      <c r="B18" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="84"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="77"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="102"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="82" t="s">
+      <c r="A19" s="84"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="84"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="77"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="103">
+      <c r="A20" s="87">
         <v>46209</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="81" t="s">
+      <c r="C20" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="103"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="81" t="s">
+      <c r="A21" s="87"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="103"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="81" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="103"/>
-      <c r="B23" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="81" t="s">
+      <c r="A23" s="87"/>
+      <c r="B23" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="103"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="82" t="s">
+      <c r="A24" s="87"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="84"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="77"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="103"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="82" t="s">
+      <c r="A25" s="87"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="84"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="77"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="103"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="82" t="s">
+      <c r="A26" s="87"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="84"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="77"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="103"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="82" t="s">
+      <c r="A27" s="87"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="84"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="77"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="103"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="82" t="s">
+      <c r="A28" s="87"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="84"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="77"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="103"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="82" t="s">
+      <c r="A29" s="87"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="84"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="77"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="103"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="82" t="s">
+      <c r="A30" s="87"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="84"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="77"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="103"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="82" t="s">
+      <c r="A31" s="87"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="84"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="77"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="103"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="82" t="s">
+      <c r="A32" s="87"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="84"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="77"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="103"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="82" t="s">
+      <c r="A33" s="87"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="84"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="77"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="103"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="82" t="s">
+      <c r="A34" s="87"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="84"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="77"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="99">
+      <c r="A35" s="85">
         <v>46210</v>
       </c>
-      <c r="B35" s="81" t="s">
+      <c r="B35" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="99"/>
-      <c r="B36" s="81"/>
-      <c r="C36" s="81" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="99"/>
-      <c r="B37" s="81"/>
-      <c r="C37" s="81" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="99"/>
-      <c r="B38" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="81" t="s">
+      <c r="A38" s="85"/>
+      <c r="B38" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="99"/>
-      <c r="B39" s="81"/>
-      <c r="C39" s="81" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="99"/>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81" t="s">
+      <c r="A40" s="85"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="99"/>
-      <c r="B41" s="81"/>
-      <c r="C41" s="81" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="99"/>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81" t="s">
+      <c r="A42" s="85"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="99"/>
-      <c r="B43" s="81"/>
-      <c r="C43" s="81" t="s">
+      <c r="A43" s="85"/>
+      <c r="B43" s="70"/>
+      <c r="C43" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="70"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="99"/>
-      <c r="B44" s="81"/>
-      <c r="C44" s="82" t="s">
+      <c r="A44" s="85"/>
+      <c r="B44" s="70"/>
+      <c r="C44" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="84"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="77"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2222,13 +2198,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="81" t="s">
+      <c r="C45" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2237,255 +2213,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="81" t="s">
+      <c r="C46" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="81"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="100">
+      <c r="A47" s="83">
         <v>46213</v>
       </c>
-      <c r="B47" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="82" t="s">
+      <c r="B47" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="84"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="77"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="101"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="82" t="s">
+      <c r="A48" s="86"/>
+      <c r="B48" s="89"/>
+      <c r="C48" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="84"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="77"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="101"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="82" t="s">
+      <c r="A49" s="86"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="84"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="77"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="101"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="82" t="s">
+      <c r="A50" s="86"/>
+      <c r="B50" s="89"/>
+      <c r="C50" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="84"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="77"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="102"/>
-      <c r="B51" s="91"/>
-      <c r="C51" s="82" t="s">
+      <c r="A51" s="84"/>
+      <c r="B51" s="82"/>
+      <c r="C51" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="84"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="77"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="80">
+      <c r="A52" s="74">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="81" t="s">
+      <c r="C52" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="80"/>
+      <c r="A53" s="74"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="80">
+      <c r="A54" s="74">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="82" t="s">
+      <c r="C54" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="84"/>
+      <c r="D54" s="76"/>
+      <c r="E54" s="76"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="77"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="80"/>
-      <c r="B55" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="104" t="s">
+      <c r="A55" s="74"/>
+      <c r="B55" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="104"/>
-      <c r="E55" s="104"/>
-      <c r="F55" s="104"/>
-      <c r="G55" s="104"/>
+      <c r="D55" s="88"/>
+      <c r="E55" s="88"/>
+      <c r="F55" s="88"/>
+      <c r="G55" s="88"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="80"/>
-      <c r="B56" s="81"/>
-      <c r="C56" s="104" t="s">
+      <c r="A56" s="74"/>
+      <c r="B56" s="70"/>
+      <c r="C56" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="104"/>
-      <c r="E56" s="104"/>
-      <c r="F56" s="104"/>
-      <c r="G56" s="104"/>
+      <c r="D56" s="88"/>
+      <c r="E56" s="88"/>
+      <c r="F56" s="88"/>
+      <c r="G56" s="88"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="80"/>
-      <c r="B57" s="81"/>
-      <c r="C57" s="104" t="s">
+      <c r="A57" s="74"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="104"/>
-      <c r="E57" s="104"/>
-      <c r="F57" s="104"/>
-      <c r="G57" s="104"/>
+      <c r="D57" s="88"/>
+      <c r="E57" s="88"/>
+      <c r="F57" s="88"/>
+      <c r="G57" s="88"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="80"/>
-      <c r="B58" s="81"/>
-      <c r="C58" s="104" t="s">
+      <c r="A58" s="74"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="104"/>
-      <c r="E58" s="104"/>
-      <c r="F58" s="104"/>
-      <c r="G58" s="104"/>
+      <c r="D58" s="88"/>
+      <c r="E58" s="88"/>
+      <c r="F58" s="88"/>
+      <c r="G58" s="88"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="80"/>
-      <c r="B59" s="81"/>
-      <c r="C59" s="104" t="s">
+      <c r="A59" s="74"/>
+      <c r="B59" s="70"/>
+      <c r="C59" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="104"/>
-      <c r="E59" s="104"/>
-      <c r="F59" s="104"/>
-      <c r="G59" s="104"/>
+      <c r="D59" s="88"/>
+      <c r="E59" s="88"/>
+      <c r="F59" s="88"/>
+      <c r="G59" s="88"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="80"/>
-      <c r="B60" s="81"/>
-      <c r="C60" s="104" t="s">
+      <c r="A60" s="74"/>
+      <c r="B60" s="70"/>
+      <c r="C60" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
+      <c r="D60" s="88"/>
+      <c r="E60" s="88"/>
+      <c r="F60" s="88"/>
+      <c r="G60" s="88"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="80"/>
-      <c r="B61" s="81"/>
-      <c r="C61" s="104" t="s">
+      <c r="A61" s="74"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="104"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="104"/>
-      <c r="G61" s="104"/>
+      <c r="D61" s="88"/>
+      <c r="E61" s="88"/>
+      <c r="F61" s="88"/>
+      <c r="G61" s="88"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="80"/>
-      <c r="B62" s="81"/>
-      <c r="C62" s="104" t="s">
+      <c r="A62" s="74"/>
+      <c r="B62" s="70"/>
+      <c r="C62" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
+      <c r="D62" s="88"/>
+      <c r="E62" s="88"/>
+      <c r="F62" s="88"/>
+      <c r="G62" s="88"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="80"/>
-      <c r="B63" s="81"/>
-      <c r="C63" s="104" t="s">
+      <c r="A63" s="74"/>
+      <c r="B63" s="70"/>
+      <c r="C63" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="104"/>
-      <c r="E63" s="104"/>
-      <c r="F63" s="104"/>
-      <c r="G63" s="104"/>
+      <c r="D63" s="88"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="88"/>
+      <c r="G63" s="88"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="80">
+      <c r="A64" s="74">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="81" t="s">
+      <c r="C64" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="81"/>
-      <c r="E64" s="81"/>
-      <c r="F64" s="81"/>
-      <c r="G64" s="81"/>
+      <c r="D64" s="70"/>
+      <c r="E64" s="70"/>
+      <c r="F64" s="70"/>
+      <c r="G64" s="70"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="80"/>
-      <c r="B65" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="81" t="s">
+      <c r="A65" s="74"/>
+      <c r="B65" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="81"/>
-      <c r="E65" s="81"/>
-      <c r="F65" s="81"/>
-      <c r="G65" s="81"/>
+      <c r="D65" s="70"/>
+      <c r="E65" s="70"/>
+      <c r="F65" s="70"/>
+      <c r="G65" s="70"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="80"/>
-      <c r="B66" s="81"/>
-      <c r="C66" s="81" t="s">
+      <c r="A66" s="74"/>
+      <c r="B66" s="70"/>
+      <c r="C66" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="81"/>
-      <c r="E66" s="81"/>
-      <c r="F66" s="81"/>
-      <c r="G66" s="81"/>
+      <c r="D66" s="70"/>
+      <c r="E66" s="70"/>
+      <c r="F66" s="70"/>
+      <c r="G66" s="70"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2494,164 +2470,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="81" t="s">
+      <c r="C67" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="81"/>
-      <c r="E67" s="81"/>
-      <c r="F67" s="81"/>
-      <c r="G67" s="81"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="80">
+      <c r="A68" s="74">
         <v>46220</v>
       </c>
-      <c r="B68" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="81" t="s">
+      <c r="B68" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="81"/>
-      <c r="E68" s="81"/>
-      <c r="F68" s="81"/>
-      <c r="G68" s="81"/>
+      <c r="D68" s="70"/>
+      <c r="E68" s="70"/>
+      <c r="F68" s="70"/>
+      <c r="G68" s="70"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="80"/>
-      <c r="B69" s="81"/>
-      <c r="C69" s="81" t="s">
+      <c r="A69" s="74"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="81"/>
-      <c r="E69" s="81"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="81"/>
+      <c r="D69" s="70"/>
+      <c r="E69" s="70"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="70"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="80">
+      <c r="A70" s="74">
         <v>46223</v>
       </c>
-      <c r="B70" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="82" t="s">
+      <c r="B70" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="83"/>
-      <c r="E70" s="83"/>
-      <c r="F70" s="83"/>
-      <c r="G70" s="84"/>
+      <c r="D70" s="76"/>
+      <c r="E70" s="76"/>
+      <c r="F70" s="76"/>
+      <c r="G70" s="77"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="80"/>
-      <c r="B71" s="81"/>
-      <c r="C71" s="82" t="s">
+      <c r="A71" s="74"/>
+      <c r="B71" s="70"/>
+      <c r="C71" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="83"/>
-      <c r="E71" s="83"/>
-      <c r="F71" s="83"/>
-      <c r="G71" s="84"/>
+      <c r="D71" s="76"/>
+      <c r="E71" s="76"/>
+      <c r="F71" s="76"/>
+      <c r="G71" s="77"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="80"/>
-      <c r="B72" s="81"/>
-      <c r="C72" s="82" t="s">
+      <c r="A72" s="74"/>
+      <c r="B72" s="70"/>
+      <c r="C72" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="83"/>
-      <c r="E72" s="83"/>
-      <c r="F72" s="83"/>
-      <c r="G72" s="84"/>
+      <c r="D72" s="76"/>
+      <c r="E72" s="76"/>
+      <c r="F72" s="76"/>
+      <c r="G72" s="77"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="80"/>
-      <c r="B73" s="81"/>
-      <c r="C73" s="82" t="s">
+      <c r="A73" s="74"/>
+      <c r="B73" s="70"/>
+      <c r="C73" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="83"/>
-      <c r="E73" s="83"/>
-      <c r="F73" s="83"/>
-      <c r="G73" s="84"/>
+      <c r="D73" s="76"/>
+      <c r="E73" s="76"/>
+      <c r="F73" s="76"/>
+      <c r="G73" s="77"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="80"/>
-      <c r="B74" s="81"/>
-      <c r="C74" s="82" t="s">
+      <c r="A74" s="74"/>
+      <c r="B74" s="70"/>
+      <c r="C74" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="83"/>
-      <c r="E74" s="83"/>
-      <c r="F74" s="83"/>
-      <c r="G74" s="84"/>
+      <c r="D74" s="76"/>
+      <c r="E74" s="76"/>
+      <c r="F74" s="76"/>
+      <c r="G74" s="77"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="80"/>
-      <c r="B75" s="81"/>
-      <c r="C75" s="82" t="s">
+      <c r="A75" s="74"/>
+      <c r="B75" s="70"/>
+      <c r="C75" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="83"/>
-      <c r="G75" s="84"/>
+      <c r="D75" s="76"/>
+      <c r="E75" s="76"/>
+      <c r="F75" s="76"/>
+      <c r="G75" s="77"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="80"/>
-      <c r="B76" s="81"/>
-      <c r="C76" s="82" t="s">
+      <c r="A76" s="74"/>
+      <c r="B76" s="70"/>
+      <c r="C76" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="83"/>
-      <c r="E76" s="83"/>
-      <c r="F76" s="83"/>
-      <c r="G76" s="84"/>
+      <c r="D76" s="76"/>
+      <c r="E76" s="76"/>
+      <c r="F76" s="76"/>
+      <c r="G76" s="77"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="80"/>
-      <c r="B77" s="81"/>
-      <c r="C77" s="77" t="s">
+      <c r="A77" s="74"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="78"/>
-      <c r="E77" s="78"/>
-      <c r="F77" s="78"/>
-      <c r="G77" s="79"/>
+      <c r="D77" s="72"/>
+      <c r="E77" s="72"/>
+      <c r="F77" s="72"/>
+      <c r="G77" s="73"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="80"/>
-      <c r="B78" s="81"/>
-      <c r="C78" s="77" t="s">
+      <c r="A78" s="74"/>
+      <c r="B78" s="70"/>
+      <c r="C78" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="78"/>
-      <c r="E78" s="78"/>
-      <c r="F78" s="78"/>
-      <c r="G78" s="79"/>
+      <c r="D78" s="72"/>
+      <c r="E78" s="72"/>
+      <c r="F78" s="72"/>
+      <c r="G78" s="73"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="80"/>
-      <c r="B79" s="81"/>
-      <c r="C79" s="77" t="s">
+      <c r="A79" s="74"/>
+      <c r="B79" s="70"/>
+      <c r="C79" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="78"/>
-      <c r="E79" s="78"/>
-      <c r="F79" s="78"/>
-      <c r="G79" s="79"/>
+      <c r="D79" s="72"/>
+      <c r="E79" s="72"/>
+      <c r="F79" s="72"/>
+      <c r="G79" s="73"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="80"/>
-      <c r="B80" s="81"/>
-      <c r="C80" s="77" t="s">
+      <c r="A80" s="74"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="78"/>
-      <c r="E80" s="78"/>
-      <c r="F80" s="78"/>
-      <c r="G80" s="79"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
+      <c r="G80" s="73"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2660,353 +2636,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="81" t="s">
+      <c r="C81" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="81"/>
-      <c r="E81" s="81"/>
-      <c r="F81" s="81"/>
-      <c r="G81" s="81"/>
+      <c r="D81" s="70"/>
+      <c r="E81" s="70"/>
+      <c r="F81" s="70"/>
+      <c r="G81" s="70"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="80">
+      <c r="A82" s="74">
         <v>46225</v>
       </c>
-      <c r="B82" s="81" t="s">
+      <c r="B82" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="81" t="s">
+      <c r="C82" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="81"/>
-      <c r="E82" s="81"/>
-      <c r="F82" s="81"/>
-      <c r="G82" s="81"/>
+      <c r="D82" s="70"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="70"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="80"/>
-      <c r="B83" s="81"/>
-      <c r="C83" s="81" t="s">
+      <c r="A83" s="74"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="81"/>
-      <c r="E83" s="81"/>
-      <c r="F83" s="81"/>
-      <c r="G83" s="81"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="70"/>
+      <c r="G83" s="70"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="80"/>
-      <c r="B84" s="81"/>
-      <c r="C84" s="81" t="s">
+      <c r="A84" s="74"/>
+      <c r="B84" s="70"/>
+      <c r="C84" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="81"/>
-      <c r="E84" s="81"/>
-      <c r="F84" s="81"/>
-      <c r="G84" s="81"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="70"/>
+      <c r="G84" s="70"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="80"/>
-      <c r="B85" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="81" t="s">
+      <c r="A85" s="74"/>
+      <c r="B85" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="81"/>
-      <c r="E85" s="81"/>
-      <c r="F85" s="81"/>
-      <c r="G85" s="81"/>
+      <c r="D85" s="70"/>
+      <c r="E85" s="70"/>
+      <c r="F85" s="70"/>
+      <c r="G85" s="70"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="80"/>
-      <c r="B86" s="81"/>
-      <c r="C86" s="81" t="s">
+      <c r="A86" s="74"/>
+      <c r="B86" s="70"/>
+      <c r="C86" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="81"/>
-      <c r="E86" s="81"/>
-      <c r="F86" s="81"/>
-      <c r="G86" s="81"/>
+      <c r="D86" s="70"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="70"/>
+      <c r="G86" s="70"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="80"/>
-      <c r="B87" s="81"/>
-      <c r="C87" s="81" t="s">
+      <c r="A87" s="74"/>
+      <c r="B87" s="70"/>
+      <c r="C87" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="81"/>
-      <c r="E87" s="81"/>
-      <c r="F87" s="81"/>
-      <c r="G87" s="81"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="70"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="80"/>
-      <c r="B88" s="81"/>
-      <c r="C88" s="81" t="s">
+      <c r="A88" s="74"/>
+      <c r="B88" s="70"/>
+      <c r="C88" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="81"/>
-      <c r="E88" s="81"/>
-      <c r="F88" s="81"/>
-      <c r="G88" s="81"/>
+      <c r="D88" s="70"/>
+      <c r="E88" s="70"/>
+      <c r="F88" s="70"/>
+      <c r="G88" s="70"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="80"/>
-      <c r="B89" s="81"/>
-      <c r="C89" s="82" t="s">
+      <c r="A89" s="74"/>
+      <c r="B89" s="70"/>
+      <c r="C89" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="83"/>
-      <c r="E89" s="83"/>
-      <c r="F89" s="83"/>
-      <c r="G89" s="84"/>
+      <c r="D89" s="76"/>
+      <c r="E89" s="76"/>
+      <c r="F89" s="76"/>
+      <c r="G89" s="77"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="80"/>
-      <c r="B90" s="81"/>
-      <c r="C90" s="81" t="s">
+      <c r="A90" s="74"/>
+      <c r="B90" s="70"/>
+      <c r="C90" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="81"/>
-      <c r="E90" s="81"/>
-      <c r="F90" s="81"/>
-      <c r="G90" s="81"/>
+      <c r="D90" s="70"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="70"/>
+      <c r="G90" s="70"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="100">
+      <c r="A91" s="83">
         <v>46227</v>
       </c>
-      <c r="B91" s="90" t="s">
+      <c r="B91" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="81" t="s">
+      <c r="C91" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="81"/>
-      <c r="E91" s="81"/>
-      <c r="F91" s="81"/>
-      <c r="G91" s="81"/>
+      <c r="D91" s="70"/>
+      <c r="E91" s="70"/>
+      <c r="F91" s="70"/>
+      <c r="G91" s="70"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="102"/>
-      <c r="B92" s="91"/>
-      <c r="C92" s="82" t="s">
+      <c r="A92" s="84"/>
+      <c r="B92" s="82"/>
+      <c r="C92" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="83"/>
-      <c r="E92" s="83"/>
-      <c r="F92" s="83"/>
-      <c r="G92" s="84"/>
+      <c r="D92" s="76"/>
+      <c r="E92" s="76"/>
+      <c r="F92" s="76"/>
+      <c r="G92" s="77"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="80">
+      <c r="A93" s="74">
         <v>46228</v>
       </c>
-      <c r="B93" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="81" t="s">
+      <c r="B93" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="81"/>
-      <c r="E93" s="81"/>
-      <c r="F93" s="81"/>
-      <c r="G93" s="81"/>
+      <c r="D93" s="70"/>
+      <c r="E93" s="70"/>
+      <c r="F93" s="70"/>
+      <c r="G93" s="70"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="80"/>
-      <c r="B94" s="81"/>
-      <c r="C94" s="81" t="s">
+      <c r="A94" s="74"/>
+      <c r="B94" s="70"/>
+      <c r="C94" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="81"/>
-      <c r="E94" s="81"/>
-      <c r="F94" s="81"/>
-      <c r="G94" s="81"/>
+      <c r="D94" s="70"/>
+      <c r="E94" s="70"/>
+      <c r="F94" s="70"/>
+      <c r="G94" s="70"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="80"/>
-      <c r="B95" s="81"/>
-      <c r="C95" s="81" t="s">
+      <c r="A95" s="74"/>
+      <c r="B95" s="70"/>
+      <c r="C95" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="81"/>
-      <c r="E95" s="81"/>
-      <c r="F95" s="81"/>
-      <c r="G95" s="81"/>
+      <c r="D95" s="70"/>
+      <c r="E95" s="70"/>
+      <c r="F95" s="70"/>
+      <c r="G95" s="70"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="80"/>
-      <c r="B96" s="81"/>
-      <c r="C96" s="81" t="s">
+      <c r="A96" s="74"/>
+      <c r="B96" s="70"/>
+      <c r="C96" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="81"/>
-      <c r="E96" s="81"/>
-      <c r="F96" s="81"/>
-      <c r="G96" s="81"/>
+      <c r="D96" s="70"/>
+      <c r="E96" s="70"/>
+      <c r="F96" s="70"/>
+      <c r="G96" s="70"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="80"/>
-      <c r="B97" s="81"/>
-      <c r="C97" s="81" t="s">
+      <c r="A97" s="74"/>
+      <c r="B97" s="70"/>
+      <c r="C97" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="81"/>
-      <c r="E97" s="81"/>
-      <c r="F97" s="81"/>
-      <c r="G97" s="81"/>
+      <c r="D97" s="70"/>
+      <c r="E97" s="70"/>
+      <c r="F97" s="70"/>
+      <c r="G97" s="70"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="80"/>
-      <c r="B98" s="81"/>
-      <c r="C98" s="81" t="s">
+      <c r="A98" s="74"/>
+      <c r="B98" s="70"/>
+      <c r="C98" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="81"/>
-      <c r="E98" s="81"/>
-      <c r="F98" s="81"/>
-      <c r="G98" s="81"/>
+      <c r="D98" s="70"/>
+      <c r="E98" s="70"/>
+      <c r="F98" s="70"/>
+      <c r="G98" s="70"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="80">
+      <c r="A99" s="74">
         <v>46230</v>
       </c>
-      <c r="B99" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="81" t="s">
+      <c r="B99" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="81"/>
-      <c r="E99" s="81"/>
-      <c r="F99" s="81"/>
-      <c r="G99" s="81"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="70"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="80"/>
-      <c r="B100" s="81"/>
-      <c r="C100" s="81" t="s">
+      <c r="A100" s="74"/>
+      <c r="B100" s="70"/>
+      <c r="C100" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="81"/>
-      <c r="E100" s="81"/>
-      <c r="F100" s="81"/>
-      <c r="G100" s="81"/>
+      <c r="D100" s="70"/>
+      <c r="E100" s="70"/>
+      <c r="F100" s="70"/>
+      <c r="G100" s="70"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="80">
+      <c r="A101" s="74">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="106" t="s">
+      <c r="C101" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="106"/>
-      <c r="E101" s="106"/>
-      <c r="F101" s="106"/>
-      <c r="G101" s="106"/>
+      <c r="D101" s="80"/>
+      <c r="E101" s="80"/>
+      <c r="F101" s="80"/>
+      <c r="G101" s="80"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="80"/>
+      <c r="A102" s="74"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="106" t="s">
+      <c r="C102" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="106"/>
-      <c r="E102" s="106"/>
-      <c r="F102" s="106"/>
-      <c r="G102" s="106"/>
+      <c r="D102" s="80"/>
+      <c r="E102" s="80"/>
+      <c r="F102" s="80"/>
+      <c r="G102" s="80"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="105" t="s">
+      <c r="A103" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="95" t="s">
+      <c r="B103" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="95"/>
-      <c r="E103" s="95"/>
-      <c r="F103" s="95"/>
-      <c r="G103" s="95"/>
+      <c r="D103" s="79"/>
+      <c r="E103" s="79"/>
+      <c r="F103" s="79"/>
+      <c r="G103" s="79"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="105"/>
-      <c r="B104" s="81"/>
-      <c r="C104" s="81" t="s">
+      <c r="A104" s="78"/>
+      <c r="B104" s="70"/>
+      <c r="C104" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="81"/>
-      <c r="E104" s="81"/>
-      <c r="F104" s="81"/>
-      <c r="G104" s="81"/>
+      <c r="D104" s="70"/>
+      <c r="E104" s="70"/>
+      <c r="F104" s="70"/>
+      <c r="G104" s="70"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="105"/>
-      <c r="B105" s="81"/>
-      <c r="C105" s="81" t="s">
+      <c r="A105" s="78"/>
+      <c r="B105" s="70"/>
+      <c r="C105" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="81"/>
-      <c r="E105" s="81"/>
-      <c r="F105" s="81"/>
-      <c r="G105" s="81"/>
+      <c r="D105" s="70"/>
+      <c r="E105" s="70"/>
+      <c r="F105" s="70"/>
+      <c r="G105" s="70"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="105"/>
-      <c r="B106" s="81"/>
-      <c r="C106" s="81" t="s">
+      <c r="A106" s="78"/>
+      <c r="B106" s="70"/>
+      <c r="C106" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="81"/>
-      <c r="E106" s="81"/>
-      <c r="F106" s="81"/>
-      <c r="G106" s="81"/>
+      <c r="D106" s="70"/>
+      <c r="E106" s="70"/>
+      <c r="F106" s="70"/>
+      <c r="G106" s="70"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="105"/>
-      <c r="B107" s="81"/>
-      <c r="C107" s="81" t="s">
+      <c r="A107" s="78"/>
+      <c r="B107" s="70"/>
+      <c r="C107" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="81"/>
-      <c r="E107" s="81"/>
-      <c r="F107" s="81"/>
-      <c r="G107" s="81"/>
+      <c r="D107" s="70"/>
+      <c r="E107" s="70"/>
+      <c r="F107" s="70"/>
+      <c r="G107" s="70"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="80">
+      <c r="A108" s="74">
         <v>46234</v>
       </c>
-      <c r="B108" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="81" t="s">
+      <c r="B108" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="81"/>
-      <c r="E108" s="81"/>
-      <c r="F108" s="81"/>
-      <c r="G108" s="81"/>
+      <c r="D108" s="70"/>
+      <c r="E108" s="70"/>
+      <c r="F108" s="70"/>
+      <c r="G108" s="70"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="80"/>
-      <c r="B109" s="81"/>
-      <c r="C109" s="81" t="s">
+      <c r="A109" s="74"/>
+      <c r="B109" s="70"/>
+      <c r="C109" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="81"/>
-      <c r="E109" s="81"/>
-      <c r="F109" s="81"/>
-      <c r="G109" s="81"/>
+      <c r="D109" s="70"/>
+      <c r="E109" s="70"/>
+      <c r="F109" s="70"/>
+      <c r="G109" s="70"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -3016,68 +2992,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -3102,67 +3077,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3180,15 +3156,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93">
+      <c r="A1" s="90">
         <v>46235</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4130,15 +4106,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="107">
+      <c r="A1" s="95">
         <v>46266</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4977,24 +4953,26 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="14" customWidth="1"/>
+    <col min="3" max="6" width="9.140625" style="14"/>
+    <col min="7" max="7" width="18.140625" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="107">
+      <c r="A1" s="95">
         <v>46296</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -5116,17 +5094,17 @@
       <c r="G10" s="54"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="52" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
@@ -5138,94 +5116,94 @@
       <c r="C12" s="52" t="s">
         <v>191</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="76"/>
+      <c r="A13" s="64"/>
       <c r="B13" s="46"/>
       <c r="C13" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="75"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="76"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="46"/>
       <c r="C14" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="37"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="76"/>
+      <c r="A15" s="64"/>
       <c r="B15" s="46" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="51"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
-      <c r="B16" s="67"/>
+      <c r="B16" s="46"/>
       <c r="C16" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
-      <c r="B17" s="67"/>
+      <c r="B17" s="46"/>
       <c r="C17" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
-      <c r="B18" s="67"/>
+      <c r="B18" s="46"/>
       <c r="C18" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="36"/>
-      <c r="B19" s="68"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="71"/>
+      <c r="G19" s="37"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="38"/>
-      <c r="B20" s="66"/>
+      <c r="B20" s="42"/>
       <c r="C20" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="73"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
@@ -5376,9 +5354,6 @@
       <c r="C32" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
       <c r="G32" s="37"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -5387,9 +5362,6 @@
       <c r="C33" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
       <c r="G33" s="37"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -5398,9 +5370,6 @@
       <c r="C34" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
       <c r="G34" s="37"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5452,26 +5421,26 @@
       <c r="G38" s="50"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="53" t="s">
+      <c r="A39" s="13"/>
+      <c r="B39" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="47" t="s">
         <v>204</v>
       </c>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="54"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="48"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
+      <c r="A40" s="33">
         <v>46310</v>
       </c>
       <c r="B40" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="108" t="s">
+      <c r="C40" s="24" t="s">
         <v>212</v>
       </c>
       <c r="D40" s="34"/>
@@ -5480,26 +5449,37 @@
       <c r="G40" s="35"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="46"/>
+      <c r="A41" s="25"/>
       <c r="B41" s="41"/>
-      <c r="C41" s="109" t="s">
+      <c r="C41" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="D41" s="111"/>
-      <c r="E41" s="111"/>
-      <c r="F41" s="111"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
       <c r="G41" s="37"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="45"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="110" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="40"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="37"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="38"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EE2733-B7F5-4458-B2CF-ADD756B27B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A31CDF-A384-44A0-BD28-D05793882E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="216">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -667,13 +667,19 @@
     <t>Nhận 2 VNSH03 A. Bảo (Kho)</t>
   </si>
   <si>
-    <t>Trả 3 VNSH03 SEA cho Tuấn Anh</t>
-  </si>
-  <si>
-    <t>Nhận  VNSH03 + 3 ổ SSD A. Bảo (SEA)</t>
-  </si>
-  <si>
     <t>Lấy thêm 300 GX12-2P (tổng 500 2 lần</t>
+  </si>
+  <si>
+    <t>Nhận  VNSH03 + 3 ổ SSD NVMe A. Bảo (SEA) xử lý xong trả cho Tuấn Anh trong ngày</t>
+  </si>
+  <si>
+    <t>Trả BH Anh Tuấn NB (trả Quỳnh HTKT)</t>
+  </si>
+  <si>
+    <t>Nhập kho 33 VNSH03 chưa làm phiếu</t>
+  </si>
+  <si>
+    <t>Nhận 180 VNSH03 Xforce tổng 2 đợt (đợt 1+2 gộp là đợt 1 254 đã trả lỗi 10 đợt 1 còn 244 + đợt 2 180  tổng 424)</t>
   </si>
 </sst>
 </file>
@@ -897,7 +903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1055,6 +1061,9 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1473,15 +1482,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="65">
+      <c r="A1" s="66">
         <v>46174</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1490,146 +1499,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="70"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="74">
+      <c r="A3" s="75">
         <v>46202</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="74"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70" t="s">
+      <c r="A4" s="75"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="74"/>
-      <c r="B6" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="70" t="s">
+      <c r="A6" s="75"/>
+      <c r="B6" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70" t="s">
+      <c r="A7" s="75"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="74"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70" t="s">
+      <c r="A8" s="75"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="74">
+      <c r="A9" s="75">
         <v>46203</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="C9" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="74"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="71" t="s">
+      <c r="A10" s="75"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="74"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="74"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="71" t="s">
+      <c r="A11" s="75"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="74"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="74"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="71" t="s">
+      <c r="A12" s="75"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="74"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="74"/>
+      <c r="A13" s="75"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="74"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1674,15 +1683,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="90">
+      <c r="A1" s="91">
         <v>46204</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1691,152 +1700,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="74">
+      <c r="A3" s="75">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="74"/>
-      <c r="B4" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="79" t="s">
+      <c r="A4" s="75"/>
+      <c r="B4" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="74"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70" t="s">
+      <c r="A6" s="75"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="92">
+      <c r="A7" s="93">
         <v>46205</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="78"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="93"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="71" t="s">
+      <c r="A8" s="94"/>
+      <c r="B8" s="90"/>
+      <c r="C8" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="74"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="93"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="71" t="s">
+      <c r="A9" s="94"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="74"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="93"/>
-      <c r="B10" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="71" t="s">
+      <c r="A10" s="94"/>
+      <c r="B10" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="74"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="93"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="71" t="s">
+      <c r="A11" s="94"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="74"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="93"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="71" t="s">
+      <c r="A12" s="94"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="74"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="94"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="71" t="s">
+      <c r="A13" s="95"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="74"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="83">
+      <c r="A14" s="84">
         <v>46206</v>
       </c>
-      <c r="B14" s="81" t="s">
+      <c r="B14" s="82" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1848,348 +1857,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="86"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="75" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="76"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="78"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="86"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="75" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="78"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="86"/>
-      <c r="B17" s="82"/>
-      <c r="C17" s="75" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="78"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="86"/>
-      <c r="B18" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="75" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="78"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="84"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="75" t="s">
+      <c r="A19" s="85"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="78"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="87">
+      <c r="A20" s="88">
         <v>46209</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="87"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70" t="s">
+      <c r="A21" s="88"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="87"/>
-      <c r="B22" s="70"/>
-      <c r="C22" s="70" t="s">
+      <c r="A22" s="88"/>
+      <c r="B22" s="71"/>
+      <c r="C22" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="87"/>
-      <c r="B23" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="70" t="s">
+      <c r="A23" s="88"/>
+      <c r="B23" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="87"/>
-      <c r="B24" s="70"/>
-      <c r="C24" s="75" t="s">
+      <c r="A24" s="88"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="78"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="87"/>
-      <c r="B25" s="70"/>
-      <c r="C25" s="75" t="s">
+      <c r="A25" s="88"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="78"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="87"/>
-      <c r="B26" s="70"/>
-      <c r="C26" s="75" t="s">
+      <c r="A26" s="88"/>
+      <c r="B26" s="71"/>
+      <c r="C26" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="78"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="87"/>
-      <c r="B27" s="70"/>
-      <c r="C27" s="75" t="s">
+      <c r="A27" s="88"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="78"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="87"/>
-      <c r="B28" s="70"/>
-      <c r="C28" s="75" t="s">
+      <c r="A28" s="88"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="78"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="87"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="75" t="s">
+      <c r="A29" s="88"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="78"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="87"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="75" t="s">
+      <c r="A30" s="88"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="78"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="87"/>
-      <c r="B31" s="70"/>
-      <c r="C31" s="75" t="s">
+      <c r="A31" s="88"/>
+      <c r="B31" s="71"/>
+      <c r="C31" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="77"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="78"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="87"/>
-      <c r="B32" s="70"/>
-      <c r="C32" s="75" t="s">
+      <c r="A32" s="88"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="78"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="87"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="75" t="s">
+      <c r="A33" s="88"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="78"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="87"/>
-      <c r="B34" s="70"/>
-      <c r="C34" s="75" t="s">
+      <c r="A34" s="88"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="78"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="85">
+      <c r="A35" s="86">
         <v>46210</v>
       </c>
-      <c r="B35" s="70" t="s">
+      <c r="B35" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="70" t="s">
+      <c r="C35" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70" t="s">
+      <c r="A36" s="86"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
-      <c r="B37" s="70"/>
-      <c r="C37" s="70" t="s">
+      <c r="A37" s="86"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="70"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
-      <c r="B38" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="70" t="s">
+      <c r="A38" s="86"/>
+      <c r="B38" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="85"/>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70" t="s">
+      <c r="A39" s="86"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70" t="s">
+      <c r="A40" s="86"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70" t="s">
+      <c r="A41" s="86"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70" t="s">
+      <c r="A42" s="86"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="70"/>
-      <c r="C43" s="70" t="s">
+      <c r="A43" s="86"/>
+      <c r="B43" s="71"/>
+      <c r="C43" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="70"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="70"/>
-      <c r="C44" s="75" t="s">
+      <c r="A44" s="86"/>
+      <c r="B44" s="71"/>
+      <c r="C44" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="77"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="78"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -2198,13 +2207,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="70" t="s">
+      <c r="C45" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="70"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -2213,255 +2222,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="70" t="s">
+      <c r="C46" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="83">
+      <c r="A47" s="84">
         <v>46213</v>
       </c>
-      <c r="B47" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="75" t="s">
+      <c r="B47" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="77"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
+      <c r="F47" s="77"/>
+      <c r="G47" s="78"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="86"/>
-      <c r="B48" s="89"/>
-      <c r="C48" s="75" t="s">
+      <c r="A48" s="87"/>
+      <c r="B48" s="90"/>
+      <c r="C48" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="77"/>
+      <c r="D48" s="77"/>
+      <c r="E48" s="77"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="78"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="86"/>
-      <c r="B49" s="89"/>
-      <c r="C49" s="75" t="s">
+      <c r="A49" s="87"/>
+      <c r="B49" s="90"/>
+      <c r="C49" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="77"/>
+      <c r="D49" s="77"/>
+      <c r="E49" s="77"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="78"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="86"/>
-      <c r="B50" s="89"/>
-      <c r="C50" s="75" t="s">
+      <c r="A50" s="87"/>
+      <c r="B50" s="90"/>
+      <c r="C50" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="76"/>
-      <c r="E50" s="76"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="77"/>
+      <c r="D50" s="77"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="78"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="84"/>
-      <c r="B51" s="82"/>
-      <c r="C51" s="75" t="s">
+      <c r="A51" s="85"/>
+      <c r="B51" s="83"/>
+      <c r="C51" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="76"/>
-      <c r="E51" s="76"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="77"/>
+      <c r="D51" s="77"/>
+      <c r="E51" s="77"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="78"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="74">
+      <c r="A52" s="75">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="70" t="s">
+      <c r="C52" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="70"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="74"/>
+      <c r="A53" s="75"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="70" t="s">
+      <c r="C53" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="70"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="74">
+      <c r="A54" s="75">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="75" t="s">
+      <c r="C54" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="76"/>
-      <c r="E54" s="76"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="77"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="77"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="78"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="74"/>
-      <c r="B55" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="88" t="s">
+      <c r="A55" s="75"/>
+      <c r="B55" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="88"/>
-      <c r="E55" s="88"/>
-      <c r="F55" s="88"/>
-      <c r="G55" s="88"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="74"/>
-      <c r="B56" s="70"/>
-      <c r="C56" s="88" t="s">
+      <c r="A56" s="75"/>
+      <c r="B56" s="71"/>
+      <c r="C56" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="88"/>
-      <c r="E56" s="88"/>
-      <c r="F56" s="88"/>
-      <c r="G56" s="88"/>
+      <c r="D56" s="89"/>
+      <c r="E56" s="89"/>
+      <c r="F56" s="89"/>
+      <c r="G56" s="89"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="74"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="88" t="s">
+      <c r="A57" s="75"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="88"/>
-      <c r="E57" s="88"/>
-      <c r="F57" s="88"/>
-      <c r="G57" s="88"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="89"/>
+      <c r="F57" s="89"/>
+      <c r="G57" s="89"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="74"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="88" t="s">
+      <c r="A58" s="75"/>
+      <c r="B58" s="71"/>
+      <c r="C58" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="88"/>
-      <c r="E58" s="88"/>
-      <c r="F58" s="88"/>
-      <c r="G58" s="88"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="89"/>
+      <c r="F58" s="89"/>
+      <c r="G58" s="89"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="74"/>
-      <c r="B59" s="70"/>
-      <c r="C59" s="88" t="s">
+      <c r="A59" s="75"/>
+      <c r="B59" s="71"/>
+      <c r="C59" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="88"/>
-      <c r="E59" s="88"/>
-      <c r="F59" s="88"/>
-      <c r="G59" s="88"/>
+      <c r="D59" s="89"/>
+      <c r="E59" s="89"/>
+      <c r="F59" s="89"/>
+      <c r="G59" s="89"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="74"/>
-      <c r="B60" s="70"/>
-      <c r="C60" s="88" t="s">
+      <c r="A60" s="75"/>
+      <c r="B60" s="71"/>
+      <c r="C60" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="88"/>
-      <c r="E60" s="88"/>
-      <c r="F60" s="88"/>
-      <c r="G60" s="88"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="74"/>
-      <c r="B61" s="70"/>
-      <c r="C61" s="88" t="s">
+      <c r="A61" s="75"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="88"/>
-      <c r="E61" s="88"/>
-      <c r="F61" s="88"/>
-      <c r="G61" s="88"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="89"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="74"/>
-      <c r="B62" s="70"/>
-      <c r="C62" s="88" t="s">
+      <c r="A62" s="75"/>
+      <c r="B62" s="71"/>
+      <c r="C62" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="88"/>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="89"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="74"/>
-      <c r="B63" s="70"/>
-      <c r="C63" s="88" t="s">
+      <c r="A63" s="75"/>
+      <c r="B63" s="71"/>
+      <c r="C63" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="88"/>
-      <c r="E63" s="88"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="88"/>
+      <c r="D63" s="89"/>
+      <c r="E63" s="89"/>
+      <c r="F63" s="89"/>
+      <c r="G63" s="89"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="74">
+      <c r="A64" s="75">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="70" t="s">
+      <c r="C64" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="70"/>
-      <c r="E64" s="70"/>
-      <c r="F64" s="70"/>
-      <c r="G64" s="70"/>
+      <c r="D64" s="71"/>
+      <c r="E64" s="71"/>
+      <c r="F64" s="71"/>
+      <c r="G64" s="71"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="74"/>
-      <c r="B65" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="70" t="s">
+      <c r="A65" s="75"/>
+      <c r="B65" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="70"/>
-      <c r="E65" s="70"/>
-      <c r="F65" s="70"/>
-      <c r="G65" s="70"/>
+      <c r="D65" s="71"/>
+      <c r="E65" s="71"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="71"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="74"/>
-      <c r="B66" s="70"/>
-      <c r="C66" s="70" t="s">
+      <c r="A66" s="75"/>
+      <c r="B66" s="71"/>
+      <c r="C66" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="70"/>
-      <c r="E66" s="70"/>
-      <c r="F66" s="70"/>
-      <c r="G66" s="70"/>
+      <c r="D66" s="71"/>
+      <c r="E66" s="71"/>
+      <c r="F66" s="71"/>
+      <c r="G66" s="71"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2470,164 +2479,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="70" t="s">
+      <c r="C67" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="70"/>
-      <c r="E67" s="70"/>
-      <c r="F67" s="70"/>
-      <c r="G67" s="70"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="71"/>
+      <c r="F67" s="71"/>
+      <c r="G67" s="71"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="74">
+      <c r="A68" s="75">
         <v>46220</v>
       </c>
-      <c r="B68" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="70" t="s">
+      <c r="B68" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="70"/>
-      <c r="E68" s="70"/>
-      <c r="F68" s="70"/>
-      <c r="G68" s="70"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
+      <c r="G68" s="71"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="74"/>
-      <c r="B69" s="70"/>
-      <c r="C69" s="70" t="s">
+      <c r="A69" s="75"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="70"/>
-      <c r="E69" s="70"/>
-      <c r="F69" s="70"/>
-      <c r="G69" s="70"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="71"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="74">
+      <c r="A70" s="75">
         <v>46223</v>
       </c>
-      <c r="B70" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="75" t="s">
+      <c r="B70" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="76"/>
-      <c r="E70" s="76"/>
-      <c r="F70" s="76"/>
-      <c r="G70" s="77"/>
+      <c r="D70" s="77"/>
+      <c r="E70" s="77"/>
+      <c r="F70" s="77"/>
+      <c r="G70" s="78"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="74"/>
-      <c r="B71" s="70"/>
-      <c r="C71" s="75" t="s">
+      <c r="A71" s="75"/>
+      <c r="B71" s="71"/>
+      <c r="C71" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="76"/>
-      <c r="E71" s="76"/>
-      <c r="F71" s="76"/>
-      <c r="G71" s="77"/>
+      <c r="D71" s="77"/>
+      <c r="E71" s="77"/>
+      <c r="F71" s="77"/>
+      <c r="G71" s="78"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="74"/>
-      <c r="B72" s="70"/>
-      <c r="C72" s="75" t="s">
+      <c r="A72" s="75"/>
+      <c r="B72" s="71"/>
+      <c r="C72" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="76"/>
-      <c r="E72" s="76"/>
-      <c r="F72" s="76"/>
-      <c r="G72" s="77"/>
+      <c r="D72" s="77"/>
+      <c r="E72" s="77"/>
+      <c r="F72" s="77"/>
+      <c r="G72" s="78"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="74"/>
-      <c r="B73" s="70"/>
-      <c r="C73" s="75" t="s">
+      <c r="A73" s="75"/>
+      <c r="B73" s="71"/>
+      <c r="C73" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="76"/>
-      <c r="E73" s="76"/>
-      <c r="F73" s="76"/>
-      <c r="G73" s="77"/>
+      <c r="D73" s="77"/>
+      <c r="E73" s="77"/>
+      <c r="F73" s="77"/>
+      <c r="G73" s="78"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="74"/>
-      <c r="B74" s="70"/>
-      <c r="C74" s="75" t="s">
+      <c r="A74" s="75"/>
+      <c r="B74" s="71"/>
+      <c r="C74" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="76"/>
-      <c r="E74" s="76"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="77"/>
+      <c r="D74" s="77"/>
+      <c r="E74" s="77"/>
+      <c r="F74" s="77"/>
+      <c r="G74" s="78"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="74"/>
-      <c r="B75" s="70"/>
-      <c r="C75" s="75" t="s">
+      <c r="A75" s="75"/>
+      <c r="B75" s="71"/>
+      <c r="C75" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="76"/>
-      <c r="E75" s="76"/>
-      <c r="F75" s="76"/>
-      <c r="G75" s="77"/>
+      <c r="D75" s="77"/>
+      <c r="E75" s="77"/>
+      <c r="F75" s="77"/>
+      <c r="G75" s="78"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="74"/>
-      <c r="B76" s="70"/>
-      <c r="C76" s="75" t="s">
+      <c r="A76" s="75"/>
+      <c r="B76" s="71"/>
+      <c r="C76" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="76"/>
-      <c r="E76" s="76"/>
-      <c r="F76" s="76"/>
-      <c r="G76" s="77"/>
+      <c r="D76" s="77"/>
+      <c r="E76" s="77"/>
+      <c r="F76" s="77"/>
+      <c r="G76" s="78"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="74"/>
-      <c r="B77" s="70"/>
-      <c r="C77" s="71" t="s">
+      <c r="A77" s="75"/>
+      <c r="B77" s="71"/>
+      <c r="C77" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="72"/>
-      <c r="E77" s="72"/>
-      <c r="F77" s="72"/>
-      <c r="G77" s="73"/>
+      <c r="D77" s="73"/>
+      <c r="E77" s="73"/>
+      <c r="F77" s="73"/>
+      <c r="G77" s="74"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="74"/>
-      <c r="B78" s="70"/>
-      <c r="C78" s="71" t="s">
+      <c r="A78" s="75"/>
+      <c r="B78" s="71"/>
+      <c r="C78" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="72"/>
-      <c r="E78" s="72"/>
-      <c r="F78" s="72"/>
-      <c r="G78" s="73"/>
+      <c r="D78" s="73"/>
+      <c r="E78" s="73"/>
+      <c r="F78" s="73"/>
+      <c r="G78" s="74"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="74"/>
-      <c r="B79" s="70"/>
-      <c r="C79" s="71" t="s">
+      <c r="A79" s="75"/>
+      <c r="B79" s="71"/>
+      <c r="C79" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="72"/>
-      <c r="E79" s="72"/>
-      <c r="F79" s="72"/>
-      <c r="G79" s="73"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
+      <c r="F79" s="73"/>
+      <c r="G79" s="74"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="74"/>
-      <c r="B80" s="70"/>
-      <c r="C80" s="71" t="s">
+      <c r="A80" s="75"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="72"/>
-      <c r="G80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="74"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2636,353 +2645,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="70" t="s">
+      <c r="C81" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="70"/>
-      <c r="E81" s="70"/>
-      <c r="F81" s="70"/>
-      <c r="G81" s="70"/>
+      <c r="D81" s="71"/>
+      <c r="E81" s="71"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="71"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="74">
+      <c r="A82" s="75">
         <v>46225</v>
       </c>
-      <c r="B82" s="70" t="s">
+      <c r="B82" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="70" t="s">
+      <c r="C82" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="70"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="70"/>
-      <c r="G82" s="70"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="71"/>
+      <c r="F82" s="71"/>
+      <c r="G82" s="71"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="74"/>
-      <c r="B83" s="70"/>
-      <c r="C83" s="70" t="s">
+      <c r="A83" s="75"/>
+      <c r="B83" s="71"/>
+      <c r="C83" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="70"/>
-      <c r="E83" s="70"/>
-      <c r="F83" s="70"/>
-      <c r="G83" s="70"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="71"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="71"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="74"/>
-      <c r="B84" s="70"/>
-      <c r="C84" s="70" t="s">
+      <c r="A84" s="75"/>
+      <c r="B84" s="71"/>
+      <c r="C84" s="71" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="70"/>
-      <c r="E84" s="70"/>
-      <c r="F84" s="70"/>
-      <c r="G84" s="70"/>
+      <c r="D84" s="71"/>
+      <c r="E84" s="71"/>
+      <c r="F84" s="71"/>
+      <c r="G84" s="71"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="74"/>
-      <c r="B85" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="70" t="s">
+      <c r="A85" s="75"/>
+      <c r="B85" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="70"/>
-      <c r="E85" s="70"/>
-      <c r="F85" s="70"/>
-      <c r="G85" s="70"/>
+      <c r="D85" s="71"/>
+      <c r="E85" s="71"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="71"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="74"/>
-      <c r="B86" s="70"/>
-      <c r="C86" s="70" t="s">
+      <c r="A86" s="75"/>
+      <c r="B86" s="71"/>
+      <c r="C86" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="70"/>
-      <c r="E86" s="70"/>
-      <c r="F86" s="70"/>
-      <c r="G86" s="70"/>
+      <c r="D86" s="71"/>
+      <c r="E86" s="71"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="71"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="74"/>
-      <c r="B87" s="70"/>
-      <c r="C87" s="70" t="s">
+      <c r="A87" s="75"/>
+      <c r="B87" s="71"/>
+      <c r="C87" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="70"/>
-      <c r="E87" s="70"/>
-      <c r="F87" s="70"/>
-      <c r="G87" s="70"/>
+      <c r="D87" s="71"/>
+      <c r="E87" s="71"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="71"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="74"/>
-      <c r="B88" s="70"/>
-      <c r="C88" s="70" t="s">
+      <c r="A88" s="75"/>
+      <c r="B88" s="71"/>
+      <c r="C88" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="70"/>
-      <c r="E88" s="70"/>
-      <c r="F88" s="70"/>
-      <c r="G88" s="70"/>
+      <c r="D88" s="71"/>
+      <c r="E88" s="71"/>
+      <c r="F88" s="71"/>
+      <c r="G88" s="71"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="74"/>
-      <c r="B89" s="70"/>
-      <c r="C89" s="75" t="s">
+      <c r="A89" s="75"/>
+      <c r="B89" s="71"/>
+      <c r="C89" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="76"/>
-      <c r="E89" s="76"/>
-      <c r="F89" s="76"/>
-      <c r="G89" s="77"/>
+      <c r="D89" s="77"/>
+      <c r="E89" s="77"/>
+      <c r="F89" s="77"/>
+      <c r="G89" s="78"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="74"/>
-      <c r="B90" s="70"/>
-      <c r="C90" s="70" t="s">
+      <c r="A90" s="75"/>
+      <c r="B90" s="71"/>
+      <c r="C90" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="70"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="70"/>
-      <c r="G90" s="70"/>
+      <c r="D90" s="71"/>
+      <c r="E90" s="71"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="71"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="83">
+      <c r="A91" s="84">
         <v>46227</v>
       </c>
-      <c r="B91" s="81" t="s">
+      <c r="B91" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="70" t="s">
+      <c r="C91" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="70"/>
-      <c r="E91" s="70"/>
-      <c r="F91" s="70"/>
-      <c r="G91" s="70"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
+      <c r="G91" s="71"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="84"/>
-      <c r="B92" s="82"/>
-      <c r="C92" s="75" t="s">
+      <c r="A92" s="85"/>
+      <c r="B92" s="83"/>
+      <c r="C92" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="76"/>
-      <c r="E92" s="76"/>
-      <c r="F92" s="76"/>
-      <c r="G92" s="77"/>
+      <c r="D92" s="77"/>
+      <c r="E92" s="77"/>
+      <c r="F92" s="77"/>
+      <c r="G92" s="78"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="74">
+      <c r="A93" s="75">
         <v>46228</v>
       </c>
-      <c r="B93" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="70" t="s">
+      <c r="B93" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="70"/>
-      <c r="E93" s="70"/>
-      <c r="F93" s="70"/>
-      <c r="G93" s="70"/>
+      <c r="D93" s="71"/>
+      <c r="E93" s="71"/>
+      <c r="F93" s="71"/>
+      <c r="G93" s="71"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="74"/>
-      <c r="B94" s="70"/>
-      <c r="C94" s="70" t="s">
+      <c r="A94" s="75"/>
+      <c r="B94" s="71"/>
+      <c r="C94" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="70"/>
-      <c r="E94" s="70"/>
-      <c r="F94" s="70"/>
-      <c r="G94" s="70"/>
+      <c r="D94" s="71"/>
+      <c r="E94" s="71"/>
+      <c r="F94" s="71"/>
+      <c r="G94" s="71"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="74"/>
-      <c r="B95" s="70"/>
-      <c r="C95" s="70" t="s">
+      <c r="A95" s="75"/>
+      <c r="B95" s="71"/>
+      <c r="C95" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="70"/>
-      <c r="E95" s="70"/>
-      <c r="F95" s="70"/>
-      <c r="G95" s="70"/>
+      <c r="D95" s="71"/>
+      <c r="E95" s="71"/>
+      <c r="F95" s="71"/>
+      <c r="G95" s="71"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="74"/>
-      <c r="B96" s="70"/>
-      <c r="C96" s="70" t="s">
+      <c r="A96" s="75"/>
+      <c r="B96" s="71"/>
+      <c r="C96" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="70"/>
-      <c r="E96" s="70"/>
-      <c r="F96" s="70"/>
-      <c r="G96" s="70"/>
+      <c r="D96" s="71"/>
+      <c r="E96" s="71"/>
+      <c r="F96" s="71"/>
+      <c r="G96" s="71"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="74"/>
-      <c r="B97" s="70"/>
-      <c r="C97" s="70" t="s">
+      <c r="A97" s="75"/>
+      <c r="B97" s="71"/>
+      <c r="C97" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="70"/>
-      <c r="E97" s="70"/>
-      <c r="F97" s="70"/>
-      <c r="G97" s="70"/>
+      <c r="D97" s="71"/>
+      <c r="E97" s="71"/>
+      <c r="F97" s="71"/>
+      <c r="G97" s="71"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="74"/>
-      <c r="B98" s="70"/>
-      <c r="C98" s="70" t="s">
+      <c r="A98" s="75"/>
+      <c r="B98" s="71"/>
+      <c r="C98" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="70"/>
-      <c r="E98" s="70"/>
-      <c r="F98" s="70"/>
-      <c r="G98" s="70"/>
+      <c r="D98" s="71"/>
+      <c r="E98" s="71"/>
+      <c r="F98" s="71"/>
+      <c r="G98" s="71"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="74">
+      <c r="A99" s="75">
         <v>46230</v>
       </c>
-      <c r="B99" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="70" t="s">
+      <c r="B99" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="70"/>
-      <c r="E99" s="70"/>
-      <c r="F99" s="70"/>
-      <c r="G99" s="70"/>
+      <c r="D99" s="71"/>
+      <c r="E99" s="71"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="71"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="74"/>
-      <c r="B100" s="70"/>
-      <c r="C100" s="70" t="s">
+      <c r="A100" s="75"/>
+      <c r="B100" s="71"/>
+      <c r="C100" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="70"/>
-      <c r="E100" s="70"/>
-      <c r="F100" s="70"/>
-      <c r="G100" s="70"/>
+      <c r="D100" s="71"/>
+      <c r="E100" s="71"/>
+      <c r="F100" s="71"/>
+      <c r="G100" s="71"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="74">
+      <c r="A101" s="75">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="80" t="s">
+      <c r="C101" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="80"/>
-      <c r="E101" s="80"/>
-      <c r="F101" s="80"/>
-      <c r="G101" s="80"/>
+      <c r="D101" s="81"/>
+      <c r="E101" s="81"/>
+      <c r="F101" s="81"/>
+      <c r="G101" s="81"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="74"/>
+      <c r="A102" s="75"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="80" t="s">
+      <c r="C102" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="80"/>
-      <c r="E102" s="80"/>
-      <c r="F102" s="80"/>
-      <c r="G102" s="80"/>
+      <c r="D102" s="81"/>
+      <c r="E102" s="81"/>
+      <c r="F102" s="81"/>
+      <c r="G102" s="81"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="78" t="s">
+      <c r="A103" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C103" s="79" t="s">
+      <c r="B103" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="79"/>
-      <c r="E103" s="79"/>
-      <c r="F103" s="79"/>
-      <c r="G103" s="79"/>
+      <c r="D103" s="80"/>
+      <c r="E103" s="80"/>
+      <c r="F103" s="80"/>
+      <c r="G103" s="80"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="78"/>
-      <c r="B104" s="70"/>
-      <c r="C104" s="70" t="s">
+      <c r="A104" s="79"/>
+      <c r="B104" s="71"/>
+      <c r="C104" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="70"/>
-      <c r="E104" s="70"/>
-      <c r="F104" s="70"/>
-      <c r="G104" s="70"/>
+      <c r="D104" s="71"/>
+      <c r="E104" s="71"/>
+      <c r="F104" s="71"/>
+      <c r="G104" s="71"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="78"/>
-      <c r="B105" s="70"/>
-      <c r="C105" s="70" t="s">
+      <c r="A105" s="79"/>
+      <c r="B105" s="71"/>
+      <c r="C105" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="70"/>
-      <c r="E105" s="70"/>
-      <c r="F105" s="70"/>
-      <c r="G105" s="70"/>
+      <c r="D105" s="71"/>
+      <c r="E105" s="71"/>
+      <c r="F105" s="71"/>
+      <c r="G105" s="71"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="78"/>
-      <c r="B106" s="70"/>
-      <c r="C106" s="70" t="s">
+      <c r="A106" s="79"/>
+      <c r="B106" s="71"/>
+      <c r="C106" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="70"/>
-      <c r="E106" s="70"/>
-      <c r="F106" s="70"/>
-      <c r="G106" s="70"/>
+      <c r="D106" s="71"/>
+      <c r="E106" s="71"/>
+      <c r="F106" s="71"/>
+      <c r="G106" s="71"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="78"/>
-      <c r="B107" s="70"/>
-      <c r="C107" s="70" t="s">
+      <c r="A107" s="79"/>
+      <c r="B107" s="71"/>
+      <c r="C107" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="70"/>
-      <c r="E107" s="70"/>
-      <c r="F107" s="70"/>
-      <c r="G107" s="70"/>
+      <c r="D107" s="71"/>
+      <c r="E107" s="71"/>
+      <c r="F107" s="71"/>
+      <c r="G107" s="71"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="74">
+      <c r="A108" s="75">
         <v>46234</v>
       </c>
-      <c r="B108" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="C108" s="70" t="s">
+      <c r="B108" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="70"/>
-      <c r="E108" s="70"/>
-      <c r="F108" s="70"/>
-      <c r="G108" s="70"/>
+      <c r="D108" s="71"/>
+      <c r="E108" s="71"/>
+      <c r="F108" s="71"/>
+      <c r="G108" s="71"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="74"/>
-      <c r="B109" s="70"/>
-      <c r="C109" s="70" t="s">
+      <c r="A109" s="75"/>
+      <c r="B109" s="71"/>
+      <c r="C109" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="70"/>
-      <c r="E109" s="70"/>
-      <c r="F109" s="70"/>
-      <c r="G109" s="70"/>
+      <c r="D109" s="71"/>
+      <c r="E109" s="71"/>
+      <c r="F109" s="71"/>
+      <c r="G109" s="71"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -3156,15 +3165,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="90">
+      <c r="A1" s="91">
         <v>46235</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4106,15 +4115,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="95">
+      <c r="A1" s="96">
         <v>46266</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -4953,7 +4962,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C2665-F910-4EB6-BFBD-382289307A7D}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="14" customWidth="1"/>
@@ -4964,15 +4973,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="95">
+      <c r="A1" s="96">
         <v>46296</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
@@ -5454,32 +5463,51 @@
       <c r="C41" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
       <c r="G41" s="37"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="25" t="s">
+      <c r="A42" s="38"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="D42" s="96"/>
-      <c r="E42" s="96"/>
-      <c r="F42" s="96"/>
-      <c r="G42" s="37"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="40"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="38"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="38" t="s">
+      <c r="A43" s="65">
+        <v>46311</v>
+      </c>
+      <c r="B43" s="97" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="97" t="s">
+        <v>215</v>
+      </c>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="97"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="65"/>
+      <c r="C44" s="14" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="40"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A31CDF-A384-44A0-BD28-D05793882E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E36E56-CE44-4BC3-9B0C-38E9B9D7CB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="